--- a/Demon Lord Roguelike/Assets/Data/Excel/excel_buff_info[buff信息].xlsx
+++ b/Demon Lord Roguelike/Assets/Data/Excel/excel_buff_info[buff信息].xlsx
@@ -1137,7 +1137,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y143"/>
+  <dimension ref="A1:Y145"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col width="24.25" customWidth="1" style="3" min="1" max="1"/>
@@ -2250,88 +2250,89 @@
     </row>
     <row r="18">
       <c r="A18" s="0" t="n">
-        <v>3000100001</v>
+        <v>2000600001</v>
       </c>
       <c r="C18" s="0" t="n">
-        <v>3</v>
-      </c>
-      <c r="D18" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="H18" s="7" t="inlineStr">
-        <is>
-          <t>BuffEntityInstantCloneDefenseCreature</t>
-        </is>
-      </c>
-      <c r="I18" s="7" t="n"/>
+        <v>2</v>
+      </c>
+      <c r="G18" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="H18" s="0" t="inlineStr">
+        <is>
+          <t>BuffEntityPeriodicShieldCast</t>
+        </is>
+      </c>
+      <c r="J18" s="0" t="inlineStr">
+        <is>
+          <t>3,2000700001</t>
+        </is>
+      </c>
+      <c r="R18" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="S18" s="0" t="n">
+        <v>10</v>
+      </c>
       <c r="T18" s="0" t="n">
         <v>0</v>
       </c>
-      <c r="U18" s="0" t="n">
-        <v>0</v>
-      </c>
       <c r="W18" s="0" t="n">
-        <v>3000100001</v>
+        <v>2000600001</v>
       </c>
       <c r="X18" s="0" t="n">
-        <v>3000100001</v>
+        <v>2000600001</v>
       </c>
       <c r="Y18" s="0" t="inlineStr">
         <is>
-          <t>增殖-随机复制一个已有的魔物</t>
+          <t>大盾战士BOSS-每10秒给最前排3个友军套伤害转移护盾（护盾持续5秒）</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="0" t="n">
-        <v>3000200001</v>
+        <v>2000700001</v>
       </c>
       <c r="C19" s="0" t="n">
-        <v>3</v>
-      </c>
-      <c r="D19" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="E19" s="0" t="n">
-        <v>3000200001</v>
-      </c>
-      <c r="F19" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="H19" s="7" t="inlineStr">
-        <is>
-          <t>BuffEntityConditionalAddDropCrystal</t>
-        </is>
-      </c>
-      <c r="I19" s="0" t="inlineStr">
-        <is>
-          <t>GameFightLogic_CreatureDeadDropCrystal</t>
-        </is>
-      </c>
-      <c r="Q19" s="0" t="n">
-        <v>0.2</v>
+        <v>2</v>
+      </c>
+      <c r="G19" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="H19" s="0" t="inlineStr">
+        <is>
+          <t>BuffEntityConditionalShieldTransfer</t>
+        </is>
+      </c>
+      <c r="J19" s="0" t="inlineStr">
+        <is>
+          <t>500004,0.6</t>
+        </is>
+      </c>
+      <c r="M19" s="0" t="n">
+        <v>5</v>
+      </c>
+      <c r="R19" s="0" t="n">
+        <v>0</v>
       </c>
       <c r="T19" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="U19" s="0" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="W19" s="0" t="n">
-        <v>3000200001</v>
+        <v>2000700001</v>
       </c>
       <c r="X19" s="0" t="n">
-        <v>3000200001</v>
+        <v>2000700001</v>
       </c>
       <c r="Y19" s="0" t="inlineStr">
         <is>
-          <t>钱多多LV1-每一次击杀有20%的概率多掉落一次魔晶</t>
+          <t>伤害转移护盾-5秒内目标零承伤，伤害转移给施加者（大盾战士BOSS援护护盾，堆叠策略须为Ignore）</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="0" t="n">
-        <v>3000200002</v>
+        <v>3000100001</v>
       </c>
       <c r="C20" s="0" t="n">
         <v>3</v>
@@ -2339,25 +2340,12 @@
       <c r="D20" s="0" t="n">
         <v>1</v>
       </c>
-      <c r="E20" s="0" t="n">
-        <v>3000200002</v>
-      </c>
-      <c r="F20" s="0" t="n">
-        <v>2</v>
-      </c>
       <c r="H20" s="7" t="inlineStr">
         <is>
-          <t>BuffEntityConditionalAddDropCrystal</t>
-        </is>
-      </c>
-      <c r="I20" s="0" t="inlineStr">
-        <is>
-          <t>GameFightLogic_CreatureDeadDropCrystal</t>
-        </is>
-      </c>
-      <c r="Q20" s="0" t="n">
-        <v>0.4</v>
-      </c>
+          <t>BuffEntityInstantCloneDefenseCreature</t>
+        </is>
+      </c>
+      <c r="I20" s="7" t="n"/>
       <c r="T20" s="0" t="n">
         <v>0</v>
       </c>
@@ -2365,20 +2353,20 @@
         <v>0</v>
       </c>
       <c r="W20" s="0" t="n">
-        <v>3000200001</v>
+        <v>3000100001</v>
       </c>
       <c r="X20" s="0" t="n">
-        <v>3000200001</v>
+        <v>3000100001</v>
       </c>
       <c r="Y20" s="0" t="inlineStr">
         <is>
-          <t>钱多多LV2-每一次击杀有40%的概率多掉落一次魔晶</t>
+          <t>增殖-随机复制一个已有的魔物</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="0" t="n">
-        <v>3000200003</v>
+        <v>3000200001</v>
       </c>
       <c r="C21" s="0" t="n">
         <v>3</v>
@@ -2387,10 +2375,10 @@
         <v>1</v>
       </c>
       <c r="E21" s="0" t="n">
-        <v>3000200003</v>
+        <v>3000200001</v>
       </c>
       <c r="F21" s="0" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H21" s="7" t="inlineStr">
         <is>
@@ -2403,7 +2391,7 @@
         </is>
       </c>
       <c r="Q21" s="0" t="n">
-        <v>0.6</v>
+        <v>0.2</v>
       </c>
       <c r="T21" s="0" t="n">
         <v>0</v>
@@ -2419,13 +2407,13 @@
       </c>
       <c r="Y21" s="0" t="inlineStr">
         <is>
-          <t>钱多多LV3-每一次击杀有60%的概率多掉落一次魔晶</t>
+          <t>钱多多LV1-每一次击杀有20%的概率多掉落一次魔晶</t>
         </is>
       </c>
     </row>
     <row r="22" ht="15" customHeight="1" s="3">
       <c r="A22" s="0" t="n">
-        <v>3000200004</v>
+        <v>3000200002</v>
       </c>
       <c r="C22" s="0" t="n">
         <v>3</v>
@@ -2434,10 +2422,10 @@
         <v>1</v>
       </c>
       <c r="E22" s="0" t="n">
-        <v>3000200003</v>
+        <v>3000200002</v>
       </c>
       <c r="F22" s="0" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H22" s="7" t="inlineStr">
         <is>
@@ -2450,7 +2438,7 @@
         </is>
       </c>
       <c r="Q22" s="0" t="n">
-        <v>0.8</v>
+        <v>0.4</v>
       </c>
       <c r="T22" s="0" t="n">
         <v>0</v>
@@ -2466,13 +2454,13 @@
       </c>
       <c r="Y22" s="0" t="inlineStr">
         <is>
-          <t>钱多多LV4-每一次击杀有80%的概率多掉落一次魔晶</t>
+          <t>钱多多LV2-每一次击杀有40%的概率多掉落一次魔晶</t>
         </is>
       </c>
     </row>
     <row r="23" ht="15" customHeight="1" s="3">
       <c r="A23" s="0" t="n">
-        <v>3000200005</v>
+        <v>3000200003</v>
       </c>
       <c r="C23" s="0" t="n">
         <v>3</v>
@@ -2484,7 +2472,7 @@
         <v>3000200003</v>
       </c>
       <c r="F23" s="0" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="H23" s="7" t="inlineStr">
         <is>
@@ -2497,7 +2485,7 @@
         </is>
       </c>
       <c r="Q23" s="0" t="n">
-        <v>1</v>
+        <v>0.6</v>
       </c>
       <c r="T23" s="0" t="n">
         <v>0</v>
@@ -2513,107 +2501,107 @@
       </c>
       <c r="Y23" s="0" t="inlineStr">
         <is>
-          <t>钱多多LV5-每一次击杀有100%的概率多掉落一次魔晶</t>
+          <t>钱多多LV3-每一次击杀有60%的概率多掉落一次魔晶</t>
         </is>
       </c>
     </row>
     <row r="24" ht="15" customHeight="1" s="3">
       <c r="A24" s="0" t="n">
-        <v>3000300001</v>
+        <v>3000200004</v>
       </c>
       <c r="C24" s="0" t="n">
         <v>3</v>
       </c>
-      <c r="G24" s="0" t="n">
-        <v>2</v>
-      </c>
-      <c r="H24" s="0" t="inlineStr">
-        <is>
-          <t>BuffEntityPeriodicAttackMultiInstant</t>
-        </is>
-      </c>
-      <c r="J24" s="0" t="inlineStr">
-        <is>
-          <t>1,300031</t>
-        </is>
-      </c>
-      <c r="M24" s="0" t="n">
+      <c r="D24" s="0" t="n">
         <v>1</v>
       </c>
+      <c r="E24" s="0" t="n">
+        <v>3000200003</v>
+      </c>
+      <c r="F24" s="0" t="n">
+        <v>4</v>
+      </c>
+      <c r="H24" s="7" t="inlineStr">
+        <is>
+          <t>BuffEntityConditionalAddDropCrystal</t>
+        </is>
+      </c>
+      <c r="I24" s="0" t="inlineStr">
+        <is>
+          <t>GameFightLogic_CreatureDeadDropCrystal</t>
+        </is>
+      </c>
       <c r="Q24" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="R24" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="S24" s="0" t="n">
-        <v>3</v>
+        <v>0.8</v>
       </c>
       <c r="T24" s="0" t="n">
         <v>0</v>
       </c>
+      <c r="U24" s="0" t="n">
+        <v>0</v>
+      </c>
       <c r="W24" s="0" t="n">
-        <v>3000300001</v>
+        <v>3000200001</v>
       </c>
       <c r="X24" s="0" t="n">
-        <v>3000300001</v>
+        <v>3000200001</v>
       </c>
       <c r="Y24" s="0" t="inlineStr">
         <is>
-          <t>闪电Lv1-每3秒1道落雷,范围0.2,单雷最多命中1个目标,伤害=魔王攻击力</t>
+          <t>钱多多LV4-每一次击杀有80%的概率多掉落一次魔晶</t>
         </is>
       </c>
     </row>
     <row r="25" ht="15" customHeight="1" s="3">
       <c r="A25" s="0" t="n">
-        <v>3000300002</v>
+        <v>3000200005</v>
       </c>
       <c r="C25" s="0" t="n">
         <v>3</v>
       </c>
-      <c r="G25" s="0" t="n">
-        <v>2</v>
-      </c>
-      <c r="H25" s="0" t="inlineStr">
-        <is>
-          <t>BuffEntityPeriodicAttackMultiInstant</t>
-        </is>
-      </c>
-      <c r="J25" s="0" t="inlineStr">
-        <is>
-          <t>2,300032</t>
-        </is>
-      </c>
-      <c r="M25" s="0" t="n">
+      <c r="D25" s="0" t="n">
         <v>1</v>
       </c>
+      <c r="E25" s="0" t="n">
+        <v>3000200003</v>
+      </c>
+      <c r="F25" s="0" t="n">
+        <v>5</v>
+      </c>
+      <c r="H25" s="7" t="inlineStr">
+        <is>
+          <t>BuffEntityConditionalAddDropCrystal</t>
+        </is>
+      </c>
+      <c r="I25" s="0" t="inlineStr">
+        <is>
+          <t>GameFightLogic_CreatureDeadDropCrystal</t>
+        </is>
+      </c>
       <c r="Q25" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="R25" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="S25" s="0" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="T25" s="0" t="n">
         <v>0</v>
       </c>
+      <c r="U25" s="0" t="n">
+        <v>0</v>
+      </c>
       <c r="W25" s="0" t="n">
-        <v>3000300001</v>
+        <v>3000200001</v>
       </c>
       <c r="X25" s="0" t="n">
-        <v>3000300001</v>
+        <v>3000200001</v>
       </c>
       <c r="Y25" s="0" t="inlineStr">
         <is>
-          <t>闪电Lv2-每3秒2道落雷,范围0.4,单雷最多命中2个目标,伤害=魔王攻击力</t>
+          <t>钱多多LV5-每一次击杀有100%的概率多掉落一次魔晶</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="0" t="n">
-        <v>3000300003</v>
+        <v>3000300001</v>
       </c>
       <c r="C26" s="0" t="n">
         <v>3</v>
@@ -2628,7 +2616,7 @@
       </c>
       <c r="J26" s="0" t="inlineStr">
         <is>
-          <t>3,300033</t>
+          <t>1,300031</t>
         </is>
       </c>
       <c r="M26" s="0" t="n">
@@ -2654,13 +2642,13 @@
       </c>
       <c r="Y26" s="0" t="inlineStr">
         <is>
-          <t>闪电Lv3-每3秒3道落雷,范围0.6,单雷最多命中3个目标,伤害=魔王攻击力</t>
+          <t>闪电Lv1-每3秒1道落雷,范围0.2,单雷最多命中1个目标,伤害=魔王攻击力</t>
         </is>
       </c>
     </row>
     <row r="27" ht="15" customHeight="1" s="3">
       <c r="A27" s="0" t="n">
-        <v>3000300004</v>
+        <v>3000300002</v>
       </c>
       <c r="C27" s="0" t="n">
         <v>3</v>
@@ -2675,7 +2663,7 @@
       </c>
       <c r="J27" s="0" t="inlineStr">
         <is>
-          <t>4,300034</t>
+          <t>2,300032</t>
         </is>
       </c>
       <c r="M27" s="0" t="n">
@@ -2701,13 +2689,13 @@
       </c>
       <c r="Y27" s="0" t="inlineStr">
         <is>
-          <t>闪电Lv4-每3秒4道落雷,范围0.8,单雷最多命中4个目标,伤害=魔王攻击力</t>
+          <t>闪电Lv2-每3秒2道落雷,范围0.4,单雷最多命中2个目标,伤害=魔王攻击力</t>
         </is>
       </c>
     </row>
     <row r="28" ht="15" customHeight="1" s="3">
       <c r="A28" s="0" t="n">
-        <v>3000300005</v>
+        <v>3000300003</v>
       </c>
       <c r="C28" s="0" t="n">
         <v>3</v>
@@ -2722,7 +2710,7 @@
       </c>
       <c r="J28" s="0" t="inlineStr">
         <is>
-          <t>5,300035</t>
+          <t>3,300033</t>
         </is>
       </c>
       <c r="M28" s="0" t="n">
@@ -2748,13 +2736,13 @@
       </c>
       <c r="Y28" s="0" t="inlineStr">
         <is>
-          <t>闪电Lv5-每3秒5道落雷,范围1,单雷最多命中5个目标,伤害=魔王攻击力</t>
+          <t>闪电Lv3-每3秒3道落雷,范围0.6,单雷最多命中3个目标,伤害=魔王攻击力</t>
         </is>
       </c>
     </row>
     <row r="29" ht="15" customHeight="1" s="3">
       <c r="A29" s="0" t="n">
-        <v>3000400001</v>
+        <v>3000300004</v>
       </c>
       <c r="C29" s="0" t="n">
         <v>3</v>
@@ -2764,12 +2752,12 @@
       </c>
       <c r="H29" s="0" t="inlineStr">
         <is>
-          <t>BuffEntityPeriodicAttackRoad</t>
+          <t>BuffEntityPeriodicAttackMultiInstant</t>
         </is>
       </c>
       <c r="J29" s="0" t="inlineStr">
         <is>
-          <t>1,300041</t>
+          <t>4,300034</t>
         </is>
       </c>
       <c r="M29" s="0" t="n">
@@ -2782,26 +2770,26 @@
         <v>0</v>
       </c>
       <c r="S29" s="0" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T29" s="0" t="n">
         <v>0</v>
       </c>
       <c r="W29" s="0" t="n">
-        <v>3000400001</v>
+        <v>3000300001</v>
       </c>
       <c r="X29" s="0" t="n">
-        <v>3000400001</v>
+        <v>3000300001</v>
       </c>
       <c r="Y29" s="0" t="inlineStr">
         <is>
-          <t>失控的矿车Lv1-每5秒随机1条道路各出1辆矿车，第1个目标伤害=魔王攻击力，之后每撞1个减半</t>
+          <t>闪电Lv4-每3秒4道落雷,范围0.8,单雷最多命中4个目标,伤害=魔王攻击力</t>
         </is>
       </c>
     </row>
     <row r="30" ht="15" customHeight="1" s="3">
       <c r="A30" s="0" t="n">
-        <v>3000400002</v>
+        <v>3000300005</v>
       </c>
       <c r="C30" s="0" t="n">
         <v>3</v>
@@ -2811,12 +2799,12 @@
       </c>
       <c r="H30" s="0" t="inlineStr">
         <is>
-          <t>BuffEntityPeriodicAttackRoad</t>
+          <t>BuffEntityPeriodicAttackMultiInstant</t>
         </is>
       </c>
       <c r="J30" s="0" t="inlineStr">
         <is>
-          <t>2,300041</t>
+          <t>5,300035</t>
         </is>
       </c>
       <c r="M30" s="0" t="n">
@@ -2829,26 +2817,26 @@
         <v>0</v>
       </c>
       <c r="S30" s="0" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T30" s="0" t="n">
         <v>0</v>
       </c>
       <c r="W30" s="0" t="n">
-        <v>3000400001</v>
+        <v>3000300001</v>
       </c>
       <c r="X30" s="0" t="n">
-        <v>3000400001</v>
+        <v>3000300001</v>
       </c>
       <c r="Y30" s="0" t="inlineStr">
         <is>
-          <t>失控的矿车Lv2-每5秒随机2条道路各出1辆矿车，第1个目标伤害=魔王攻击力，之后每撞1个减半</t>
+          <t>闪电Lv5-每3秒5道落雷,范围1,单雷最多命中5个目标,伤害=魔王攻击力</t>
         </is>
       </c>
     </row>
     <row r="31" customFormat="1" s="2">
       <c r="A31" s="0" t="n">
-        <v>3000400003</v>
+        <v>3000400001</v>
       </c>
       <c r="C31" s="0" t="n">
         <v>3</v>
@@ -2863,7 +2851,7 @@
       </c>
       <c r="J31" s="0" t="inlineStr">
         <is>
-          <t>3,300041</t>
+          <t>1,300041</t>
         </is>
       </c>
       <c r="M31" s="0" t="n">
@@ -2889,13 +2877,13 @@
       </c>
       <c r="Y31" s="0" t="inlineStr">
         <is>
-          <t>失控的矿车Lv3-每5秒随机3条道路各出1辆矿车，第1个目标伤害=魔王攻击力，之后每撞1个减半</t>
+          <t>失控的矿车Lv1-每5秒随机1条道路各出1辆矿车，第1个目标伤害=魔王攻击力，之后每撞1个减半</t>
         </is>
       </c>
     </row>
     <row r="32" customFormat="1" s="2">
       <c r="A32" s="0" t="n">
-        <v>3000400004</v>
+        <v>3000400002</v>
       </c>
       <c r="C32" s="0" t="n">
         <v>3</v>
@@ -2910,7 +2898,7 @@
       </c>
       <c r="J32" s="0" t="inlineStr">
         <is>
-          <t>4,300041</t>
+          <t>2,300041</t>
         </is>
       </c>
       <c r="M32" s="0" t="n">
@@ -2936,13 +2924,13 @@
       </c>
       <c r="Y32" s="0" t="inlineStr">
         <is>
-          <t>失控的矿车Lv4-每5秒随机4条道路各出1辆矿车，第1个目标伤害=魔王攻击力，之后每撞1个减半</t>
+          <t>失控的矿车Lv2-每5秒随机2条道路各出1辆矿车，第1个目标伤害=魔王攻击力，之后每撞1个减半</t>
         </is>
       </c>
     </row>
     <row r="33" customFormat="1" s="2">
       <c r="A33" s="0" t="n">
-        <v>3000400005</v>
+        <v>3000400003</v>
       </c>
       <c r="C33" s="0" t="n">
         <v>3</v>
@@ -2957,7 +2945,7 @@
       </c>
       <c r="J33" s="0" t="inlineStr">
         <is>
-          <t>5,300041</t>
+          <t>3,300041</t>
         </is>
       </c>
       <c r="M33" s="0" t="n">
@@ -2983,51 +2971,33 @@
       </c>
       <c r="Y33" s="0" t="inlineStr">
         <is>
-          <t>失控的矿车Lv5-每5秒随机5条道路各出1辆矿车，第1个目标伤害=魔王攻击力，之后每撞1个减半</t>
+          <t>失控的矿车Lv3-每5秒随机3条道路各出1辆矿车，第1个目标伤害=魔王攻击力，之后每撞1个减半</t>
         </is>
       </c>
     </row>
     <row r="34" ht="13" customHeight="1" s="3">
       <c r="A34" s="0" t="n">
-        <v>3000600001</v>
+        <v>3000400004</v>
       </c>
       <c r="C34" s="0" t="n">
         <v>3</v>
-      </c>
-      <c r="D34" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="E34" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="F34" s="0" t="n">
-        <v>0</v>
       </c>
       <c r="G34" s="0" t="n">
         <v>2</v>
       </c>
       <c r="H34" s="0" t="inlineStr">
         <is>
-          <t>BuffEntityPeriodicAttackBounceAxe</t>
+          <t>BuffEntityPeriodicAttackRoad</t>
         </is>
       </c>
       <c r="J34" s="0" t="inlineStr">
         <is>
-          <t>1,300061,1</t>
+          <t>4,300041</t>
         </is>
       </c>
       <c r="M34" s="0" t="n">
         <v>1</v>
       </c>
-      <c r="N34" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="O34" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="P34" s="0" t="n">
-        <v>0</v>
-      </c>
       <c r="Q34" s="0" t="n">
         <v>0</v>
       </c>
@@ -3040,65 +3010,41 @@
       <c r="T34" s="0" t="n">
         <v>0</v>
       </c>
-      <c r="U34" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="V34" s="0" t="n">
-        <v>0</v>
-      </c>
       <c r="W34" s="0" t="n">
-        <v>3000600001</v>
+        <v>3000400001</v>
       </c>
       <c r="X34" s="0" t="n">
-        <v>3000600001</v>
+        <v>3000400001</v>
       </c>
       <c r="Y34" s="0" t="inlineStr">
         <is>
-          <t>跳跳斧Lv1-每5秒扔出1把斧头,伤害=魔王攻击力,命中后弹跳1次,伤害逐目标减半保底1</t>
+          <t>失控的矿车Lv4-每5秒随机4条道路各出1辆矿车，第1个目标伤害=魔王攻击力，之后每撞1个减半</t>
         </is>
       </c>
     </row>
     <row r="35" ht="14.25" customHeight="1" s="3">
       <c r="A35" s="0" t="n">
-        <v>3000600002</v>
+        <v>3000400005</v>
       </c>
       <c r="C35" s="0" t="n">
         <v>3</v>
-      </c>
-      <c r="D35" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="E35" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="F35" s="0" t="n">
-        <v>0</v>
       </c>
       <c r="G35" s="0" t="n">
         <v>2</v>
       </c>
       <c r="H35" s="0" t="inlineStr">
         <is>
-          <t>BuffEntityPeriodicAttackBounceAxe</t>
+          <t>BuffEntityPeriodicAttackRoad</t>
         </is>
       </c>
       <c r="J35" s="0" t="inlineStr">
         <is>
-          <t>2,300061,2</t>
+          <t>5,300041</t>
         </is>
       </c>
       <c r="M35" s="0" t="n">
         <v>1</v>
       </c>
-      <c r="N35" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="O35" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="P35" s="0" t="n">
-        <v>0</v>
-      </c>
       <c r="Q35" s="0" t="n">
         <v>0</v>
       </c>
@@ -3111,27 +3057,21 @@
       <c r="T35" s="0" t="n">
         <v>0</v>
       </c>
-      <c r="U35" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="V35" s="0" t="n">
-        <v>0</v>
-      </c>
       <c r="W35" s="0" t="n">
-        <v>3000600001</v>
+        <v>3000400001</v>
       </c>
       <c r="X35" s="0" t="n">
-        <v>3000600001</v>
+        <v>3000400001</v>
       </c>
       <c r="Y35" s="0" t="inlineStr">
         <is>
-          <t>跳跳斧Lv2-每5秒扔出2把斧头,命中后弹跳2次,伤害逐目标减半保底1</t>
+          <t>失控的矿车Lv5-每5秒随机5条道路各出1辆矿车，第1个目标伤害=魔王攻击力，之后每撞1个减半</t>
         </is>
       </c>
     </row>
     <row r="36" ht="14.25" customHeight="1" s="3">
       <c r="A36" s="0" t="n">
-        <v>3000600003</v>
+        <v>3000600001</v>
       </c>
       <c r="C36" s="0" t="n">
         <v>3</v>
@@ -3155,7 +3095,7 @@
       </c>
       <c r="J36" s="0" t="inlineStr">
         <is>
-          <t>3,300061,3</t>
+          <t>1,300061,1</t>
         </is>
       </c>
       <c r="M36" s="0" t="n">
@@ -3196,13 +3136,13 @@
       </c>
       <c r="Y36" s="0" t="inlineStr">
         <is>
-          <t>跳跳斧Lv3-每5秒扔出3把斧头,命中后弹跳3次,伤害逐目标减半保底1</t>
+          <t>跳跳斧Lv1-每5秒扔出1把斧头,伤害=魔王攻击力,命中后弹跳1次,伤害逐目标减半保底1</t>
         </is>
       </c>
     </row>
     <row r="37" ht="14.25" customHeight="1" s="3">
       <c r="A37" s="0" t="n">
-        <v>3000600004</v>
+        <v>3000600002</v>
       </c>
       <c r="C37" s="0" t="n">
         <v>3</v>
@@ -3226,7 +3166,7 @@
       </c>
       <c r="J37" s="0" t="inlineStr">
         <is>
-          <t>4,300061,4</t>
+          <t>2,300061,2</t>
         </is>
       </c>
       <c r="M37" s="0" t="n">
@@ -3267,13 +3207,13 @@
       </c>
       <c r="Y37" s="0" t="inlineStr">
         <is>
-          <t>跳跳斧Lv4-每5秒扔出4把斧头,命中后弹跳4次,伤害逐目标减半保底1</t>
+          <t>跳跳斧Lv2-每5秒扔出2把斧头,命中后弹跳2次,伤害逐目标减半保底1</t>
         </is>
       </c>
     </row>
     <row r="38" ht="14.25" customHeight="1" s="3">
       <c r="A38" s="0" t="n">
-        <v>3000600005</v>
+        <v>3000600003</v>
       </c>
       <c r="C38" s="0" t="n">
         <v>3</v>
@@ -3297,7 +3237,7 @@
       </c>
       <c r="J38" s="0" t="inlineStr">
         <is>
-          <t>5,300061,5</t>
+          <t>3,300061,3</t>
         </is>
       </c>
       <c r="M38" s="0" t="n">
@@ -3338,13 +3278,13 @@
       </c>
       <c r="Y38" s="0" t="inlineStr">
         <is>
-          <t>跳跳斧Lv5-每5秒扔出5把斧头,命中后弹跳5次,伤害逐目标减半保底1</t>
+          <t>跳跳斧Lv3-每5秒扔出3把斧头,命中后弹跳3次,伤害逐目标减半保底1</t>
         </is>
       </c>
     </row>
     <row r="39" ht="14.25" customHeight="1" s="3">
       <c r="A39" s="0" t="n">
-        <v>3000700001</v>
+        <v>3000600004</v>
       </c>
       <c r="C39" s="0" t="n">
         <v>3</v>
@@ -3363,16 +3303,16 @@
       </c>
       <c r="H39" s="0" t="inlineStr">
         <is>
-          <t>BuffEntityPeriodicAttackOrbit</t>
+          <t>BuffEntityPeriodicAttackBounceAxe</t>
         </is>
       </c>
       <c r="J39" s="0" t="inlineStr">
         <is>
-          <t>1,300071,0.6</t>
+          <t>4,300061,4</t>
         </is>
       </c>
       <c r="M39" s="0" t="n">
-        <v>0.4</v>
+        <v>1</v>
       </c>
       <c r="N39" s="0" t="n">
         <v>0</v>
@@ -3390,7 +3330,7 @@
         <v>0</v>
       </c>
       <c r="S39" s="0" t="n">
-        <v>9999</v>
+        <v>5</v>
       </c>
       <c r="T39" s="0" t="n">
         <v>0</v>
@@ -3402,20 +3342,20 @@
         <v>0</v>
       </c>
       <c r="W39" s="0" t="n">
-        <v>3000700001</v>
+        <v>3000600001</v>
       </c>
       <c r="X39" s="0" t="n">
-        <v>3000700001</v>
+        <v>3000600001</v>
       </c>
       <c r="Y39" s="0" t="inlineStr">
         <is>
-          <t>知识的力量Lv1-环绕1本书(半径0.75,转速0.6弧度/秒),触碰伤害=魔王攻击力40%</t>
+          <t>跳跳斧Lv4-每5秒扔出4把斧头,命中后弹跳4次,伤害逐目标减半保底1</t>
         </is>
       </c>
     </row>
     <row r="40" ht="14.25" customHeight="1" s="3">
       <c r="A40" s="0" t="n">
-        <v>3000700002</v>
+        <v>3000600005</v>
       </c>
       <c r="C40" s="0" t="n">
         <v>3</v>
@@ -3434,16 +3374,16 @@
       </c>
       <c r="H40" s="0" t="inlineStr">
         <is>
-          <t>BuffEntityPeriodicAttackOrbit</t>
+          <t>BuffEntityPeriodicAttackBounceAxe</t>
         </is>
       </c>
       <c r="J40" s="0" t="inlineStr">
         <is>
-          <t>2,300071,1.2</t>
+          <t>5,300061,5</t>
         </is>
       </c>
       <c r="M40" s="0" t="n">
-        <v>0.4</v>
+        <v>1</v>
       </c>
       <c r="N40" s="0" t="n">
         <v>0</v>
@@ -3461,7 +3401,7 @@
         <v>0</v>
       </c>
       <c r="S40" s="0" t="n">
-        <v>9999</v>
+        <v>5</v>
       </c>
       <c r="T40" s="0" t="n">
         <v>0</v>
@@ -3473,20 +3413,20 @@
         <v>0</v>
       </c>
       <c r="W40" s="0" t="n">
-        <v>3000700001</v>
+        <v>3000600001</v>
       </c>
       <c r="X40" s="0" t="n">
-        <v>3000700001</v>
+        <v>3000600001</v>
       </c>
       <c r="Y40" s="0" t="inlineStr">
         <is>
-          <t>知识的力量Lv2-环绕2本书(半径0.75,转速1.2弧度/秒),触碰伤害=魔王攻击力40%</t>
+          <t>跳跳斧Lv5-每5秒扔出5把斧头,命中后弹跳5次,伤害逐目标减半保底1</t>
         </is>
       </c>
     </row>
     <row r="41" ht="14.25" customHeight="1" s="3">
       <c r="A41" s="0" t="n">
-        <v>3000700003</v>
+        <v>3000700001</v>
       </c>
       <c r="C41" s="0" t="n">
         <v>3</v>
@@ -3510,7 +3450,7 @@
       </c>
       <c r="J41" s="0" t="inlineStr">
         <is>
-          <t>3,300071,1.8</t>
+          <t>1,300071,0.6</t>
         </is>
       </c>
       <c r="M41" s="0" t="n">
@@ -3551,13 +3491,13 @@
       </c>
       <c r="Y41" s="0" t="inlineStr">
         <is>
-          <t>知识的力量Lv3-环绕3本书(半径0.75,转速1.8弧度/秒),触碰伤害=魔王攻击力40%</t>
+          <t>知识的力量Lv1-环绕1本书(半径0.75,转速0.6弧度/秒),触碰伤害=魔王攻击力40%</t>
         </is>
       </c>
     </row>
     <row r="42" ht="14.25" customHeight="1" s="3">
       <c r="A42" s="0" t="n">
-        <v>3000700004</v>
+        <v>3000700002</v>
       </c>
       <c r="C42" s="0" t="n">
         <v>3</v>
@@ -3581,7 +3521,7 @@
       </c>
       <c r="J42" s="0" t="inlineStr">
         <is>
-          <t>4,300071,2.4</t>
+          <t>2,300071,1.2</t>
         </is>
       </c>
       <c r="M42" s="0" t="n">
@@ -3622,13 +3562,13 @@
       </c>
       <c r="Y42" s="0" t="inlineStr">
         <is>
-          <t>知识的力量Lv4-环绕4本书(半径0.75,转速2.4弧度/秒),触碰伤害=魔王攻击力40%</t>
+          <t>知识的力量Lv2-环绕2本书(半径0.75,转速1.2弧度/秒),触碰伤害=魔王攻击力40%</t>
         </is>
       </c>
     </row>
     <row r="43" ht="14.25" customHeight="1" s="3">
       <c r="A43" s="0" t="n">
-        <v>3000700005</v>
+        <v>3000700003</v>
       </c>
       <c r="C43" s="0" t="n">
         <v>3</v>
@@ -3652,7 +3592,7 @@
       </c>
       <c r="J43" s="0" t="inlineStr">
         <is>
-          <t>5,300071,3</t>
+          <t>3,300071,1.8</t>
         </is>
       </c>
       <c r="M43" s="0" t="n">
@@ -3693,13 +3633,13 @@
       </c>
       <c r="Y43" s="0" t="inlineStr">
         <is>
-          <t>知识的力量Lv5-环绕5本书(半径0.75,转速3弧度/秒),触碰伤害=魔王攻击力40%</t>
+          <t>知识的力量Lv3-环绕3本书(半径0.75,转速1.8弧度/秒),触碰伤害=魔王攻击力40%</t>
         </is>
       </c>
     </row>
     <row r="44" ht="14.25" customHeight="1" s="3">
       <c r="A44" s="0" t="n">
-        <v>3000800001</v>
+        <v>3000700004</v>
       </c>
       <c r="C44" s="0" t="n">
         <v>3</v>
@@ -3718,16 +3658,16 @@
       </c>
       <c r="H44" s="0" t="inlineStr">
         <is>
-          <t>BuffEntityPeriodicAttackRebound</t>
+          <t>BuffEntityPeriodicAttackOrbit</t>
         </is>
       </c>
       <c r="J44" s="0" t="inlineStr">
         <is>
-          <t>1,300081</t>
+          <t>4,300071,2.4</t>
         </is>
       </c>
       <c r="M44" s="0" t="n">
-        <v>1</v>
+        <v>0.4</v>
       </c>
       <c r="N44" s="0" t="n">
         <v>0</v>
@@ -3745,7 +3685,7 @@
         <v>0</v>
       </c>
       <c r="S44" s="0" t="n">
-        <v>1</v>
+        <v>9999</v>
       </c>
       <c r="T44" s="0" t="n">
         <v>0</v>
@@ -3757,20 +3697,20 @@
         <v>0</v>
       </c>
       <c r="W44" s="0" t="n">
-        <v>3000800001</v>
+        <v>3000700001</v>
       </c>
       <c r="X44" s="0" t="n">
-        <v>3000800001</v>
+        <v>3000700001</v>
       </c>
       <c r="Y44" s="0" t="inlineStr">
         <is>
-          <t>回弹菱块Lv1-场上维持1颗永久反弹菱块(速度2),伤害=魔王攻击力100%,同目标1秒冷却</t>
+          <t>知识的力量Lv4-环绕4本书(半径0.75,转速2.4弧度/秒),触碰伤害=魔王攻击力40%</t>
         </is>
       </c>
     </row>
     <row r="45" ht="14.25" customHeight="1" s="3">
       <c r="A45" s="0" t="n">
-        <v>3000800002</v>
+        <v>3000700005</v>
       </c>
       <c r="C45" s="0" t="n">
         <v>3</v>
@@ -3789,16 +3729,16 @@
       </c>
       <c r="H45" s="0" t="inlineStr">
         <is>
-          <t>BuffEntityPeriodicAttackRebound</t>
+          <t>BuffEntityPeriodicAttackOrbit</t>
         </is>
       </c>
       <c r="J45" s="0" t="inlineStr">
         <is>
-          <t>2,300082</t>
+          <t>5,300071,3</t>
         </is>
       </c>
       <c r="M45" s="0" t="n">
-        <v>1</v>
+        <v>0.4</v>
       </c>
       <c r="N45" s="0" t="n">
         <v>0</v>
@@ -3816,7 +3756,7 @@
         <v>0</v>
       </c>
       <c r="S45" s="0" t="n">
-        <v>1</v>
+        <v>9999</v>
       </c>
       <c r="T45" s="0" t="n">
         <v>0</v>
@@ -3828,20 +3768,20 @@
         <v>0</v>
       </c>
       <c r="W45" s="0" t="n">
-        <v>3000800001</v>
+        <v>3000700001</v>
       </c>
       <c r="X45" s="0" t="n">
-        <v>3000800001</v>
+        <v>3000700001</v>
       </c>
       <c r="Y45" s="0" t="inlineStr">
         <is>
-          <t>回弹菱块Lv2-场上维持2颗永久反弹菱块(速度2.5),伤害=魔王攻击力100%,同目标1秒冷却</t>
+          <t>知识的力量Lv5-环绕5本书(半径0.75,转速3弧度/秒),触碰伤害=魔王攻击力40%</t>
         </is>
       </c>
     </row>
     <row r="46" ht="14.25" customHeight="1" s="3">
       <c r="A46" s="0" t="n">
-        <v>3000800003</v>
+        <v>3000800001</v>
       </c>
       <c r="C46" s="0" t="n">
         <v>3</v>
@@ -3865,7 +3805,7 @@
       </c>
       <c r="J46" s="0" t="inlineStr">
         <is>
-          <t>3,300083</t>
+          <t>1,300081</t>
         </is>
       </c>
       <c r="M46" s="0" t="n">
@@ -3906,13 +3846,13 @@
       </c>
       <c r="Y46" s="0" t="inlineStr">
         <is>
-          <t>回弹菱块Lv3-场上维持3颗永久反弹菱块(速度3),伤害=魔王攻击力100%,同目标1秒冷却</t>
+          <t>回弹菱块Lv1-场上维持1颗永久反弹菱块(速度2),伤害=魔王攻击力100%,同目标1秒冷却</t>
         </is>
       </c>
     </row>
     <row r="47" ht="14.25" customHeight="1" s="3">
       <c r="A47" s="0" t="n">
-        <v>3000800004</v>
+        <v>3000800002</v>
       </c>
       <c r="C47" s="0" t="n">
         <v>3</v>
@@ -3936,7 +3876,7 @@
       </c>
       <c r="J47" s="0" t="inlineStr">
         <is>
-          <t>4,300084</t>
+          <t>2,300082</t>
         </is>
       </c>
       <c r="M47" s="0" t="n">
@@ -3977,13 +3917,13 @@
       </c>
       <c r="Y47" s="0" t="inlineStr">
         <is>
-          <t>回弹菱块Lv4-场上维持4颗永久反弹菱块(速度3.5),伤害=魔王攻击力100%,同目标1秒冷却</t>
+          <t>回弹菱块Lv2-场上维持2颗永久反弹菱块(速度2.5),伤害=魔王攻击力100%,同目标1秒冷却</t>
         </is>
       </c>
     </row>
     <row r="48" ht="14.25" customHeight="1" s="3">
       <c r="A48" s="0" t="n">
-        <v>3000800005</v>
+        <v>3000800003</v>
       </c>
       <c r="C48" s="0" t="n">
         <v>3</v>
@@ -4007,7 +3947,7 @@
       </c>
       <c r="J48" s="0" t="inlineStr">
         <is>
-          <t>5,300085</t>
+          <t>3,300083</t>
         </is>
       </c>
       <c r="M48" s="0" t="n">
@@ -4048,229 +3988,229 @@
       </c>
       <c r="Y48" s="0" t="inlineStr">
         <is>
+          <t>回弹菱块Lv3-场上维持3颗永久反弹菱块(速度3),伤害=魔王攻击力100%,同目标1秒冷却</t>
+        </is>
+      </c>
+    </row>
+    <row r="49" ht="15" customHeight="1" s="3">
+      <c r="A49" s="0" t="n">
+        <v>3000800004</v>
+      </c>
+      <c r="C49" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="D49" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="E49" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="F49" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="G49" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="H49" s="0" t="inlineStr">
+        <is>
+          <t>BuffEntityPeriodicAttackRebound</t>
+        </is>
+      </c>
+      <c r="J49" s="0" t="inlineStr">
+        <is>
+          <t>4,300084</t>
+        </is>
+      </c>
+      <c r="M49" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="N49" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="O49" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="P49" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q49" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="R49" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="S49" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="T49" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="U49" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="V49" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="W49" s="0" t="n">
+        <v>3000800001</v>
+      </c>
+      <c r="X49" s="0" t="n">
+        <v>3000800001</v>
+      </c>
+      <c r="Y49" s="0" t="inlineStr">
+        <is>
+          <t>回弹菱块Lv4-场上维持4颗永久反弹菱块(速度3.5),伤害=魔王攻击力100%,同目标1秒冷却</t>
+        </is>
+      </c>
+    </row>
+    <row r="50" ht="14.25" customHeight="1" s="3">
+      <c r="A50" s="0" t="n">
+        <v>3000800005</v>
+      </c>
+      <c r="C50" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="D50" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="E50" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="F50" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="G50" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="H50" s="0" t="inlineStr">
+        <is>
+          <t>BuffEntityPeriodicAttackRebound</t>
+        </is>
+      </c>
+      <c r="J50" s="0" t="inlineStr">
+        <is>
+          <t>5,300085</t>
+        </is>
+      </c>
+      <c r="M50" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="N50" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="O50" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="P50" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q50" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="R50" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="S50" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="T50" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="U50" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="V50" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="W50" s="0" t="n">
+        <v>3000800001</v>
+      </c>
+      <c r="X50" s="0" t="n">
+        <v>3000800001</v>
+      </c>
+      <c r="Y50" s="0" t="inlineStr">
+        <is>
           <t>回弹菱块Lv5-场上维持5颗永久反弹菱块(速度4),伤害=魔王攻击力100%,同目标1秒冷却</t>
         </is>
       </c>
     </row>
-    <row r="49" ht="15" customHeight="1" s="3">
-      <c r="A49" s="2" t="n">
+    <row r="51" ht="14.25" customHeight="1" s="3">
+      <c r="A51" s="2" t="n">
         <v>3000900001</v>
       </c>
-      <c r="C49" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="D49" s="2" t="n">
+      <c r="C51" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="D51" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="H49" s="2" t="inlineStr">
+      <c r="H51" s="2" t="inlineStr">
         <is>
           <t>BuffEntityInstantRewardMoreItem</t>
         </is>
       </c>
-      <c r="I49" s="2" t="n"/>
-      <c r="J49" s="2" t="n"/>
-      <c r="O49" s="2" t="n"/>
-      <c r="P49" s="2" t="n"/>
-      <c r="T49" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="U49" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="W49" s="2" t="n">
+      <c r="I51" s="2" t="n"/>
+      <c r="J51" s="2" t="n"/>
+      <c r="O51" s="2" t="n"/>
+      <c r="P51" s="2" t="n"/>
+      <c r="T51" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="U51" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="W51" s="2" t="n">
         <v>3000900001</v>
       </c>
-      <c r="X49" s="2" t="n">
+      <c r="X51" s="2" t="n">
         <v>3000900001</v>
       </c>
-      <c r="Y49" s="2" t="inlineStr">
+      <c r="Y51" s="2" t="inlineStr">
         <is>
           <t>奖励多多-通关奖励数量+1</t>
         </is>
       </c>
     </row>
-    <row r="50" ht="14.25" customHeight="1" s="3">
-      <c r="A50" s="2" t="n">
+    <row r="52" ht="14.25" customHeight="1" s="3">
+      <c r="A52" s="2" t="n">
         <v>3001000001</v>
       </c>
-      <c r="C50" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="D50" s="2" t="n">
+      <c r="C52" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="D52" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="H50" s="2" t="inlineStr">
+      <c r="H52" s="2" t="inlineStr">
         <is>
           <t>BuffEntityInstantRewardMoreSelect</t>
         </is>
       </c>
-      <c r="I50" s="2" t="n"/>
-      <c r="J50" s="2" t="n"/>
-      <c r="O50" s="2" t="n"/>
-      <c r="P50" s="2" t="n"/>
-      <c r="T50" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="U50" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="W50" s="2" t="n">
+      <c r="I52" s="2" t="n"/>
+      <c r="J52" s="2" t="n"/>
+      <c r="O52" s="2" t="n"/>
+      <c r="P52" s="2" t="n"/>
+      <c r="T52" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="U52" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="W52" s="2" t="n">
         <v>3001000001</v>
       </c>
-      <c r="X50" s="2" t="n">
+      <c r="X52" s="2" t="n">
         <v>3001000001</v>
       </c>
-      <c r="Y50" s="2" t="inlineStr">
+      <c r="Y52" s="2" t="inlineStr">
         <is>
           <t>再来一瓶-通关奖励可选次数+1</t>
-        </is>
-      </c>
-    </row>
-    <row r="51" ht="14.25" customHeight="1" s="3">
-      <c r="A51" s="0" t="n">
-        <v>3001100005</v>
-      </c>
-      <c r="C51" s="0" t="n">
-        <v>3</v>
-      </c>
-      <c r="D51" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="E51" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="F51" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="G51" s="0" t="n">
-        <v>2</v>
-      </c>
-      <c r="H51" s="0" t="inlineStr">
-        <is>
-          <t>BuffEntityPeriodicAttackShockwave</t>
-        </is>
-      </c>
-      <c r="J51" s="0" t="inlineStr">
-        <is>
-          <t>300091</t>
-        </is>
-      </c>
-      <c r="M51" s="0" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="N51" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="O51" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="P51" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q51" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="R51" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="S51" s="0" t="n">
-        <v>10</v>
-      </c>
-      <c r="T51" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="U51" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="V51" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="W51" s="0" t="n">
-        <v>3001100005</v>
-      </c>
-      <c r="X51" s="0" t="n">
-        <v>3001100005</v>
-      </c>
-      <c r="Y51" s="0" t="inlineStr">
-        <is>
-          <t>第六次冲击Lv5-每10秒从魔王发出冲击波，伤害=魔王攻击力x0.3</t>
-        </is>
-      </c>
-    </row>
-    <row r="52" ht="14.25" customHeight="1" s="3">
-      <c r="A52" s="0" t="n">
-        <v>3001100004</v>
-      </c>
-      <c r="C52" s="0" t="n">
-        <v>3</v>
-      </c>
-      <c r="D52" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="E52" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="F52" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="G52" s="0" t="n">
-        <v>2</v>
-      </c>
-      <c r="H52" s="0" t="inlineStr">
-        <is>
-          <t>BuffEntityPeriodicAttackShockwave</t>
-        </is>
-      </c>
-      <c r="J52" s="0" t="inlineStr">
-        <is>
-          <t>300091</t>
-        </is>
-      </c>
-      <c r="M52" s="0" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="N52" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="O52" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="P52" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q52" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="R52" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="S52" s="0" t="n">
-        <v>10</v>
-      </c>
-      <c r="T52" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="U52" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="V52" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="W52" s="0" t="n">
-        <v>3001100004</v>
-      </c>
-      <c r="X52" s="0" t="n">
-        <v>3001100004</v>
-      </c>
-      <c r="Y52" s="0" t="inlineStr">
-        <is>
-          <t>第六次冲击Lv4-每10秒从魔王发出冲击波，伤害=魔王攻击力x0.25</t>
         </is>
       </c>
     </row>
     <row r="53" ht="14.25" customHeight="1" s="3">
       <c r="A53" s="0" t="n">
-        <v>3001100003</v>
+        <v>3001100005</v>
       </c>
       <c r="C53" s="0" t="n">
         <v>3</v>
@@ -4298,7 +4238,7 @@
         </is>
       </c>
       <c r="M53" s="0" t="n">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="N53" s="0" t="n">
         <v>0</v>
@@ -4328,20 +4268,20 @@
         <v>0</v>
       </c>
       <c r="W53" s="0" t="n">
-        <v>3001100003</v>
+        <v>3001100005</v>
       </c>
       <c r="X53" s="0" t="n">
-        <v>3001100003</v>
+        <v>3001100005</v>
       </c>
       <c r="Y53" s="0" t="inlineStr">
         <is>
-          <t>第六次冲击Lv3-每10秒从魔王发出冲击波，伤害=魔王攻击力x0.2</t>
+          <t>第六次冲击Lv5-每10秒从魔王发出冲击波，伤害=魔王攻击力x0.3</t>
         </is>
       </c>
     </row>
     <row r="54" ht="14.25" customHeight="1" s="3">
       <c r="A54" s="0" t="n">
-        <v>3001100002</v>
+        <v>3001100004</v>
       </c>
       <c r="C54" s="0" t="n">
         <v>3</v>
@@ -4369,7 +4309,7 @@
         </is>
       </c>
       <c r="M54" s="0" t="n">
-        <v>0.15</v>
+        <v>0.25</v>
       </c>
       <c r="N54" s="0" t="n">
         <v>0</v>
@@ -4399,20 +4339,20 @@
         <v>0</v>
       </c>
       <c r="W54" s="0" t="n">
-        <v>3001100002</v>
+        <v>3001100004</v>
       </c>
       <c r="X54" s="0" t="n">
-        <v>3001100002</v>
+        <v>3001100004</v>
       </c>
       <c r="Y54" s="0" t="inlineStr">
         <is>
-          <t>第六次冲击Lv2-每10秒从魔王发出冲击波，伤害=魔王攻击力x0.15</t>
+          <t>第六次冲击Lv4-每10秒从魔王发出冲击波，伤害=魔王攻击力x0.25</t>
         </is>
       </c>
     </row>
     <row r="55" ht="14.25" customFormat="1" customHeight="1" s="2">
       <c r="A55" s="0" t="n">
-        <v>3001100001</v>
+        <v>3001100003</v>
       </c>
       <c r="C55" s="0" t="n">
         <v>3</v>
@@ -4440,7 +4380,7 @@
         </is>
       </c>
       <c r="M55" s="0" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="N55" s="0" t="n">
         <v>0</v>
@@ -4470,22 +4410,21 @@
         <v>0</v>
       </c>
       <c r="W55" s="0" t="n">
-        <v>3001100001</v>
+        <v>3001100003</v>
       </c>
       <c r="X55" s="0" t="n">
-        <v>3001100001</v>
+        <v>3001100003</v>
       </c>
       <c r="Y55" s="0" t="inlineStr">
         <is>
-          <t>第六次冲击Lv1-每10秒从魔王发出冲击波，伤害=魔王攻击力x0.1</t>
+          <t>第六次冲击Lv3-每10秒从魔王发出冲击波，伤害=魔王攻击力x0.2</t>
         </is>
       </c>
     </row>
     <row r="56" ht="14.25" customFormat="1" customHeight="1" s="2">
       <c r="A56" s="0" t="n">
-        <v>3001200001</v>
-      </c>
-      <c r="B56" s="0" t="inlineStr"/>
+        <v>3001100002</v>
+      </c>
       <c r="C56" s="0" t="n">
         <v>3</v>
       </c>
@@ -4503,19 +4442,16 @@
       </c>
       <c r="H56" s="0" t="inlineStr">
         <is>
-          <t>BuffEntityPeriodicAttackFireBottle</t>
-        </is>
-      </c>
-      <c r="I56" s="0" t="inlineStr"/>
+          <t>BuffEntityPeriodicAttackShockwave</t>
+        </is>
+      </c>
       <c r="J56" s="0" t="inlineStr">
         <is>
-          <t>1,300101</t>
-        </is>
-      </c>
-      <c r="K56" s="0" t="inlineStr"/>
-      <c r="L56" s="0" t="inlineStr"/>
+          <t>300091</t>
+        </is>
+      </c>
       <c r="M56" s="0" t="n">
-        <v>0.2</v>
+        <v>0.15</v>
       </c>
       <c r="N56" s="0" t="n">
         <v>0</v>
@@ -4545,22 +4481,21 @@
         <v>0</v>
       </c>
       <c r="W56" s="0" t="n">
-        <v>3001200001</v>
+        <v>3001100002</v>
       </c>
       <c r="X56" s="0" t="n">
-        <v>3001200001</v>
+        <v>3001100002</v>
       </c>
       <c r="Y56" s="0" t="inlineStr">
         <is>
-          <t>瓶装炼狱火Lv1-每10秒向1个敌人投掷炼狱火瓶,落地燃放地形火焰,每1秒对半径1.2内敌人造成魔王攻击力20%伤害,持续5秒</t>
+          <t>第六次冲击Lv2-每10秒从魔王发出冲击波，伤害=魔王攻击力x0.15</t>
         </is>
       </c>
     </row>
     <row r="57" ht="14.25" customFormat="1" customHeight="1" s="2">
       <c r="A57" s="0" t="n">
-        <v>3001200002</v>
-      </c>
-      <c r="B57" s="0" t="inlineStr"/>
+        <v>3001100001</v>
+      </c>
       <c r="C57" s="0" t="n">
         <v>3</v>
       </c>
@@ -4578,19 +4513,16 @@
       </c>
       <c r="H57" s="0" t="inlineStr">
         <is>
-          <t>BuffEntityPeriodicAttackFireBottle</t>
-        </is>
-      </c>
-      <c r="I57" s="0" t="inlineStr"/>
+          <t>BuffEntityPeriodicAttackShockwave</t>
+        </is>
+      </c>
       <c r="J57" s="0" t="inlineStr">
         <is>
-          <t>2,300101</t>
-        </is>
-      </c>
-      <c r="K57" s="0" t="inlineStr"/>
-      <c r="L57" s="0" t="inlineStr"/>
+          <t>300091</t>
+        </is>
+      </c>
       <c r="M57" s="0" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="N57" s="0" t="n">
         <v>0</v>
@@ -4620,20 +4552,20 @@
         <v>0</v>
       </c>
       <c r="W57" s="0" t="n">
-        <v>3001200001</v>
+        <v>3001100001</v>
       </c>
       <c r="X57" s="0" t="n">
-        <v>3001200001</v>
+        <v>3001100001</v>
       </c>
       <c r="Y57" s="0" t="inlineStr">
         <is>
-          <t>瓶装炼狱火Lv2-每10秒向2个敌人投掷炼狱火瓶,落地燃放地形火焰,每1秒对半径1.2内敌人造成魔王攻击力20%伤害,持续5秒</t>
+          <t>第六次冲击Lv1-每10秒从魔王发出冲击波，伤害=魔王攻击力x0.1</t>
         </is>
       </c>
     </row>
     <row r="58" ht="14.25" customFormat="1" customHeight="1" s="2">
       <c r="A58" s="0" t="n">
-        <v>3001200003</v>
+        <v>3001200001</v>
       </c>
       <c r="B58" s="0" t="inlineStr"/>
       <c r="C58" s="0" t="n">
@@ -4659,7 +4591,7 @@
       <c r="I58" s="0" t="inlineStr"/>
       <c r="J58" s="0" t="inlineStr">
         <is>
-          <t>3,300101</t>
+          <t>1,300101</t>
         </is>
       </c>
       <c r="K58" s="0" t="inlineStr"/>
@@ -4702,13 +4634,13 @@
       </c>
       <c r="Y58" s="0" t="inlineStr">
         <is>
-          <t>瓶装炼狱火Lv3-每10秒向3个敌人投掷炼狱火瓶,落地燃放地形火焰,每1秒对半径1.2内敌人造成魔王攻击力20%伤害,持续5秒</t>
+          <t>瓶装炼狱火Lv1-每10秒向1个敌人投掷炼狱火瓶,落地燃放地形火焰,每1秒对半径1.2内敌人造成魔王攻击力20%伤害,持续5秒</t>
         </is>
       </c>
     </row>
     <row r="59" ht="14.25" customFormat="1" customHeight="1" s="2">
       <c r="A59" s="0" t="n">
-        <v>3001200004</v>
+        <v>3001200002</v>
       </c>
       <c r="B59" s="0" t="inlineStr"/>
       <c r="C59" s="0" t="n">
@@ -4734,7 +4666,7 @@
       <c r="I59" s="0" t="inlineStr"/>
       <c r="J59" s="0" t="inlineStr">
         <is>
-          <t>4,300101</t>
+          <t>2,300101</t>
         </is>
       </c>
       <c r="K59" s="0" t="inlineStr"/>
@@ -4777,13 +4709,13 @@
       </c>
       <c r="Y59" s="0" t="inlineStr">
         <is>
-          <t>瓶装炼狱火Lv4-每10秒向4个敌人投掷炼狱火瓶,落地燃放地形火焰,每1秒对半径1.2内敌人造成魔王攻击力20%伤害,持续5秒</t>
+          <t>瓶装炼狱火Lv2-每10秒向2个敌人投掷炼狱火瓶,落地燃放地形火焰,每1秒对半径1.2内敌人造成魔王攻击力20%伤害,持续5秒</t>
         </is>
       </c>
     </row>
     <row r="60" ht="14.25" customFormat="1" customHeight="1" s="2">
       <c r="A60" s="0" t="n">
-        <v>3001200005</v>
+        <v>3001200003</v>
       </c>
       <c r="B60" s="0" t="inlineStr"/>
       <c r="C60" s="0" t="n">
@@ -4809,7 +4741,7 @@
       <c r="I60" s="0" t="inlineStr"/>
       <c r="J60" s="0" t="inlineStr">
         <is>
-          <t>5,300101</t>
+          <t>3,300101</t>
         </is>
       </c>
       <c r="K60" s="0" t="inlineStr"/>
@@ -4852,111 +4784,163 @@
       </c>
       <c r="Y60" s="0" t="inlineStr">
         <is>
+          <t>瓶装炼狱火Lv3-每10秒向3个敌人投掷炼狱火瓶,落地燃放地形火焰,每1秒对半径1.2内敌人造成魔王攻击力20%伤害,持续5秒</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="0" t="n">
+        <v>3001200004</v>
+      </c>
+      <c r="B61" s="0" t="inlineStr"/>
+      <c r="C61" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="D61" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="E61" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="F61" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="G61" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="H61" s="0" t="inlineStr">
+        <is>
+          <t>BuffEntityPeriodicAttackFireBottle</t>
+        </is>
+      </c>
+      <c r="I61" s="0" t="inlineStr"/>
+      <c r="J61" s="0" t="inlineStr">
+        <is>
+          <t>4,300101</t>
+        </is>
+      </c>
+      <c r="K61" s="0" t="inlineStr"/>
+      <c r="L61" s="0" t="inlineStr"/>
+      <c r="M61" s="0" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="N61" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="O61" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="P61" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q61" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="R61" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="S61" s="0" t="n">
+        <v>10</v>
+      </c>
+      <c r="T61" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="U61" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="V61" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="W61" s="0" t="n">
+        <v>3001200001</v>
+      </c>
+      <c r="X61" s="0" t="n">
+        <v>3001200001</v>
+      </c>
+      <c r="Y61" s="0" t="inlineStr">
+        <is>
+          <t>瓶装炼狱火Lv4-每10秒向4个敌人投掷炼狱火瓶,落地燃放地形火焰,每1秒对半径1.2内敌人造成魔王攻击力20%伤害,持续5秒</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="0" t="n">
+        <v>3001200005</v>
+      </c>
+      <c r="B62" s="0" t="inlineStr"/>
+      <c r="C62" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="D62" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="E62" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="F62" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="G62" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="H62" s="0" t="inlineStr">
+        <is>
+          <t>BuffEntityPeriodicAttackFireBottle</t>
+        </is>
+      </c>
+      <c r="I62" s="0" t="inlineStr"/>
+      <c r="J62" s="0" t="inlineStr">
+        <is>
+          <t>5,300101</t>
+        </is>
+      </c>
+      <c r="K62" s="0" t="inlineStr"/>
+      <c r="L62" s="0" t="inlineStr"/>
+      <c r="M62" s="0" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="N62" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="O62" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="P62" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q62" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="R62" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="S62" s="0" t="n">
+        <v>10</v>
+      </c>
+      <c r="T62" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="U62" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="V62" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="W62" s="0" t="n">
+        <v>3001200001</v>
+      </c>
+      <c r="X62" s="0" t="n">
+        <v>3001200001</v>
+      </c>
+      <c r="Y62" s="0" t="inlineStr">
+        <is>
           <t>瓶装炼狱火Lv5-每10秒向5个敌人投掷炼狱火瓶,落地燃放地形火焰,每1秒对半径1.2内敌人造成魔王攻击力20%伤害,持续5秒</t>
-        </is>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" s="2" t="n">
-        <v>11000100001</v>
-      </c>
-      <c r="C61" s="2" t="n">
-        <v>11</v>
-      </c>
-      <c r="D61" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="H61" s="2" t="inlineStr">
-        <is>
-          <t>BuffEntityAttribute</t>
-        </is>
-      </c>
-      <c r="I61" s="5" t="inlineStr">
-        <is>
-          <t>GameFightLogic_CreatureDeadEnd</t>
-        </is>
-      </c>
-      <c r="J61" s="5" t="inlineStr">
-        <is>
-          <t>HP</t>
-        </is>
-      </c>
-      <c r="O61" s="2" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="P61" s="2" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="T61" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="U61" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="W61" s="2" t="n">
-        <v>11000100001</v>
-      </c>
-      <c r="X61" s="2" t="n">
-        <v>11000100001</v>
-      </c>
-      <c r="Y61" s="2" t="inlineStr">
-        <is>
-          <t>生命增加{Percentage}%</t>
-        </is>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" s="2" t="n">
-        <v>11000200001</v>
-      </c>
-      <c r="C62" s="2" t="n">
-        <v>11</v>
-      </c>
-      <c r="D62" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="H62" s="2" t="inlineStr">
-        <is>
-          <t>BuffEntityAttribute</t>
-        </is>
-      </c>
-      <c r="I62" s="5" t="inlineStr">
-        <is>
-          <t>GameFightLogic_CreatureDeadEnd</t>
-        </is>
-      </c>
-      <c r="J62" s="5" t="inlineStr">
-        <is>
-          <t>DR</t>
-        </is>
-      </c>
-      <c r="O62" s="2" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="P62" s="2" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="T62" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="U62" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="W62" s="2" t="n">
-        <v>11000200001</v>
-      </c>
-      <c r="X62" s="2" t="n">
-        <v>11000200001</v>
-      </c>
-      <c r="Y62" s="2" t="inlineStr">
-        <is>
-          <t>护甲增加{Percentage}%</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="n">
-        <v>11000300001</v>
+        <v>11000100001</v>
       </c>
       <c r="C63" s="2" t="n">
         <v>11</v>
@@ -4974,129 +4958,139 @@
           <t>GameFightLogic_CreatureDeadEnd</t>
         </is>
       </c>
-      <c r="J63" s="0" t="inlineStr">
+      <c r="J63" s="5" t="inlineStr">
+        <is>
+          <t>HP</t>
+        </is>
+      </c>
+      <c r="O63" s="2" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="P63" s="2" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="T63" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="U63" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="W63" s="2" t="n">
+        <v>11000100001</v>
+      </c>
+      <c r="X63" s="2" t="n">
+        <v>11000100001</v>
+      </c>
+      <c r="Y63" s="2" t="inlineStr">
+        <is>
+          <t>生命增加{Percentage}%</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="2" t="n">
+        <v>11000200001</v>
+      </c>
+      <c r="C64" s="2" t="n">
+        <v>11</v>
+      </c>
+      <c r="D64" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="H64" s="2" t="inlineStr">
+        <is>
+          <t>BuffEntityAttribute</t>
+        </is>
+      </c>
+      <c r="I64" s="5" t="inlineStr">
+        <is>
+          <t>GameFightLogic_CreatureDeadEnd</t>
+        </is>
+      </c>
+      <c r="J64" s="5" t="inlineStr">
+        <is>
+          <t>DR</t>
+        </is>
+      </c>
+      <c r="O64" s="2" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="P64" s="2" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="T64" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="U64" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="W64" s="2" t="n">
+        <v>11000200001</v>
+      </c>
+      <c r="X64" s="2" t="n">
+        <v>11000200001</v>
+      </c>
+      <c r="Y64" s="2" t="inlineStr">
+        <is>
+          <t>护甲增加{Percentage}%</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="2" t="n">
+        <v>11000300001</v>
+      </c>
+      <c r="C65" s="2" t="n">
+        <v>11</v>
+      </c>
+      <c r="D65" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="H65" s="2" t="inlineStr">
+        <is>
+          <t>BuffEntityAttribute</t>
+        </is>
+      </c>
+      <c r="I65" s="5" t="inlineStr">
+        <is>
+          <t>GameFightLogic_CreatureDeadEnd</t>
+        </is>
+      </c>
+      <c r="J65" s="0" t="inlineStr">
         <is>
           <t>ATK</t>
         </is>
       </c>
-      <c r="O63" s="0" t="n">
+      <c r="O65" s="0" t="n">
         <v>0.2</v>
       </c>
-      <c r="P63" s="0" t="n">
+      <c r="P65" s="0" t="n">
         <v>0.1</v>
       </c>
-      <c r="Q63" s="2" t="n">
+      <c r="Q65" s="2" t="n">
         <v>0.2</v>
       </c>
-      <c r="T63" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="U63" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="W63" s="2" t="n">
+      <c r="T65" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="U65" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="W65" s="2" t="n">
         <v>11000300001</v>
       </c>
-      <c r="X63" s="2" t="n">
+      <c r="X65" s="2" t="n">
         <v>11000300001</v>
       </c>
-      <c r="Y63" s="2" t="inlineStr">
+      <c r="Y65" s="2" t="inlineStr">
         <is>
           <t>攻击力增加{Percentage}%</t>
-        </is>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" s="0" t="n">
-        <v>11000400001</v>
-      </c>
-      <c r="C64" s="0" t="n">
-        <v>11</v>
-      </c>
-      <c r="D64" s="0" t="n">
-        <v>2</v>
-      </c>
-      <c r="H64" s="0" t="inlineStr">
-        <is>
-          <t>BuffEntityAttribute</t>
-        </is>
-      </c>
-      <c r="J64" s="0" t="inlineStr">
-        <is>
-          <t>ASPD</t>
-        </is>
-      </c>
-      <c r="O64" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="P64" s="0" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="T64" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="U64" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="W64" s="0" t="n">
-        <v>11000400001</v>
-      </c>
-      <c r="X64" s="0" t="n">
-        <v>11000400001</v>
-      </c>
-      <c r="Y64" s="0" t="inlineStr">
-        <is>
-          <t>攻击速度增加{Percentage}%</t>
-        </is>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" s="0" t="n">
-        <v>11000500001</v>
-      </c>
-      <c r="C65" s="0" t="n">
-        <v>11</v>
-      </c>
-      <c r="D65" s="0" t="n">
-        <v>2</v>
-      </c>
-      <c r="H65" s="0" t="inlineStr">
-        <is>
-          <t>BuffEntityAttribute</t>
-        </is>
-      </c>
-      <c r="J65" s="0" t="inlineStr">
-        <is>
-          <t>RCD</t>
-        </is>
-      </c>
-      <c r="O65" s="0" t="n">
-        <v>-0.25</v>
-      </c>
-      <c r="P65" s="0" t="n">
-        <v>-0.5</v>
-      </c>
-      <c r="T65" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="U65" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="W65" s="0" t="n">
-        <v>11000500001</v>
-      </c>
-      <c r="X65" s="0" t="n">
-        <v>11000500001</v>
-      </c>
-      <c r="Y65" s="0" t="inlineStr">
-        <is>
-          <t>召唤CD{Percentage}%</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="0" t="n">
-        <v>11000600001</v>
+        <v>11000400001</v>
       </c>
       <c r="C66" s="0" t="n">
         <v>11</v>
@@ -5111,14 +5105,14 @@
       </c>
       <c r="J66" s="0" t="inlineStr">
         <is>
-          <t>CMP</t>
+          <t>ASPD</t>
         </is>
       </c>
       <c r="O66" s="0" t="n">
-        <v>-0.25</v>
+        <v>1</v>
       </c>
       <c r="P66" s="0" t="n">
-        <v>-0.5</v>
+        <v>0.5</v>
       </c>
       <c r="T66" s="0" t="n">
         <v>0</v>
@@ -5127,20 +5121,20 @@
         <v>0</v>
       </c>
       <c r="W66" s="0" t="n">
-        <v>11000600001</v>
+        <v>11000400001</v>
       </c>
       <c r="X66" s="0" t="n">
-        <v>11000600001</v>
+        <v>11000400001</v>
       </c>
       <c r="Y66" s="0" t="inlineStr">
         <is>
-          <t>召唤魔力消耗{Percentage}%</t>
+          <t>攻击速度增加{Percentage}%</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="0" t="n">
-        <v>11000700001</v>
+        <v>11000500001</v>
       </c>
       <c r="C67" s="0" t="n">
         <v>11</v>
@@ -5148,27 +5142,21 @@
       <c r="D67" s="0" t="n">
         <v>2</v>
       </c>
-      <c r="G67" s="0" t="n">
-        <v>0</v>
-      </c>
       <c r="H67" s="0" t="inlineStr">
         <is>
-          <t>BuffEntityAttributeMulti</t>
+          <t>BuffEntityAttribute</t>
         </is>
       </c>
       <c r="J67" s="0" t="inlineStr">
         <is>
-          <t>ATK:1|HP:-1</t>
+          <t>RCD</t>
         </is>
       </c>
       <c r="O67" s="0" t="n">
-        <v>0.5</v>
+        <v>-0.25</v>
       </c>
       <c r="P67" s="0" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="R67" s="0" t="n">
-        <v>0</v>
+        <v>-0.5</v>
       </c>
       <c r="T67" s="0" t="n">
         <v>0</v>
@@ -5177,20 +5165,20 @@
         <v>0</v>
       </c>
       <c r="W67" s="0" t="n">
-        <v>11000700001</v>
+        <v>11000500001</v>
       </c>
       <c r="X67" s="0" t="n">
-        <v>11000700001</v>
+        <v>11000500001</v>
       </c>
       <c r="Y67" s="0" t="inlineStr">
         <is>
-          <t>狂战士-A</t>
+          <t>召唤CD{Percentage}%</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="0" t="n">
-        <v>11000700002</v>
+        <v>11000600001</v>
       </c>
       <c r="C68" s="0" t="n">
         <v>11</v>
@@ -5198,27 +5186,21 @@
       <c r="D68" s="0" t="n">
         <v>2</v>
       </c>
-      <c r="G68" s="0" t="n">
-        <v>0</v>
-      </c>
       <c r="H68" s="0" t="inlineStr">
         <is>
-          <t>BuffEntityAttributeMulti</t>
+          <t>BuffEntityAttribute</t>
         </is>
       </c>
       <c r="J68" s="0" t="inlineStr">
         <is>
-          <t>ATK:1|DR:-1</t>
+          <t>CMP</t>
         </is>
       </c>
       <c r="O68" s="0" t="n">
-        <v>0.5</v>
+        <v>-0.25</v>
       </c>
       <c r="P68" s="0" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="R68" s="0" t="n">
-        <v>0</v>
+        <v>-0.5</v>
       </c>
       <c r="T68" s="0" t="n">
         <v>0</v>
@@ -5227,20 +5209,20 @@
         <v>0</v>
       </c>
       <c r="W68" s="0" t="n">
-        <v>11000700002</v>
+        <v>11000600001</v>
       </c>
       <c r="X68" s="0" t="n">
-        <v>11000700002</v>
+        <v>11000600001</v>
       </c>
       <c r="Y68" s="0" t="inlineStr">
         <is>
-          <t>狂战士-B</t>
+          <t>召唤魔力消耗{Percentage}%</t>
         </is>
       </c>
     </row>
     <row r="69" ht="15" customHeight="1" s="3">
       <c r="A69" s="0" t="n">
-        <v>11000700003</v>
+        <v>11000700001</v>
       </c>
       <c r="C69" s="0" t="n">
         <v>11</v>
@@ -5258,7 +5240,7 @@
       </c>
       <c r="J69" s="0" t="inlineStr">
         <is>
-          <t>ATK:1|ASPD:-1</t>
+          <t>ATK:1|HP:-1</t>
         </is>
       </c>
       <c r="O69" s="0" t="n">
@@ -5277,20 +5259,20 @@
         <v>0</v>
       </c>
       <c r="W69" s="0" t="n">
-        <v>11000700003</v>
+        <v>11000700001</v>
       </c>
       <c r="X69" s="0" t="n">
-        <v>11000700003</v>
+        <v>11000700001</v>
       </c>
       <c r="Y69" s="0" t="inlineStr">
         <is>
-          <t>狂战士-C</t>
+          <t>狂战士-A</t>
         </is>
       </c>
     </row>
     <row r="70" ht="15" customHeight="1" s="3">
       <c r="A70" s="0" t="n">
-        <v>11000800001</v>
+        <v>11000700002</v>
       </c>
       <c r="C70" s="0" t="n">
         <v>11</v>
@@ -5308,7 +5290,7 @@
       </c>
       <c r="J70" s="0" t="inlineStr">
         <is>
-          <t>ASPD:1|DR:-1</t>
+          <t>ATK:1|DR:-1</t>
         </is>
       </c>
       <c r="O70" s="0" t="n">
@@ -5327,20 +5309,20 @@
         <v>0</v>
       </c>
       <c r="W70" s="0" t="n">
-        <v>11000800001</v>
+        <v>11000700002</v>
       </c>
       <c r="X70" s="0" t="n">
-        <v>11000800001</v>
+        <v>11000700002</v>
       </c>
       <c r="Y70" s="0" t="inlineStr">
         <is>
-          <t>快枪手-A</t>
+          <t>狂战士-B</t>
         </is>
       </c>
     </row>
     <row r="71" ht="15" customHeight="1" s="3">
       <c r="A71" s="0" t="n">
-        <v>11000800002</v>
+        <v>11000700003</v>
       </c>
       <c r="C71" s="0" t="n">
         <v>11</v>
@@ -5358,7 +5340,7 @@
       </c>
       <c r="J71" s="0" t="inlineStr">
         <is>
-          <t>ASPD:1|HP:-1</t>
+          <t>ATK:1|ASPD:-1</t>
         </is>
       </c>
       <c r="O71" s="0" t="n">
@@ -5377,20 +5359,20 @@
         <v>0</v>
       </c>
       <c r="W71" s="0" t="n">
-        <v>11000800002</v>
+        <v>11000700003</v>
       </c>
       <c r="X71" s="0" t="n">
-        <v>11000800002</v>
+        <v>11000700003</v>
       </c>
       <c r="Y71" s="0" t="inlineStr">
         <is>
-          <t>快枪手-B</t>
+          <t>狂战士-C</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="0" t="n">
-        <v>11000800003</v>
+        <v>11000800001</v>
       </c>
       <c r="C72" s="0" t="n">
         <v>11</v>
@@ -5408,7 +5390,7 @@
       </c>
       <c r="J72" s="0" t="inlineStr">
         <is>
-          <t>ASPD:1|ATK:-1</t>
+          <t>ASPD:1|DR:-1</t>
         </is>
       </c>
       <c r="O72" s="0" t="n">
@@ -5427,20 +5409,20 @@
         <v>0</v>
       </c>
       <c r="W72" s="0" t="n">
-        <v>11000800003</v>
+        <v>11000800001</v>
       </c>
       <c r="X72" s="0" t="n">
-        <v>11000800003</v>
+        <v>11000800001</v>
       </c>
       <c r="Y72" s="0" t="inlineStr">
         <is>
-          <t>快枪手-C</t>
+          <t>快枪手-A</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="0" t="n">
-        <v>11000900001</v>
+        <v>11000800002</v>
       </c>
       <c r="C73" s="0" t="n">
         <v>11</v>
@@ -5458,7 +5440,7 @@
       </c>
       <c r="J73" s="0" t="inlineStr">
         <is>
-          <t>DR:1|HP:-1</t>
+          <t>ASPD:1|HP:-1</t>
         </is>
       </c>
       <c r="O73" s="0" t="n">
@@ -5477,20 +5459,20 @@
         <v>0</v>
       </c>
       <c r="W73" s="0" t="n">
-        <v>11000900001</v>
+        <v>11000800002</v>
       </c>
       <c r="X73" s="0" t="n">
-        <v>11000900001</v>
+        <v>11000800002</v>
       </c>
       <c r="Y73" s="0" t="inlineStr">
         <is>
-          <t>铜墙铁壁-A</t>
+          <t>快枪手-B</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="0" t="n">
-        <v>11000900002</v>
+        <v>11000800003</v>
       </c>
       <c r="C74" s="0" t="n">
         <v>11</v>
@@ -5508,7 +5490,7 @@
       </c>
       <c r="J74" s="0" t="inlineStr">
         <is>
-          <t>DR:1|ATK:-1</t>
+          <t>ASPD:1|ATK:-1</t>
         </is>
       </c>
       <c r="O74" s="0" t="n">
@@ -5527,20 +5509,20 @@
         <v>0</v>
       </c>
       <c r="W74" s="0" t="n">
-        <v>11000900002</v>
+        <v>11000800003</v>
       </c>
       <c r="X74" s="0" t="n">
-        <v>11000900002</v>
+        <v>11000800003</v>
       </c>
       <c r="Y74" s="0" t="inlineStr">
         <is>
-          <t>铜墙铁壁-B</t>
+          <t>快枪手-C</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="0" t="n">
-        <v>11000900003</v>
+        <v>11000900001</v>
       </c>
       <c r="C75" s="0" t="n">
         <v>11</v>
@@ -5558,7 +5540,7 @@
       </c>
       <c r="J75" s="0" t="inlineStr">
         <is>
-          <t>DR:1|ASPD:-1</t>
+          <t>DR:1|HP:-1</t>
         </is>
       </c>
       <c r="O75" s="0" t="n">
@@ -5577,20 +5559,20 @@
         <v>0</v>
       </c>
       <c r="W75" s="0" t="n">
-        <v>11000900003</v>
+        <v>11000900001</v>
       </c>
       <c r="X75" s="0" t="n">
-        <v>11000900003</v>
+        <v>11000900001</v>
       </c>
       <c r="Y75" s="0" t="inlineStr">
         <is>
-          <t>铜墙铁壁-C</t>
+          <t>铜墙铁壁-A</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="0" t="n">
-        <v>11001000001</v>
+        <v>11000900002</v>
       </c>
       <c r="C76" s="0" t="n">
         <v>11</v>
@@ -5608,7 +5590,7 @@
       </c>
       <c r="J76" s="0" t="inlineStr">
         <is>
-          <t>HP:1|ASPD:-1</t>
+          <t>DR:1|ATK:-1</t>
         </is>
       </c>
       <c r="O76" s="0" t="n">
@@ -5627,20 +5609,20 @@
         <v>0</v>
       </c>
       <c r="W76" s="0" t="n">
-        <v>11001000001</v>
+        <v>11000900002</v>
       </c>
       <c r="X76" s="0" t="n">
-        <v>11001000001</v>
+        <v>11000900002</v>
       </c>
       <c r="Y76" s="0" t="inlineStr">
         <is>
-          <t>大块头-A</t>
+          <t>铜墙铁壁-B</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="0" t="n">
-        <v>11001000002</v>
+        <v>11000900003</v>
       </c>
       <c r="C77" s="0" t="n">
         <v>11</v>
@@ -5658,7 +5640,7 @@
       </c>
       <c r="J77" s="0" t="inlineStr">
         <is>
-          <t>HP:1|DR:-1</t>
+          <t>DR:1|ASPD:-1</t>
         </is>
       </c>
       <c r="O77" s="0" t="n">
@@ -5677,20 +5659,20 @@
         <v>0</v>
       </c>
       <c r="W77" s="0" t="n">
-        <v>11001000002</v>
+        <v>11000900003</v>
       </c>
       <c r="X77" s="0" t="n">
-        <v>11001000002</v>
+        <v>11000900003</v>
       </c>
       <c r="Y77" s="0" t="inlineStr">
         <is>
-          <t>大块头-B</t>
+          <t>铜墙铁壁-C</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="0" t="n">
-        <v>11001000003</v>
+        <v>11001000001</v>
       </c>
       <c r="C78" s="0" t="n">
         <v>11</v>
@@ -5708,7 +5690,7 @@
       </c>
       <c r="J78" s="0" t="inlineStr">
         <is>
-          <t>HP:1|ATK:-1</t>
+          <t>HP:1|ASPD:-1</t>
         </is>
       </c>
       <c r="O78" s="0" t="n">
@@ -5727,20 +5709,20 @@
         <v>0</v>
       </c>
       <c r="W78" s="0" t="n">
-        <v>11001000003</v>
+        <v>11001000001</v>
       </c>
       <c r="X78" s="0" t="n">
-        <v>11001000003</v>
+        <v>11001000001</v>
       </c>
       <c r="Y78" s="0" t="inlineStr">
         <is>
-          <t>大块头-C</t>
+          <t>大块头-A</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="0" t="n">
-        <v>11000700004</v>
+        <v>11001000002</v>
       </c>
       <c r="C79" s="0" t="n">
         <v>11</v>
@@ -5758,7 +5740,7 @@
       </c>
       <c r="J79" s="0" t="inlineStr">
         <is>
-          <t>ATK:1|RCD:1</t>
+          <t>HP:1|DR:-1</t>
         </is>
       </c>
       <c r="O79" s="0" t="n">
@@ -5777,20 +5759,20 @@
         <v>0</v>
       </c>
       <c r="W79" s="0" t="n">
-        <v>11000700004</v>
+        <v>11001000002</v>
       </c>
       <c r="X79" s="0" t="n">
-        <v>11000700004</v>
+        <v>11001000002</v>
       </c>
       <c r="Y79" s="0" t="inlineStr">
         <is>
-          <t>狂战士-D</t>
+          <t>大块头-B</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="0" t="n">
-        <v>11000700005</v>
+        <v>11001000003</v>
       </c>
       <c r="C80" s="0" t="n">
         <v>11</v>
@@ -5808,7 +5790,7 @@
       </c>
       <c r="J80" s="0" t="inlineStr">
         <is>
-          <t>ATK:1|CMP:1</t>
+          <t>HP:1|ATK:-1</t>
         </is>
       </c>
       <c r="O80" s="0" t="n">
@@ -5827,20 +5809,20 @@
         <v>0</v>
       </c>
       <c r="W80" s="0" t="n">
-        <v>11000700005</v>
+        <v>11001000003</v>
       </c>
       <c r="X80" s="0" t="n">
-        <v>11000700005</v>
+        <v>11001000003</v>
       </c>
       <c r="Y80" s="0" t="inlineStr">
         <is>
-          <t>狂战士-E</t>
+          <t>大块头-C</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="0" t="n">
-        <v>11000800004</v>
+        <v>11000700004</v>
       </c>
       <c r="C81" s="0" t="n">
         <v>11</v>
@@ -5858,7 +5840,7 @@
       </c>
       <c r="J81" s="0" t="inlineStr">
         <is>
-          <t>ASPD:1|RCD:1</t>
+          <t>ATK:1|RCD:1</t>
         </is>
       </c>
       <c r="O81" s="0" t="n">
@@ -5877,20 +5859,20 @@
         <v>0</v>
       </c>
       <c r="W81" s="0" t="n">
-        <v>11000800004</v>
+        <v>11000700004</v>
       </c>
       <c r="X81" s="0" t="n">
-        <v>11000800004</v>
+        <v>11000700004</v>
       </c>
       <c r="Y81" s="0" t="inlineStr">
         <is>
-          <t>快枪手-D</t>
+          <t>狂战士-D</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="0" t="n">
-        <v>11000800005</v>
+        <v>11000700005</v>
       </c>
       <c r="C82" s="0" t="n">
         <v>11</v>
@@ -5908,7 +5890,7 @@
       </c>
       <c r="J82" s="0" t="inlineStr">
         <is>
-          <t>ASPD:1|CMP:1</t>
+          <t>ATK:1|CMP:1</t>
         </is>
       </c>
       <c r="O82" s="0" t="n">
@@ -5927,20 +5909,20 @@
         <v>0</v>
       </c>
       <c r="W82" s="0" t="n">
-        <v>11000800005</v>
+        <v>11000700005</v>
       </c>
       <c r="X82" s="0" t="n">
-        <v>11000800005</v>
+        <v>11000700005</v>
       </c>
       <c r="Y82" s="0" t="inlineStr">
         <is>
-          <t>快枪手-E</t>
+          <t>狂战士-E</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="0" t="n">
-        <v>11000900004</v>
+        <v>11000800004</v>
       </c>
       <c r="C83" s="0" t="n">
         <v>11</v>
@@ -5958,7 +5940,7 @@
       </c>
       <c r="J83" s="0" t="inlineStr">
         <is>
-          <t>DR:1|RCD:1</t>
+          <t>ASPD:1|RCD:1</t>
         </is>
       </c>
       <c r="O83" s="0" t="n">
@@ -5977,20 +5959,20 @@
         <v>0</v>
       </c>
       <c r="W83" s="0" t="n">
-        <v>11000900004</v>
+        <v>11000800004</v>
       </c>
       <c r="X83" s="0" t="n">
-        <v>11000900004</v>
+        <v>11000800004</v>
       </c>
       <c r="Y83" s="0" t="inlineStr">
         <is>
-          <t>铜墙铁壁-D</t>
+          <t>快枪手-D</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="0" t="n">
-        <v>11000900005</v>
+        <v>11000800005</v>
       </c>
       <c r="C84" s="0" t="n">
         <v>11</v>
@@ -6008,7 +5990,7 @@
       </c>
       <c r="J84" s="0" t="inlineStr">
         <is>
-          <t>DR:1|CMP:1</t>
+          <t>ASPD:1|CMP:1</t>
         </is>
       </c>
       <c r="O84" s="0" t="n">
@@ -6027,20 +6009,20 @@
         <v>0</v>
       </c>
       <c r="W84" s="0" t="n">
-        <v>11000900005</v>
+        <v>11000800005</v>
       </c>
       <c r="X84" s="0" t="n">
-        <v>11000900005</v>
+        <v>11000800005</v>
       </c>
       <c r="Y84" s="0" t="inlineStr">
         <is>
-          <t>铜墙铁壁-E</t>
+          <t>快枪手-E</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="0" t="n">
-        <v>11001000004</v>
+        <v>11000900004</v>
       </c>
       <c r="C85" s="0" t="n">
         <v>11</v>
@@ -6058,7 +6040,7 @@
       </c>
       <c r="J85" s="0" t="inlineStr">
         <is>
-          <t>HP:1|RCD:1</t>
+          <t>DR:1|RCD:1</t>
         </is>
       </c>
       <c r="O85" s="0" t="n">
@@ -6077,20 +6059,20 @@
         <v>0</v>
       </c>
       <c r="W85" s="0" t="n">
-        <v>11001000004</v>
+        <v>11000900004</v>
       </c>
       <c r="X85" s="0" t="n">
-        <v>11001000004</v>
+        <v>11000900004</v>
       </c>
       <c r="Y85" s="0" t="inlineStr">
         <is>
-          <t>大块头-D</t>
+          <t>铜墙铁壁-D</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="0" t="n">
-        <v>11001000005</v>
+        <v>11000900005</v>
       </c>
       <c r="C86" s="0" t="n">
         <v>11</v>
@@ -6108,7 +6090,7 @@
       </c>
       <c r="J86" s="0" t="inlineStr">
         <is>
-          <t>HP:1|CMP:1</t>
+          <t>DR:1|CMP:1</t>
         </is>
       </c>
       <c r="O86" s="0" t="n">
@@ -6127,20 +6109,20 @@
         <v>0</v>
       </c>
       <c r="W86" s="0" t="n">
-        <v>11001000005</v>
+        <v>11000900005</v>
       </c>
       <c r="X86" s="0" t="n">
-        <v>11001000005</v>
+        <v>11000900005</v>
       </c>
       <c r="Y86" s="0" t="inlineStr">
         <is>
-          <t>大块头-E</t>
+          <t>铜墙铁壁-E</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="0" t="n">
-        <v>11001100001</v>
+        <v>11001000004</v>
       </c>
       <c r="C87" s="0" t="n">
         <v>11</v>
@@ -6158,14 +6140,14 @@
       </c>
       <c r="J87" s="0" t="inlineStr">
         <is>
-          <t>RCD:-1|HP:-0.5</t>
+          <t>HP:1|RCD:1</t>
         </is>
       </c>
       <c r="O87" s="0" t="n">
-        <v>0.75</v>
+        <v>0.5</v>
       </c>
       <c r="P87" s="0" t="n">
-        <v>0.5</v>
+        <v>0.2</v>
       </c>
       <c r="R87" s="0" t="n">
         <v>0</v>
@@ -6177,20 +6159,20 @@
         <v>0</v>
       </c>
       <c r="W87" s="0" t="n">
-        <v>11001100001</v>
+        <v>11001000004</v>
       </c>
       <c r="X87" s="0" t="n">
-        <v>11001100001</v>
+        <v>11001000004</v>
       </c>
       <c r="Y87" s="0" t="inlineStr">
         <is>
-          <t>魂牵梦绕-A</t>
+          <t>大块头-D</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="0" t="n">
-        <v>11001100002</v>
+        <v>11001000005</v>
       </c>
       <c r="C88" s="0" t="n">
         <v>11</v>
@@ -6208,14 +6190,14 @@
       </c>
       <c r="J88" s="0" t="inlineStr">
         <is>
-          <t>RCD:-1|DR:-0.5</t>
+          <t>HP:1|CMP:1</t>
         </is>
       </c>
       <c r="O88" s="0" t="n">
-        <v>0.75</v>
+        <v>0.5</v>
       </c>
       <c r="P88" s="0" t="n">
-        <v>0.5</v>
+        <v>0.2</v>
       </c>
       <c r="R88" s="0" t="n">
         <v>0</v>
@@ -6227,20 +6209,20 @@
         <v>0</v>
       </c>
       <c r="W88" s="0" t="n">
-        <v>11001100002</v>
+        <v>11001000005</v>
       </c>
       <c r="X88" s="0" t="n">
-        <v>11001100002</v>
+        <v>11001000005</v>
       </c>
       <c r="Y88" s="0" t="inlineStr">
         <is>
-          <t>魂牵梦绕-B</t>
+          <t>大块头-E</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="0" t="n">
-        <v>11001100003</v>
+        <v>11001100001</v>
       </c>
       <c r="C89" s="0" t="n">
         <v>11</v>
@@ -6258,7 +6240,7 @@
       </c>
       <c r="J89" s="0" t="inlineStr">
         <is>
-          <t>RCD:-1|ATK:-0.5</t>
+          <t>RCD:-1|HP:-0.5</t>
         </is>
       </c>
       <c r="O89" s="0" t="n">
@@ -6277,20 +6259,20 @@
         <v>0</v>
       </c>
       <c r="W89" s="0" t="n">
-        <v>11001100003</v>
+        <v>11001100001</v>
       </c>
       <c r="X89" s="0" t="n">
-        <v>11001100003</v>
+        <v>11001100001</v>
       </c>
       <c r="Y89" s="0" t="inlineStr">
         <is>
-          <t>魂牵梦绕-C</t>
+          <t>魂牵梦绕-A</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="0" t="n">
-        <v>11001100004</v>
+        <v>11001100002</v>
       </c>
       <c r="C90" s="0" t="n">
         <v>11</v>
@@ -6308,7 +6290,7 @@
       </c>
       <c r="J90" s="0" t="inlineStr">
         <is>
-          <t>RCD:-1|ASPD:-0.5</t>
+          <t>RCD:-1|DR:-0.5</t>
         </is>
       </c>
       <c r="O90" s="0" t="n">
@@ -6327,20 +6309,20 @@
         <v>0</v>
       </c>
       <c r="W90" s="0" t="n">
-        <v>11001100004</v>
+        <v>11001100002</v>
       </c>
       <c r="X90" s="0" t="n">
-        <v>11001100004</v>
+        <v>11001100002</v>
       </c>
       <c r="Y90" s="0" t="inlineStr">
         <is>
-          <t>魂牵梦绕-D</t>
+          <t>魂牵梦绕-B</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="0" t="n">
-        <v>11001100005</v>
+        <v>11001100003</v>
       </c>
       <c r="C91" s="0" t="n">
         <v>11</v>
@@ -6358,7 +6340,7 @@
       </c>
       <c r="J91" s="0" t="inlineStr">
         <is>
-          <t>RCD:-1|CMP:0.5</t>
+          <t>RCD:-1|ATK:-0.5</t>
         </is>
       </c>
       <c r="O91" s="0" t="n">
@@ -6377,20 +6359,20 @@
         <v>0</v>
       </c>
       <c r="W91" s="0" t="n">
-        <v>11001100005</v>
+        <v>11001100003</v>
       </c>
       <c r="X91" s="0" t="n">
-        <v>11001100005</v>
+        <v>11001100003</v>
       </c>
       <c r="Y91" s="0" t="inlineStr">
         <is>
-          <t>魂牵梦绕-E</t>
+          <t>魂牵梦绕-C</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="0" t="n">
-        <v>11001200001</v>
+        <v>11001100004</v>
       </c>
       <c r="C92" s="0" t="n">
         <v>11</v>
@@ -6408,7 +6390,7 @@
       </c>
       <c r="J92" s="0" t="inlineStr">
         <is>
-          <t>CMP:-1|HP:-0.5</t>
+          <t>RCD:-1|ASPD:-0.5</t>
         </is>
       </c>
       <c r="O92" s="0" t="n">
@@ -6427,20 +6409,20 @@
         <v>0</v>
       </c>
       <c r="W92" s="0" t="n">
-        <v>11001200001</v>
+        <v>11001100004</v>
       </c>
       <c r="X92" s="0" t="n">
-        <v>11001200001</v>
+        <v>11001100004</v>
       </c>
       <c r="Y92" s="0" t="inlineStr">
         <is>
-          <t>折上折-A</t>
+          <t>魂牵梦绕-D</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="0" t="n">
-        <v>11001200002</v>
+        <v>11001100005</v>
       </c>
       <c r="C93" s="0" t="n">
         <v>11</v>
@@ -6458,7 +6440,7 @@
       </c>
       <c r="J93" s="0" t="inlineStr">
         <is>
-          <t>CMP:-1|DR:-0.5</t>
+          <t>RCD:-1|CMP:0.5</t>
         </is>
       </c>
       <c r="O93" s="0" t="n">
@@ -6477,20 +6459,20 @@
         <v>0</v>
       </c>
       <c r="W93" s="0" t="n">
-        <v>11001200002</v>
+        <v>11001100005</v>
       </c>
       <c r="X93" s="0" t="n">
-        <v>11001200002</v>
+        <v>11001100005</v>
       </c>
       <c r="Y93" s="0" t="inlineStr">
         <is>
-          <t>折上折-B</t>
+          <t>魂牵梦绕-E</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="0" t="n">
-        <v>11001200003</v>
+        <v>11001200001</v>
       </c>
       <c r="C94" s="0" t="n">
         <v>11</v>
@@ -6508,7 +6490,7 @@
       </c>
       <c r="J94" s="0" t="inlineStr">
         <is>
-          <t>CMP:-1|ATK:-0.5</t>
+          <t>CMP:-1|HP:-0.5</t>
         </is>
       </c>
       <c r="O94" s="0" t="n">
@@ -6527,20 +6509,20 @@
         <v>0</v>
       </c>
       <c r="W94" s="0" t="n">
-        <v>11001200003</v>
+        <v>11001200001</v>
       </c>
       <c r="X94" s="0" t="n">
-        <v>11001200003</v>
+        <v>11001200001</v>
       </c>
       <c r="Y94" s="0" t="inlineStr">
         <is>
-          <t>折上折-C</t>
+          <t>折上折-A</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="0" t="n">
-        <v>11001200004</v>
+        <v>11001200002</v>
       </c>
       <c r="C95" s="0" t="n">
         <v>11</v>
@@ -6558,7 +6540,7 @@
       </c>
       <c r="J95" s="0" t="inlineStr">
         <is>
-          <t>CMP:-1|ASPD:-0.5</t>
+          <t>CMP:-1|DR:-0.5</t>
         </is>
       </c>
       <c r="O95" s="0" t="n">
@@ -6577,20 +6559,20 @@
         <v>0</v>
       </c>
       <c r="W95" s="0" t="n">
-        <v>11001200004</v>
+        <v>11001200002</v>
       </c>
       <c r="X95" s="0" t="n">
-        <v>11001200004</v>
+        <v>11001200002</v>
       </c>
       <c r="Y95" s="0" t="inlineStr">
         <is>
-          <t>折上折-D</t>
+          <t>折上折-B</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="0" t="n">
-        <v>11001200005</v>
+        <v>11001200003</v>
       </c>
       <c r="C96" s="0" t="n">
         <v>11</v>
@@ -6608,7 +6590,7 @@
       </c>
       <c r="J96" s="0" t="inlineStr">
         <is>
-          <t>CMP:-1|RCD:0.5</t>
+          <t>CMP:-1|ATK:-0.5</t>
         </is>
       </c>
       <c r="O96" s="0" t="n">
@@ -6627,40 +6609,48 @@
         <v>0</v>
       </c>
       <c r="W96" s="0" t="n">
-        <v>11001200005</v>
+        <v>11001200003</v>
       </c>
       <c r="X96" s="0" t="n">
-        <v>11001200005</v>
+        <v>11001200003</v>
       </c>
       <c r="Y96" s="0" t="inlineStr">
         <is>
-          <t>折上折-E</t>
+          <t>折上折-C</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="0" t="n">
-        <v>12000100001</v>
+        <v>11001200004</v>
       </c>
       <c r="C97" s="0" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D97" s="0" t="n">
-        <v>3</v>
+        <v>2</v>
+      </c>
+      <c r="G97" s="0" t="n">
+        <v>0</v>
       </c>
       <c r="H97" s="0" t="inlineStr">
         <is>
-          <t>BuffEntityBaseHPChange</t>
+          <t>BuffEntityAttributeMulti</t>
+        </is>
+      </c>
+      <c r="J97" s="0" t="inlineStr">
+        <is>
+          <t>CMP:-1|ASPD:-0.5</t>
         </is>
       </c>
       <c r="O97" s="0" t="n">
-        <v>0.05</v>
+        <v>0.75</v>
       </c>
       <c r="P97" s="0" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="S97" s="0" t="n">
-        <v>5</v>
+        <v>0.5</v>
+      </c>
+      <c r="R97" s="0" t="n">
+        <v>0</v>
       </c>
       <c r="T97" s="0" t="n">
         <v>0</v>
@@ -6668,44 +6658,49 @@
       <c r="U97" s="0" t="n">
         <v>0</v>
       </c>
-      <c r="V97" s="0" t="n">
-        <v>500001</v>
-      </c>
       <c r="W97" s="0" t="n">
-        <v>12000100001</v>
+        <v>11001200004</v>
       </c>
       <c r="X97" s="0" t="n">
-        <v>12000100001</v>
+        <v>11001200004</v>
       </c>
       <c r="Y97" s="0" t="inlineStr">
         <is>
-          <t>每隔{Time_S}秒恢复{Percentage}%生命</t>
+          <t>折上折-D</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="0" t="n">
-        <v>12000200001</v>
+        <v>11001200005</v>
       </c>
       <c r="C98" s="0" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D98" s="0" t="n">
-        <v>3</v>
+        <v>2</v>
+      </c>
+      <c r="G98" s="0" t="n">
+        <v>0</v>
       </c>
       <c r="H98" s="0" t="inlineStr">
         <is>
-          <t>BuffEntityBaseDRChange</t>
+          <t>BuffEntityAttributeMulti</t>
+        </is>
+      </c>
+      <c r="J98" s="0" t="inlineStr">
+        <is>
+          <t>CMP:-1|RCD:0.5</t>
         </is>
       </c>
       <c r="O98" s="0" t="n">
-        <v>0.05</v>
+        <v>0.75</v>
       </c>
       <c r="P98" s="0" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="S98" s="0" t="n">
-        <v>5</v>
+        <v>0.5</v>
+      </c>
+      <c r="R98" s="0" t="n">
+        <v>0</v>
       </c>
       <c r="T98" s="0" t="n">
         <v>0</v>
@@ -6713,24 +6708,21 @@
       <c r="U98" s="0" t="n">
         <v>0</v>
       </c>
-      <c r="V98" s="0" t="n">
-        <v>500002</v>
-      </c>
       <c r="W98" s="0" t="n">
-        <v>12000200001</v>
+        <v>11001200005</v>
       </c>
       <c r="X98" s="0" t="n">
-        <v>12000200001</v>
+        <v>11001200005</v>
       </c>
       <c r="Y98" s="0" t="inlineStr">
         <is>
-          <t>每隔{Time_S}秒恢复{Percentage}%护甲</t>
+          <t>折上折-E</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="0" t="n">
-        <v>12000300001</v>
+        <v>12000100001</v>
       </c>
       <c r="C99" s="0" t="n">
         <v>12</v>
@@ -6740,8 +6732,14 @@
       </c>
       <c r="H99" s="0" t="inlineStr">
         <is>
-          <t>BuffEntityPeriodicAttackAgain</t>
-        </is>
+          <t>BuffEntityBaseHPChange</t>
+        </is>
+      </c>
+      <c r="O99" s="0" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="P99" s="0" t="n">
+        <v>0.01</v>
       </c>
       <c r="S99" s="0" t="n">
         <v>5</v>
@@ -6752,21 +6750,24 @@
       <c r="U99" s="0" t="n">
         <v>0</v>
       </c>
+      <c r="V99" s="0" t="n">
+        <v>500001</v>
+      </c>
       <c r="W99" s="0" t="n">
-        <v>12000300001</v>
+        <v>12000100001</v>
       </c>
       <c r="X99" s="0" t="n">
-        <v>12000300001</v>
+        <v>12000100001</v>
       </c>
       <c r="Y99" s="0" t="inlineStr">
         <is>
-          <t>每隔{Time_S}秒立即攻击一次</t>
+          <t>每隔{Time_S}秒恢复{Percentage}%生命</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="0" t="n">
-        <v>12001100001</v>
+        <v>12000200001</v>
       </c>
       <c r="C100" s="0" t="n">
         <v>12</v>
@@ -6776,29 +6777,17 @@
       </c>
       <c r="H100" s="0" t="inlineStr">
         <is>
-          <t>BuffEntityConditionalAttribute</t>
-        </is>
-      </c>
-      <c r="I100" s="0" t="inlineStr">
-        <is>
-          <t>GameFightLogic_UnderAttack_Dead</t>
-        </is>
-      </c>
-      <c r="J100" s="0" t="inlineStr">
-        <is>
-          <t>HP</t>
-        </is>
-      </c>
-      <c r="L100" s="0" t="inlineStr">
-        <is>
-          <t>2001:10&amp;</t>
+          <t>BuffEntityBaseDRChange</t>
         </is>
       </c>
       <c r="O100" s="0" t="n">
-        <v>0.25</v>
+        <v>0.05</v>
       </c>
       <c r="P100" s="0" t="n">
-        <v>0.1</v>
+        <v>0.01</v>
+      </c>
+      <c r="S100" s="0" t="n">
+        <v>5</v>
       </c>
       <c r="T100" s="0" t="n">
         <v>0</v>
@@ -6806,21 +6795,24 @@
       <c r="U100" s="0" t="n">
         <v>0</v>
       </c>
+      <c r="V100" s="0" t="n">
+        <v>500002</v>
+      </c>
       <c r="W100" s="0" t="n">
-        <v>12001100001</v>
+        <v>12000200001</v>
       </c>
       <c r="X100" s="0" t="n">
-        <v>12001100001</v>
+        <v>12000200001</v>
       </c>
       <c r="Y100" s="0" t="inlineStr">
         <is>
-          <t>击杀{KillNum}次生物，生命增加{Percentage}%</t>
+          <t>每隔{Time_S}秒恢复{Percentage}%护甲</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="0" t="n">
-        <v>12001200001</v>
+        <v>12000300001</v>
       </c>
       <c r="C101" s="0" t="n">
         <v>12</v>
@@ -6830,29 +6822,11 @@
       </c>
       <c r="H101" s="0" t="inlineStr">
         <is>
-          <t>BuffEntityConditionalAttribute</t>
-        </is>
-      </c>
-      <c r="I101" s="0" t="inlineStr">
-        <is>
-          <t>GameFightLogic_UnderAttack_Dead</t>
-        </is>
-      </c>
-      <c r="J101" s="0" t="inlineStr">
-        <is>
-          <t>DR</t>
-        </is>
-      </c>
-      <c r="L101" s="0" t="inlineStr">
-        <is>
-          <t>2001:10&amp;</t>
-        </is>
-      </c>
-      <c r="O101" s="0" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="P101" s="0" t="n">
-        <v>0.1</v>
+          <t>BuffEntityPeriodicAttackAgain</t>
+        </is>
+      </c>
+      <c r="S101" s="0" t="n">
+        <v>5</v>
       </c>
       <c r="T101" s="0" t="n">
         <v>0</v>
@@ -6861,20 +6835,20 @@
         <v>0</v>
       </c>
       <c r="W101" s="0" t="n">
-        <v>12001200001</v>
+        <v>12000300001</v>
       </c>
       <c r="X101" s="0" t="n">
-        <v>12001200001</v>
+        <v>12000300001</v>
       </c>
       <c r="Y101" s="0" t="inlineStr">
         <is>
-          <t>击杀{KillNum}次生物，护甲增加{Percentage}%</t>
+          <t>每隔{Time_S}秒立即攻击一次</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="0" t="n">
-        <v>12001300001</v>
+        <v>12001100001</v>
       </c>
       <c r="C102" s="0" t="n">
         <v>12</v>
@@ -6894,7 +6868,7 @@
       </c>
       <c r="J102" s="0" t="inlineStr">
         <is>
-          <t>ATK</t>
+          <t>HP</t>
         </is>
       </c>
       <c r="L102" s="0" t="inlineStr">
@@ -6915,20 +6889,20 @@
         <v>0</v>
       </c>
       <c r="W102" s="0" t="n">
-        <v>12001300001</v>
+        <v>12001100001</v>
       </c>
       <c r="X102" s="0" t="n">
-        <v>12001300001</v>
+        <v>12001100001</v>
       </c>
       <c r="Y102" s="0" t="inlineStr">
         <is>
-          <t>击杀{KillNum}次生物，攻击力增加{Percentage}%</t>
+          <t>击杀{KillNum}次生物，生命增加{Percentage}%</t>
         </is>
       </c>
     </row>
     <row r="103" ht="12" customHeight="1" s="3">
       <c r="A103" s="0" t="n">
-        <v>12001400001</v>
+        <v>12001200001</v>
       </c>
       <c r="C103" s="0" t="n">
         <v>12</v>
@@ -6948,7 +6922,7 @@
       </c>
       <c r="J103" s="0" t="inlineStr">
         <is>
-          <t>ASPD</t>
+          <t>DR</t>
         </is>
       </c>
       <c r="L103" s="0" t="inlineStr">
@@ -6969,20 +6943,20 @@
         <v>0</v>
       </c>
       <c r="W103" s="0" t="n">
-        <v>12001400001</v>
+        <v>12001200001</v>
       </c>
       <c r="X103" s="0" t="n">
-        <v>12001400001</v>
+        <v>12001200001</v>
       </c>
       <c r="Y103" s="0" t="inlineStr">
         <is>
-          <t>击杀{KillNum}次生物，攻击速度增加{Percentage}%</t>
+          <t>击杀{KillNum}次生物，护甲增加{Percentage}%</t>
         </is>
       </c>
     </row>
     <row r="104" ht="12" customHeight="1" s="3">
       <c r="A104" s="0" t="n">
-        <v>12002100001</v>
+        <v>12001300001</v>
       </c>
       <c r="C104" s="0" t="n">
         <v>12</v>
@@ -6997,17 +6971,17 @@
       </c>
       <c r="I104" s="0" t="inlineStr">
         <is>
-          <t>GameFightLogic_UnderAttack</t>
+          <t>GameFightLogic_UnderAttack_Dead</t>
         </is>
       </c>
       <c r="J104" s="0" t="inlineStr">
         <is>
-          <t>HP</t>
+          <t>ATK</t>
         </is>
       </c>
       <c r="L104" s="0" t="inlineStr">
         <is>
-          <t>3001:1000&amp;</t>
+          <t>2001:10&amp;</t>
         </is>
       </c>
       <c r="O104" s="0" t="n">
@@ -7023,20 +6997,20 @@
         <v>0</v>
       </c>
       <c r="W104" s="0" t="n">
-        <v>12002100001</v>
+        <v>12001300001</v>
       </c>
       <c r="X104" s="0" t="n">
-        <v>12002100001</v>
+        <v>12001300001</v>
       </c>
       <c r="Y104" s="0" t="inlineStr">
         <is>
-          <t>受到{UnderAttackDamage}点伤害，生命增加{Percentage}%</t>
+          <t>击杀{KillNum}次生物，攻击力增加{Percentage}%</t>
         </is>
       </c>
     </row>
     <row r="105" ht="12" customHeight="1" s="3">
       <c r="A105" s="0" t="n">
-        <v>12002200001</v>
+        <v>12001400001</v>
       </c>
       <c r="C105" s="0" t="n">
         <v>12</v>
@@ -7051,17 +7025,17 @@
       </c>
       <c r="I105" s="0" t="inlineStr">
         <is>
-          <t>GameFightLogic_UnderAttack</t>
+          <t>GameFightLogic_UnderAttack_Dead</t>
         </is>
       </c>
       <c r="J105" s="0" t="inlineStr">
         <is>
-          <t>DR</t>
+          <t>ASPD</t>
         </is>
       </c>
       <c r="L105" s="0" t="inlineStr">
         <is>
-          <t>3001:1000&amp;</t>
+          <t>2001:10&amp;</t>
         </is>
       </c>
       <c r="O105" s="0" t="n">
@@ -7077,20 +7051,20 @@
         <v>0</v>
       </c>
       <c r="W105" s="0" t="n">
-        <v>12002200001</v>
+        <v>12001400001</v>
       </c>
       <c r="X105" s="0" t="n">
-        <v>12002200001</v>
+        <v>12001400001</v>
       </c>
       <c r="Y105" s="0" t="inlineStr">
         <is>
-          <t>受到{UnderAttackDamage}点伤害，护甲增加{Percentage}%</t>
+          <t>击杀{KillNum}次生物，攻击速度增加{Percentage}%</t>
         </is>
       </c>
     </row>
     <row r="106" ht="12" customHeight="1" s="3">
       <c r="A106" s="0" t="n">
-        <v>12002300001</v>
+        <v>12002100001</v>
       </c>
       <c r="C106" s="0" t="n">
         <v>12</v>
@@ -7110,7 +7084,7 @@
       </c>
       <c r="J106" s="0" t="inlineStr">
         <is>
-          <t>ATK</t>
+          <t>HP</t>
         </is>
       </c>
       <c r="L106" s="0" t="inlineStr">
@@ -7131,20 +7105,20 @@
         <v>0</v>
       </c>
       <c r="W106" s="0" t="n">
-        <v>12002300001</v>
+        <v>12002100001</v>
       </c>
       <c r="X106" s="0" t="n">
-        <v>12002300001</v>
+        <v>12002100001</v>
       </c>
       <c r="Y106" s="0" t="inlineStr">
         <is>
-          <t>受到{UnderAttackDamage}点伤害，攻击力增加{Percentage}%</t>
+          <t>受到{UnderAttackDamage}点伤害，生命增加{Percentage}%</t>
         </is>
       </c>
     </row>
     <row r="107" ht="12" customHeight="1" s="3">
       <c r="A107" s="0" t="n">
-        <v>12002400001</v>
+        <v>12002200001</v>
       </c>
       <c r="C107" s="0" t="n">
         <v>12</v>
@@ -7164,7 +7138,7 @@
       </c>
       <c r="J107" s="0" t="inlineStr">
         <is>
-          <t>ASPD</t>
+          <t>DR</t>
         </is>
       </c>
       <c r="L107" s="0" t="inlineStr">
@@ -7185,20 +7159,20 @@
         <v>0</v>
       </c>
       <c r="W107" s="0" t="n">
-        <v>12002400001</v>
+        <v>12002200001</v>
       </c>
       <c r="X107" s="0" t="n">
-        <v>12002400001</v>
+        <v>12002200001</v>
       </c>
       <c r="Y107" s="0" t="inlineStr">
         <is>
-          <t>受到{UnderAttackDamage}点伤害，攻击速度增加{Percentage}%</t>
+          <t>受到{UnderAttackDamage}点伤害，护甲增加{Percentage}%</t>
         </is>
       </c>
     </row>
     <row r="108" ht="12" customHeight="1" s="3">
       <c r="A108" s="0" t="n">
-        <v>12003100001</v>
+        <v>12002300001</v>
       </c>
       <c r="C108" s="0" t="n">
         <v>12</v>
@@ -7218,12 +7192,12 @@
       </c>
       <c r="J108" s="0" t="inlineStr">
         <is>
-          <t>HP</t>
+          <t>ATK</t>
         </is>
       </c>
       <c r="L108" s="0" t="inlineStr">
         <is>
-          <t>1001:0.5&amp;</t>
+          <t>3001:1000&amp;</t>
         </is>
       </c>
       <c r="O108" s="0" t="n">
@@ -7239,20 +7213,20 @@
         <v>0</v>
       </c>
       <c r="W108" s="0" t="n">
-        <v>12003100001</v>
+        <v>12002300001</v>
       </c>
       <c r="X108" s="0" t="n">
-        <v>12003100001</v>
+        <v>12002300001</v>
       </c>
       <c r="Y108" s="0" t="inlineStr">
         <is>
-          <t>血量少于{HPRateLess}%，生命增加{Percentage}%</t>
+          <t>受到{UnderAttackDamage}点伤害，攻击力增加{Percentage}%</t>
         </is>
       </c>
     </row>
     <row r="109" ht="12" customHeight="1" s="3">
       <c r="A109" s="0" t="n">
-        <v>12003200001</v>
+        <v>12002400001</v>
       </c>
       <c r="C109" s="0" t="n">
         <v>12</v>
@@ -7272,12 +7246,12 @@
       </c>
       <c r="J109" s="0" t="inlineStr">
         <is>
-          <t>DR</t>
+          <t>ASPD</t>
         </is>
       </c>
       <c r="L109" s="0" t="inlineStr">
         <is>
-          <t>1001:0.5&amp;</t>
+          <t>3001:1000&amp;</t>
         </is>
       </c>
       <c r="O109" s="0" t="n">
@@ -7293,20 +7267,20 @@
         <v>0</v>
       </c>
       <c r="W109" s="0" t="n">
-        <v>12003200001</v>
+        <v>12002400001</v>
       </c>
       <c r="X109" s="0" t="n">
-        <v>12003200001</v>
+        <v>12002400001</v>
       </c>
       <c r="Y109" s="0" t="inlineStr">
         <is>
-          <t>血量少于{HPRateLess}%，护甲增加{Percentage}%</t>
+          <t>受到{UnderAttackDamage}点伤害，攻击速度增加{Percentage}%</t>
         </is>
       </c>
     </row>
     <row r="110" ht="12" customHeight="1" s="3">
       <c r="A110" s="0" t="n">
-        <v>12003300001</v>
+        <v>12003100001</v>
       </c>
       <c r="C110" s="0" t="n">
         <v>12</v>
@@ -7326,7 +7300,7 @@
       </c>
       <c r="J110" s="0" t="inlineStr">
         <is>
-          <t>ATK</t>
+          <t>HP</t>
         </is>
       </c>
       <c r="L110" s="0" t="inlineStr">
@@ -7347,20 +7321,20 @@
         <v>0</v>
       </c>
       <c r="W110" s="0" t="n">
-        <v>12003300001</v>
+        <v>12003100001</v>
       </c>
       <c r="X110" s="0" t="n">
-        <v>12003300001</v>
+        <v>12003100001</v>
       </c>
       <c r="Y110" s="0" t="inlineStr">
         <is>
-          <t>血量少于{HPRateLess}%，攻击力增加{Percentage}%</t>
+          <t>血量少于{HPRateLess}%，生命增加{Percentage}%</t>
         </is>
       </c>
     </row>
     <row r="111" ht="12" customHeight="1" s="3">
       <c r="A111" s="0" t="n">
-        <v>12003400001</v>
+        <v>12003200001</v>
       </c>
       <c r="C111" s="0" t="n">
         <v>12</v>
@@ -7380,7 +7354,7 @@
       </c>
       <c r="J111" s="0" t="inlineStr">
         <is>
-          <t>ASPD</t>
+          <t>DR</t>
         </is>
       </c>
       <c r="L111" s="0" t="inlineStr">
@@ -7401,20 +7375,20 @@
         <v>0</v>
       </c>
       <c r="W111" s="0" t="n">
-        <v>12003400001</v>
+        <v>12003200001</v>
       </c>
       <c r="X111" s="0" t="n">
-        <v>12003400001</v>
+        <v>12003200001</v>
       </c>
       <c r="Y111" s="0" t="inlineStr">
         <is>
-          <t>血量少于{HPRateLess}%，攻击速度增加{Percentage}%</t>
+          <t>血量少于{HPRateLess}%，护甲增加{Percentage}%</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="0" t="n">
-        <v>12004100001</v>
+        <v>12003300001</v>
       </c>
       <c r="C112" s="0" t="n">
         <v>12</v>
@@ -7424,18 +7398,22 @@
       </c>
       <c r="H112" s="0" t="inlineStr">
         <is>
-          <t>BuffEntityConditionalAttributeTime</t>
-        </is>
-      </c>
-      <c r="I112" s="0" t="inlineStr"/>
+          <t>BuffEntityConditionalAttribute</t>
+        </is>
+      </c>
+      <c r="I112" s="0" t="inlineStr">
+        <is>
+          <t>GameFightLogic_UnderAttack</t>
+        </is>
+      </c>
       <c r="J112" s="0" t="inlineStr">
         <is>
-          <t>HP</t>
+          <t>ATK</t>
         </is>
       </c>
       <c r="L112" s="0" t="inlineStr">
         <is>
-          <t>7001:300&amp;</t>
+          <t>1001:0.5&amp;</t>
         </is>
       </c>
       <c r="O112" s="0" t="n">
@@ -7451,20 +7429,20 @@
         <v>0</v>
       </c>
       <c r="W112" s="0" t="n">
-        <v>12004100001</v>
+        <v>12003300001</v>
       </c>
       <c r="X112" s="0" t="n">
-        <v>12004100001</v>
+        <v>12003300001</v>
       </c>
       <c r="Y112" s="0" t="inlineStr">
         <is>
-          <t>在场存活超过{OnFieldTime}秒后，生命增加{Percentage}%</t>
+          <t>血量少于{HPRateLess}%，攻击力增加{Percentage}%</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="0" t="n">
-        <v>12004200001</v>
+        <v>12003400001</v>
       </c>
       <c r="C113" s="0" t="n">
         <v>12</v>
@@ -7474,18 +7452,22 @@
       </c>
       <c r="H113" s="0" t="inlineStr">
         <is>
-          <t>BuffEntityConditionalAttributeTime</t>
-        </is>
-      </c>
-      <c r="I113" s="0" t="inlineStr"/>
+          <t>BuffEntityConditionalAttribute</t>
+        </is>
+      </c>
+      <c r="I113" s="0" t="inlineStr">
+        <is>
+          <t>GameFightLogic_UnderAttack</t>
+        </is>
+      </c>
       <c r="J113" s="0" t="inlineStr">
         <is>
-          <t>DR</t>
+          <t>ASPD</t>
         </is>
       </c>
       <c r="L113" s="0" t="inlineStr">
         <is>
-          <t>7001:300&amp;</t>
+          <t>1001:0.5&amp;</t>
         </is>
       </c>
       <c r="O113" s="0" t="n">
@@ -7501,20 +7483,20 @@
         <v>0</v>
       </c>
       <c r="W113" s="0" t="n">
-        <v>12004200001</v>
+        <v>12003400001</v>
       </c>
       <c r="X113" s="0" t="n">
-        <v>12004200001</v>
+        <v>12003400001</v>
       </c>
       <c r="Y113" s="0" t="inlineStr">
         <is>
-          <t>在场存活超过{OnFieldTime}秒后，护甲增加{Percentage}%</t>
+          <t>血量少于{HPRateLess}%，攻击速度增加{Percentage}%</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="0" t="n">
-        <v>12004300001</v>
+        <v>12004100001</v>
       </c>
       <c r="C114" s="0" t="n">
         <v>12</v>
@@ -7530,7 +7512,7 @@
       <c r="I114" s="0" t="inlineStr"/>
       <c r="J114" s="0" t="inlineStr">
         <is>
-          <t>ATK</t>
+          <t>HP</t>
         </is>
       </c>
       <c r="L114" s="0" t="inlineStr">
@@ -7551,20 +7533,20 @@
         <v>0</v>
       </c>
       <c r="W114" s="0" t="n">
-        <v>12004300001</v>
+        <v>12004100001</v>
       </c>
       <c r="X114" s="0" t="n">
-        <v>12004300001</v>
+        <v>12004100001</v>
       </c>
       <c r="Y114" s="0" t="inlineStr">
         <is>
-          <t>在场存活超过{OnFieldTime}秒后，攻击力增加{Percentage}%</t>
+          <t>在场存活超过{OnFieldTime}秒后，生命增加{Percentage}%</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="0" t="n">
-        <v>12004400001</v>
+        <v>12004200001</v>
       </c>
       <c r="C115" s="0" t="n">
         <v>12</v>
@@ -7580,7 +7562,7 @@
       <c r="I115" s="0" t="inlineStr"/>
       <c r="J115" s="0" t="inlineStr">
         <is>
-          <t>ASPD</t>
+          <t>DR</t>
         </is>
       </c>
       <c r="L115" s="0" t="inlineStr">
@@ -7601,20 +7583,20 @@
         <v>0</v>
       </c>
       <c r="W115" s="0" t="n">
-        <v>12004400001</v>
+        <v>12004200001</v>
       </c>
       <c r="X115" s="0" t="n">
-        <v>12004400001</v>
+        <v>12004200001</v>
       </c>
       <c r="Y115" s="0" t="inlineStr">
         <is>
-          <t>在场存活超过{OnFieldTime}秒后，攻击速度增加{Percentage}%</t>
+          <t>在场存活超过{OnFieldTime}秒后，护甲增加{Percentage}%</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="0" t="n">
-        <v>12010100001</v>
+        <v>12004300001</v>
       </c>
       <c r="C116" s="0" t="n">
         <v>12</v>
@@ -7624,18 +7606,25 @@
       </c>
       <c r="H116" s="0" t="inlineStr">
         <is>
-          <t>BuffEntityConditionalCreateCrystal</t>
-        </is>
-      </c>
-      <c r="I116" s="0" t="inlineStr">
-        <is>
-          <t>GameFightLogic_UnderAttack_Dead</t>
+          <t>BuffEntityConditionalAttributeTime</t>
+        </is>
+      </c>
+      <c r="I116" s="0" t="inlineStr"/>
+      <c r="J116" s="0" t="inlineStr">
+        <is>
+          <t>ATK</t>
         </is>
       </c>
       <c r="L116" s="0" t="inlineStr">
         <is>
-          <t>2001:10&amp;</t>
-        </is>
+          <t>7001:300&amp;</t>
+        </is>
+      </c>
+      <c r="O116" s="0" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="P116" s="0" t="n">
+        <v>0.1</v>
       </c>
       <c r="T116" s="0" t="n">
         <v>0</v>
@@ -7644,20 +7633,20 @@
         <v>0</v>
       </c>
       <c r="W116" s="0" t="n">
-        <v>12010100001</v>
+        <v>12004300001</v>
       </c>
       <c r="X116" s="0" t="n">
-        <v>12010100001</v>
+        <v>12004300001</v>
       </c>
       <c r="Y116" s="0" t="inlineStr">
         <is>
-          <t>击杀{KillNum}次生物，掉落一次魔晶</t>
+          <t>在场存活超过{OnFieldTime}秒后，攻击力增加{Percentage}%</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="0" t="n">
-        <v>12010200001</v>
+        <v>12004400001</v>
       </c>
       <c r="C117" s="0" t="n">
         <v>12</v>
@@ -7667,18 +7656,25 @@
       </c>
       <c r="H117" s="0" t="inlineStr">
         <is>
-          <t>BuffEntityConditionalCreateCrystal</t>
-        </is>
-      </c>
-      <c r="I117" s="0" t="inlineStr">
-        <is>
-          <t>GameFightLogic_UnderAttack</t>
+          <t>BuffEntityConditionalAttributeTime</t>
+        </is>
+      </c>
+      <c r="I117" s="0" t="inlineStr"/>
+      <c r="J117" s="0" t="inlineStr">
+        <is>
+          <t>ASPD</t>
         </is>
       </c>
       <c r="L117" s="0" t="inlineStr">
         <is>
-          <t>3001:1000&amp;</t>
-        </is>
+          <t>7001:300&amp;</t>
+        </is>
+      </c>
+      <c r="O117" s="0" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="P117" s="0" t="n">
+        <v>0.1</v>
       </c>
       <c r="T117" s="0" t="n">
         <v>0</v>
@@ -7687,20 +7683,20 @@
         <v>0</v>
       </c>
       <c r="W117" s="0" t="n">
-        <v>12010200001</v>
+        <v>12004400001</v>
       </c>
       <c r="X117" s="0" t="n">
-        <v>12010200001</v>
+        <v>12004400001</v>
       </c>
       <c r="Y117" s="0" t="inlineStr">
         <is>
-          <t>受到{UnderAttackDamage}点伤害，掉落一次魔晶</t>
+          <t>在场存活超过{OnFieldTime}秒后，攻击速度增加{Percentage}%</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="0" t="n">
-        <v>12010300001</v>
+        <v>12010100001</v>
       </c>
       <c r="C118" s="0" t="n">
         <v>12</v>
@@ -7715,12 +7711,12 @@
       </c>
       <c r="I118" s="0" t="inlineStr">
         <is>
-          <t>GameFightLogic_UnderAttack</t>
+          <t>GameFightLogic_UnderAttack_Dead</t>
         </is>
       </c>
       <c r="L118" s="0" t="inlineStr">
         <is>
-          <t>4001:1000&amp;</t>
+          <t>2001:10&amp;</t>
         </is>
       </c>
       <c r="T118" s="0" t="n">
@@ -7730,20 +7726,20 @@
         <v>0</v>
       </c>
       <c r="W118" s="0" t="n">
-        <v>12010300001</v>
+        <v>12010100001</v>
       </c>
       <c r="X118" s="0" t="n">
-        <v>12010300001</v>
+        <v>12010100001</v>
       </c>
       <c r="Y118" s="0" t="inlineStr">
         <is>
-          <t>造成{AttackDamage}点伤害，掉落一次魔晶</t>
+          <t>击杀{KillNum}次生物，掉落一次魔晶</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="0" t="n">
-        <v>12010400001</v>
+        <v>12010200001</v>
       </c>
       <c r="C119" s="0" t="n">
         <v>12</v>
@@ -7758,12 +7754,12 @@
       </c>
       <c r="I119" s="0" t="inlineStr">
         <is>
-          <t>GameFightLogic_RegainHP</t>
+          <t>GameFightLogic_UnderAttack</t>
         </is>
       </c>
       <c r="L119" s="0" t="inlineStr">
         <is>
-          <t>5001:500&amp;</t>
+          <t>3001:1000&amp;</t>
         </is>
       </c>
       <c r="T119" s="0" t="n">
@@ -7773,20 +7769,20 @@
         <v>0</v>
       </c>
       <c r="W119" s="0" t="n">
-        <v>12010400001</v>
+        <v>12010200001</v>
       </c>
       <c r="X119" s="0" t="n">
-        <v>12010400001</v>
+        <v>12010200001</v>
       </c>
       <c r="Y119" s="0" t="inlineStr">
         <is>
-          <t>累计被治疗{RegainHPReceived}点，掉落一次魔晶</t>
+          <t>受到{UnderAttackDamage}点伤害，掉落一次魔晶</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="0" t="n">
-        <v>12010500001</v>
+        <v>12010300001</v>
       </c>
       <c r="C120" s="0" t="n">
         <v>12</v>
@@ -7801,12 +7797,12 @@
       </c>
       <c r="I120" s="0" t="inlineStr">
         <is>
-          <t>GameFightLogic_RegainHP</t>
+          <t>GameFightLogic_UnderAttack</t>
         </is>
       </c>
       <c r="L120" s="0" t="inlineStr">
         <is>
-          <t>6001:1000&amp;</t>
+          <t>4001:1000&amp;</t>
         </is>
       </c>
       <c r="T120" s="0" t="n">
@@ -7816,20 +7812,20 @@
         <v>0</v>
       </c>
       <c r="W120" s="0" t="n">
-        <v>12010500001</v>
+        <v>12010300001</v>
       </c>
       <c r="X120" s="0" t="n">
-        <v>12010500001</v>
+        <v>12010300001</v>
       </c>
       <c r="Y120" s="0" t="inlineStr">
         <is>
-          <t>累计治疗{RegainHPCast}点，掉落一次魔晶</t>
+          <t>造成{AttackDamage}点伤害，掉落一次魔晶</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="0" t="n">
-        <v>12011100001</v>
+        <v>12010400001</v>
       </c>
       <c r="C121" s="0" t="n">
         <v>12</v>
@@ -7839,17 +7835,17 @@
       </c>
       <c r="H121" s="0" t="inlineStr">
         <is>
-          <t>BuffEntityConditionalAttackAgain</t>
+          <t>BuffEntityConditionalCreateCrystal</t>
         </is>
       </c>
       <c r="I121" s="0" t="inlineStr">
         <is>
-          <t>GameFightLogic_UnderAttack_Dead</t>
+          <t>GameFightLogic_RegainHP</t>
         </is>
       </c>
       <c r="L121" s="0" t="inlineStr">
         <is>
-          <t>2001:1&amp;</t>
+          <t>5001:500&amp;</t>
         </is>
       </c>
       <c r="T121" s="0" t="n">
@@ -7859,20 +7855,20 @@
         <v>0</v>
       </c>
       <c r="W121" s="0" t="n">
-        <v>12011100001</v>
+        <v>12010400001</v>
       </c>
       <c r="X121" s="0" t="n">
-        <v>12011100001</v>
+        <v>12010400001</v>
       </c>
       <c r="Y121" s="0" t="inlineStr">
         <is>
-          <t>击杀{KillNum}次生物，立即攻击一次</t>
+          <t>累计被治疗{RegainHPReceived}点，掉落一次魔晶</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="0" t="n">
-        <v>12011200001</v>
+        <v>12010500001</v>
       </c>
       <c r="C122" s="0" t="n">
         <v>12</v>
@@ -7882,17 +7878,17 @@
       </c>
       <c r="H122" s="0" t="inlineStr">
         <is>
-          <t>BuffEntityConditionalAttackAgain</t>
+          <t>BuffEntityConditionalCreateCrystal</t>
         </is>
       </c>
       <c r="I122" s="0" t="inlineStr">
         <is>
-          <t>GameFightLogic_UnderAttack</t>
+          <t>GameFightLogic_RegainHP</t>
         </is>
       </c>
       <c r="L122" s="0" t="inlineStr">
         <is>
-          <t>3001:200&amp;</t>
+          <t>6001:1000&amp;</t>
         </is>
       </c>
       <c r="T122" s="0" t="n">
@@ -7902,20 +7898,20 @@
         <v>0</v>
       </c>
       <c r="W122" s="0" t="n">
-        <v>12011200001</v>
+        <v>12010500001</v>
       </c>
       <c r="X122" s="0" t="n">
-        <v>12011200001</v>
+        <v>12010500001</v>
       </c>
       <c r="Y122" s="0" t="inlineStr">
         <is>
-          <t>受到{UnderAttackDamage}点伤害，秒再攻击一次</t>
+          <t>累计治疗{RegainHPCast}点，掉落一次魔晶</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="0" t="n">
-        <v>12011300001</v>
+        <v>12011100001</v>
       </c>
       <c r="C123" s="0" t="n">
         <v>12</v>
@@ -7930,12 +7926,12 @@
       </c>
       <c r="I123" s="0" t="inlineStr">
         <is>
-          <t>GameFightLogic_UnderAttack</t>
+          <t>GameFightLogic_UnderAttack_Dead</t>
         </is>
       </c>
       <c r="L123" s="0" t="inlineStr">
         <is>
-          <t>4001:200&amp;</t>
+          <t>2001:1&amp;</t>
         </is>
       </c>
       <c r="T123" s="0" t="n">
@@ -7945,20 +7941,20 @@
         <v>0</v>
       </c>
       <c r="W123" s="0" t="n">
-        <v>12011300001</v>
+        <v>12011100001</v>
       </c>
       <c r="X123" s="0" t="n">
-        <v>12011300001</v>
+        <v>12011100001</v>
       </c>
       <c r="Y123" s="0" t="inlineStr">
         <is>
-          <t>造成{AttackDamage}点伤害，秒再攻击一次</t>
+          <t>击杀{KillNum}次生物，立即攻击一次</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="0" t="n">
-        <v>12012100001</v>
+        <v>12011200001</v>
       </c>
       <c r="C124" s="0" t="n">
         <v>12</v>
@@ -7968,24 +7964,18 @@
       </c>
       <c r="H124" s="0" t="inlineStr">
         <is>
-          <t>BuffEntityConditionalDemonLordMPRegain</t>
+          <t>BuffEntityConditionalAttackAgain</t>
         </is>
       </c>
       <c r="I124" s="0" t="inlineStr">
         <is>
-          <t>GameFightLogic_UnderAttack_Dead</t>
+          <t>GameFightLogic_UnderAttack</t>
         </is>
       </c>
       <c r="L124" s="0" t="inlineStr">
         <is>
-          <t>2001:1&amp;</t>
-        </is>
-      </c>
-      <c r="M124" s="0" t="n">
-        <v>20</v>
-      </c>
-      <c r="N124" s="0" t="n">
-        <v>10</v>
+          <t>3001:200&amp;</t>
+        </is>
       </c>
       <c r="T124" s="0" t="n">
         <v>0</v>
@@ -7994,20 +7984,20 @@
         <v>0</v>
       </c>
       <c r="W124" s="0" t="n">
-        <v>12012100001</v>
+        <v>12011200001</v>
       </c>
       <c r="X124" s="0" t="n">
-        <v>12012100001</v>
+        <v>12011200001</v>
       </c>
       <c r="Y124" s="0" t="inlineStr">
         <is>
-          <t>每击杀{KillNum}个生物，魔王回复{Value}点魔力</t>
+          <t>受到{UnderAttackDamage}点伤害，秒再攻击一次</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="0" t="n">
-        <v>12012200001</v>
+        <v>12011300001</v>
       </c>
       <c r="C125" s="0" t="n">
         <v>12</v>
@@ -8017,7 +8007,7 @@
       </c>
       <c r="H125" s="0" t="inlineStr">
         <is>
-          <t>BuffEntityConditionalDemonLordMPRegain</t>
+          <t>BuffEntityConditionalAttackAgain</t>
         </is>
       </c>
       <c r="I125" s="0" t="inlineStr">
@@ -8027,14 +8017,8 @@
       </c>
       <c r="L125" s="0" t="inlineStr">
         <is>
-          <t>3001:100&amp;</t>
-        </is>
-      </c>
-      <c r="M125" s="0" t="n">
-        <v>20</v>
-      </c>
-      <c r="N125" s="0" t="n">
-        <v>10</v>
+          <t>4001:200&amp;</t>
+        </is>
       </c>
       <c r="T125" s="0" t="n">
         <v>0</v>
@@ -8043,40 +8027,47 @@
         <v>0</v>
       </c>
       <c r="W125" s="0" t="n">
-        <v>12012200001</v>
+        <v>12011300001</v>
       </c>
       <c r="X125" s="0" t="n">
-        <v>12012200001</v>
+        <v>12011300001</v>
       </c>
       <c r="Y125" s="0" t="inlineStr">
         <is>
-          <t>累计受到{UnderAttackDamage}点伤害，魔王回复{Value}点魔力</t>
+          <t>造成{AttackDamage}点伤害，秒再攻击一次</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="0" t="n">
-        <v>13000100001</v>
+        <v>12012100001</v>
       </c>
       <c r="C126" s="0" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D126" s="0" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H126" s="0" t="inlineStr">
         <is>
-          <t>BuffEntityPeriodicPickupCrystal</t>
+          <t>BuffEntityConditionalDemonLordMPRegain</t>
+        </is>
+      </c>
+      <c r="I126" s="0" t="inlineStr">
+        <is>
+          <t>GameFightLogic_UnderAttack_Dead</t>
+        </is>
+      </c>
+      <c r="L126" s="0" t="inlineStr">
+        <is>
+          <t>2001:1&amp;</t>
         </is>
       </c>
       <c r="M126" s="0" t="n">
-        <v>3</v>
+        <v>20</v>
       </c>
       <c r="N126" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="S126" s="0" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T126" s="0" t="n">
         <v>0</v>
@@ -8085,36 +8076,47 @@
         <v>0</v>
       </c>
       <c r="W126" s="0" t="n">
-        <v>13000100001</v>
+        <v>12012100001</v>
       </c>
       <c r="X126" s="0" t="n">
-        <v>13000100001</v>
+        <v>12012100001</v>
       </c>
       <c r="Y126" s="0" t="inlineStr">
         <is>
-          <t>每隔{Time_S}秒自动拾取附近魔晶</t>
+          <t>每击杀{KillNum}个生物，魔王回复{Value}点魔力</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" s="0" t="n">
-        <v>13000200001</v>
+        <v>12012200001</v>
       </c>
       <c r="C127" s="0" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D127" s="0" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H127" s="0" t="inlineStr">
         <is>
-          <t>BuffEntityConditionalDeadRebirth</t>
+          <t>BuffEntityConditionalDemonLordMPRegain</t>
         </is>
       </c>
       <c r="I127" s="0" t="inlineStr">
         <is>
-          <t>GameFightLogic_CreatureDeadEnd</t>
-        </is>
+          <t>GameFightLogic_UnderAttack</t>
+        </is>
+      </c>
+      <c r="L127" s="0" t="inlineStr">
+        <is>
+          <t>3001:100&amp;</t>
+        </is>
+      </c>
+      <c r="M127" s="0" t="n">
+        <v>20</v>
+      </c>
+      <c r="N127" s="0" t="n">
+        <v>10</v>
       </c>
       <c r="T127" s="0" t="n">
         <v>0</v>
@@ -8122,24 +8124,21 @@
       <c r="U127" s="0" t="n">
         <v>0</v>
       </c>
-      <c r="V127" s="0" t="n">
-        <v>500001</v>
-      </c>
       <c r="W127" s="0" t="n">
-        <v>13000200001</v>
+        <v>12012200001</v>
       </c>
       <c r="X127" s="0" t="n">
-        <v>13000200001</v>
+        <v>12012200001</v>
       </c>
       <c r="Y127" s="0" t="inlineStr">
         <is>
-          <t>死亡后重生</t>
+          <t>累计受到{UnderAttackDamage}点伤害，魔王回复{Value}点魔力</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" s="0" t="n">
-        <v>13000300001</v>
+        <v>13000100001</v>
       </c>
       <c r="C128" s="0" t="n">
         <v>13</v>
@@ -8149,20 +8148,18 @@
       </c>
       <c r="H128" s="0" t="inlineStr">
         <is>
-          <t>BuffEntityConditionalDeadAttack</t>
-        </is>
-      </c>
-      <c r="I128" s="0" t="inlineStr">
-        <is>
-          <t>GameFightLogic_CreatureDeadEnd</t>
-        </is>
-      </c>
-      <c r="J128" s="0" t="n">
-        <v>300001</v>
-      </c>
-      <c r="O128" s="0" t="n">
+          <t>BuffEntityPeriodicPickupCrystal</t>
+        </is>
+      </c>
+      <c r="M128" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="N128" s="0" t="n">
         <v>1</v>
       </c>
+      <c r="S128" s="0" t="n">
+        <v>3</v>
+      </c>
       <c r="T128" s="0" t="n">
         <v>0</v>
       </c>
@@ -8170,20 +8167,20 @@
         <v>0</v>
       </c>
       <c r="W128" s="0" t="n">
-        <v>13000300001</v>
+        <v>13000100001</v>
       </c>
       <c r="X128" s="0" t="n">
-        <v>13000300001</v>
+        <v>13000100001</v>
       </c>
       <c r="Y128" s="0" t="inlineStr">
         <is>
-          <t>死亡后爆炸</t>
+          <t>每隔{Time_S}秒自动拾取附近魔晶</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" s="0" t="n">
-        <v>13000400001</v>
+        <v>13000200001</v>
       </c>
       <c r="C129" s="0" t="n">
         <v>13</v>
@@ -8193,7 +8190,7 @@
       </c>
       <c r="H129" s="0" t="inlineStr">
         <is>
-          <t>BuffEntityConditionalDeadAreaHPChange</t>
+          <t>BuffEntityConditionalDeadRebirth</t>
         </is>
       </c>
       <c r="I129" s="0" t="inlineStr">
@@ -8201,36 +8198,30 @@
           <t>GameFightLogic_CreatureDeadEnd</t>
         </is>
       </c>
-      <c r="J129" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="O129" s="0" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="P129" s="0" t="n">
-        <v>0.01</v>
-      </c>
       <c r="T129" s="0" t="n">
         <v>0</v>
       </c>
       <c r="U129" s="0" t="n">
         <v>0</v>
       </c>
+      <c r="V129" s="0" t="n">
+        <v>500001</v>
+      </c>
       <c r="W129" s="0" t="n">
-        <v>13000400001</v>
+        <v>13000200001</v>
       </c>
       <c r="X129" s="0" t="n">
-        <v>13000400001</v>
+        <v>13000200001</v>
       </c>
       <c r="Y129" s="0" t="inlineStr">
         <is>
-          <t>死亡后恢复附近友军生命，恢复量:自身生命上限的{Percentage}%</t>
+          <t>死亡后重生</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" s="0" t="n">
-        <v>13000500001</v>
+        <v>13000300001</v>
       </c>
       <c r="C130" s="0" t="n">
         <v>13</v>
@@ -8240,7 +8231,7 @@
       </c>
       <c r="H130" s="0" t="inlineStr">
         <is>
-          <t>BuffEntityConditionalDeadAreaDRChange</t>
+          <t>BuffEntityConditionalDeadAttack</t>
         </is>
       </c>
       <c r="I130" s="0" t="inlineStr">
@@ -8249,14 +8240,11 @@
         </is>
       </c>
       <c r="J130" s="0" t="n">
+        <v>300001</v>
+      </c>
+      <c r="O130" s="0" t="n">
         <v>1</v>
       </c>
-      <c r="O130" s="0" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="P130" s="0" t="n">
-        <v>0.01</v>
-      </c>
       <c r="T130" s="0" t="n">
         <v>0</v>
       </c>
@@ -8264,20 +8252,20 @@
         <v>0</v>
       </c>
       <c r="W130" s="0" t="n">
-        <v>13000500001</v>
+        <v>13000300001</v>
       </c>
       <c r="X130" s="0" t="n">
-        <v>13000500001</v>
+        <v>13000300001</v>
       </c>
       <c r="Y130" s="0" t="inlineStr">
         <is>
-          <t>死亡后恢复附近友军护甲，恢复量:自身护甲上限的{Percentage}%</t>
+          <t>死亡后爆炸</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" s="0" t="n">
-        <v>13000600001</v>
+        <v>13000400001</v>
       </c>
       <c r="C131" s="0" t="n">
         <v>13</v>
@@ -8287,7 +8275,7 @@
       </c>
       <c r="H131" s="0" t="inlineStr">
         <is>
-          <t>BuffEntityConditionalDeadCreateCrystal</t>
+          <t>BuffEntityConditionalDeadAreaHPChange</t>
         </is>
       </c>
       <c r="I131" s="0" t="inlineStr">
@@ -8295,8 +8283,14 @@
           <t>GameFightLogic_CreatureDeadEnd</t>
         </is>
       </c>
-      <c r="Q131" s="0" t="n">
-        <v>0.2</v>
+      <c r="J131" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="O131" s="0" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="P131" s="0" t="n">
+        <v>0.01</v>
       </c>
       <c r="T131" s="0" t="n">
         <v>0</v>
@@ -8305,70 +8299,45 @@
         <v>0</v>
       </c>
       <c r="W131" s="0" t="n">
-        <v>13000600001</v>
+        <v>13000400001</v>
       </c>
       <c r="X131" s="0" t="n">
-        <v>13000600001</v>
+        <v>13000400001</v>
       </c>
       <c r="Y131" s="0" t="inlineStr">
         <is>
-          <t>死亡后{Percentage}%生成魔晶</t>
+          <t>死亡后恢复附近友军生命，恢复量:自身生命上限的{Percentage}%</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" s="0" t="n">
-        <v>3000500001</v>
-      </c>
-      <c r="B132" s="0" t="inlineStr"/>
+        <v>13000500001</v>
+      </c>
       <c r="C132" s="0" t="n">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="D132" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="E132" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="F132" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="G132" s="0" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H132" s="0" t="inlineStr">
         <is>
-          <t>BuffEntityPeriodicAttackBoomerang</t>
-        </is>
-      </c>
-      <c r="I132" s="0" t="inlineStr"/>
-      <c r="J132" s="0" t="inlineStr">
-        <is>
-          <t>1,300051</t>
-        </is>
-      </c>
-      <c r="K132" s="0" t="inlineStr"/>
-      <c r="L132" s="0" t="inlineStr"/>
-      <c r="M132" s="0" t="n">
+          <t>BuffEntityConditionalDeadAreaDRChange</t>
+        </is>
+      </c>
+      <c r="I132" s="0" t="inlineStr">
+        <is>
+          <t>GameFightLogic_CreatureDeadEnd</t>
+        </is>
+      </c>
+      <c r="J132" s="0" t="n">
         <v>1</v>
       </c>
-      <c r="N132" s="0" t="n">
-        <v>0</v>
-      </c>
       <c r="O132" s="0" t="n">
-        <v>0</v>
+        <v>0.05</v>
       </c>
       <c r="P132" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q132" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="R132" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="S132" s="0" t="n">
-        <v>5</v>
+        <v>0.01</v>
       </c>
       <c r="T132" s="0" t="n">
         <v>0</v>
@@ -8376,74 +8345,40 @@
       <c r="U132" s="0" t="n">
         <v>0</v>
       </c>
-      <c r="V132" s="0" t="n">
-        <v>0</v>
-      </c>
       <c r="W132" s="0" t="n">
-        <v>3000500001</v>
+        <v>13000500001</v>
       </c>
       <c r="X132" s="0" t="n">
-        <v>3000500001</v>
+        <v>13000500001</v>
       </c>
       <c r="Y132" s="0" t="inlineStr">
         <is>
-          <t>死亡回旋Lv1-每5秒发射1枚回旋镖,伤害=魔王攻击力,逐目标减半保底1</t>
+          <t>死亡后恢复附近友军护甲，恢复量:自身护甲上限的{Percentage}%</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" s="0" t="n">
-        <v>3000500002</v>
-      </c>
-      <c r="B133" s="0" t="inlineStr"/>
+        <v>13000600001</v>
+      </c>
       <c r="C133" s="0" t="n">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="D133" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="E133" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="F133" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="G133" s="0" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H133" s="0" t="inlineStr">
         <is>
-          <t>BuffEntityPeriodicAttackBoomerang</t>
-        </is>
-      </c>
-      <c r="I133" s="0" t="inlineStr"/>
-      <c r="J133" s="0" t="inlineStr">
-        <is>
-          <t>2,300051</t>
-        </is>
-      </c>
-      <c r="K133" s="0" t="inlineStr"/>
-      <c r="L133" s="0" t="inlineStr"/>
-      <c r="M133" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="N133" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="O133" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="P133" s="0" t="n">
-        <v>0</v>
+          <t>BuffEntityConditionalDeadCreateCrystal</t>
+        </is>
+      </c>
+      <c r="I133" s="0" t="inlineStr">
+        <is>
+          <t>GameFightLogic_CreatureDeadEnd</t>
+        </is>
       </c>
       <c r="Q133" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="R133" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="S133" s="0" t="n">
-        <v>5</v>
+        <v>0.2</v>
       </c>
       <c r="T133" s="0" t="n">
         <v>0</v>
@@ -8451,24 +8386,21 @@
       <c r="U133" s="0" t="n">
         <v>0</v>
       </c>
-      <c r="V133" s="0" t="n">
-        <v>0</v>
-      </c>
       <c r="W133" s="0" t="n">
-        <v>3000500001</v>
+        <v>13000600001</v>
       </c>
       <c r="X133" s="0" t="n">
-        <v>3000500001</v>
+        <v>13000600001</v>
       </c>
       <c r="Y133" s="0" t="inlineStr">
         <is>
-          <t>死亡回旋Lv2-每5秒发射2枚回旋镖,伤害=魔王攻击力,逐目标减半保底1</t>
+          <t>死亡后{Percentage}%生成魔晶</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" s="0" t="n">
-        <v>3000500003</v>
+        <v>3000500001</v>
       </c>
       <c r="B134" s="0" t="inlineStr"/>
       <c r="C134" s="0" t="n">
@@ -8494,7 +8426,7 @@
       <c r="I134" s="0" t="inlineStr"/>
       <c r="J134" s="0" t="inlineStr">
         <is>
-          <t>3,300051</t>
+          <t>1,300051</t>
         </is>
       </c>
       <c r="K134" s="0" t="inlineStr"/>
@@ -8537,13 +8469,13 @@
       </c>
       <c r="Y134" s="0" t="inlineStr">
         <is>
-          <t>死亡回旋Lv3-每5秒发射3枚回旋镖,伤害=魔王攻击力,逐目标减半保底1</t>
+          <t>死亡回旋Lv1-每5秒发射1枚回旋镖,伤害=魔王攻击力,逐目标减半保底1</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" s="0" t="n">
-        <v>3000500004</v>
+        <v>3000500002</v>
       </c>
       <c r="B135" s="0" t="inlineStr"/>
       <c r="C135" s="0" t="n">
@@ -8569,7 +8501,7 @@
       <c r="I135" s="0" t="inlineStr"/>
       <c r="J135" s="0" t="inlineStr">
         <is>
-          <t>4,300051</t>
+          <t>2,300051</t>
         </is>
       </c>
       <c r="K135" s="0" t="inlineStr"/>
@@ -8612,13 +8544,13 @@
       </c>
       <c r="Y135" s="0" t="inlineStr">
         <is>
-          <t>死亡回旋Lv4-每5秒发射4枚回旋镖,伤害=魔王攻击力,逐目标减半保底1</t>
+          <t>死亡回旋Lv2-每5秒发射2枚回旋镖,伤害=魔王攻击力,逐目标减半保底1</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" s="0" t="n">
-        <v>3000500005</v>
+        <v>3000500003</v>
       </c>
       <c r="B136" s="0" t="inlineStr"/>
       <c r="C136" s="0" t="n">
@@ -8644,7 +8576,7 @@
       <c r="I136" s="0" t="inlineStr"/>
       <c r="J136" s="0" t="inlineStr">
         <is>
-          <t>5,300051</t>
+          <t>3,300051</t>
         </is>
       </c>
       <c r="K136" s="0" t="inlineStr"/>
@@ -8687,95 +8619,163 @@
       </c>
       <c r="Y136" s="0" t="inlineStr">
         <is>
-          <t>死亡回旋Lv5-每5秒发射5枚回旋镖,伤害=魔王攻击力,逐目标减半保底1</t>
+          <t>死亡回旋Lv3-每5秒发射3枚回旋镖,伤害=魔王攻击力,逐目标减半保底1</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" s="0" t="n">
-        <v>13000700001</v>
-      </c>
+        <v>3000500004</v>
+      </c>
+      <c r="B137" s="0" t="inlineStr"/>
       <c r="C137" s="0" t="n">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="D137" s="0" t="n">
-        <v>4</v>
+        <v>0</v>
+      </c>
+      <c r="E137" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="F137" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="G137" s="0" t="n">
+        <v>2</v>
       </c>
       <c r="H137" s="0" t="inlineStr">
         <is>
-          <t>BuffEntityConditionalThorns</t>
-        </is>
-      </c>
-      <c r="I137" s="0" t="inlineStr">
-        <is>
-          <t>GameFightLogic_UnderAttack</t>
-        </is>
+          <t>BuffEntityPeriodicAttackBoomerang</t>
+        </is>
+      </c>
+      <c r="I137" s="0" t="inlineStr"/>
+      <c r="J137" s="0" t="inlineStr">
+        <is>
+          <t>4,300051</t>
+        </is>
+      </c>
+      <c r="K137" s="0" t="inlineStr"/>
+      <c r="L137" s="0" t="inlineStr"/>
+      <c r="M137" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="N137" s="0" t="n">
+        <v>0</v>
       </c>
       <c r="O137" s="0" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="P137" s="0" t="n">
-        <v>0.1</v>
+        <v>0</v>
+      </c>
+      <c r="Q137" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="R137" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="S137" s="0" t="n">
+        <v>5</v>
       </c>
       <c r="T137" s="0" t="n">
         <v>0</v>
       </c>
+      <c r="U137" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="V137" s="0" t="n">
+        <v>0</v>
+      </c>
       <c r="W137" s="0" t="n">
-        <v>13000700001</v>
+        <v>3000500001</v>
       </c>
       <c r="X137" s="0" t="n">
-        <v>13000700001</v>
+        <v>3000500001</v>
       </c>
       <c r="Y137" s="0" t="inlineStr">
         <is>
-          <t>受到攻击时，反弹承伤的{Percentage}%给攻击者（上限为自身当前生命值）</t>
+          <t>死亡回旋Lv4-每5秒发射4枚回旋镖,伤害=魔王攻击力,逐目标减半保底1</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" s="0" t="n">
-        <v>13000800001</v>
-      </c>
+        <v>3000500005</v>
+      </c>
+      <c r="B138" s="0" t="inlineStr"/>
       <c r="C138" s="0" t="n">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="D138" s="0" t="n">
-        <v>4</v>
+        <v>0</v>
+      </c>
+      <c r="E138" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="F138" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="G138" s="0" t="n">
+        <v>2</v>
       </c>
       <c r="H138" s="0" t="inlineStr">
         <is>
-          <t>BuffEntityConditionalLifeSteal</t>
-        </is>
-      </c>
-      <c r="I138" s="0" t="inlineStr">
-        <is>
-          <t>GameFightLogic_UnderAttack</t>
-        </is>
+          <t>BuffEntityPeriodicAttackBoomerang</t>
+        </is>
+      </c>
+      <c r="I138" s="0" t="inlineStr"/>
+      <c r="J138" s="0" t="inlineStr">
+        <is>
+          <t>5,300051</t>
+        </is>
+      </c>
+      <c r="K138" s="0" t="inlineStr"/>
+      <c r="L138" s="0" t="inlineStr"/>
+      <c r="M138" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="N138" s="0" t="n">
+        <v>0</v>
       </c>
       <c r="O138" s="0" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="P138" s="0" t="n">
-        <v>0.1</v>
+        <v>0</v>
+      </c>
+      <c r="Q138" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="R138" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="S138" s="0" t="n">
+        <v>5</v>
       </c>
       <c r="T138" s="0" t="n">
         <v>0</v>
       </c>
+      <c r="U138" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="V138" s="0" t="n">
+        <v>0</v>
+      </c>
       <c r="W138" s="0" t="n">
-        <v>13000800001</v>
+        <v>3000500001</v>
       </c>
       <c r="X138" s="0" t="n">
-        <v>13000800001</v>
+        <v>3000500001</v>
       </c>
       <c r="Y138" s="0" t="inlineStr">
         <is>
-          <t>造成伤害的{Percentage}%转化为自身生命</t>
+          <t>死亡回旋Lv5-每5秒发射5枚回旋镖,伤害=魔王攻击力,逐目标减半保底1</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" s="0" t="n">
-        <v>13000900001</v>
+        <v>13000700001</v>
       </c>
       <c r="C139" s="0" t="n">
         <v>13</v>
@@ -8785,156 +8785,120 @@
       </c>
       <c r="H139" s="0" t="inlineStr">
         <is>
-          <t>BuffEntityConditionalInvincible</t>
-        </is>
-      </c>
-      <c r="K139" s="0" t="inlineStr">
-        <is>
-          <t>#FFD700</t>
-        </is>
-      </c>
-      <c r="M139" s="0" t="n">
-        <v>10</v>
-      </c>
-      <c r="N139" s="0" t="n">
-        <v>5</v>
+          <t>BuffEntityConditionalThorns</t>
+        </is>
+      </c>
+      <c r="I139" s="0" t="inlineStr">
+        <is>
+          <t>GameFightLogic_UnderAttack</t>
+        </is>
+      </c>
+      <c r="O139" s="0" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="P139" s="0" t="n">
+        <v>0.1</v>
       </c>
       <c r="T139" s="0" t="n">
         <v>0</v>
       </c>
       <c r="W139" s="0" t="n">
-        <v>13000900001</v>
+        <v>13000700001</v>
       </c>
       <c r="X139" s="0" t="n">
-        <v>13000900001</v>
+        <v>13000700001</v>
       </c>
       <c r="Y139" s="0" t="inlineStr">
         <is>
-          <t>上场后无敌{Value}秒，期间身体变为金色</t>
+          <t>受到攻击时，反弹承伤的{Percentage}%给攻击者（上限为自身当前生命值）</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" s="0" t="n">
-        <v>11001300001</v>
+        <v>13000800001</v>
       </c>
       <c r="C140" s="0" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="D140" s="0" t="n">
-        <v>2</v>
-      </c>
-      <c r="G140" s="0" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H140" s="0" t="inlineStr">
         <is>
-          <t>BuffEntityAttributeDecayByAllyCount</t>
-        </is>
-      </c>
-      <c r="J140" s="0" t="inlineStr">
-        <is>
-          <t>ATK</t>
-        </is>
-      </c>
-      <c r="M140" s="0" t="n">
-        <v>50</v>
-      </c>
-      <c r="N140" s="0" t="n">
-        <v>50</v>
+          <t>BuffEntityConditionalLifeSteal</t>
+        </is>
+      </c>
+      <c r="I140" s="0" t="inlineStr">
+        <is>
+          <t>GameFightLogic_UnderAttack</t>
+        </is>
       </c>
       <c r="O140" s="0" t="n">
-        <v>3</v>
+        <v>0.2</v>
       </c>
       <c r="P140" s="0" t="n">
-        <v>3</v>
-      </c>
-      <c r="Q140" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="R140" s="0" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="T140" s="0" t="n">
         <v>0</v>
       </c>
-      <c r="U140" s="0" t="n">
-        <v>0</v>
-      </c>
       <c r="W140" s="0" t="n">
-        <v>11001300001</v>
+        <v>13000800001</v>
       </c>
       <c r="X140" s="0" t="n">
-        <v>11001300001</v>
+        <v>13000800001</v>
       </c>
       <c r="Y140" s="0" t="inlineStr">
         <is>
-          <t>独行者-A</t>
+          <t>造成伤害的{Percentage}%转化为自身生命</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" s="0" t="n">
-        <v>11001300002</v>
+        <v>13000900001</v>
       </c>
       <c r="C141" s="0" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="D141" s="0" t="n">
-        <v>2</v>
-      </c>
-      <c r="G141" s="0" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H141" s="0" t="inlineStr">
         <is>
-          <t>BuffEntityAttributeDecayByAllyCount</t>
-        </is>
-      </c>
-      <c r="J141" s="0" t="inlineStr">
-        <is>
-          <t>ASPD</t>
+          <t>BuffEntityConditionalInvincible</t>
+        </is>
+      </c>
+      <c r="K141" s="0" t="inlineStr">
+        <is>
+          <t>#FFD700</t>
         </is>
       </c>
       <c r="M141" s="0" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="N141" s="0" t="n">
-        <v>50</v>
-      </c>
-      <c r="O141" s="0" t="n">
-        <v>3</v>
-      </c>
-      <c r="P141" s="0" t="n">
-        <v>3</v>
-      </c>
-      <c r="Q141" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="R141" s="0" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="T141" s="0" t="n">
         <v>0</v>
       </c>
-      <c r="U141" s="0" t="n">
-        <v>0</v>
-      </c>
       <c r="W141" s="0" t="n">
-        <v>11001300002</v>
+        <v>13000900001</v>
       </c>
       <c r="X141" s="0" t="n">
-        <v>11001300002</v>
+        <v>13000900001</v>
       </c>
       <c r="Y141" s="0" t="inlineStr">
         <is>
-          <t>独行者-B</t>
+          <t>上场后无敌{Value}秒，期间身体变为金色</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" s="0" t="n">
-        <v>11001300003</v>
+        <v>11001300001</v>
       </c>
       <c r="C142" s="0" t="n">
         <v>11</v>
@@ -8952,7 +8916,7 @@
       </c>
       <c r="J142" s="0" t="inlineStr">
         <is>
-          <t>DR</t>
+          <t>ATK</t>
         </is>
       </c>
       <c r="M142" s="0" t="n">
@@ -8980,20 +8944,20 @@
         <v>0</v>
       </c>
       <c r="W142" s="0" t="n">
-        <v>11001300003</v>
+        <v>11001300001</v>
       </c>
       <c r="X142" s="0" t="n">
-        <v>11001300003</v>
+        <v>11001300001</v>
       </c>
       <c r="Y142" s="0" t="inlineStr">
         <is>
-          <t>独行者-C</t>
+          <t>独行者-A</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" s="0" t="n">
-        <v>11001300004</v>
+        <v>11001300002</v>
       </c>
       <c r="C143" s="0" t="n">
         <v>11</v>
@@ -9011,7 +8975,7 @@
       </c>
       <c r="J143" s="0" t="inlineStr">
         <is>
-          <t>HP</t>
+          <t>ASPD</t>
         </is>
       </c>
       <c r="M143" s="0" t="n">
@@ -9039,12 +9003,130 @@
         <v>0</v>
       </c>
       <c r="W143" s="0" t="n">
+        <v>11001300002</v>
+      </c>
+      <c r="X143" s="0" t="n">
+        <v>11001300002</v>
+      </c>
+      <c r="Y143" s="0" t="inlineStr">
+        <is>
+          <t>独行者-B</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" s="0" t="n">
+        <v>11001300003</v>
+      </c>
+      <c r="C144" s="0" t="n">
+        <v>11</v>
+      </c>
+      <c r="D144" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="G144" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="H144" s="0" t="inlineStr">
+        <is>
+          <t>BuffEntityAttributeDecayByAllyCount</t>
+        </is>
+      </c>
+      <c r="J144" s="0" t="inlineStr">
+        <is>
+          <t>DR</t>
+        </is>
+      </c>
+      <c r="M144" s="0" t="n">
+        <v>50</v>
+      </c>
+      <c r="N144" s="0" t="n">
+        <v>50</v>
+      </c>
+      <c r="O144" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="P144" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q144" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="R144" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="T144" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="U144" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="W144" s="0" t="n">
+        <v>11001300003</v>
+      </c>
+      <c r="X144" s="0" t="n">
+        <v>11001300003</v>
+      </c>
+      <c r="Y144" s="0" t="inlineStr">
+        <is>
+          <t>独行者-C</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" s="0" t="n">
         <v>11001300004</v>
       </c>
-      <c r="X143" s="0" t="n">
+      <c r="C145" s="0" t="n">
+        <v>11</v>
+      </c>
+      <c r="D145" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="G145" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="H145" s="0" t="inlineStr">
+        <is>
+          <t>BuffEntityAttributeDecayByAllyCount</t>
+        </is>
+      </c>
+      <c r="J145" s="0" t="inlineStr">
+        <is>
+          <t>HP</t>
+        </is>
+      </c>
+      <c r="M145" s="0" t="n">
+        <v>50</v>
+      </c>
+      <c r="N145" s="0" t="n">
+        <v>50</v>
+      </c>
+      <c r="O145" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="P145" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q145" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="R145" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="T145" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="U145" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="W145" s="0" t="n">
         <v>11001300004</v>
       </c>
-      <c r="Y143" s="0" t="inlineStr">
+      <c r="X145" s="0" t="n">
+        <v>11001300004</v>
+      </c>
+      <c r="Y145" s="0" t="inlineStr">
         <is>
           <t>独行者-D</t>
         </is>

--- a/Demon Lord Roguelike/Assets/Data/Excel/excel_buff_info[buff信息].xlsx
+++ b/Demon Lord Roguelike/Assets/Data/Excel/excel_buff_info[buff信息].xlsx
@@ -2310,7 +2310,7 @@
         </is>
       </c>
       <c r="M19" s="0" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="R19" s="0" t="n">
         <v>0</v>
@@ -2326,7 +2326,7 @@
       </c>
       <c r="Y19" s="0" t="inlineStr">
         <is>
-          <t>伤害转移护盾-5秒内目标零承伤，伤害转移给施加者（大盾战士BOSS援护护盾，堆叠策略须为Ignore）</t>
+          <t>伤害转移护盾-9秒内目标零承伤，伤害转移给施加者（大盾战士BOSS援护护盾，堆叠策略须为Ignore）</t>
         </is>
       </c>
     </row>

--- a/Demon Lord Roguelike/Assets/Data/Excel/excel_buff_info[buff信息].xlsx
+++ b/Demon Lord Roguelike/Assets/Data/Excel/excel_buff_info[buff信息].xlsx
@@ -1911,6 +1911,9 @@
       <c r="O11" s="1" t="n">
         <v>-0.2</v>
       </c>
+      <c r="R11" t="n">
+        <v>1</v>
+      </c>
       <c r="S11" s="1" t="n">
         <v>10</v>
       </c>
@@ -1956,6 +1959,9 @@
       </c>
       <c r="O12" s="1" t="n">
         <v>2</v>
+      </c>
+      <c r="R12" t="n">
+        <v>1</v>
       </c>
       <c r="S12" s="1" t="n">
         <v>5</v>

--- a/Demon Lord Roguelike/Assets/Data/Excel/excel_buff_info[buff信息].xlsx
+++ b/Demon Lord Roguelike/Assets/Data/Excel/excel_buff_info[buff信息].xlsx
@@ -1911,7 +1911,7 @@
       <c r="O11" s="1" t="n">
         <v>-0.2</v>
       </c>
-      <c r="R11" t="n">
+      <c r="R11" s="0" t="n">
         <v>1</v>
       </c>
       <c r="S11" s="1" t="n">
@@ -1960,7 +1960,7 @@
       <c r="O12" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="R12" t="n">
+      <c r="R12" s="0" t="n">
         <v>1</v>
       </c>
       <c r="S12" s="1" t="n">
@@ -7095,7 +7095,7 @@
       </c>
       <c r="L106" s="0" t="inlineStr">
         <is>
-          <t>3001:1000&amp;</t>
+          <t>3001:100&amp;</t>
         </is>
       </c>
       <c r="O106" s="0" t="n">
@@ -7149,7 +7149,7 @@
       </c>
       <c r="L107" s="0" t="inlineStr">
         <is>
-          <t>3001:1000&amp;</t>
+          <t>3001:100&amp;</t>
         </is>
       </c>
       <c r="O107" s="0" t="n">
@@ -7203,7 +7203,7 @@
       </c>
       <c r="L108" s="0" t="inlineStr">
         <is>
-          <t>3001:1000&amp;</t>
+          <t>3001:100&amp;</t>
         </is>
       </c>
       <c r="O108" s="0" t="n">
@@ -7257,7 +7257,7 @@
       </c>
       <c r="L109" s="0" t="inlineStr">
         <is>
-          <t>3001:1000&amp;</t>
+          <t>3001:100&amp;</t>
         </is>
       </c>
       <c r="O109" s="0" t="n">
@@ -7765,7 +7765,7 @@
       </c>
       <c r="L119" s="0" t="inlineStr">
         <is>
-          <t>3001:1000&amp;</t>
+          <t>3001:100&amp;</t>
         </is>
       </c>
       <c r="T119" s="0" t="n">
@@ -7980,7 +7980,7 @@
       </c>
       <c r="L124" s="0" t="inlineStr">
         <is>
-          <t>3001:200&amp;</t>
+          <t>3001:100&amp;</t>
         </is>
       </c>
       <c r="T124" s="0" t="n">

--- a/Demon Lord Roguelike/Assets/Data/Excel/excel_buff_info[buff信息].xlsx
+++ b/Demon Lord Roguelike/Assets/Data/Excel/excel_buff_info[buff信息].xlsx
@@ -1137,7 +1137,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y145"/>
+  <dimension ref="A1:Y146"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col width="24.25" customWidth="1" style="3" min="1" max="1"/>
@@ -2041,7 +2041,7 @@
     </row>
     <row r="14" ht="14.25" customHeight="1" s="3">
       <c r="A14" s="2" t="n">
-        <v>2000200001</v>
+        <v>2000100002</v>
       </c>
       <c r="B14" s="2" t="n"/>
       <c r="C14" s="2" t="n">
@@ -2061,7 +2061,7 @@
       <c r="I14" s="2" t="n"/>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>CRT</t>
+          <t>EVA</t>
         </is>
       </c>
       <c r="K14" s="2" t="n"/>
@@ -2069,7 +2069,7 @@
       <c r="M14" s="2" t="n"/>
       <c r="N14" s="2" t="n"/>
       <c r="O14" s="2" t="n">
-        <v>0.5</v>
+        <v>0.25</v>
       </c>
       <c r="P14" s="2" t="n"/>
       <c r="Q14" s="2" t="n"/>
@@ -2083,121 +2083,117 @@
       </c>
       <c r="V14" s="2" t="n"/>
       <c r="W14" s="2" t="n">
+        <v>2000100002</v>
+      </c>
+      <c r="X14" s="2" t="n">
+        <v>2000100002</v>
+      </c>
+      <c r="Y14" s="2" t="inlineStr">
+        <is>
+          <t>闪避25%</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="n">
         <v>2000200001</v>
       </c>
-      <c r="X14" s="2" t="n">
+      <c r="B15" s="2" t="n"/>
+      <c r="C15" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="D15" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="E15" s="2" t="n"/>
+      <c r="F15" s="2" t="n"/>
+      <c r="G15" s="2" t="n"/>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>BuffEntityAttribute</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="n"/>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>CRT</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="n"/>
+      <c r="L15" s="2" t="n"/>
+      <c r="M15" s="2" t="n"/>
+      <c r="N15" s="2" t="n"/>
+      <c r="O15" s="2" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="P15" s="2" t="n"/>
+      <c r="Q15" s="2" t="n"/>
+      <c r="R15" s="2" t="n"/>
+      <c r="S15" s="2" t="n"/>
+      <c r="T15" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="U15" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="V15" s="2" t="n"/>
+      <c r="W15" s="2" t="n">
         <v>2000200001</v>
       </c>
-      <c r="Y14" s="2" t="inlineStr">
+      <c r="X15" s="2" t="n">
+        <v>2000200001</v>
+      </c>
+      <c r="Y15" s="2" t="inlineStr">
         <is>
           <t>暴击50%</t>
         </is>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" s="0" t="n">
+    <row r="16">
+      <c r="A16" s="0" t="n">
         <v>2000500001</v>
       </c>
-      <c r="C15" s="0" t="n">
+      <c r="C16" s="0" t="n">
         <v>2</v>
       </c>
-      <c r="D15" s="0" t="n">
+      <c r="D16" s="0" t="n">
         <v>1</v>
       </c>
-      <c r="H15" s="0" t="inlineStr">
+      <c r="H16" s="0" t="inlineStr">
         <is>
           <t>BuffEntityAttribute</t>
         </is>
       </c>
-      <c r="J15" s="0" t="inlineStr">
+      <c r="J16" s="0" t="inlineStr">
         <is>
           <t>CDMG</t>
         </is>
       </c>
-      <c r="O15" s="0" t="n">
+      <c r="O16" s="0" t="n">
         <v>0.5</v>
       </c>
-      <c r="T15" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="U15" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="V15" s="0" t="n"/>
-      <c r="W15" s="0" t="n">
+      <c r="T16" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="U16" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="V16" s="0" t="n"/>
+      <c r="W16" s="0" t="n">
         <v>2000500001</v>
       </c>
-      <c r="X15" s="0" t="n">
+      <c r="X16" s="0" t="n">
         <v>2000500001</v>
       </c>
-      <c r="Y15" s="0" t="inlineStr">
+      <c r="Y16" s="0" t="inlineStr">
         <is>
           <t>暴击伤害100%</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="2" t="n">
-        <v>2000300001</v>
-      </c>
-      <c r="B16" s="2" t="n"/>
-      <c r="C16" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="D16" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="E16" s="2" t="n"/>
-      <c r="F16" s="2" t="n"/>
-      <c r="G16" s="2" t="n"/>
-      <c r="H16" s="5" t="inlineStr">
-        <is>
-          <t>BuffEntityConditionalAttribute</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="n"/>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>ATK</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="n"/>
-      <c r="L16" s="6" t="inlineStr">
-        <is>
-          <t>1001:0.5&amp;</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="n"/>
-      <c r="N16" s="2" t="n"/>
-      <c r="O16" s="2" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="P16" s="2" t="n"/>
-      <c r="Q16" s="2" t="n"/>
-      <c r="R16" s="2" t="n"/>
-      <c r="S16" s="2" t="n"/>
-      <c r="T16" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="U16" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="V16" s="2" t="n"/>
-      <c r="W16" s="2" t="n">
-        <v>2000300001</v>
-      </c>
-      <c r="X16" s="2" t="n">
-        <v>2000300001</v>
-      </c>
-      <c r="Y16" s="2" t="inlineStr">
-        <is>
-          <t>血量低于50% 攻击力提升</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="n">
-        <v>2000400001</v>
+        <v>2000300001</v>
       </c>
       <c r="B17" s="2" t="n"/>
       <c r="C17" s="2" t="n">
@@ -2217,7 +2213,7 @@
       <c r="I17" s="2" t="n"/>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>ASPD</t>
+          <t>ATK</t>
         </is>
       </c>
       <c r="K17" s="2" t="n"/>
@@ -2229,7 +2225,7 @@
       <c r="M17" s="2" t="n"/>
       <c r="N17" s="2" t="n"/>
       <c r="O17" s="2" t="n">
-        <v>-0.5</v>
+        <v>0.5</v>
       </c>
       <c r="P17" s="2" t="n"/>
       <c r="Q17" s="2" t="n"/>
@@ -2243,61 +2239,79 @@
       </c>
       <c r="V17" s="2" t="n"/>
       <c r="W17" s="2" t="n">
+        <v>2000300001</v>
+      </c>
+      <c r="X17" s="2" t="n">
+        <v>2000300001</v>
+      </c>
+      <c r="Y17" s="2" t="inlineStr">
+        <is>
+          <t>血量低于50% 攻击力提升</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="n">
         <v>2000400001</v>
       </c>
-      <c r="X17" s="2" t="n">
+      <c r="B18" s="2" t="n"/>
+      <c r="C18" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="D18" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="E18" s="2" t="n"/>
+      <c r="F18" s="2" t="n"/>
+      <c r="G18" s="2" t="n"/>
+      <c r="H18" s="5" t="inlineStr">
+        <is>
+          <t>BuffEntityConditionalAttribute</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="n"/>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>ASPD</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="n"/>
+      <c r="L18" s="6" t="inlineStr">
+        <is>
+          <t>1001:0.5&amp;</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="n"/>
+      <c r="N18" s="2" t="n"/>
+      <c r="O18" s="2" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="P18" s="2" t="n"/>
+      <c r="Q18" s="2" t="n"/>
+      <c r="R18" s="2" t="n"/>
+      <c r="S18" s="2" t="n"/>
+      <c r="T18" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="U18" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="V18" s="2" t="n"/>
+      <c r="W18" s="2" t="n">
         <v>2000400001</v>
       </c>
-      <c r="Y17" s="2" t="inlineStr">
+      <c r="X18" s="2" t="n">
+        <v>2000400001</v>
+      </c>
+      <c r="Y18" s="2" t="inlineStr">
         <is>
           <t>血量低于50% 攻击速度提升</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="0" t="n">
-        <v>2000600001</v>
-      </c>
-      <c r="C18" s="0" t="n">
-        <v>2</v>
-      </c>
-      <c r="G18" s="0" t="n">
-        <v>2</v>
-      </c>
-      <c r="H18" s="0" t="inlineStr">
-        <is>
-          <t>BuffEntityPeriodicShieldCast</t>
-        </is>
-      </c>
-      <c r="J18" s="0" t="inlineStr">
-        <is>
-          <t>3,2000700001</t>
-        </is>
-      </c>
-      <c r="R18" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="S18" s="0" t="n">
-        <v>10</v>
-      </c>
-      <c r="T18" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="W18" s="0" t="n">
-        <v>2000600001</v>
-      </c>
-      <c r="X18" s="0" t="n">
-        <v>2000600001</v>
-      </c>
-      <c r="Y18" s="0" t="inlineStr">
-        <is>
-          <t>大盾战士BOSS-每10秒给最前排3个友军套伤害转移护盾（护盾持续5秒）</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="0" t="n">
-        <v>2000700001</v>
+        <v>2000600001</v>
       </c>
       <c r="C19" s="0" t="n">
         <v>2</v>
@@ -2307,72 +2321,79 @@
       </c>
       <c r="H19" s="0" t="inlineStr">
         <is>
-          <t>BuffEntityConditionalShieldTransfer</t>
+          <t>BuffEntityPeriodicShieldCast</t>
         </is>
       </c>
       <c r="J19" s="0" t="inlineStr">
         <is>
-          <t>500004,0.6</t>
-        </is>
-      </c>
-      <c r="M19" s="0" t="n">
-        <v>9</v>
+          <t>3,2000700001</t>
+        </is>
       </c>
       <c r="R19" s="0" t="n">
         <v>0</v>
       </c>
+      <c r="S19" s="0" t="n">
+        <v>10</v>
+      </c>
       <c r="T19" s="0" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="W19" s="0" t="n">
-        <v>2000700001</v>
+        <v>2000600001</v>
       </c>
       <c r="X19" s="0" t="n">
-        <v>2000700001</v>
+        <v>2000600001</v>
       </c>
       <c r="Y19" s="0" t="inlineStr">
         <is>
-          <t>伤害转移护盾-9秒内目标零承伤，伤害转移给施加者（大盾战士BOSS援护护盾，堆叠策略须为Ignore）</t>
+          <t>大盾战士BOSS-每10秒给最前排3个友军套伤害转移护盾（护盾持续5秒）</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="0" t="n">
-        <v>3000100001</v>
+        <v>2000700001</v>
       </c>
       <c r="C20" s="0" t="n">
-        <v>3</v>
-      </c>
-      <c r="D20" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="H20" s="7" t="inlineStr">
-        <is>
-          <t>BuffEntityInstantCloneDefenseCreature</t>
-        </is>
-      </c>
-      <c r="I20" s="7" t="n"/>
+        <v>2</v>
+      </c>
+      <c r="G20" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="H20" s="0" t="inlineStr">
+        <is>
+          <t>BuffEntityConditionalShieldTransfer</t>
+        </is>
+      </c>
+      <c r="J20" s="0" t="inlineStr">
+        <is>
+          <t>500004,0.6</t>
+        </is>
+      </c>
+      <c r="M20" s="0" t="n">
+        <v>9</v>
+      </c>
+      <c r="R20" s="0" t="n">
+        <v>0</v>
+      </c>
       <c r="T20" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="U20" s="0" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="W20" s="0" t="n">
-        <v>3000100001</v>
+        <v>2000700001</v>
       </c>
       <c r="X20" s="0" t="n">
-        <v>3000100001</v>
+        <v>2000700001</v>
       </c>
       <c r="Y20" s="0" t="inlineStr">
         <is>
-          <t>增殖-随机复制一个已有的魔物</t>
+          <t>伤害转移护盾-9秒内目标零承伤，伤害转移给施加者（大盾战士BOSS援护护盾，堆叠策略须为Ignore）</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="0" t="n">
-        <v>3000200001</v>
+        <v>3000100001</v>
       </c>
       <c r="C21" s="0" t="n">
         <v>3</v>
@@ -2380,25 +2401,12 @@
       <c r="D21" s="0" t="n">
         <v>1</v>
       </c>
-      <c r="E21" s="0" t="n">
-        <v>3000200001</v>
-      </c>
-      <c r="F21" s="0" t="n">
-        <v>1</v>
-      </c>
       <c r="H21" s="7" t="inlineStr">
         <is>
-          <t>BuffEntityConditionalAddDropCrystal</t>
-        </is>
-      </c>
-      <c r="I21" s="0" t="inlineStr">
-        <is>
-          <t>GameFightLogic_CreatureDeadDropCrystal</t>
-        </is>
-      </c>
-      <c r="Q21" s="0" t="n">
-        <v>0.2</v>
-      </c>
+          <t>BuffEntityInstantCloneDefenseCreature</t>
+        </is>
+      </c>
+      <c r="I21" s="7" t="n"/>
       <c r="T21" s="0" t="n">
         <v>0</v>
       </c>
@@ -2406,20 +2414,20 @@
         <v>0</v>
       </c>
       <c r="W21" s="0" t="n">
-        <v>3000200001</v>
+        <v>3000100001</v>
       </c>
       <c r="X21" s="0" t="n">
-        <v>3000200001</v>
+        <v>3000100001</v>
       </c>
       <c r="Y21" s="0" t="inlineStr">
         <is>
-          <t>钱多多LV1-每一次击杀有20%的概率多掉落一次魔晶</t>
+          <t>增殖-随机复制一个已有的魔物</t>
         </is>
       </c>
     </row>
     <row r="22" ht="15" customHeight="1" s="3">
       <c r="A22" s="0" t="n">
-        <v>3000200002</v>
+        <v>3000200001</v>
       </c>
       <c r="C22" s="0" t="n">
         <v>3</v>
@@ -2428,10 +2436,10 @@
         <v>1</v>
       </c>
       <c r="E22" s="0" t="n">
-        <v>3000200002</v>
+        <v>3000200001</v>
       </c>
       <c r="F22" s="0" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H22" s="7" t="inlineStr">
         <is>
@@ -2444,7 +2452,7 @@
         </is>
       </c>
       <c r="Q22" s="0" t="n">
-        <v>0.4</v>
+        <v>0.2</v>
       </c>
       <c r="T22" s="0" t="n">
         <v>0</v>
@@ -2460,13 +2468,13 @@
       </c>
       <c r="Y22" s="0" t="inlineStr">
         <is>
-          <t>钱多多LV2-每一次击杀有40%的概率多掉落一次魔晶</t>
+          <t>钱多多LV1-每一次击杀有20%的概率多掉落一次魔晶</t>
         </is>
       </c>
     </row>
     <row r="23" ht="15" customHeight="1" s="3">
       <c r="A23" s="0" t="n">
-        <v>3000200003</v>
+        <v>3000200002</v>
       </c>
       <c r="C23" s="0" t="n">
         <v>3</v>
@@ -2475,10 +2483,10 @@
         <v>1</v>
       </c>
       <c r="E23" s="0" t="n">
-        <v>3000200003</v>
+        <v>3000200002</v>
       </c>
       <c r="F23" s="0" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H23" s="7" t="inlineStr">
         <is>
@@ -2491,7 +2499,7 @@
         </is>
       </c>
       <c r="Q23" s="0" t="n">
-        <v>0.6</v>
+        <v>0.4</v>
       </c>
       <c r="T23" s="0" t="n">
         <v>0</v>
@@ -2507,13 +2515,13 @@
       </c>
       <c r="Y23" s="0" t="inlineStr">
         <is>
-          <t>钱多多LV3-每一次击杀有60%的概率多掉落一次魔晶</t>
+          <t>钱多多LV2-每一次击杀有40%的概率多掉落一次魔晶</t>
         </is>
       </c>
     </row>
     <row r="24" ht="15" customHeight="1" s="3">
       <c r="A24" s="0" t="n">
-        <v>3000200004</v>
+        <v>3000200003</v>
       </c>
       <c r="C24" s="0" t="n">
         <v>3</v>
@@ -2525,7 +2533,7 @@
         <v>3000200003</v>
       </c>
       <c r="F24" s="0" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H24" s="7" t="inlineStr">
         <is>
@@ -2538,7 +2546,7 @@
         </is>
       </c>
       <c r="Q24" s="0" t="n">
-        <v>0.8</v>
+        <v>0.6</v>
       </c>
       <c r="T24" s="0" t="n">
         <v>0</v>
@@ -2554,13 +2562,13 @@
       </c>
       <c r="Y24" s="0" t="inlineStr">
         <is>
-          <t>钱多多LV4-每一次击杀有80%的概率多掉落一次魔晶</t>
+          <t>钱多多LV3-每一次击杀有60%的概率多掉落一次魔晶</t>
         </is>
       </c>
     </row>
     <row r="25" ht="15" customHeight="1" s="3">
       <c r="A25" s="0" t="n">
-        <v>3000200005</v>
+        <v>3000200004</v>
       </c>
       <c r="C25" s="0" t="n">
         <v>3</v>
@@ -2572,7 +2580,7 @@
         <v>3000200003</v>
       </c>
       <c r="F25" s="0" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H25" s="7" t="inlineStr">
         <is>
@@ -2585,7 +2593,7 @@
         </is>
       </c>
       <c r="Q25" s="0" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="T25" s="0" t="n">
         <v>0</v>
@@ -2601,60 +2609,60 @@
       </c>
       <c r="Y25" s="0" t="inlineStr">
         <is>
-          <t>钱多多LV5-每一次击杀有100%的概率多掉落一次魔晶</t>
+          <t>钱多多LV4-每一次击杀有80%的概率多掉落一次魔晶</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="0" t="n">
-        <v>3000300001</v>
+        <v>3000200005</v>
       </c>
       <c r="C26" s="0" t="n">
         <v>3</v>
       </c>
-      <c r="G26" s="0" t="n">
-        <v>2</v>
-      </c>
-      <c r="H26" s="0" t="inlineStr">
-        <is>
-          <t>BuffEntityPeriodicAttackMultiInstant</t>
-        </is>
-      </c>
-      <c r="J26" s="0" t="inlineStr">
-        <is>
-          <t>1,300031</t>
-        </is>
-      </c>
-      <c r="M26" s="0" t="n">
+      <c r="D26" s="0" t="n">
         <v>1</v>
       </c>
+      <c r="E26" s="0" t="n">
+        <v>3000200003</v>
+      </c>
+      <c r="F26" s="0" t="n">
+        <v>5</v>
+      </c>
+      <c r="H26" s="7" t="inlineStr">
+        <is>
+          <t>BuffEntityConditionalAddDropCrystal</t>
+        </is>
+      </c>
+      <c r="I26" s="0" t="inlineStr">
+        <is>
+          <t>GameFightLogic_CreatureDeadDropCrystal</t>
+        </is>
+      </c>
       <c r="Q26" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="R26" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="S26" s="0" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="T26" s="0" t="n">
         <v>0</v>
       </c>
+      <c r="U26" s="0" t="n">
+        <v>0</v>
+      </c>
       <c r="W26" s="0" t="n">
-        <v>3000300001</v>
+        <v>3000200001</v>
       </c>
       <c r="X26" s="0" t="n">
-        <v>3000300001</v>
+        <v>3000200001</v>
       </c>
       <c r="Y26" s="0" t="inlineStr">
         <is>
-          <t>闪电Lv1-每3秒1道落雷,范围0.2,单雷最多命中1个目标,伤害=魔王攻击力</t>
+          <t>钱多多LV5-每一次击杀有100%的概率多掉落一次魔晶</t>
         </is>
       </c>
     </row>
     <row r="27" ht="15" customHeight="1" s="3">
       <c r="A27" s="0" t="n">
-        <v>3000300002</v>
+        <v>3000300001</v>
       </c>
       <c r="C27" s="0" t="n">
         <v>3</v>
@@ -2669,7 +2677,7 @@
       </c>
       <c r="J27" s="0" t="inlineStr">
         <is>
-          <t>2,300032</t>
+          <t>1,300031</t>
         </is>
       </c>
       <c r="M27" s="0" t="n">
@@ -2695,13 +2703,13 @@
       </c>
       <c r="Y27" s="0" t="inlineStr">
         <is>
-          <t>闪电Lv2-每3秒2道落雷,范围0.4,单雷最多命中2个目标,伤害=魔王攻击力</t>
+          <t>闪电Lv1-每3秒1道落雷,范围0.2,单雷最多命中1个目标,伤害=魔王攻击力</t>
         </is>
       </c>
     </row>
     <row r="28" ht="15" customHeight="1" s="3">
       <c r="A28" s="0" t="n">
-        <v>3000300003</v>
+        <v>3000300002</v>
       </c>
       <c r="C28" s="0" t="n">
         <v>3</v>
@@ -2716,7 +2724,7 @@
       </c>
       <c r="J28" s="0" t="inlineStr">
         <is>
-          <t>3,300033</t>
+          <t>2,300032</t>
         </is>
       </c>
       <c r="M28" s="0" t="n">
@@ -2742,13 +2750,13 @@
       </c>
       <c r="Y28" s="0" t="inlineStr">
         <is>
-          <t>闪电Lv3-每3秒3道落雷,范围0.6,单雷最多命中3个目标,伤害=魔王攻击力</t>
+          <t>闪电Lv2-每3秒2道落雷,范围0.4,单雷最多命中2个目标,伤害=魔王攻击力</t>
         </is>
       </c>
     </row>
     <row r="29" ht="15" customHeight="1" s="3">
       <c r="A29" s="0" t="n">
-        <v>3000300004</v>
+        <v>3000300003</v>
       </c>
       <c r="C29" s="0" t="n">
         <v>3</v>
@@ -2763,7 +2771,7 @@
       </c>
       <c r="J29" s="0" t="inlineStr">
         <is>
-          <t>4,300034</t>
+          <t>3,300033</t>
         </is>
       </c>
       <c r="M29" s="0" t="n">
@@ -2789,13 +2797,13 @@
       </c>
       <c r="Y29" s="0" t="inlineStr">
         <is>
-          <t>闪电Lv4-每3秒4道落雷,范围0.8,单雷最多命中4个目标,伤害=魔王攻击力</t>
+          <t>闪电Lv3-每3秒3道落雷,范围0.6,单雷最多命中3个目标,伤害=魔王攻击力</t>
         </is>
       </c>
     </row>
     <row r="30" ht="15" customHeight="1" s="3">
       <c r="A30" s="0" t="n">
-        <v>3000300005</v>
+        <v>3000300004</v>
       </c>
       <c r="C30" s="0" t="n">
         <v>3</v>
@@ -2810,7 +2818,7 @@
       </c>
       <c r="J30" s="0" t="inlineStr">
         <is>
-          <t>5,300035</t>
+          <t>4,300034</t>
         </is>
       </c>
       <c r="M30" s="0" t="n">
@@ -2836,13 +2844,13 @@
       </c>
       <c r="Y30" s="0" t="inlineStr">
         <is>
-          <t>闪电Lv5-每3秒5道落雷,范围1,单雷最多命中5个目标,伤害=魔王攻击力</t>
+          <t>闪电Lv4-每3秒4道落雷,范围0.8,单雷最多命中4个目标,伤害=魔王攻击力</t>
         </is>
       </c>
     </row>
     <row r="31" customFormat="1" s="2">
       <c r="A31" s="0" t="n">
-        <v>3000400001</v>
+        <v>3000300005</v>
       </c>
       <c r="C31" s="0" t="n">
         <v>3</v>
@@ -2852,12 +2860,12 @@
       </c>
       <c r="H31" s="0" t="inlineStr">
         <is>
-          <t>BuffEntityPeriodicAttackRoad</t>
+          <t>BuffEntityPeriodicAttackMultiInstant</t>
         </is>
       </c>
       <c r="J31" s="0" t="inlineStr">
         <is>
-          <t>1,300041</t>
+          <t>5,300035</t>
         </is>
       </c>
       <c r="M31" s="0" t="n">
@@ -2870,26 +2878,26 @@
         <v>0</v>
       </c>
       <c r="S31" s="0" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T31" s="0" t="n">
         <v>0</v>
       </c>
       <c r="W31" s="0" t="n">
-        <v>3000400001</v>
+        <v>3000300001</v>
       </c>
       <c r="X31" s="0" t="n">
-        <v>3000400001</v>
+        <v>3000300001</v>
       </c>
       <c r="Y31" s="0" t="inlineStr">
         <is>
-          <t>失控的矿车Lv1-每5秒随机1条道路各出1辆矿车，第1个目标伤害=魔王攻击力，之后每撞1个减半</t>
+          <t>闪电Lv5-每3秒5道落雷,范围1,单雷最多命中5个目标,伤害=魔王攻击力</t>
         </is>
       </c>
     </row>
     <row r="32" customFormat="1" s="2">
       <c r="A32" s="0" t="n">
-        <v>3000400002</v>
+        <v>3000400001</v>
       </c>
       <c r="C32" s="0" t="n">
         <v>3</v>
@@ -2904,7 +2912,7 @@
       </c>
       <c r="J32" s="0" t="inlineStr">
         <is>
-          <t>2,300041</t>
+          <t>1,300041</t>
         </is>
       </c>
       <c r="M32" s="0" t="n">
@@ -2930,13 +2938,13 @@
       </c>
       <c r="Y32" s="0" t="inlineStr">
         <is>
-          <t>失控的矿车Lv2-每5秒随机2条道路各出1辆矿车，第1个目标伤害=魔王攻击力，之后每撞1个减半</t>
+          <t>失控的矿车Lv1-每5秒随机1条道路各出1辆矿车，第1个目标伤害=魔王攻击力，之后每撞1个减半</t>
         </is>
       </c>
     </row>
     <row r="33" customFormat="1" s="2">
       <c r="A33" s="0" t="n">
-        <v>3000400003</v>
+        <v>3000400002</v>
       </c>
       <c r="C33" s="0" t="n">
         <v>3</v>
@@ -2951,7 +2959,7 @@
       </c>
       <c r="J33" s="0" t="inlineStr">
         <is>
-          <t>3,300041</t>
+          <t>2,300041</t>
         </is>
       </c>
       <c r="M33" s="0" t="n">
@@ -2977,13 +2985,13 @@
       </c>
       <c r="Y33" s="0" t="inlineStr">
         <is>
-          <t>失控的矿车Lv3-每5秒随机3条道路各出1辆矿车，第1个目标伤害=魔王攻击力，之后每撞1个减半</t>
+          <t>失控的矿车Lv2-每5秒随机2条道路各出1辆矿车，第1个目标伤害=魔王攻击力，之后每撞1个减半</t>
         </is>
       </c>
     </row>
     <row r="34" ht="13" customHeight="1" s="3">
       <c r="A34" s="0" t="n">
-        <v>3000400004</v>
+        <v>3000400003</v>
       </c>
       <c r="C34" s="0" t="n">
         <v>3</v>
@@ -2998,7 +3006,7 @@
       </c>
       <c r="J34" s="0" t="inlineStr">
         <is>
-          <t>4,300041</t>
+          <t>3,300041</t>
         </is>
       </c>
       <c r="M34" s="0" t="n">
@@ -3024,13 +3032,13 @@
       </c>
       <c r="Y34" s="0" t="inlineStr">
         <is>
-          <t>失控的矿车Lv4-每5秒随机4条道路各出1辆矿车，第1个目标伤害=魔王攻击力，之后每撞1个减半</t>
+          <t>失控的矿车Lv3-每5秒随机3条道路各出1辆矿车，第1个目标伤害=魔王攻击力，之后每撞1个减半</t>
         </is>
       </c>
     </row>
     <row r="35" ht="14.25" customHeight="1" s="3">
       <c r="A35" s="0" t="n">
-        <v>3000400005</v>
+        <v>3000400004</v>
       </c>
       <c r="C35" s="0" t="n">
         <v>3</v>
@@ -3045,7 +3053,7 @@
       </c>
       <c r="J35" s="0" t="inlineStr">
         <is>
-          <t>5,300041</t>
+          <t>4,300041</t>
         </is>
       </c>
       <c r="M35" s="0" t="n">
@@ -3071,51 +3079,33 @@
       </c>
       <c r="Y35" s="0" t="inlineStr">
         <is>
-          <t>失控的矿车Lv5-每5秒随机5条道路各出1辆矿车，第1个目标伤害=魔王攻击力，之后每撞1个减半</t>
+          <t>失控的矿车Lv4-每5秒随机4条道路各出1辆矿车，第1个目标伤害=魔王攻击力，之后每撞1个减半</t>
         </is>
       </c>
     </row>
     <row r="36" ht="14.25" customHeight="1" s="3">
       <c r="A36" s="0" t="n">
-        <v>3000600001</v>
+        <v>3000400005</v>
       </c>
       <c r="C36" s="0" t="n">
         <v>3</v>
-      </c>
-      <c r="D36" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="E36" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="F36" s="0" t="n">
-        <v>0</v>
       </c>
       <c r="G36" s="0" t="n">
         <v>2</v>
       </c>
       <c r="H36" s="0" t="inlineStr">
         <is>
-          <t>BuffEntityPeriodicAttackBounceAxe</t>
+          <t>BuffEntityPeriodicAttackRoad</t>
         </is>
       </c>
       <c r="J36" s="0" t="inlineStr">
         <is>
-          <t>1,300061,1</t>
+          <t>5,300041</t>
         </is>
       </c>
       <c r="M36" s="0" t="n">
         <v>1</v>
       </c>
-      <c r="N36" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="O36" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="P36" s="0" t="n">
-        <v>0</v>
-      </c>
       <c r="Q36" s="0" t="n">
         <v>0</v>
       </c>
@@ -3128,27 +3118,21 @@
       <c r="T36" s="0" t="n">
         <v>0</v>
       </c>
-      <c r="U36" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="V36" s="0" t="n">
-        <v>0</v>
-      </c>
       <c r="W36" s="0" t="n">
-        <v>3000600001</v>
+        <v>3000400001</v>
       </c>
       <c r="X36" s="0" t="n">
-        <v>3000600001</v>
+        <v>3000400001</v>
       </c>
       <c r="Y36" s="0" t="inlineStr">
         <is>
-          <t>跳跳斧Lv1-每5秒扔出1把斧头,伤害=魔王攻击力,命中后弹跳1次,伤害逐目标减半保底1</t>
+          <t>失控的矿车Lv5-每5秒随机5条道路各出1辆矿车，第1个目标伤害=魔王攻击力，之后每撞1个减半</t>
         </is>
       </c>
     </row>
     <row r="37" ht="14.25" customHeight="1" s="3">
       <c r="A37" s="0" t="n">
-        <v>3000600002</v>
+        <v>3000600001</v>
       </c>
       <c r="C37" s="0" t="n">
         <v>3</v>
@@ -3172,7 +3156,7 @@
       </c>
       <c r="J37" s="0" t="inlineStr">
         <is>
-          <t>2,300061,2</t>
+          <t>1,300061,1</t>
         </is>
       </c>
       <c r="M37" s="0" t="n">
@@ -3213,13 +3197,13 @@
       </c>
       <c r="Y37" s="0" t="inlineStr">
         <is>
-          <t>跳跳斧Lv2-每5秒扔出2把斧头,命中后弹跳2次,伤害逐目标减半保底1</t>
+          <t>跳跳斧Lv1-每5秒扔出1把斧头,伤害=魔王攻击力,命中后弹跳1次,伤害逐目标减半保底1</t>
         </is>
       </c>
     </row>
     <row r="38" ht="14.25" customHeight="1" s="3">
       <c r="A38" s="0" t="n">
-        <v>3000600003</v>
+        <v>3000600002</v>
       </c>
       <c r="C38" s="0" t="n">
         <v>3</v>
@@ -3243,7 +3227,7 @@
       </c>
       <c r="J38" s="0" t="inlineStr">
         <is>
-          <t>3,300061,3</t>
+          <t>2,300061,2</t>
         </is>
       </c>
       <c r="M38" s="0" t="n">
@@ -3284,13 +3268,13 @@
       </c>
       <c r="Y38" s="0" t="inlineStr">
         <is>
-          <t>跳跳斧Lv3-每5秒扔出3把斧头,命中后弹跳3次,伤害逐目标减半保底1</t>
+          <t>跳跳斧Lv2-每5秒扔出2把斧头,命中后弹跳2次,伤害逐目标减半保底1</t>
         </is>
       </c>
     </row>
     <row r="39" ht="14.25" customHeight="1" s="3">
       <c r="A39" s="0" t="n">
-        <v>3000600004</v>
+        <v>3000600003</v>
       </c>
       <c r="C39" s="0" t="n">
         <v>3</v>
@@ -3314,7 +3298,7 @@
       </c>
       <c r="J39" s="0" t="inlineStr">
         <is>
-          <t>4,300061,4</t>
+          <t>3,300061,3</t>
         </is>
       </c>
       <c r="M39" s="0" t="n">
@@ -3355,13 +3339,13 @@
       </c>
       <c r="Y39" s="0" t="inlineStr">
         <is>
-          <t>跳跳斧Lv4-每5秒扔出4把斧头,命中后弹跳4次,伤害逐目标减半保底1</t>
+          <t>跳跳斧Lv3-每5秒扔出3把斧头,命中后弹跳3次,伤害逐目标减半保底1</t>
         </is>
       </c>
     </row>
     <row r="40" ht="14.25" customHeight="1" s="3">
       <c r="A40" s="0" t="n">
-        <v>3000600005</v>
+        <v>3000600004</v>
       </c>
       <c r="C40" s="0" t="n">
         <v>3</v>
@@ -3385,7 +3369,7 @@
       </c>
       <c r="J40" s="0" t="inlineStr">
         <is>
-          <t>5,300061,5</t>
+          <t>4,300061,4</t>
         </is>
       </c>
       <c r="M40" s="0" t="n">
@@ -3426,13 +3410,13 @@
       </c>
       <c r="Y40" s="0" t="inlineStr">
         <is>
-          <t>跳跳斧Lv5-每5秒扔出5把斧头,命中后弹跳5次,伤害逐目标减半保底1</t>
+          <t>跳跳斧Lv4-每5秒扔出4把斧头,命中后弹跳4次,伤害逐目标减半保底1</t>
         </is>
       </c>
     </row>
     <row r="41" ht="14.25" customHeight="1" s="3">
       <c r="A41" s="0" t="n">
-        <v>3000700001</v>
+        <v>3000600005</v>
       </c>
       <c r="C41" s="0" t="n">
         <v>3</v>
@@ -3451,16 +3435,16 @@
       </c>
       <c r="H41" s="0" t="inlineStr">
         <is>
-          <t>BuffEntityPeriodicAttackOrbit</t>
+          <t>BuffEntityPeriodicAttackBounceAxe</t>
         </is>
       </c>
       <c r="J41" s="0" t="inlineStr">
         <is>
-          <t>1,300071,0.6</t>
+          <t>5,300061,5</t>
         </is>
       </c>
       <c r="M41" s="0" t="n">
-        <v>0.4</v>
+        <v>1</v>
       </c>
       <c r="N41" s="0" t="n">
         <v>0</v>
@@ -3478,7 +3462,7 @@
         <v>0</v>
       </c>
       <c r="S41" s="0" t="n">
-        <v>9999</v>
+        <v>5</v>
       </c>
       <c r="T41" s="0" t="n">
         <v>0</v>
@@ -3490,20 +3474,20 @@
         <v>0</v>
       </c>
       <c r="W41" s="0" t="n">
-        <v>3000700001</v>
+        <v>3000600001</v>
       </c>
       <c r="X41" s="0" t="n">
-        <v>3000700001</v>
+        <v>3000600001</v>
       </c>
       <c r="Y41" s="0" t="inlineStr">
         <is>
-          <t>知识的力量Lv1-环绕1本书(半径0.75,转速0.6弧度/秒),触碰伤害=魔王攻击力40%</t>
+          <t>跳跳斧Lv5-每5秒扔出5把斧头,命中后弹跳5次,伤害逐目标减半保底1</t>
         </is>
       </c>
     </row>
     <row r="42" ht="14.25" customHeight="1" s="3">
       <c r="A42" s="0" t="n">
-        <v>3000700002</v>
+        <v>3000700001</v>
       </c>
       <c r="C42" s="0" t="n">
         <v>3</v>
@@ -3527,7 +3511,7 @@
       </c>
       <c r="J42" s="0" t="inlineStr">
         <is>
-          <t>2,300071,1.2</t>
+          <t>1,300071,0.6</t>
         </is>
       </c>
       <c r="M42" s="0" t="n">
@@ -3568,13 +3552,13 @@
       </c>
       <c r="Y42" s="0" t="inlineStr">
         <is>
-          <t>知识的力量Lv2-环绕2本书(半径0.75,转速1.2弧度/秒),触碰伤害=魔王攻击力40%</t>
+          <t>知识的力量Lv1-环绕1本书(半径0.75,转速0.6弧度/秒),触碰伤害=魔王攻击力40%</t>
         </is>
       </c>
     </row>
     <row r="43" ht="14.25" customHeight="1" s="3">
       <c r="A43" s="0" t="n">
-        <v>3000700003</v>
+        <v>3000700002</v>
       </c>
       <c r="C43" s="0" t="n">
         <v>3</v>
@@ -3598,7 +3582,7 @@
       </c>
       <c r="J43" s="0" t="inlineStr">
         <is>
-          <t>3,300071,1.8</t>
+          <t>2,300071,1.2</t>
         </is>
       </c>
       <c r="M43" s="0" t="n">
@@ -3639,13 +3623,13 @@
       </c>
       <c r="Y43" s="0" t="inlineStr">
         <is>
-          <t>知识的力量Lv3-环绕3本书(半径0.75,转速1.8弧度/秒),触碰伤害=魔王攻击力40%</t>
+          <t>知识的力量Lv2-环绕2本书(半径0.75,转速1.2弧度/秒),触碰伤害=魔王攻击力40%</t>
         </is>
       </c>
     </row>
     <row r="44" ht="14.25" customHeight="1" s="3">
       <c r="A44" s="0" t="n">
-        <v>3000700004</v>
+        <v>3000700003</v>
       </c>
       <c r="C44" s="0" t="n">
         <v>3</v>
@@ -3669,7 +3653,7 @@
       </c>
       <c r="J44" s="0" t="inlineStr">
         <is>
-          <t>4,300071,2.4</t>
+          <t>3,300071,1.8</t>
         </is>
       </c>
       <c r="M44" s="0" t="n">
@@ -3710,13 +3694,13 @@
       </c>
       <c r="Y44" s="0" t="inlineStr">
         <is>
-          <t>知识的力量Lv4-环绕4本书(半径0.75,转速2.4弧度/秒),触碰伤害=魔王攻击力40%</t>
+          <t>知识的力量Lv3-环绕3本书(半径0.75,转速1.8弧度/秒),触碰伤害=魔王攻击力40%</t>
         </is>
       </c>
     </row>
     <row r="45" ht="14.25" customHeight="1" s="3">
       <c r="A45" s="0" t="n">
-        <v>3000700005</v>
+        <v>3000700004</v>
       </c>
       <c r="C45" s="0" t="n">
         <v>3</v>
@@ -3740,7 +3724,7 @@
       </c>
       <c r="J45" s="0" t="inlineStr">
         <is>
-          <t>5,300071,3</t>
+          <t>4,300071,2.4</t>
         </is>
       </c>
       <c r="M45" s="0" t="n">
@@ -3781,13 +3765,13 @@
       </c>
       <c r="Y45" s="0" t="inlineStr">
         <is>
-          <t>知识的力量Lv5-环绕5本书(半径0.75,转速3弧度/秒),触碰伤害=魔王攻击力40%</t>
+          <t>知识的力量Lv4-环绕4本书(半径0.75,转速2.4弧度/秒),触碰伤害=魔王攻击力40%</t>
         </is>
       </c>
     </row>
     <row r="46" ht="14.25" customHeight="1" s="3">
       <c r="A46" s="0" t="n">
-        <v>3000800001</v>
+        <v>3000700005</v>
       </c>
       <c r="C46" s="0" t="n">
         <v>3</v>
@@ -3806,16 +3790,16 @@
       </c>
       <c r="H46" s="0" t="inlineStr">
         <is>
-          <t>BuffEntityPeriodicAttackRebound</t>
+          <t>BuffEntityPeriodicAttackOrbit</t>
         </is>
       </c>
       <c r="J46" s="0" t="inlineStr">
         <is>
-          <t>1,300081</t>
+          <t>5,300071,3</t>
         </is>
       </c>
       <c r="M46" s="0" t="n">
-        <v>1</v>
+        <v>0.4</v>
       </c>
       <c r="N46" s="0" t="n">
         <v>0</v>
@@ -3833,7 +3817,7 @@
         <v>0</v>
       </c>
       <c r="S46" s="0" t="n">
-        <v>1</v>
+        <v>9999</v>
       </c>
       <c r="T46" s="0" t="n">
         <v>0</v>
@@ -3845,20 +3829,20 @@
         <v>0</v>
       </c>
       <c r="W46" s="0" t="n">
-        <v>3000800001</v>
+        <v>3000700001</v>
       </c>
       <c r="X46" s="0" t="n">
-        <v>3000800001</v>
+        <v>3000700001</v>
       </c>
       <c r="Y46" s="0" t="inlineStr">
         <is>
-          <t>回弹菱块Lv1-场上维持1颗永久反弹菱块(速度2),伤害=魔王攻击力100%,同目标1秒冷却</t>
+          <t>知识的力量Lv5-环绕5本书(半径0.75,转速3弧度/秒),触碰伤害=魔王攻击力40%</t>
         </is>
       </c>
     </row>
     <row r="47" ht="14.25" customHeight="1" s="3">
       <c r="A47" s="0" t="n">
-        <v>3000800002</v>
+        <v>3000800001</v>
       </c>
       <c r="C47" s="0" t="n">
         <v>3</v>
@@ -3882,7 +3866,7 @@
       </c>
       <c r="J47" s="0" t="inlineStr">
         <is>
-          <t>2,300082</t>
+          <t>1,300081</t>
         </is>
       </c>
       <c r="M47" s="0" t="n">
@@ -3923,13 +3907,13 @@
       </c>
       <c r="Y47" s="0" t="inlineStr">
         <is>
-          <t>回弹菱块Lv2-场上维持2颗永久反弹菱块(速度2.5),伤害=魔王攻击力100%,同目标1秒冷却</t>
+          <t>回弹菱块Lv1-场上维持1颗永久反弹菱块(速度2),伤害=魔王攻击力100%,同目标1秒冷却</t>
         </is>
       </c>
     </row>
     <row r="48" ht="14.25" customHeight="1" s="3">
       <c r="A48" s="0" t="n">
-        <v>3000800003</v>
+        <v>3000800002</v>
       </c>
       <c r="C48" s="0" t="n">
         <v>3</v>
@@ -3953,7 +3937,7 @@
       </c>
       <c r="J48" s="0" t="inlineStr">
         <is>
-          <t>3,300083</t>
+          <t>2,300082</t>
         </is>
       </c>
       <c r="M48" s="0" t="n">
@@ -3994,13 +3978,13 @@
       </c>
       <c r="Y48" s="0" t="inlineStr">
         <is>
-          <t>回弹菱块Lv3-场上维持3颗永久反弹菱块(速度3),伤害=魔王攻击力100%,同目标1秒冷却</t>
+          <t>回弹菱块Lv2-场上维持2颗永久反弹菱块(速度2.5),伤害=魔王攻击力100%,同目标1秒冷却</t>
         </is>
       </c>
     </row>
     <row r="49" ht="15" customHeight="1" s="3">
       <c r="A49" s="0" t="n">
-        <v>3000800004</v>
+        <v>3000800003</v>
       </c>
       <c r="C49" s="0" t="n">
         <v>3</v>
@@ -4024,7 +4008,7 @@
       </c>
       <c r="J49" s="0" t="inlineStr">
         <is>
-          <t>4,300084</t>
+          <t>3,300083</t>
         </is>
       </c>
       <c r="M49" s="0" t="n">
@@ -4065,13 +4049,13 @@
       </c>
       <c r="Y49" s="0" t="inlineStr">
         <is>
-          <t>回弹菱块Lv4-场上维持4颗永久反弹菱块(速度3.5),伤害=魔王攻击力100%,同目标1秒冷却</t>
+          <t>回弹菱块Lv3-场上维持3颗永久反弹菱块(速度3),伤害=魔王攻击力100%,同目标1秒冷却</t>
         </is>
       </c>
     </row>
     <row r="50" ht="14.25" customHeight="1" s="3">
       <c r="A50" s="0" t="n">
-        <v>3000800005</v>
+        <v>3000800004</v>
       </c>
       <c r="C50" s="0" t="n">
         <v>3</v>
@@ -4095,7 +4079,7 @@
       </c>
       <c r="J50" s="0" t="inlineStr">
         <is>
-          <t>5,300085</t>
+          <t>4,300084</t>
         </is>
       </c>
       <c r="M50" s="0" t="n">
@@ -4136,50 +4120,84 @@
       </c>
       <c r="Y50" s="0" t="inlineStr">
         <is>
+          <t>回弹菱块Lv4-场上维持4颗永久反弹菱块(速度3.5),伤害=魔王攻击力100%,同目标1秒冷却</t>
+        </is>
+      </c>
+    </row>
+    <row r="51" ht="14.25" customHeight="1" s="3">
+      <c r="A51" s="0" t="n">
+        <v>3000800005</v>
+      </c>
+      <c r="C51" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="D51" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="E51" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="F51" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="G51" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="H51" s="0" t="inlineStr">
+        <is>
+          <t>BuffEntityPeriodicAttackRebound</t>
+        </is>
+      </c>
+      <c r="J51" s="0" t="inlineStr">
+        <is>
+          <t>5,300085</t>
+        </is>
+      </c>
+      <c r="M51" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="N51" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="O51" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="P51" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q51" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="R51" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="S51" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="T51" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="U51" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="V51" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="W51" s="0" t="n">
+        <v>3000800001</v>
+      </c>
+      <c r="X51" s="0" t="n">
+        <v>3000800001</v>
+      </c>
+      <c r="Y51" s="0" t="inlineStr">
+        <is>
           <t>回弹菱块Lv5-场上维持5颗永久反弹菱块(速度4),伤害=魔王攻击力100%,同目标1秒冷却</t>
-        </is>
-      </c>
-    </row>
-    <row r="51" ht="14.25" customHeight="1" s="3">
-      <c r="A51" s="2" t="n">
-        <v>3000900001</v>
-      </c>
-      <c r="C51" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="D51" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="H51" s="2" t="inlineStr">
-        <is>
-          <t>BuffEntityInstantRewardMoreItem</t>
-        </is>
-      </c>
-      <c r="I51" s="2" t="n"/>
-      <c r="J51" s="2" t="n"/>
-      <c r="O51" s="2" t="n"/>
-      <c r="P51" s="2" t="n"/>
-      <c r="T51" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="U51" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="W51" s="2" t="n">
-        <v>3000900001</v>
-      </c>
-      <c r="X51" s="2" t="n">
-        <v>3000900001</v>
-      </c>
-      <c r="Y51" s="2" t="inlineStr">
-        <is>
-          <t>奖励多多-通关奖励数量+1</t>
         </is>
       </c>
     </row>
     <row r="52" ht="14.25" customHeight="1" s="3">
       <c r="A52" s="2" t="n">
-        <v>3001000001</v>
+        <v>3000900001</v>
       </c>
       <c r="C52" s="2" t="n">
         <v>3</v>
@@ -4189,7 +4207,7 @@
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
-          <t>BuffEntityInstantRewardMoreSelect</t>
+          <t>BuffEntityInstantRewardMoreItem</t>
         </is>
       </c>
       <c r="I52" s="2" t="n"/>
@@ -4203,91 +4221,57 @@
         <v>0</v>
       </c>
       <c r="W52" s="2" t="n">
+        <v>3000900001</v>
+      </c>
+      <c r="X52" s="2" t="n">
+        <v>3000900001</v>
+      </c>
+      <c r="Y52" s="2" t="inlineStr">
+        <is>
+          <t>奖励多多-通关奖励数量+1</t>
+        </is>
+      </c>
+    </row>
+    <row r="53" ht="14.25" customHeight="1" s="3">
+      <c r="A53" s="2" t="n">
         <v>3001000001</v>
       </c>
-      <c r="X52" s="2" t="n">
+      <c r="C53" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="D53" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H53" s="2" t="inlineStr">
+        <is>
+          <t>BuffEntityInstantRewardMoreSelect</t>
+        </is>
+      </c>
+      <c r="I53" s="2" t="n"/>
+      <c r="J53" s="2" t="n"/>
+      <c r="O53" s="2" t="n"/>
+      <c r="P53" s="2" t="n"/>
+      <c r="T53" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="U53" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="W53" s="2" t="n">
         <v>3001000001</v>
       </c>
-      <c r="Y52" s="2" t="inlineStr">
+      <c r="X53" s="2" t="n">
+        <v>3001000001</v>
+      </c>
+      <c r="Y53" s="2" t="inlineStr">
         <is>
           <t>再来一瓶-通关奖励可选次数+1</t>
-        </is>
-      </c>
-    </row>
-    <row r="53" ht="14.25" customHeight="1" s="3">
-      <c r="A53" s="0" t="n">
-        <v>3001100005</v>
-      </c>
-      <c r="C53" s="0" t="n">
-        <v>3</v>
-      </c>
-      <c r="D53" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="E53" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="F53" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="G53" s="0" t="n">
-        <v>2</v>
-      </c>
-      <c r="H53" s="0" t="inlineStr">
-        <is>
-          <t>BuffEntityPeriodicAttackShockwave</t>
-        </is>
-      </c>
-      <c r="J53" s="0" t="inlineStr">
-        <is>
-          <t>300091</t>
-        </is>
-      </c>
-      <c r="M53" s="0" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="N53" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="O53" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="P53" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q53" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="R53" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="S53" s="0" t="n">
-        <v>10</v>
-      </c>
-      <c r="T53" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="U53" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="V53" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="W53" s="0" t="n">
-        <v>3001100005</v>
-      </c>
-      <c r="X53" s="0" t="n">
-        <v>3001100005</v>
-      </c>
-      <c r="Y53" s="0" t="inlineStr">
-        <is>
-          <t>第六次冲击Lv5-每10秒从魔王发出冲击波，伤害=魔王攻击力x0.3</t>
         </is>
       </c>
     </row>
     <row r="54" ht="14.25" customHeight="1" s="3">
       <c r="A54" s="0" t="n">
-        <v>3001100004</v>
+        <v>3001100005</v>
       </c>
       <c r="C54" s="0" t="n">
         <v>3</v>
@@ -4315,7 +4299,7 @@
         </is>
       </c>
       <c r="M54" s="0" t="n">
-        <v>0.25</v>
+        <v>0.3</v>
       </c>
       <c r="N54" s="0" t="n">
         <v>0</v>
@@ -4345,20 +4329,20 @@
         <v>0</v>
       </c>
       <c r="W54" s="0" t="n">
-        <v>3001100004</v>
+        <v>3001100005</v>
       </c>
       <c r="X54" s="0" t="n">
-        <v>3001100004</v>
+        <v>3001100005</v>
       </c>
       <c r="Y54" s="0" t="inlineStr">
         <is>
-          <t>第六次冲击Lv4-每10秒从魔王发出冲击波，伤害=魔王攻击力x0.25</t>
+          <t>第六次冲击Lv5-每10秒从魔王发出冲击波，伤害=魔王攻击力x0.3</t>
         </is>
       </c>
     </row>
     <row r="55" ht="14.25" customFormat="1" customHeight="1" s="2">
       <c r="A55" s="0" t="n">
-        <v>3001100003</v>
+        <v>3001100004</v>
       </c>
       <c r="C55" s="0" t="n">
         <v>3</v>
@@ -4386,7 +4370,7 @@
         </is>
       </c>
       <c r="M55" s="0" t="n">
-        <v>0.2</v>
+        <v>0.25</v>
       </c>
       <c r="N55" s="0" t="n">
         <v>0</v>
@@ -4416,20 +4400,20 @@
         <v>0</v>
       </c>
       <c r="W55" s="0" t="n">
-        <v>3001100003</v>
+        <v>3001100004</v>
       </c>
       <c r="X55" s="0" t="n">
-        <v>3001100003</v>
+        <v>3001100004</v>
       </c>
       <c r="Y55" s="0" t="inlineStr">
         <is>
-          <t>第六次冲击Lv3-每10秒从魔王发出冲击波，伤害=魔王攻击力x0.2</t>
+          <t>第六次冲击Lv4-每10秒从魔王发出冲击波，伤害=魔王攻击力x0.25</t>
         </is>
       </c>
     </row>
     <row r="56" ht="14.25" customFormat="1" customHeight="1" s="2">
       <c r="A56" s="0" t="n">
-        <v>3001100002</v>
+        <v>3001100003</v>
       </c>
       <c r="C56" s="0" t="n">
         <v>3</v>
@@ -4457,7 +4441,7 @@
         </is>
       </c>
       <c r="M56" s="0" t="n">
-        <v>0.15</v>
+        <v>0.2</v>
       </c>
       <c r="N56" s="0" t="n">
         <v>0</v>
@@ -4487,20 +4471,20 @@
         <v>0</v>
       </c>
       <c r="W56" s="0" t="n">
-        <v>3001100002</v>
+        <v>3001100003</v>
       </c>
       <c r="X56" s="0" t="n">
-        <v>3001100002</v>
+        <v>3001100003</v>
       </c>
       <c r="Y56" s="0" t="inlineStr">
         <is>
-          <t>第六次冲击Lv2-每10秒从魔王发出冲击波，伤害=魔王攻击力x0.15</t>
+          <t>第六次冲击Lv3-每10秒从魔王发出冲击波，伤害=魔王攻击力x0.2</t>
         </is>
       </c>
     </row>
     <row r="57" ht="14.25" customFormat="1" customHeight="1" s="2">
       <c r="A57" s="0" t="n">
-        <v>3001100001</v>
+        <v>3001100002</v>
       </c>
       <c r="C57" s="0" t="n">
         <v>3</v>
@@ -4528,7 +4512,7 @@
         </is>
       </c>
       <c r="M57" s="0" t="n">
-        <v>0.1</v>
+        <v>0.15</v>
       </c>
       <c r="N57" s="0" t="n">
         <v>0</v>
@@ -4558,22 +4542,21 @@
         <v>0</v>
       </c>
       <c r="W57" s="0" t="n">
-        <v>3001100001</v>
+        <v>3001100002</v>
       </c>
       <c r="X57" s="0" t="n">
-        <v>3001100001</v>
+        <v>3001100002</v>
       </c>
       <c r="Y57" s="0" t="inlineStr">
         <is>
-          <t>第六次冲击Lv1-每10秒从魔王发出冲击波，伤害=魔王攻击力x0.1</t>
+          <t>第六次冲击Lv2-每10秒从魔王发出冲击波，伤害=魔王攻击力x0.15</t>
         </is>
       </c>
     </row>
     <row r="58" ht="14.25" customFormat="1" customHeight="1" s="2">
       <c r="A58" s="0" t="n">
-        <v>3001200001</v>
-      </c>
-      <c r="B58" s="0" t="inlineStr"/>
+        <v>3001100001</v>
+      </c>
       <c r="C58" s="0" t="n">
         <v>3</v>
       </c>
@@ -4591,19 +4574,16 @@
       </c>
       <c r="H58" s="0" t="inlineStr">
         <is>
-          <t>BuffEntityPeriodicAttackFireBottle</t>
-        </is>
-      </c>
-      <c r="I58" s="0" t="inlineStr"/>
+          <t>BuffEntityPeriodicAttackShockwave</t>
+        </is>
+      </c>
       <c r="J58" s="0" t="inlineStr">
         <is>
-          <t>1,300101</t>
-        </is>
-      </c>
-      <c r="K58" s="0" t="inlineStr"/>
-      <c r="L58" s="0" t="inlineStr"/>
+          <t>300091</t>
+        </is>
+      </c>
       <c r="M58" s="0" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="N58" s="0" t="n">
         <v>0</v>
@@ -4633,20 +4613,20 @@
         <v>0</v>
       </c>
       <c r="W58" s="0" t="n">
-        <v>3001200001</v>
+        <v>3001100001</v>
       </c>
       <c r="X58" s="0" t="n">
-        <v>3001200001</v>
+        <v>3001100001</v>
       </c>
       <c r="Y58" s="0" t="inlineStr">
         <is>
-          <t>瓶装炼狱火Lv1-每10秒向1个敌人投掷炼狱火瓶,落地燃放地形火焰,每1秒对半径1.2内敌人造成魔王攻击力20%伤害,持续5秒</t>
+          <t>第六次冲击Lv1-每10秒从魔王发出冲击波，伤害=魔王攻击力x0.1</t>
         </is>
       </c>
     </row>
     <row r="59" ht="14.25" customFormat="1" customHeight="1" s="2">
       <c r="A59" s="0" t="n">
-        <v>3001200002</v>
+        <v>3001200001</v>
       </c>
       <c r="B59" s="0" t="inlineStr"/>
       <c r="C59" s="0" t="n">
@@ -4672,7 +4652,7 @@
       <c r="I59" s="0" t="inlineStr"/>
       <c r="J59" s="0" t="inlineStr">
         <is>
-          <t>2,300101</t>
+          <t>1,300101</t>
         </is>
       </c>
       <c r="K59" s="0" t="inlineStr"/>
@@ -4715,13 +4695,13 @@
       </c>
       <c r="Y59" s="0" t="inlineStr">
         <is>
-          <t>瓶装炼狱火Lv2-每10秒向2个敌人投掷炼狱火瓶,落地燃放地形火焰,每1秒对半径1.2内敌人造成魔王攻击力20%伤害,持续5秒</t>
+          <t>瓶装炼狱火Lv1-每10秒向1个敌人投掷炼狱火瓶,落地燃放地形火焰,每1秒对半径1.2内敌人造成魔王攻击力20%伤害,持续5秒</t>
         </is>
       </c>
     </row>
     <row r="60" ht="14.25" customFormat="1" customHeight="1" s="2">
       <c r="A60" s="0" t="n">
-        <v>3001200003</v>
+        <v>3001200002</v>
       </c>
       <c r="B60" s="0" t="inlineStr"/>
       <c r="C60" s="0" t="n">
@@ -4747,7 +4727,7 @@
       <c r="I60" s="0" t="inlineStr"/>
       <c r="J60" s="0" t="inlineStr">
         <is>
-          <t>3,300101</t>
+          <t>2,300101</t>
         </is>
       </c>
       <c r="K60" s="0" t="inlineStr"/>
@@ -4790,13 +4770,13 @@
       </c>
       <c r="Y60" s="0" t="inlineStr">
         <is>
-          <t>瓶装炼狱火Lv3-每10秒向3个敌人投掷炼狱火瓶,落地燃放地形火焰,每1秒对半径1.2内敌人造成魔王攻击力20%伤害,持续5秒</t>
+          <t>瓶装炼狱火Lv2-每10秒向2个敌人投掷炼狱火瓶,落地燃放地形火焰,每1秒对半径1.2内敌人造成魔王攻击力20%伤害,持续5秒</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="0" t="n">
-        <v>3001200004</v>
+        <v>3001200003</v>
       </c>
       <c r="B61" s="0" t="inlineStr"/>
       <c r="C61" s="0" t="n">
@@ -4822,7 +4802,7 @@
       <c r="I61" s="0" t="inlineStr"/>
       <c r="J61" s="0" t="inlineStr">
         <is>
-          <t>4,300101</t>
+          <t>3,300101</t>
         </is>
       </c>
       <c r="K61" s="0" t="inlineStr"/>
@@ -4865,13 +4845,13 @@
       </c>
       <c r="Y61" s="0" t="inlineStr">
         <is>
-          <t>瓶装炼狱火Lv4-每10秒向4个敌人投掷炼狱火瓶,落地燃放地形火焰,每1秒对半径1.2内敌人造成魔王攻击力20%伤害,持续5秒</t>
+          <t>瓶装炼狱火Lv3-每10秒向3个敌人投掷炼狱火瓶,落地燃放地形火焰,每1秒对半径1.2内敌人造成魔王攻击力20%伤害,持续5秒</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="0" t="n">
-        <v>3001200005</v>
+        <v>3001200004</v>
       </c>
       <c r="B62" s="0" t="inlineStr"/>
       <c r="C62" s="0" t="n">
@@ -4897,7 +4877,7 @@
       <c r="I62" s="0" t="inlineStr"/>
       <c r="J62" s="0" t="inlineStr">
         <is>
-          <t>5,300101</t>
+          <t>4,300101</t>
         </is>
       </c>
       <c r="K62" s="0" t="inlineStr"/>
@@ -4940,62 +4920,88 @@
       </c>
       <c r="Y62" s="0" t="inlineStr">
         <is>
+          <t>瓶装炼狱火Lv4-每10秒向4个敌人投掷炼狱火瓶,落地燃放地形火焰,每1秒对半径1.2内敌人造成魔王攻击力20%伤害,持续5秒</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="0" t="n">
+        <v>3001200005</v>
+      </c>
+      <c r="B63" s="0" t="inlineStr"/>
+      <c r="C63" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="D63" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="E63" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="F63" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="G63" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="H63" s="0" t="inlineStr">
+        <is>
+          <t>BuffEntityPeriodicAttackFireBottle</t>
+        </is>
+      </c>
+      <c r="I63" s="0" t="inlineStr"/>
+      <c r="J63" s="0" t="inlineStr">
+        <is>
+          <t>5,300101</t>
+        </is>
+      </c>
+      <c r="K63" s="0" t="inlineStr"/>
+      <c r="L63" s="0" t="inlineStr"/>
+      <c r="M63" s="0" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="N63" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="O63" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="P63" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q63" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="R63" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="S63" s="0" t="n">
+        <v>10</v>
+      </c>
+      <c r="T63" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="U63" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="V63" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="W63" s="0" t="n">
+        <v>3001200001</v>
+      </c>
+      <c r="X63" s="0" t="n">
+        <v>3001200001</v>
+      </c>
+      <c r="Y63" s="0" t="inlineStr">
+        <is>
           <t>瓶装炼狱火Lv5-每10秒向5个敌人投掷炼狱火瓶,落地燃放地形火焰,每1秒对半径1.2内敌人造成魔王攻击力20%伤害,持续5秒</t>
-        </is>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" s="2" t="n">
-        <v>11000100001</v>
-      </c>
-      <c r="C63" s="2" t="n">
-        <v>11</v>
-      </c>
-      <c r="D63" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="H63" s="2" t="inlineStr">
-        <is>
-          <t>BuffEntityAttribute</t>
-        </is>
-      </c>
-      <c r="I63" s="5" t="inlineStr">
-        <is>
-          <t>GameFightLogic_CreatureDeadEnd</t>
-        </is>
-      </c>
-      <c r="J63" s="5" t="inlineStr">
-        <is>
-          <t>HP</t>
-        </is>
-      </c>
-      <c r="O63" s="2" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="P63" s="2" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="T63" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="U63" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="W63" s="2" t="n">
-        <v>11000100001</v>
-      </c>
-      <c r="X63" s="2" t="n">
-        <v>11000100001</v>
-      </c>
-      <c r="Y63" s="2" t="inlineStr">
-        <is>
-          <t>生命增加{Percentage}%</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="n">
-        <v>11000200001</v>
+        <v>11000100001</v>
       </c>
       <c r="C64" s="2" t="n">
         <v>11</v>
@@ -5015,7 +5021,7 @@
       </c>
       <c r="J64" s="5" t="inlineStr">
         <is>
-          <t>DR</t>
+          <t>HP</t>
         </is>
       </c>
       <c r="O64" s="2" t="n">
@@ -5031,20 +5037,20 @@
         <v>0</v>
       </c>
       <c r="W64" s="2" t="n">
-        <v>11000200001</v>
+        <v>11000100001</v>
       </c>
       <c r="X64" s="2" t="n">
-        <v>11000200001</v>
+        <v>11000100001</v>
       </c>
       <c r="Y64" s="2" t="inlineStr">
         <is>
-          <t>护甲增加{Percentage}%</t>
+          <t>生命增加{Percentage}%</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="n">
-        <v>11000300001</v>
+        <v>11000200001</v>
       </c>
       <c r="C65" s="2" t="n">
         <v>11</v>
@@ -5062,85 +5068,90 @@
           <t>GameFightLogic_CreatureDeadEnd</t>
         </is>
       </c>
-      <c r="J65" s="0" t="inlineStr">
+      <c r="J65" s="5" t="inlineStr">
+        <is>
+          <t>DR</t>
+        </is>
+      </c>
+      <c r="O65" s="2" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="P65" s="2" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="T65" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="U65" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="W65" s="2" t="n">
+        <v>11000200001</v>
+      </c>
+      <c r="X65" s="2" t="n">
+        <v>11000200001</v>
+      </c>
+      <c r="Y65" s="2" t="inlineStr">
+        <is>
+          <t>护甲增加{Percentage}%</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="2" t="n">
+        <v>11000300001</v>
+      </c>
+      <c r="C66" s="2" t="n">
+        <v>11</v>
+      </c>
+      <c r="D66" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="H66" s="2" t="inlineStr">
+        <is>
+          <t>BuffEntityAttribute</t>
+        </is>
+      </c>
+      <c r="I66" s="5" t="inlineStr">
+        <is>
+          <t>GameFightLogic_CreatureDeadEnd</t>
+        </is>
+      </c>
+      <c r="J66" s="0" t="inlineStr">
         <is>
           <t>ATK</t>
         </is>
       </c>
-      <c r="O65" s="0" t="n">
+      <c r="O66" s="0" t="n">
         <v>0.2</v>
       </c>
-      <c r="P65" s="0" t="n">
+      <c r="P66" s="0" t="n">
         <v>0.1</v>
       </c>
-      <c r="Q65" s="2" t="n">
+      <c r="Q66" s="2" t="n">
         <v>0.2</v>
       </c>
-      <c r="T65" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="U65" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="W65" s="2" t="n">
+      <c r="T66" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="U66" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="W66" s="2" t="n">
         <v>11000300001</v>
       </c>
-      <c r="X65" s="2" t="n">
+      <c r="X66" s="2" t="n">
         <v>11000300001</v>
       </c>
-      <c r="Y65" s="2" t="inlineStr">
+      <c r="Y66" s="2" t="inlineStr">
         <is>
           <t>攻击力增加{Percentage}%</t>
-        </is>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" s="0" t="n">
-        <v>11000400001</v>
-      </c>
-      <c r="C66" s="0" t="n">
-        <v>11</v>
-      </c>
-      <c r="D66" s="0" t="n">
-        <v>2</v>
-      </c>
-      <c r="H66" s="0" t="inlineStr">
-        <is>
-          <t>BuffEntityAttribute</t>
-        </is>
-      </c>
-      <c r="J66" s="0" t="inlineStr">
-        <is>
-          <t>ASPD</t>
-        </is>
-      </c>
-      <c r="O66" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="P66" s="0" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="T66" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="U66" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="W66" s="0" t="n">
-        <v>11000400001</v>
-      </c>
-      <c r="X66" s="0" t="n">
-        <v>11000400001</v>
-      </c>
-      <c r="Y66" s="0" t="inlineStr">
-        <is>
-          <t>攻击速度增加{Percentage}%</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="0" t="n">
-        <v>11000500001</v>
+        <v>11000400001</v>
       </c>
       <c r="C67" s="0" t="n">
         <v>11</v>
@@ -5155,14 +5166,14 @@
       </c>
       <c r="J67" s="0" t="inlineStr">
         <is>
-          <t>RCD</t>
+          <t>ASPD</t>
         </is>
       </c>
       <c r="O67" s="0" t="n">
-        <v>-0.25</v>
+        <v>1</v>
       </c>
       <c r="P67" s="0" t="n">
-        <v>-0.5</v>
+        <v>0.5</v>
       </c>
       <c r="T67" s="0" t="n">
         <v>0</v>
@@ -5171,20 +5182,20 @@
         <v>0</v>
       </c>
       <c r="W67" s="0" t="n">
-        <v>11000500001</v>
+        <v>11000400001</v>
       </c>
       <c r="X67" s="0" t="n">
-        <v>11000500001</v>
+        <v>11000400001</v>
       </c>
       <c r="Y67" s="0" t="inlineStr">
         <is>
-          <t>召唤CD{Percentage}%</t>
+          <t>攻击速度增加{Percentage}%</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="0" t="n">
-        <v>11000600001</v>
+        <v>11000500001</v>
       </c>
       <c r="C68" s="0" t="n">
         <v>11</v>
@@ -5199,7 +5210,7 @@
       </c>
       <c r="J68" s="0" t="inlineStr">
         <is>
-          <t>CMP</t>
+          <t>RCD</t>
         </is>
       </c>
       <c r="O68" s="0" t="n">
@@ -5215,20 +5226,20 @@
         <v>0</v>
       </c>
       <c r="W68" s="0" t="n">
-        <v>11000600001</v>
+        <v>11000500001</v>
       </c>
       <c r="X68" s="0" t="n">
-        <v>11000600001</v>
+        <v>11000500001</v>
       </c>
       <c r="Y68" s="0" t="inlineStr">
         <is>
-          <t>召唤魔力消耗{Percentage}%</t>
+          <t>召唤CD{Percentage}%</t>
         </is>
       </c>
     </row>
     <row r="69" ht="15" customHeight="1" s="3">
       <c r="A69" s="0" t="n">
-        <v>11000700001</v>
+        <v>11000600001</v>
       </c>
       <c r="C69" s="0" t="n">
         <v>11</v>
@@ -5236,27 +5247,21 @@
       <c r="D69" s="0" t="n">
         <v>2</v>
       </c>
-      <c r="G69" s="0" t="n">
-        <v>0</v>
-      </c>
       <c r="H69" s="0" t="inlineStr">
         <is>
-          <t>BuffEntityAttributeMulti</t>
+          <t>BuffEntityAttribute</t>
         </is>
       </c>
       <c r="J69" s="0" t="inlineStr">
         <is>
-          <t>ATK:1|HP:-1</t>
+          <t>CMP</t>
         </is>
       </c>
       <c r="O69" s="0" t="n">
-        <v>0.5</v>
+        <v>-0.25</v>
       </c>
       <c r="P69" s="0" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="R69" s="0" t="n">
-        <v>0</v>
+        <v>-0.5</v>
       </c>
       <c r="T69" s="0" t="n">
         <v>0</v>
@@ -5265,20 +5270,20 @@
         <v>0</v>
       </c>
       <c r="W69" s="0" t="n">
-        <v>11000700001</v>
+        <v>11000600001</v>
       </c>
       <c r="X69" s="0" t="n">
-        <v>11000700001</v>
+        <v>11000600001</v>
       </c>
       <c r="Y69" s="0" t="inlineStr">
         <is>
-          <t>狂战士-A</t>
+          <t>召唤魔力消耗{Percentage}%</t>
         </is>
       </c>
     </row>
     <row r="70" ht="15" customHeight="1" s="3">
       <c r="A70" s="0" t="n">
-        <v>11000700002</v>
+        <v>11000700001</v>
       </c>
       <c r="C70" s="0" t="n">
         <v>11</v>
@@ -5296,7 +5301,7 @@
       </c>
       <c r="J70" s="0" t="inlineStr">
         <is>
-          <t>ATK:1|DR:-1</t>
+          <t>ATK:1|HP:-1</t>
         </is>
       </c>
       <c r="O70" s="0" t="n">
@@ -5315,20 +5320,20 @@
         <v>0</v>
       </c>
       <c r="W70" s="0" t="n">
-        <v>11000700002</v>
+        <v>11000700001</v>
       </c>
       <c r="X70" s="0" t="n">
-        <v>11000700002</v>
+        <v>11000700001</v>
       </c>
       <c r="Y70" s="0" t="inlineStr">
         <is>
-          <t>狂战士-B</t>
+          <t>狂战士-A</t>
         </is>
       </c>
     </row>
     <row r="71" ht="15" customHeight="1" s="3">
       <c r="A71" s="0" t="n">
-        <v>11000700003</v>
+        <v>11000700002</v>
       </c>
       <c r="C71" s="0" t="n">
         <v>11</v>
@@ -5346,7 +5351,7 @@
       </c>
       <c r="J71" s="0" t="inlineStr">
         <is>
-          <t>ATK:1|ASPD:-1</t>
+          <t>ATK:1|DR:-1</t>
         </is>
       </c>
       <c r="O71" s="0" t="n">
@@ -5365,20 +5370,20 @@
         <v>0</v>
       </c>
       <c r="W71" s="0" t="n">
-        <v>11000700003</v>
+        <v>11000700002</v>
       </c>
       <c r="X71" s="0" t="n">
-        <v>11000700003</v>
+        <v>11000700002</v>
       </c>
       <c r="Y71" s="0" t="inlineStr">
         <is>
-          <t>狂战士-C</t>
+          <t>狂战士-B</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="0" t="n">
-        <v>11000800001</v>
+        <v>11000700003</v>
       </c>
       <c r="C72" s="0" t="n">
         <v>11</v>
@@ -5396,7 +5401,7 @@
       </c>
       <c r="J72" s="0" t="inlineStr">
         <is>
-          <t>ASPD:1|DR:-1</t>
+          <t>ATK:1|ASPD:-1</t>
         </is>
       </c>
       <c r="O72" s="0" t="n">
@@ -5415,20 +5420,20 @@
         <v>0</v>
       </c>
       <c r="W72" s="0" t="n">
-        <v>11000800001</v>
+        <v>11000700003</v>
       </c>
       <c r="X72" s="0" t="n">
-        <v>11000800001</v>
+        <v>11000700003</v>
       </c>
       <c r="Y72" s="0" t="inlineStr">
         <is>
-          <t>快枪手-A</t>
+          <t>狂战士-C</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="0" t="n">
-        <v>11000800002</v>
+        <v>11000800001</v>
       </c>
       <c r="C73" s="0" t="n">
         <v>11</v>
@@ -5446,7 +5451,7 @@
       </c>
       <c r="J73" s="0" t="inlineStr">
         <is>
-          <t>ASPD:1|HP:-1</t>
+          <t>ASPD:1|DR:-1</t>
         </is>
       </c>
       <c r="O73" s="0" t="n">
@@ -5465,20 +5470,20 @@
         <v>0</v>
       </c>
       <c r="W73" s="0" t="n">
-        <v>11000800002</v>
+        <v>11000800001</v>
       </c>
       <c r="X73" s="0" t="n">
-        <v>11000800002</v>
+        <v>11000800001</v>
       </c>
       <c r="Y73" s="0" t="inlineStr">
         <is>
-          <t>快枪手-B</t>
+          <t>快枪手-A</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="0" t="n">
-        <v>11000800003</v>
+        <v>11000800002</v>
       </c>
       <c r="C74" s="0" t="n">
         <v>11</v>
@@ -5496,7 +5501,7 @@
       </c>
       <c r="J74" s="0" t="inlineStr">
         <is>
-          <t>ASPD:1|ATK:-1</t>
+          <t>ASPD:1|HP:-1</t>
         </is>
       </c>
       <c r="O74" s="0" t="n">
@@ -5515,20 +5520,20 @@
         <v>0</v>
       </c>
       <c r="W74" s="0" t="n">
-        <v>11000800003</v>
+        <v>11000800002</v>
       </c>
       <c r="X74" s="0" t="n">
-        <v>11000800003</v>
+        <v>11000800002</v>
       </c>
       <c r="Y74" s="0" t="inlineStr">
         <is>
-          <t>快枪手-C</t>
+          <t>快枪手-B</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="0" t="n">
-        <v>11000900001</v>
+        <v>11000800003</v>
       </c>
       <c r="C75" s="0" t="n">
         <v>11</v>
@@ -5546,7 +5551,7 @@
       </c>
       <c r="J75" s="0" t="inlineStr">
         <is>
-          <t>DR:1|HP:-1</t>
+          <t>ASPD:1|ATK:-1</t>
         </is>
       </c>
       <c r="O75" s="0" t="n">
@@ -5565,20 +5570,20 @@
         <v>0</v>
       </c>
       <c r="W75" s="0" t="n">
-        <v>11000900001</v>
+        <v>11000800003</v>
       </c>
       <c r="X75" s="0" t="n">
-        <v>11000900001</v>
+        <v>11000800003</v>
       </c>
       <c r="Y75" s="0" t="inlineStr">
         <is>
-          <t>铜墙铁壁-A</t>
+          <t>快枪手-C</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="0" t="n">
-        <v>11000900002</v>
+        <v>11000900001</v>
       </c>
       <c r="C76" s="0" t="n">
         <v>11</v>
@@ -5596,7 +5601,7 @@
       </c>
       <c r="J76" s="0" t="inlineStr">
         <is>
-          <t>DR:1|ATK:-1</t>
+          <t>DR:1|HP:-1</t>
         </is>
       </c>
       <c r="O76" s="0" t="n">
@@ -5615,20 +5620,20 @@
         <v>0</v>
       </c>
       <c r="W76" s="0" t="n">
-        <v>11000900002</v>
+        <v>11000900001</v>
       </c>
       <c r="X76" s="0" t="n">
-        <v>11000900002</v>
+        <v>11000900001</v>
       </c>
       <c r="Y76" s="0" t="inlineStr">
         <is>
-          <t>铜墙铁壁-B</t>
+          <t>铜墙铁壁-A</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="0" t="n">
-        <v>11000900003</v>
+        <v>11000900002</v>
       </c>
       <c r="C77" s="0" t="n">
         <v>11</v>
@@ -5646,7 +5651,7 @@
       </c>
       <c r="J77" s="0" t="inlineStr">
         <is>
-          <t>DR:1|ASPD:-1</t>
+          <t>DR:1|ATK:-1</t>
         </is>
       </c>
       <c r="O77" s="0" t="n">
@@ -5665,20 +5670,20 @@
         <v>0</v>
       </c>
       <c r="W77" s="0" t="n">
-        <v>11000900003</v>
+        <v>11000900002</v>
       </c>
       <c r="X77" s="0" t="n">
-        <v>11000900003</v>
+        <v>11000900002</v>
       </c>
       <c r="Y77" s="0" t="inlineStr">
         <is>
-          <t>铜墙铁壁-C</t>
+          <t>铜墙铁壁-B</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="0" t="n">
-        <v>11001000001</v>
+        <v>11000900003</v>
       </c>
       <c r="C78" s="0" t="n">
         <v>11</v>
@@ -5696,7 +5701,7 @@
       </c>
       <c r="J78" s="0" t="inlineStr">
         <is>
-          <t>HP:1|ASPD:-1</t>
+          <t>DR:1|ASPD:-1</t>
         </is>
       </c>
       <c r="O78" s="0" t="n">
@@ -5715,20 +5720,20 @@
         <v>0</v>
       </c>
       <c r="W78" s="0" t="n">
-        <v>11001000001</v>
+        <v>11000900003</v>
       </c>
       <c r="X78" s="0" t="n">
-        <v>11001000001</v>
+        <v>11000900003</v>
       </c>
       <c r="Y78" s="0" t="inlineStr">
         <is>
-          <t>大块头-A</t>
+          <t>铜墙铁壁-C</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="0" t="n">
-        <v>11001000002</v>
+        <v>11001000001</v>
       </c>
       <c r="C79" s="0" t="n">
         <v>11</v>
@@ -5746,7 +5751,7 @@
       </c>
       <c r="J79" s="0" t="inlineStr">
         <is>
-          <t>HP:1|DR:-1</t>
+          <t>HP:1|ASPD:-1</t>
         </is>
       </c>
       <c r="O79" s="0" t="n">
@@ -5765,20 +5770,20 @@
         <v>0</v>
       </c>
       <c r="W79" s="0" t="n">
-        <v>11001000002</v>
+        <v>11001000001</v>
       </c>
       <c r="X79" s="0" t="n">
-        <v>11001000002</v>
+        <v>11001000001</v>
       </c>
       <c r="Y79" s="0" t="inlineStr">
         <is>
-          <t>大块头-B</t>
+          <t>大块头-A</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="0" t="n">
-        <v>11001000003</v>
+        <v>11001000002</v>
       </c>
       <c r="C80" s="0" t="n">
         <v>11</v>
@@ -5796,7 +5801,7 @@
       </c>
       <c r="J80" s="0" t="inlineStr">
         <is>
-          <t>HP:1|ATK:-1</t>
+          <t>HP:1|DR:-1</t>
         </is>
       </c>
       <c r="O80" s="0" t="n">
@@ -5815,20 +5820,20 @@
         <v>0</v>
       </c>
       <c r="W80" s="0" t="n">
-        <v>11001000003</v>
+        <v>11001000002</v>
       </c>
       <c r="X80" s="0" t="n">
-        <v>11001000003</v>
+        <v>11001000002</v>
       </c>
       <c r="Y80" s="0" t="inlineStr">
         <is>
-          <t>大块头-C</t>
+          <t>大块头-B</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="0" t="n">
-        <v>11000700004</v>
+        <v>11001000003</v>
       </c>
       <c r="C81" s="0" t="n">
         <v>11</v>
@@ -5846,7 +5851,7 @@
       </c>
       <c r="J81" s="0" t="inlineStr">
         <is>
-          <t>ATK:1|RCD:1</t>
+          <t>HP:1|ATK:-1</t>
         </is>
       </c>
       <c r="O81" s="0" t="n">
@@ -5865,20 +5870,20 @@
         <v>0</v>
       </c>
       <c r="W81" s="0" t="n">
-        <v>11000700004</v>
+        <v>11001000003</v>
       </c>
       <c r="X81" s="0" t="n">
-        <v>11000700004</v>
+        <v>11001000003</v>
       </c>
       <c r="Y81" s="0" t="inlineStr">
         <is>
-          <t>狂战士-D</t>
+          <t>大块头-C</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="0" t="n">
-        <v>11000700005</v>
+        <v>11000700004</v>
       </c>
       <c r="C82" s="0" t="n">
         <v>11</v>
@@ -5896,7 +5901,7 @@
       </c>
       <c r="J82" s="0" t="inlineStr">
         <is>
-          <t>ATK:1|CMP:1</t>
+          <t>ATK:1|RCD:1</t>
         </is>
       </c>
       <c r="O82" s="0" t="n">
@@ -5915,20 +5920,20 @@
         <v>0</v>
       </c>
       <c r="W82" s="0" t="n">
-        <v>11000700005</v>
+        <v>11000700004</v>
       </c>
       <c r="X82" s="0" t="n">
-        <v>11000700005</v>
+        <v>11000700004</v>
       </c>
       <c r="Y82" s="0" t="inlineStr">
         <is>
-          <t>狂战士-E</t>
+          <t>狂战士-D</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="0" t="n">
-        <v>11000800004</v>
+        <v>11000700005</v>
       </c>
       <c r="C83" s="0" t="n">
         <v>11</v>
@@ -5946,7 +5951,7 @@
       </c>
       <c r="J83" s="0" t="inlineStr">
         <is>
-          <t>ASPD:1|RCD:1</t>
+          <t>ATK:1|CMP:1</t>
         </is>
       </c>
       <c r="O83" s="0" t="n">
@@ -5965,20 +5970,20 @@
         <v>0</v>
       </c>
       <c r="W83" s="0" t="n">
-        <v>11000800004</v>
+        <v>11000700005</v>
       </c>
       <c r="X83" s="0" t="n">
-        <v>11000800004</v>
+        <v>11000700005</v>
       </c>
       <c r="Y83" s="0" t="inlineStr">
         <is>
-          <t>快枪手-D</t>
+          <t>狂战士-E</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="0" t="n">
-        <v>11000800005</v>
+        <v>11000800004</v>
       </c>
       <c r="C84" s="0" t="n">
         <v>11</v>
@@ -5996,7 +6001,7 @@
       </c>
       <c r="J84" s="0" t="inlineStr">
         <is>
-          <t>ASPD:1|CMP:1</t>
+          <t>ASPD:1|RCD:1</t>
         </is>
       </c>
       <c r="O84" s="0" t="n">
@@ -6015,20 +6020,20 @@
         <v>0</v>
       </c>
       <c r="W84" s="0" t="n">
-        <v>11000800005</v>
+        <v>11000800004</v>
       </c>
       <c r="X84" s="0" t="n">
-        <v>11000800005</v>
+        <v>11000800004</v>
       </c>
       <c r="Y84" s="0" t="inlineStr">
         <is>
-          <t>快枪手-E</t>
+          <t>快枪手-D</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="0" t="n">
-        <v>11000900004</v>
+        <v>11000800005</v>
       </c>
       <c r="C85" s="0" t="n">
         <v>11</v>
@@ -6046,7 +6051,7 @@
       </c>
       <c r="J85" s="0" t="inlineStr">
         <is>
-          <t>DR:1|RCD:1</t>
+          <t>ASPD:1|CMP:1</t>
         </is>
       </c>
       <c r="O85" s="0" t="n">
@@ -6065,20 +6070,20 @@
         <v>0</v>
       </c>
       <c r="W85" s="0" t="n">
-        <v>11000900004</v>
+        <v>11000800005</v>
       </c>
       <c r="X85" s="0" t="n">
-        <v>11000900004</v>
+        <v>11000800005</v>
       </c>
       <c r="Y85" s="0" t="inlineStr">
         <is>
-          <t>铜墙铁壁-D</t>
+          <t>快枪手-E</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="0" t="n">
-        <v>11000900005</v>
+        <v>11000900004</v>
       </c>
       <c r="C86" s="0" t="n">
         <v>11</v>
@@ -6096,7 +6101,7 @@
       </c>
       <c r="J86" s="0" t="inlineStr">
         <is>
-          <t>DR:1|CMP:1</t>
+          <t>DR:1|RCD:1</t>
         </is>
       </c>
       <c r="O86" s="0" t="n">
@@ -6115,20 +6120,20 @@
         <v>0</v>
       </c>
       <c r="W86" s="0" t="n">
-        <v>11000900005</v>
+        <v>11000900004</v>
       </c>
       <c r="X86" s="0" t="n">
-        <v>11000900005</v>
+        <v>11000900004</v>
       </c>
       <c r="Y86" s="0" t="inlineStr">
         <is>
-          <t>铜墙铁壁-E</t>
+          <t>铜墙铁壁-D</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="0" t="n">
-        <v>11001000004</v>
+        <v>11000900005</v>
       </c>
       <c r="C87" s="0" t="n">
         <v>11</v>
@@ -6146,7 +6151,7 @@
       </c>
       <c r="J87" s="0" t="inlineStr">
         <is>
-          <t>HP:1|RCD:1</t>
+          <t>DR:1|CMP:1</t>
         </is>
       </c>
       <c r="O87" s="0" t="n">
@@ -6165,20 +6170,20 @@
         <v>0</v>
       </c>
       <c r="W87" s="0" t="n">
-        <v>11001000004</v>
+        <v>11000900005</v>
       </c>
       <c r="X87" s="0" t="n">
-        <v>11001000004</v>
+        <v>11000900005</v>
       </c>
       <c r="Y87" s="0" t="inlineStr">
         <is>
-          <t>大块头-D</t>
+          <t>铜墙铁壁-E</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="0" t="n">
-        <v>11001000005</v>
+        <v>11001000004</v>
       </c>
       <c r="C88" s="0" t="n">
         <v>11</v>
@@ -6196,7 +6201,7 @@
       </c>
       <c r="J88" s="0" t="inlineStr">
         <is>
-          <t>HP:1|CMP:1</t>
+          <t>HP:1|RCD:1</t>
         </is>
       </c>
       <c r="O88" s="0" t="n">
@@ -6215,20 +6220,20 @@
         <v>0</v>
       </c>
       <c r="W88" s="0" t="n">
-        <v>11001000005</v>
+        <v>11001000004</v>
       </c>
       <c r="X88" s="0" t="n">
-        <v>11001000005</v>
+        <v>11001000004</v>
       </c>
       <c r="Y88" s="0" t="inlineStr">
         <is>
-          <t>大块头-E</t>
+          <t>大块头-D</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="0" t="n">
-        <v>11001100001</v>
+        <v>11001000005</v>
       </c>
       <c r="C89" s="0" t="n">
         <v>11</v>
@@ -6246,14 +6251,14 @@
       </c>
       <c r="J89" s="0" t="inlineStr">
         <is>
-          <t>RCD:-1|HP:-0.5</t>
+          <t>HP:1|CMP:1</t>
         </is>
       </c>
       <c r="O89" s="0" t="n">
-        <v>0.75</v>
+        <v>0.5</v>
       </c>
       <c r="P89" s="0" t="n">
-        <v>0.5</v>
+        <v>0.2</v>
       </c>
       <c r="R89" s="0" t="n">
         <v>0</v>
@@ -6265,20 +6270,20 @@
         <v>0</v>
       </c>
       <c r="W89" s="0" t="n">
-        <v>11001100001</v>
+        <v>11001000005</v>
       </c>
       <c r="X89" s="0" t="n">
-        <v>11001100001</v>
+        <v>11001000005</v>
       </c>
       <c r="Y89" s="0" t="inlineStr">
         <is>
-          <t>魂牵梦绕-A</t>
+          <t>大块头-E</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="0" t="n">
-        <v>11001100002</v>
+        <v>11001100001</v>
       </c>
       <c r="C90" s="0" t="n">
         <v>11</v>
@@ -6296,7 +6301,7 @@
       </c>
       <c r="J90" s="0" t="inlineStr">
         <is>
-          <t>RCD:-1|DR:-0.5</t>
+          <t>RCD:-1|HP:-0.5</t>
         </is>
       </c>
       <c r="O90" s="0" t="n">
@@ -6315,20 +6320,20 @@
         <v>0</v>
       </c>
       <c r="W90" s="0" t="n">
-        <v>11001100002</v>
+        <v>11001100001</v>
       </c>
       <c r="X90" s="0" t="n">
-        <v>11001100002</v>
+        <v>11001100001</v>
       </c>
       <c r="Y90" s="0" t="inlineStr">
         <is>
-          <t>魂牵梦绕-B</t>
+          <t>魂牵梦绕-A</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="0" t="n">
-        <v>11001100003</v>
+        <v>11001100002</v>
       </c>
       <c r="C91" s="0" t="n">
         <v>11</v>
@@ -6346,7 +6351,7 @@
       </c>
       <c r="J91" s="0" t="inlineStr">
         <is>
-          <t>RCD:-1|ATK:-0.5</t>
+          <t>RCD:-1|DR:-0.5</t>
         </is>
       </c>
       <c r="O91" s="0" t="n">
@@ -6365,20 +6370,20 @@
         <v>0</v>
       </c>
       <c r="W91" s="0" t="n">
-        <v>11001100003</v>
+        <v>11001100002</v>
       </c>
       <c r="X91" s="0" t="n">
-        <v>11001100003</v>
+        <v>11001100002</v>
       </c>
       <c r="Y91" s="0" t="inlineStr">
         <is>
-          <t>魂牵梦绕-C</t>
+          <t>魂牵梦绕-B</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="0" t="n">
-        <v>11001100004</v>
+        <v>11001100003</v>
       </c>
       <c r="C92" s="0" t="n">
         <v>11</v>
@@ -6396,7 +6401,7 @@
       </c>
       <c r="J92" s="0" t="inlineStr">
         <is>
-          <t>RCD:-1|ASPD:-0.5</t>
+          <t>RCD:-1|ATK:-0.5</t>
         </is>
       </c>
       <c r="O92" s="0" t="n">
@@ -6415,20 +6420,20 @@
         <v>0</v>
       </c>
       <c r="W92" s="0" t="n">
-        <v>11001100004</v>
+        <v>11001100003</v>
       </c>
       <c r="X92" s="0" t="n">
-        <v>11001100004</v>
+        <v>11001100003</v>
       </c>
       <c r="Y92" s="0" t="inlineStr">
         <is>
-          <t>魂牵梦绕-D</t>
+          <t>魂牵梦绕-C</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="0" t="n">
-        <v>11001100005</v>
+        <v>11001100004</v>
       </c>
       <c r="C93" s="0" t="n">
         <v>11</v>
@@ -6446,7 +6451,7 @@
       </c>
       <c r="J93" s="0" t="inlineStr">
         <is>
-          <t>RCD:-1|CMP:0.5</t>
+          <t>RCD:-1|ASPD:-0.5</t>
         </is>
       </c>
       <c r="O93" s="0" t="n">
@@ -6465,20 +6470,20 @@
         <v>0</v>
       </c>
       <c r="W93" s="0" t="n">
-        <v>11001100005</v>
+        <v>11001100004</v>
       </c>
       <c r="X93" s="0" t="n">
-        <v>11001100005</v>
+        <v>11001100004</v>
       </c>
       <c r="Y93" s="0" t="inlineStr">
         <is>
-          <t>魂牵梦绕-E</t>
+          <t>魂牵梦绕-D</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="0" t="n">
-        <v>11001200001</v>
+        <v>11001100005</v>
       </c>
       <c r="C94" s="0" t="n">
         <v>11</v>
@@ -6496,7 +6501,7 @@
       </c>
       <c r="J94" s="0" t="inlineStr">
         <is>
-          <t>CMP:-1|HP:-0.5</t>
+          <t>RCD:-1|CMP:0.5</t>
         </is>
       </c>
       <c r="O94" s="0" t="n">
@@ -6515,20 +6520,20 @@
         <v>0</v>
       </c>
       <c r="W94" s="0" t="n">
-        <v>11001200001</v>
+        <v>11001100005</v>
       </c>
       <c r="X94" s="0" t="n">
-        <v>11001200001</v>
+        <v>11001100005</v>
       </c>
       <c r="Y94" s="0" t="inlineStr">
         <is>
-          <t>折上折-A</t>
+          <t>魂牵梦绕-E</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="0" t="n">
-        <v>11001200002</v>
+        <v>11001200001</v>
       </c>
       <c r="C95" s="0" t="n">
         <v>11</v>
@@ -6546,7 +6551,7 @@
       </c>
       <c r="J95" s="0" t="inlineStr">
         <is>
-          <t>CMP:-1|DR:-0.5</t>
+          <t>CMP:-1|HP:-0.5</t>
         </is>
       </c>
       <c r="O95" s="0" t="n">
@@ -6565,20 +6570,20 @@
         <v>0</v>
       </c>
       <c r="W95" s="0" t="n">
-        <v>11001200002</v>
+        <v>11001200001</v>
       </c>
       <c r="X95" s="0" t="n">
-        <v>11001200002</v>
+        <v>11001200001</v>
       </c>
       <c r="Y95" s="0" t="inlineStr">
         <is>
-          <t>折上折-B</t>
+          <t>折上折-A</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="0" t="n">
-        <v>11001200003</v>
+        <v>11001200002</v>
       </c>
       <c r="C96" s="0" t="n">
         <v>11</v>
@@ -6596,7 +6601,7 @@
       </c>
       <c r="J96" s="0" t="inlineStr">
         <is>
-          <t>CMP:-1|ATK:-0.5</t>
+          <t>CMP:-1|DR:-0.5</t>
         </is>
       </c>
       <c r="O96" s="0" t="n">
@@ -6615,20 +6620,20 @@
         <v>0</v>
       </c>
       <c r="W96" s="0" t="n">
-        <v>11001200003</v>
+        <v>11001200002</v>
       </c>
       <c r="X96" s="0" t="n">
-        <v>11001200003</v>
+        <v>11001200002</v>
       </c>
       <c r="Y96" s="0" t="inlineStr">
         <is>
-          <t>折上折-C</t>
+          <t>折上折-B</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="0" t="n">
-        <v>11001200004</v>
+        <v>11001200003</v>
       </c>
       <c r="C97" s="0" t="n">
         <v>11</v>
@@ -6646,7 +6651,7 @@
       </c>
       <c r="J97" s="0" t="inlineStr">
         <is>
-          <t>CMP:-1|ASPD:-0.5</t>
+          <t>CMP:-1|ATK:-0.5</t>
         </is>
       </c>
       <c r="O97" s="0" t="n">
@@ -6665,20 +6670,20 @@
         <v>0</v>
       </c>
       <c r="W97" s="0" t="n">
-        <v>11001200004</v>
+        <v>11001200003</v>
       </c>
       <c r="X97" s="0" t="n">
-        <v>11001200004</v>
+        <v>11001200003</v>
       </c>
       <c r="Y97" s="0" t="inlineStr">
         <is>
-          <t>折上折-D</t>
+          <t>折上折-C</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="0" t="n">
-        <v>11001200005</v>
+        <v>11001200004</v>
       </c>
       <c r="C98" s="0" t="n">
         <v>11</v>
@@ -6696,7 +6701,7 @@
       </c>
       <c r="J98" s="0" t="inlineStr">
         <is>
-          <t>CMP:-1|RCD:0.5</t>
+          <t>CMP:-1|ASPD:-0.5</t>
         </is>
       </c>
       <c r="O98" s="0" t="n">
@@ -6715,40 +6720,48 @@
         <v>0</v>
       </c>
       <c r="W98" s="0" t="n">
-        <v>11001200005</v>
+        <v>11001200004</v>
       </c>
       <c r="X98" s="0" t="n">
-        <v>11001200005</v>
+        <v>11001200004</v>
       </c>
       <c r="Y98" s="0" t="inlineStr">
         <is>
-          <t>折上折-E</t>
+          <t>折上折-D</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="0" t="n">
-        <v>12000100001</v>
+        <v>11001200005</v>
       </c>
       <c r="C99" s="0" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D99" s="0" t="n">
-        <v>3</v>
+        <v>2</v>
+      </c>
+      <c r="G99" s="0" t="n">
+        <v>0</v>
       </c>
       <c r="H99" s="0" t="inlineStr">
         <is>
-          <t>BuffEntityBaseHPChange</t>
+          <t>BuffEntityAttributeMulti</t>
+        </is>
+      </c>
+      <c r="J99" s="0" t="inlineStr">
+        <is>
+          <t>CMP:-1|RCD:0.5</t>
         </is>
       </c>
       <c r="O99" s="0" t="n">
-        <v>0.05</v>
+        <v>0.75</v>
       </c>
       <c r="P99" s="0" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="S99" s="0" t="n">
-        <v>5</v>
+        <v>0.5</v>
+      </c>
+      <c r="R99" s="0" t="n">
+        <v>0</v>
       </c>
       <c r="T99" s="0" t="n">
         <v>0</v>
@@ -6756,24 +6769,21 @@
       <c r="U99" s="0" t="n">
         <v>0</v>
       </c>
-      <c r="V99" s="0" t="n">
-        <v>500001</v>
-      </c>
       <c r="W99" s="0" t="n">
-        <v>12000100001</v>
+        <v>11001200005</v>
       </c>
       <c r="X99" s="0" t="n">
-        <v>12000100001</v>
+        <v>11001200005</v>
       </c>
       <c r="Y99" s="0" t="inlineStr">
         <is>
-          <t>每隔{Time_S}秒恢复{Percentage}%生命</t>
+          <t>折上折-E</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="0" t="n">
-        <v>12000200001</v>
+        <v>12000100001</v>
       </c>
       <c r="C100" s="0" t="n">
         <v>12</v>
@@ -6783,7 +6793,7 @@
       </c>
       <c r="H100" s="0" t="inlineStr">
         <is>
-          <t>BuffEntityBaseDRChange</t>
+          <t>BuffEntityBaseHPChange</t>
         </is>
       </c>
       <c r="O100" s="0" t="n">
@@ -6802,23 +6812,23 @@
         <v>0</v>
       </c>
       <c r="V100" s="0" t="n">
-        <v>500002</v>
+        <v>500001</v>
       </c>
       <c r="W100" s="0" t="n">
-        <v>12000200001</v>
+        <v>12000100001</v>
       </c>
       <c r="X100" s="0" t="n">
-        <v>12000200001</v>
+        <v>12000100001</v>
       </c>
       <c r="Y100" s="0" t="inlineStr">
         <is>
-          <t>每隔{Time_S}秒恢复{Percentage}%护甲</t>
+          <t>每隔{Time_S}秒恢复{Percentage}%生命</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="0" t="n">
-        <v>12000300001</v>
+        <v>12000200001</v>
       </c>
       <c r="C101" s="0" t="n">
         <v>12</v>
@@ -6828,8 +6838,14 @@
       </c>
       <c r="H101" s="0" t="inlineStr">
         <is>
-          <t>BuffEntityPeriodicAttackAgain</t>
-        </is>
+          <t>BuffEntityBaseDRChange</t>
+        </is>
+      </c>
+      <c r="O101" s="0" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="P101" s="0" t="n">
+        <v>0.01</v>
       </c>
       <c r="S101" s="0" t="n">
         <v>5</v>
@@ -6840,21 +6856,24 @@
       <c r="U101" s="0" t="n">
         <v>0</v>
       </c>
+      <c r="V101" s="0" t="n">
+        <v>500002</v>
+      </c>
       <c r="W101" s="0" t="n">
-        <v>12000300001</v>
+        <v>12000200001</v>
       </c>
       <c r="X101" s="0" t="n">
-        <v>12000300001</v>
+        <v>12000200001</v>
       </c>
       <c r="Y101" s="0" t="inlineStr">
         <is>
-          <t>每隔{Time_S}秒立即攻击一次</t>
+          <t>每隔{Time_S}秒恢复{Percentage}%护甲</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="0" t="n">
-        <v>12001100001</v>
+        <v>12000300001</v>
       </c>
       <c r="C102" s="0" t="n">
         <v>12</v>
@@ -6864,29 +6883,11 @@
       </c>
       <c r="H102" s="0" t="inlineStr">
         <is>
-          <t>BuffEntityConditionalAttribute</t>
-        </is>
-      </c>
-      <c r="I102" s="0" t="inlineStr">
-        <is>
-          <t>GameFightLogic_UnderAttack_Dead</t>
-        </is>
-      </c>
-      <c r="J102" s="0" t="inlineStr">
-        <is>
-          <t>HP</t>
-        </is>
-      </c>
-      <c r="L102" s="0" t="inlineStr">
-        <is>
-          <t>2001:10&amp;</t>
-        </is>
-      </c>
-      <c r="O102" s="0" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="P102" s="0" t="n">
-        <v>0.1</v>
+          <t>BuffEntityPeriodicAttackAgain</t>
+        </is>
+      </c>
+      <c r="S102" s="0" t="n">
+        <v>5</v>
       </c>
       <c r="T102" s="0" t="n">
         <v>0</v>
@@ -6895,20 +6896,20 @@
         <v>0</v>
       </c>
       <c r="W102" s="0" t="n">
-        <v>12001100001</v>
+        <v>12000300001</v>
       </c>
       <c r="X102" s="0" t="n">
-        <v>12001100001</v>
+        <v>12000300001</v>
       </c>
       <c r="Y102" s="0" t="inlineStr">
         <is>
-          <t>击杀{KillNum}次生物，生命增加{Percentage}%</t>
+          <t>每隔{Time_S}秒立即攻击一次</t>
         </is>
       </c>
     </row>
     <row r="103" ht="12" customHeight="1" s="3">
       <c r="A103" s="0" t="n">
-        <v>12001200001</v>
+        <v>12001100001</v>
       </c>
       <c r="C103" s="0" t="n">
         <v>12</v>
@@ -6928,7 +6929,7 @@
       </c>
       <c r="J103" s="0" t="inlineStr">
         <is>
-          <t>DR</t>
+          <t>HP</t>
         </is>
       </c>
       <c r="L103" s="0" t="inlineStr">
@@ -6949,20 +6950,20 @@
         <v>0</v>
       </c>
       <c r="W103" s="0" t="n">
-        <v>12001200001</v>
+        <v>12001100001</v>
       </c>
       <c r="X103" s="0" t="n">
-        <v>12001200001</v>
+        <v>12001100001</v>
       </c>
       <c r="Y103" s="0" t="inlineStr">
         <is>
-          <t>击杀{KillNum}次生物，护甲增加{Percentage}%</t>
+          <t>击杀{KillNum}次生物，生命增加{Percentage}%</t>
         </is>
       </c>
     </row>
     <row r="104" ht="12" customHeight="1" s="3">
       <c r="A104" s="0" t="n">
-        <v>12001300001</v>
+        <v>12001200001</v>
       </c>
       <c r="C104" s="0" t="n">
         <v>12</v>
@@ -6982,7 +6983,7 @@
       </c>
       <c r="J104" s="0" t="inlineStr">
         <is>
-          <t>ATK</t>
+          <t>DR</t>
         </is>
       </c>
       <c r="L104" s="0" t="inlineStr">
@@ -7003,20 +7004,20 @@
         <v>0</v>
       </c>
       <c r="W104" s="0" t="n">
-        <v>12001300001</v>
+        <v>12001200001</v>
       </c>
       <c r="X104" s="0" t="n">
-        <v>12001300001</v>
+        <v>12001200001</v>
       </c>
       <c r="Y104" s="0" t="inlineStr">
         <is>
-          <t>击杀{KillNum}次生物，攻击力增加{Percentage}%</t>
+          <t>击杀{KillNum}次生物，护甲增加{Percentage}%</t>
         </is>
       </c>
     </row>
     <row r="105" ht="12" customHeight="1" s="3">
       <c r="A105" s="0" t="n">
-        <v>12001400001</v>
+        <v>12001300001</v>
       </c>
       <c r="C105" s="0" t="n">
         <v>12</v>
@@ -7036,7 +7037,7 @@
       </c>
       <c r="J105" s="0" t="inlineStr">
         <is>
-          <t>ASPD</t>
+          <t>ATK</t>
         </is>
       </c>
       <c r="L105" s="0" t="inlineStr">
@@ -7057,20 +7058,20 @@
         <v>0</v>
       </c>
       <c r="W105" s="0" t="n">
-        <v>12001400001</v>
+        <v>12001300001</v>
       </c>
       <c r="X105" s="0" t="n">
-        <v>12001400001</v>
+        <v>12001300001</v>
       </c>
       <c r="Y105" s="0" t="inlineStr">
         <is>
-          <t>击杀{KillNum}次生物，攻击速度增加{Percentage}%</t>
+          <t>击杀{KillNum}次生物，攻击力增加{Percentage}%</t>
         </is>
       </c>
     </row>
     <row r="106" ht="12" customHeight="1" s="3">
       <c r="A106" s="0" t="n">
-        <v>12002100001</v>
+        <v>12001400001</v>
       </c>
       <c r="C106" s="0" t="n">
         <v>12</v>
@@ -7085,17 +7086,17 @@
       </c>
       <c r="I106" s="0" t="inlineStr">
         <is>
-          <t>GameFightLogic_UnderAttack</t>
+          <t>GameFightLogic_UnderAttack_Dead</t>
         </is>
       </c>
       <c r="J106" s="0" t="inlineStr">
         <is>
-          <t>HP</t>
+          <t>ASPD</t>
         </is>
       </c>
       <c r="L106" s="0" t="inlineStr">
         <is>
-          <t>3001:100&amp;</t>
+          <t>2001:10&amp;</t>
         </is>
       </c>
       <c r="O106" s="0" t="n">
@@ -7111,20 +7112,20 @@
         <v>0</v>
       </c>
       <c r="W106" s="0" t="n">
-        <v>12002100001</v>
+        <v>12001400001</v>
       </c>
       <c r="X106" s="0" t="n">
-        <v>12002100001</v>
+        <v>12001400001</v>
       </c>
       <c r="Y106" s="0" t="inlineStr">
         <is>
-          <t>受到{UnderAttackDamage}点伤害，生命增加{Percentage}%</t>
+          <t>击杀{KillNum}次生物，攻击速度增加{Percentage}%</t>
         </is>
       </c>
     </row>
     <row r="107" ht="12" customHeight="1" s="3">
       <c r="A107" s="0" t="n">
-        <v>12002200001</v>
+        <v>12002100001</v>
       </c>
       <c r="C107" s="0" t="n">
         <v>12</v>
@@ -7144,7 +7145,7 @@
       </c>
       <c r="J107" s="0" t="inlineStr">
         <is>
-          <t>DR</t>
+          <t>HP</t>
         </is>
       </c>
       <c r="L107" s="0" t="inlineStr">
@@ -7165,20 +7166,20 @@
         <v>0</v>
       </c>
       <c r="W107" s="0" t="n">
-        <v>12002200001</v>
+        <v>12002100001</v>
       </c>
       <c r="X107" s="0" t="n">
-        <v>12002200001</v>
+        <v>12002100001</v>
       </c>
       <c r="Y107" s="0" t="inlineStr">
         <is>
-          <t>受到{UnderAttackDamage}点伤害，护甲增加{Percentage}%</t>
+          <t>受到{UnderAttackDamage}点伤害，生命增加{Percentage}%</t>
         </is>
       </c>
     </row>
     <row r="108" ht="12" customHeight="1" s="3">
       <c r="A108" s="0" t="n">
-        <v>12002300001</v>
+        <v>12002200001</v>
       </c>
       <c r="C108" s="0" t="n">
         <v>12</v>
@@ -7198,7 +7199,7 @@
       </c>
       <c r="J108" s="0" t="inlineStr">
         <is>
-          <t>ATK</t>
+          <t>DR</t>
         </is>
       </c>
       <c r="L108" s="0" t="inlineStr">
@@ -7219,20 +7220,20 @@
         <v>0</v>
       </c>
       <c r="W108" s="0" t="n">
-        <v>12002300001</v>
+        <v>12002200001</v>
       </c>
       <c r="X108" s="0" t="n">
-        <v>12002300001</v>
+        <v>12002200001</v>
       </c>
       <c r="Y108" s="0" t="inlineStr">
         <is>
-          <t>受到{UnderAttackDamage}点伤害，攻击力增加{Percentage}%</t>
+          <t>受到{UnderAttackDamage}点伤害，护甲增加{Percentage}%</t>
         </is>
       </c>
     </row>
     <row r="109" ht="12" customHeight="1" s="3">
       <c r="A109" s="0" t="n">
-        <v>12002400001</v>
+        <v>12002300001</v>
       </c>
       <c r="C109" s="0" t="n">
         <v>12</v>
@@ -7252,7 +7253,7 @@
       </c>
       <c r="J109" s="0" t="inlineStr">
         <is>
-          <t>ASPD</t>
+          <t>ATK</t>
         </is>
       </c>
       <c r="L109" s="0" t="inlineStr">
@@ -7273,20 +7274,20 @@
         <v>0</v>
       </c>
       <c r="W109" s="0" t="n">
-        <v>12002400001</v>
+        <v>12002300001</v>
       </c>
       <c r="X109" s="0" t="n">
-        <v>12002400001</v>
+        <v>12002300001</v>
       </c>
       <c r="Y109" s="0" t="inlineStr">
         <is>
-          <t>受到{UnderAttackDamage}点伤害，攻击速度增加{Percentage}%</t>
+          <t>受到{UnderAttackDamage}点伤害，攻击力增加{Percentage}%</t>
         </is>
       </c>
     </row>
     <row r="110" ht="12" customHeight="1" s="3">
       <c r="A110" s="0" t="n">
-        <v>12003100001</v>
+        <v>12002400001</v>
       </c>
       <c r="C110" s="0" t="n">
         <v>12</v>
@@ -7306,12 +7307,12 @@
       </c>
       <c r="J110" s="0" t="inlineStr">
         <is>
-          <t>HP</t>
+          <t>ASPD</t>
         </is>
       </c>
       <c r="L110" s="0" t="inlineStr">
         <is>
-          <t>1001:0.5&amp;</t>
+          <t>3001:100&amp;</t>
         </is>
       </c>
       <c r="O110" s="0" t="n">
@@ -7327,20 +7328,20 @@
         <v>0</v>
       </c>
       <c r="W110" s="0" t="n">
-        <v>12003100001</v>
+        <v>12002400001</v>
       </c>
       <c r="X110" s="0" t="n">
-        <v>12003100001</v>
+        <v>12002400001</v>
       </c>
       <c r="Y110" s="0" t="inlineStr">
         <is>
-          <t>血量少于{HPRateLess}%，生命增加{Percentage}%</t>
+          <t>受到{UnderAttackDamage}点伤害，攻击速度增加{Percentage}%</t>
         </is>
       </c>
     </row>
     <row r="111" ht="12" customHeight="1" s="3">
       <c r="A111" s="0" t="n">
-        <v>12003200001</v>
+        <v>12003100001</v>
       </c>
       <c r="C111" s="0" t="n">
         <v>12</v>
@@ -7360,7 +7361,7 @@
       </c>
       <c r="J111" s="0" t="inlineStr">
         <is>
-          <t>DR</t>
+          <t>HP</t>
         </is>
       </c>
       <c r="L111" s="0" t="inlineStr">
@@ -7381,20 +7382,20 @@
         <v>0</v>
       </c>
       <c r="W111" s="0" t="n">
-        <v>12003200001</v>
+        <v>12003100001</v>
       </c>
       <c r="X111" s="0" t="n">
-        <v>12003200001</v>
+        <v>12003100001</v>
       </c>
       <c r="Y111" s="0" t="inlineStr">
         <is>
-          <t>血量少于{HPRateLess}%，护甲增加{Percentage}%</t>
+          <t>血量少于{HPRateLess}%，生命增加{Percentage}%</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="0" t="n">
-        <v>12003300001</v>
+        <v>12003200001</v>
       </c>
       <c r="C112" s="0" t="n">
         <v>12</v>
@@ -7414,7 +7415,7 @@
       </c>
       <c r="J112" s="0" t="inlineStr">
         <is>
-          <t>ATK</t>
+          <t>DR</t>
         </is>
       </c>
       <c r="L112" s="0" t="inlineStr">
@@ -7435,20 +7436,20 @@
         <v>0</v>
       </c>
       <c r="W112" s="0" t="n">
-        <v>12003300001</v>
+        <v>12003200001</v>
       </c>
       <c r="X112" s="0" t="n">
-        <v>12003300001</v>
+        <v>12003200001</v>
       </c>
       <c r="Y112" s="0" t="inlineStr">
         <is>
-          <t>血量少于{HPRateLess}%，攻击力增加{Percentage}%</t>
+          <t>血量少于{HPRateLess}%，护甲增加{Percentage}%</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="0" t="n">
-        <v>12003400001</v>
+        <v>12003300001</v>
       </c>
       <c r="C113" s="0" t="n">
         <v>12</v>
@@ -7468,7 +7469,7 @@
       </c>
       <c r="J113" s="0" t="inlineStr">
         <is>
-          <t>ASPD</t>
+          <t>ATK</t>
         </is>
       </c>
       <c r="L113" s="0" t="inlineStr">
@@ -7489,20 +7490,20 @@
         <v>0</v>
       </c>
       <c r="W113" s="0" t="n">
-        <v>12003400001</v>
+        <v>12003300001</v>
       </c>
       <c r="X113" s="0" t="n">
-        <v>12003400001</v>
+        <v>12003300001</v>
       </c>
       <c r="Y113" s="0" t="inlineStr">
         <is>
-          <t>血量少于{HPRateLess}%，攻击速度增加{Percentage}%</t>
+          <t>血量少于{HPRateLess}%，攻击力增加{Percentage}%</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="0" t="n">
-        <v>12004100001</v>
+        <v>12003400001</v>
       </c>
       <c r="C114" s="0" t="n">
         <v>12</v>
@@ -7512,18 +7513,22 @@
       </c>
       <c r="H114" s="0" t="inlineStr">
         <is>
-          <t>BuffEntityConditionalAttributeTime</t>
-        </is>
-      </c>
-      <c r="I114" s="0" t="inlineStr"/>
+          <t>BuffEntityConditionalAttribute</t>
+        </is>
+      </c>
+      <c r="I114" s="0" t="inlineStr">
+        <is>
+          <t>GameFightLogic_UnderAttack</t>
+        </is>
+      </c>
       <c r="J114" s="0" t="inlineStr">
         <is>
-          <t>HP</t>
+          <t>ASPD</t>
         </is>
       </c>
       <c r="L114" s="0" t="inlineStr">
         <is>
-          <t>7001:300&amp;</t>
+          <t>1001:0.5&amp;</t>
         </is>
       </c>
       <c r="O114" s="0" t="n">
@@ -7539,20 +7544,20 @@
         <v>0</v>
       </c>
       <c r="W114" s="0" t="n">
-        <v>12004100001</v>
+        <v>12003400001</v>
       </c>
       <c r="X114" s="0" t="n">
-        <v>12004100001</v>
+        <v>12003400001</v>
       </c>
       <c r="Y114" s="0" t="inlineStr">
         <is>
-          <t>在场存活超过{OnFieldTime}秒后，生命增加{Percentage}%</t>
+          <t>血量少于{HPRateLess}%，攻击速度增加{Percentage}%</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="0" t="n">
-        <v>12004200001</v>
+        <v>12004100001</v>
       </c>
       <c r="C115" s="0" t="n">
         <v>12</v>
@@ -7568,7 +7573,7 @@
       <c r="I115" s="0" t="inlineStr"/>
       <c r="J115" s="0" t="inlineStr">
         <is>
-          <t>DR</t>
+          <t>HP</t>
         </is>
       </c>
       <c r="L115" s="0" t="inlineStr">
@@ -7589,20 +7594,20 @@
         <v>0</v>
       </c>
       <c r="W115" s="0" t="n">
-        <v>12004200001</v>
+        <v>12004100001</v>
       </c>
       <c r="X115" s="0" t="n">
-        <v>12004200001</v>
+        <v>12004100001</v>
       </c>
       <c r="Y115" s="0" t="inlineStr">
         <is>
-          <t>在场存活超过{OnFieldTime}秒后，护甲增加{Percentage}%</t>
+          <t>在场存活超过{OnFieldTime}秒后，生命增加{Percentage}%</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="0" t="n">
-        <v>12004300001</v>
+        <v>12004200001</v>
       </c>
       <c r="C116" s="0" t="n">
         <v>12</v>
@@ -7618,7 +7623,7 @@
       <c r="I116" s="0" t="inlineStr"/>
       <c r="J116" s="0" t="inlineStr">
         <is>
-          <t>ATK</t>
+          <t>DR</t>
         </is>
       </c>
       <c r="L116" s="0" t="inlineStr">
@@ -7639,20 +7644,20 @@
         <v>0</v>
       </c>
       <c r="W116" s="0" t="n">
-        <v>12004300001</v>
+        <v>12004200001</v>
       </c>
       <c r="X116" s="0" t="n">
-        <v>12004300001</v>
+        <v>12004200001</v>
       </c>
       <c r="Y116" s="0" t="inlineStr">
         <is>
-          <t>在场存活超过{OnFieldTime}秒后，攻击力增加{Percentage}%</t>
+          <t>在场存活超过{OnFieldTime}秒后，护甲增加{Percentage}%</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="0" t="n">
-        <v>12004400001</v>
+        <v>12004300001</v>
       </c>
       <c r="C117" s="0" t="n">
         <v>12</v>
@@ -7668,7 +7673,7 @@
       <c r="I117" s="0" t="inlineStr"/>
       <c r="J117" s="0" t="inlineStr">
         <is>
-          <t>ASPD</t>
+          <t>ATK</t>
         </is>
       </c>
       <c r="L117" s="0" t="inlineStr">
@@ -7689,20 +7694,20 @@
         <v>0</v>
       </c>
       <c r="W117" s="0" t="n">
-        <v>12004400001</v>
+        <v>12004300001</v>
       </c>
       <c r="X117" s="0" t="n">
-        <v>12004400001</v>
+        <v>12004300001</v>
       </c>
       <c r="Y117" s="0" t="inlineStr">
         <is>
-          <t>在场存活超过{OnFieldTime}秒后，攻击速度增加{Percentage}%</t>
+          <t>在场存活超过{OnFieldTime}秒后，攻击力增加{Percentage}%</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="0" t="n">
-        <v>12010100001</v>
+        <v>12004400001</v>
       </c>
       <c r="C118" s="0" t="n">
         <v>12</v>
@@ -7712,18 +7717,25 @@
       </c>
       <c r="H118" s="0" t="inlineStr">
         <is>
-          <t>BuffEntityConditionalCreateCrystal</t>
-        </is>
-      </c>
-      <c r="I118" s="0" t="inlineStr">
-        <is>
-          <t>GameFightLogic_UnderAttack_Dead</t>
+          <t>BuffEntityConditionalAttributeTime</t>
+        </is>
+      </c>
+      <c r="I118" s="0" t="inlineStr"/>
+      <c r="J118" s="0" t="inlineStr">
+        <is>
+          <t>ASPD</t>
         </is>
       </c>
       <c r="L118" s="0" t="inlineStr">
         <is>
-          <t>2001:10&amp;</t>
-        </is>
+          <t>7001:300&amp;</t>
+        </is>
+      </c>
+      <c r="O118" s="0" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="P118" s="0" t="n">
+        <v>0.1</v>
       </c>
       <c r="T118" s="0" t="n">
         <v>0</v>
@@ -7732,20 +7744,20 @@
         <v>0</v>
       </c>
       <c r="W118" s="0" t="n">
-        <v>12010100001</v>
+        <v>12004400001</v>
       </c>
       <c r="X118" s="0" t="n">
-        <v>12010100001</v>
+        <v>12004400001</v>
       </c>
       <c r="Y118" s="0" t="inlineStr">
         <is>
-          <t>击杀{KillNum}次生物，掉落一次魔晶</t>
+          <t>在场存活超过{OnFieldTime}秒后，攻击速度增加{Percentage}%</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="0" t="n">
-        <v>12010200001</v>
+        <v>12010100001</v>
       </c>
       <c r="C119" s="0" t="n">
         <v>12</v>
@@ -7760,12 +7772,12 @@
       </c>
       <c r="I119" s="0" t="inlineStr">
         <is>
-          <t>GameFightLogic_UnderAttack</t>
+          <t>GameFightLogic_UnderAttack_Dead</t>
         </is>
       </c>
       <c r="L119" s="0" t="inlineStr">
         <is>
-          <t>3001:100&amp;</t>
+          <t>2001:10&amp;</t>
         </is>
       </c>
       <c r="T119" s="0" t="n">
@@ -7775,20 +7787,20 @@
         <v>0</v>
       </c>
       <c r="W119" s="0" t="n">
-        <v>12010200001</v>
+        <v>12010100001</v>
       </c>
       <c r="X119" s="0" t="n">
-        <v>12010200001</v>
+        <v>12010100001</v>
       </c>
       <c r="Y119" s="0" t="inlineStr">
         <is>
-          <t>受到{UnderAttackDamage}点伤害，掉落一次魔晶</t>
+          <t>击杀{KillNum}次生物，掉落一次魔晶</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="0" t="n">
-        <v>12010300001</v>
+        <v>12010200001</v>
       </c>
       <c r="C120" s="0" t="n">
         <v>12</v>
@@ -7808,7 +7820,7 @@
       </c>
       <c r="L120" s="0" t="inlineStr">
         <is>
-          <t>4001:1000&amp;</t>
+          <t>3001:100&amp;</t>
         </is>
       </c>
       <c r="T120" s="0" t="n">
@@ -7818,20 +7830,20 @@
         <v>0</v>
       </c>
       <c r="W120" s="0" t="n">
-        <v>12010300001</v>
+        <v>12010200001</v>
       </c>
       <c r="X120" s="0" t="n">
-        <v>12010300001</v>
+        <v>12010200001</v>
       </c>
       <c r="Y120" s="0" t="inlineStr">
         <is>
-          <t>造成{AttackDamage}点伤害，掉落一次魔晶</t>
+          <t>受到{UnderAttackDamage}点伤害，掉落一次魔晶</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="0" t="n">
-        <v>12010400001</v>
+        <v>12010300001</v>
       </c>
       <c r="C121" s="0" t="n">
         <v>12</v>
@@ -7846,12 +7858,12 @@
       </c>
       <c r="I121" s="0" t="inlineStr">
         <is>
-          <t>GameFightLogic_RegainHP</t>
+          <t>GameFightLogic_UnderAttack</t>
         </is>
       </c>
       <c r="L121" s="0" t="inlineStr">
         <is>
-          <t>5001:500&amp;</t>
+          <t>4001:1000&amp;</t>
         </is>
       </c>
       <c r="T121" s="0" t="n">
@@ -7861,20 +7873,20 @@
         <v>0</v>
       </c>
       <c r="W121" s="0" t="n">
-        <v>12010400001</v>
+        <v>12010300001</v>
       </c>
       <c r="X121" s="0" t="n">
-        <v>12010400001</v>
+        <v>12010300001</v>
       </c>
       <c r="Y121" s="0" t="inlineStr">
         <is>
-          <t>累计被治疗{RegainHPReceived}点，掉落一次魔晶</t>
+          <t>造成{AttackDamage}点伤害，掉落一次魔晶</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="0" t="n">
-        <v>12010500001</v>
+        <v>12010400001</v>
       </c>
       <c r="C122" s="0" t="n">
         <v>12</v>
@@ -7894,7 +7906,7 @@
       </c>
       <c r="L122" s="0" t="inlineStr">
         <is>
-          <t>6001:1000&amp;</t>
+          <t>5001:500&amp;</t>
         </is>
       </c>
       <c r="T122" s="0" t="n">
@@ -7904,20 +7916,20 @@
         <v>0</v>
       </c>
       <c r="W122" s="0" t="n">
-        <v>12010500001</v>
+        <v>12010400001</v>
       </c>
       <c r="X122" s="0" t="n">
-        <v>12010500001</v>
+        <v>12010400001</v>
       </c>
       <c r="Y122" s="0" t="inlineStr">
         <is>
-          <t>累计治疗{RegainHPCast}点，掉落一次魔晶</t>
+          <t>累计被治疗{RegainHPReceived}点，掉落一次魔晶</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="0" t="n">
-        <v>12011100001</v>
+        <v>12010500001</v>
       </c>
       <c r="C123" s="0" t="n">
         <v>12</v>
@@ -7927,17 +7939,17 @@
       </c>
       <c r="H123" s="0" t="inlineStr">
         <is>
-          <t>BuffEntityConditionalAttackAgain</t>
+          <t>BuffEntityConditionalCreateCrystal</t>
         </is>
       </c>
       <c r="I123" s="0" t="inlineStr">
         <is>
-          <t>GameFightLogic_UnderAttack_Dead</t>
+          <t>GameFightLogic_RegainHP</t>
         </is>
       </c>
       <c r="L123" s="0" t="inlineStr">
         <is>
-          <t>2001:1&amp;</t>
+          <t>6001:1000&amp;</t>
         </is>
       </c>
       <c r="T123" s="0" t="n">
@@ -7947,20 +7959,20 @@
         <v>0</v>
       </c>
       <c r="W123" s="0" t="n">
-        <v>12011100001</v>
+        <v>12010500001</v>
       </c>
       <c r="X123" s="0" t="n">
-        <v>12011100001</v>
+        <v>12010500001</v>
       </c>
       <c r="Y123" s="0" t="inlineStr">
         <is>
-          <t>击杀{KillNum}次生物，立即攻击一次</t>
+          <t>累计治疗{RegainHPCast}点，掉落一次魔晶</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="0" t="n">
-        <v>12011200001</v>
+        <v>12011100001</v>
       </c>
       <c r="C124" s="0" t="n">
         <v>12</v>
@@ -7975,12 +7987,12 @@
       </c>
       <c r="I124" s="0" t="inlineStr">
         <is>
-          <t>GameFightLogic_UnderAttack</t>
+          <t>GameFightLogic_UnderAttack_Dead</t>
         </is>
       </c>
       <c r="L124" s="0" t="inlineStr">
         <is>
-          <t>3001:100&amp;</t>
+          <t>2001:1&amp;</t>
         </is>
       </c>
       <c r="T124" s="0" t="n">
@@ -7990,20 +8002,20 @@
         <v>0</v>
       </c>
       <c r="W124" s="0" t="n">
-        <v>12011200001</v>
+        <v>12011100001</v>
       </c>
       <c r="X124" s="0" t="n">
-        <v>12011200001</v>
+        <v>12011100001</v>
       </c>
       <c r="Y124" s="0" t="inlineStr">
         <is>
-          <t>受到{UnderAttackDamage}点伤害，秒再攻击一次</t>
+          <t>击杀{KillNum}次生物，立即攻击一次</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="0" t="n">
-        <v>12011300001</v>
+        <v>12011200001</v>
       </c>
       <c r="C125" s="0" t="n">
         <v>12</v>
@@ -8023,7 +8035,7 @@
       </c>
       <c r="L125" s="0" t="inlineStr">
         <is>
-          <t>4001:200&amp;</t>
+          <t>3001:100&amp;</t>
         </is>
       </c>
       <c r="T125" s="0" t="n">
@@ -8033,20 +8045,20 @@
         <v>0</v>
       </c>
       <c r="W125" s="0" t="n">
-        <v>12011300001</v>
+        <v>12011200001</v>
       </c>
       <c r="X125" s="0" t="n">
-        <v>12011300001</v>
+        <v>12011200001</v>
       </c>
       <c r="Y125" s="0" t="inlineStr">
         <is>
-          <t>造成{AttackDamage}点伤害，秒再攻击一次</t>
+          <t>受到{UnderAttackDamage}点伤害，秒再攻击一次</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="0" t="n">
-        <v>12012100001</v>
+        <v>12011300001</v>
       </c>
       <c r="C126" s="0" t="n">
         <v>12</v>
@@ -8056,24 +8068,18 @@
       </c>
       <c r="H126" s="0" t="inlineStr">
         <is>
-          <t>BuffEntityConditionalDemonLordMPRegain</t>
+          <t>BuffEntityConditionalAttackAgain</t>
         </is>
       </c>
       <c r="I126" s="0" t="inlineStr">
         <is>
-          <t>GameFightLogic_UnderAttack_Dead</t>
+          <t>GameFightLogic_UnderAttack</t>
         </is>
       </c>
       <c r="L126" s="0" t="inlineStr">
         <is>
-          <t>2001:1&amp;</t>
-        </is>
-      </c>
-      <c r="M126" s="0" t="n">
-        <v>20</v>
-      </c>
-      <c r="N126" s="0" t="n">
-        <v>10</v>
+          <t>4001:200&amp;</t>
+        </is>
       </c>
       <c r="T126" s="0" t="n">
         <v>0</v>
@@ -8082,20 +8088,20 @@
         <v>0</v>
       </c>
       <c r="W126" s="0" t="n">
-        <v>12012100001</v>
+        <v>12011300001</v>
       </c>
       <c r="X126" s="0" t="n">
-        <v>12012100001</v>
+        <v>12011300001</v>
       </c>
       <c r="Y126" s="0" t="inlineStr">
         <is>
-          <t>每击杀{KillNum}个生物，魔王回复{Value}点魔力</t>
+          <t>造成{AttackDamage}点伤害，秒再攻击一次</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" s="0" t="n">
-        <v>12012200001</v>
+        <v>12012100001</v>
       </c>
       <c r="C127" s="0" t="n">
         <v>12</v>
@@ -8110,12 +8116,12 @@
       </c>
       <c r="I127" s="0" t="inlineStr">
         <is>
-          <t>GameFightLogic_UnderAttack</t>
+          <t>GameFightLogic_UnderAttack_Dead</t>
         </is>
       </c>
       <c r="L127" s="0" t="inlineStr">
         <is>
-          <t>3001:100&amp;</t>
+          <t>2001:1&amp;</t>
         </is>
       </c>
       <c r="M127" s="0" t="n">
@@ -8131,40 +8137,47 @@
         <v>0</v>
       </c>
       <c r="W127" s="0" t="n">
-        <v>12012200001</v>
+        <v>12012100001</v>
       </c>
       <c r="X127" s="0" t="n">
-        <v>12012200001</v>
+        <v>12012100001</v>
       </c>
       <c r="Y127" s="0" t="inlineStr">
         <is>
-          <t>累计受到{UnderAttackDamage}点伤害，魔王回复{Value}点魔力</t>
+          <t>每击杀{KillNum}个生物，魔王回复{Value}点魔力</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" s="0" t="n">
-        <v>13000100001</v>
+        <v>12012200001</v>
       </c>
       <c r="C128" s="0" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D128" s="0" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H128" s="0" t="inlineStr">
         <is>
-          <t>BuffEntityPeriodicPickupCrystal</t>
+          <t>BuffEntityConditionalDemonLordMPRegain</t>
+        </is>
+      </c>
+      <c r="I128" s="0" t="inlineStr">
+        <is>
+          <t>GameFightLogic_UnderAttack</t>
+        </is>
+      </c>
+      <c r="L128" s="0" t="inlineStr">
+        <is>
+          <t>3001:100&amp;</t>
         </is>
       </c>
       <c r="M128" s="0" t="n">
-        <v>3</v>
+        <v>20</v>
       </c>
       <c r="N128" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="S128" s="0" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T128" s="0" t="n">
         <v>0</v>
@@ -8173,20 +8186,20 @@
         <v>0</v>
       </c>
       <c r="W128" s="0" t="n">
-        <v>13000100001</v>
+        <v>12012200001</v>
       </c>
       <c r="X128" s="0" t="n">
-        <v>13000100001</v>
+        <v>12012200001</v>
       </c>
       <c r="Y128" s="0" t="inlineStr">
         <is>
-          <t>每隔{Time_S}秒自动拾取附近魔晶</t>
+          <t>累计受到{UnderAttackDamage}点伤害，魔王回复{Value}点魔力</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" s="0" t="n">
-        <v>13000200001</v>
+        <v>13000100001</v>
       </c>
       <c r="C129" s="0" t="n">
         <v>13</v>
@@ -8196,13 +8209,17 @@
       </c>
       <c r="H129" s="0" t="inlineStr">
         <is>
-          <t>BuffEntityConditionalDeadRebirth</t>
-        </is>
-      </c>
-      <c r="I129" s="0" t="inlineStr">
-        <is>
-          <t>GameFightLogic_CreatureDeadEnd</t>
-        </is>
+          <t>BuffEntityPeriodicPickupCrystal</t>
+        </is>
+      </c>
+      <c r="M129" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="N129" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="S129" s="0" t="n">
+        <v>3</v>
       </c>
       <c r="T129" s="0" t="n">
         <v>0</v>
@@ -8210,24 +8227,21 @@
       <c r="U129" s="0" t="n">
         <v>0</v>
       </c>
-      <c r="V129" s="0" t="n">
-        <v>500001</v>
-      </c>
       <c r="W129" s="0" t="n">
-        <v>13000200001</v>
+        <v>13000100001</v>
       </c>
       <c r="X129" s="0" t="n">
-        <v>13000200001</v>
+        <v>13000100001</v>
       </c>
       <c r="Y129" s="0" t="inlineStr">
         <is>
-          <t>死亡后重生</t>
+          <t>每隔{Time_S}秒自动拾取附近魔晶</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" s="0" t="n">
-        <v>13000300001</v>
+        <v>13000200001</v>
       </c>
       <c r="C130" s="0" t="n">
         <v>13</v>
@@ -8237,7 +8251,7 @@
       </c>
       <c r="H130" s="0" t="inlineStr">
         <is>
-          <t>BuffEntityConditionalDeadAttack</t>
+          <t>BuffEntityConditionalDeadRebirth</t>
         </is>
       </c>
       <c r="I130" s="0" t="inlineStr">
@@ -8245,33 +8259,30 @@
           <t>GameFightLogic_CreatureDeadEnd</t>
         </is>
       </c>
-      <c r="J130" s="0" t="n">
-        <v>300001</v>
-      </c>
-      <c r="O130" s="0" t="n">
-        <v>1</v>
-      </c>
       <c r="T130" s="0" t="n">
         <v>0</v>
       </c>
       <c r="U130" s="0" t="n">
         <v>0</v>
       </c>
+      <c r="V130" s="0" t="n">
+        <v>500001</v>
+      </c>
       <c r="W130" s="0" t="n">
-        <v>13000300001</v>
+        <v>13000200001</v>
       </c>
       <c r="X130" s="0" t="n">
-        <v>13000300001</v>
+        <v>13000200001</v>
       </c>
       <c r="Y130" s="0" t="inlineStr">
         <is>
-          <t>死亡后爆炸</t>
+          <t>死亡后重生</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" s="0" t="n">
-        <v>13000400001</v>
+        <v>13000300001</v>
       </c>
       <c r="C131" s="0" t="n">
         <v>13</v>
@@ -8281,7 +8292,7 @@
       </c>
       <c r="H131" s="0" t="inlineStr">
         <is>
-          <t>BuffEntityConditionalDeadAreaHPChange</t>
+          <t>BuffEntityConditionalDeadAttack</t>
         </is>
       </c>
       <c r="I131" s="0" t="inlineStr">
@@ -8290,14 +8301,11 @@
         </is>
       </c>
       <c r="J131" s="0" t="n">
+        <v>300001</v>
+      </c>
+      <c r="O131" s="0" t="n">
         <v>1</v>
       </c>
-      <c r="O131" s="0" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="P131" s="0" t="n">
-        <v>0.01</v>
-      </c>
       <c r="T131" s="0" t="n">
         <v>0</v>
       </c>
@@ -8305,20 +8313,20 @@
         <v>0</v>
       </c>
       <c r="W131" s="0" t="n">
-        <v>13000400001</v>
+        <v>13000300001</v>
       </c>
       <c r="X131" s="0" t="n">
-        <v>13000400001</v>
+        <v>13000300001</v>
       </c>
       <c r="Y131" s="0" t="inlineStr">
         <is>
-          <t>死亡后恢复附近友军生命，恢复量:自身生命上限的{Percentage}%</t>
+          <t>死亡后爆炸</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" s="0" t="n">
-        <v>13000500001</v>
+        <v>13000400001</v>
       </c>
       <c r="C132" s="0" t="n">
         <v>13</v>
@@ -8328,7 +8336,7 @@
       </c>
       <c r="H132" s="0" t="inlineStr">
         <is>
-          <t>BuffEntityConditionalDeadAreaDRChange</t>
+          <t>BuffEntityConditionalDeadAreaHPChange</t>
         </is>
       </c>
       <c r="I132" s="0" t="inlineStr">
@@ -8352,20 +8360,20 @@
         <v>0</v>
       </c>
       <c r="W132" s="0" t="n">
-        <v>13000500001</v>
+        <v>13000400001</v>
       </c>
       <c r="X132" s="0" t="n">
-        <v>13000500001</v>
+        <v>13000400001</v>
       </c>
       <c r="Y132" s="0" t="inlineStr">
         <is>
-          <t>死亡后恢复附近友军护甲，恢复量:自身护甲上限的{Percentage}%</t>
+          <t>死亡后恢复附近友军生命，恢复量:自身生命上限的{Percentage}%</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" s="0" t="n">
-        <v>13000600001</v>
+        <v>13000500001</v>
       </c>
       <c r="C133" s="0" t="n">
         <v>13</v>
@@ -8375,7 +8383,7 @@
       </c>
       <c r="H133" s="0" t="inlineStr">
         <is>
-          <t>BuffEntityConditionalDeadCreateCrystal</t>
+          <t>BuffEntityConditionalDeadAreaDRChange</t>
         </is>
       </c>
       <c r="I133" s="0" t="inlineStr">
@@ -8383,8 +8391,14 @@
           <t>GameFightLogic_CreatureDeadEnd</t>
         </is>
       </c>
-      <c r="Q133" s="0" t="n">
-        <v>0.2</v>
+      <c r="J133" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="O133" s="0" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="P133" s="0" t="n">
+        <v>0.01</v>
       </c>
       <c r="T133" s="0" t="n">
         <v>0</v>
@@ -8393,70 +8407,39 @@
         <v>0</v>
       </c>
       <c r="W133" s="0" t="n">
-        <v>13000600001</v>
+        <v>13000500001</v>
       </c>
       <c r="X133" s="0" t="n">
-        <v>13000600001</v>
+        <v>13000500001</v>
       </c>
       <c r="Y133" s="0" t="inlineStr">
         <is>
-          <t>死亡后{Percentage}%生成魔晶</t>
+          <t>死亡后恢复附近友军护甲，恢复量:自身护甲上限的{Percentage}%</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" s="0" t="n">
-        <v>3000500001</v>
-      </c>
-      <c r="B134" s="0" t="inlineStr"/>
+        <v>13000600001</v>
+      </c>
       <c r="C134" s="0" t="n">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="D134" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="E134" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="F134" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="G134" s="0" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H134" s="0" t="inlineStr">
         <is>
-          <t>BuffEntityPeriodicAttackBoomerang</t>
-        </is>
-      </c>
-      <c r="I134" s="0" t="inlineStr"/>
-      <c r="J134" s="0" t="inlineStr">
-        <is>
-          <t>1,300051</t>
-        </is>
-      </c>
-      <c r="K134" s="0" t="inlineStr"/>
-      <c r="L134" s="0" t="inlineStr"/>
-      <c r="M134" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="N134" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="O134" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="P134" s="0" t="n">
-        <v>0</v>
+          <t>BuffEntityConditionalDeadCreateCrystal</t>
+        </is>
+      </c>
+      <c r="I134" s="0" t="inlineStr">
+        <is>
+          <t>GameFightLogic_CreatureDeadEnd</t>
+        </is>
       </c>
       <c r="Q134" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="R134" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="S134" s="0" t="n">
-        <v>5</v>
+        <v>0.2</v>
       </c>
       <c r="T134" s="0" t="n">
         <v>0</v>
@@ -8464,24 +8447,21 @@
       <c r="U134" s="0" t="n">
         <v>0</v>
       </c>
-      <c r="V134" s="0" t="n">
-        <v>0</v>
-      </c>
       <c r="W134" s="0" t="n">
-        <v>3000500001</v>
+        <v>13000600001</v>
       </c>
       <c r="X134" s="0" t="n">
-        <v>3000500001</v>
+        <v>13000600001</v>
       </c>
       <c r="Y134" s="0" t="inlineStr">
         <is>
-          <t>死亡回旋Lv1-每5秒发射1枚回旋镖,伤害=魔王攻击力,逐目标减半保底1</t>
+          <t>死亡后{Percentage}%生成魔晶</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" s="0" t="n">
-        <v>3000500002</v>
+        <v>3000500001</v>
       </c>
       <c r="B135" s="0" t="inlineStr"/>
       <c r="C135" s="0" t="n">
@@ -8507,7 +8487,7 @@
       <c r="I135" s="0" t="inlineStr"/>
       <c r="J135" s="0" t="inlineStr">
         <is>
-          <t>2,300051</t>
+          <t>1,300051</t>
         </is>
       </c>
       <c r="K135" s="0" t="inlineStr"/>
@@ -8550,13 +8530,13 @@
       </c>
       <c r="Y135" s="0" t="inlineStr">
         <is>
-          <t>死亡回旋Lv2-每5秒发射2枚回旋镖,伤害=魔王攻击力,逐目标减半保底1</t>
+          <t>死亡回旋Lv1-每5秒发射1枚回旋镖,伤害=魔王攻击力,逐目标减半保底1</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" s="0" t="n">
-        <v>3000500003</v>
+        <v>3000500002</v>
       </c>
       <c r="B136" s="0" t="inlineStr"/>
       <c r="C136" s="0" t="n">
@@ -8582,7 +8562,7 @@
       <c r="I136" s="0" t="inlineStr"/>
       <c r="J136" s="0" t="inlineStr">
         <is>
-          <t>3,300051</t>
+          <t>2,300051</t>
         </is>
       </c>
       <c r="K136" s="0" t="inlineStr"/>
@@ -8625,13 +8605,13 @@
       </c>
       <c r="Y136" s="0" t="inlineStr">
         <is>
-          <t>死亡回旋Lv3-每5秒发射3枚回旋镖,伤害=魔王攻击力,逐目标减半保底1</t>
+          <t>死亡回旋Lv2-每5秒发射2枚回旋镖,伤害=魔王攻击力,逐目标减半保底1</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" s="0" t="n">
-        <v>3000500004</v>
+        <v>3000500003</v>
       </c>
       <c r="B137" s="0" t="inlineStr"/>
       <c r="C137" s="0" t="n">
@@ -8657,7 +8637,7 @@
       <c r="I137" s="0" t="inlineStr"/>
       <c r="J137" s="0" t="inlineStr">
         <is>
-          <t>4,300051</t>
+          <t>3,300051</t>
         </is>
       </c>
       <c r="K137" s="0" t="inlineStr"/>
@@ -8700,13 +8680,13 @@
       </c>
       <c r="Y137" s="0" t="inlineStr">
         <is>
-          <t>死亡回旋Lv4-每5秒发射4枚回旋镖,伤害=魔王攻击力,逐目标减半保底1</t>
+          <t>死亡回旋Lv3-每5秒发射3枚回旋镖,伤害=魔王攻击力,逐目标减半保底1</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" s="0" t="n">
-        <v>3000500005</v>
+        <v>3000500004</v>
       </c>
       <c r="B138" s="0" t="inlineStr"/>
       <c r="C138" s="0" t="n">
@@ -8732,7 +8712,7 @@
       <c r="I138" s="0" t="inlineStr"/>
       <c r="J138" s="0" t="inlineStr">
         <is>
-          <t>5,300051</t>
+          <t>4,300051</t>
         </is>
       </c>
       <c r="K138" s="0" t="inlineStr"/>
@@ -8775,54 +8755,88 @@
       </c>
       <c r="Y138" s="0" t="inlineStr">
         <is>
-          <t>死亡回旋Lv5-每5秒发射5枚回旋镖,伤害=魔王攻击力,逐目标减半保底1</t>
+          <t>死亡回旋Lv4-每5秒发射4枚回旋镖,伤害=魔王攻击力,逐目标减半保底1</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" s="0" t="n">
-        <v>13000700001</v>
-      </c>
+        <v>3000500005</v>
+      </c>
+      <c r="B139" s="0" t="inlineStr"/>
       <c r="C139" s="0" t="n">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="D139" s="0" t="n">
-        <v>4</v>
+        <v>0</v>
+      </c>
+      <c r="E139" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="F139" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="G139" s="0" t="n">
+        <v>2</v>
       </c>
       <c r="H139" s="0" t="inlineStr">
         <is>
-          <t>BuffEntityConditionalThorns</t>
-        </is>
-      </c>
-      <c r="I139" s="0" t="inlineStr">
-        <is>
-          <t>GameFightLogic_UnderAttack</t>
-        </is>
+          <t>BuffEntityPeriodicAttackBoomerang</t>
+        </is>
+      </c>
+      <c r="I139" s="0" t="inlineStr"/>
+      <c r="J139" s="0" t="inlineStr">
+        <is>
+          <t>5,300051</t>
+        </is>
+      </c>
+      <c r="K139" s="0" t="inlineStr"/>
+      <c r="L139" s="0" t="inlineStr"/>
+      <c r="M139" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="N139" s="0" t="n">
+        <v>0</v>
       </c>
       <c r="O139" s="0" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="P139" s="0" t="n">
-        <v>0.1</v>
+        <v>0</v>
+      </c>
+      <c r="Q139" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="R139" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="S139" s="0" t="n">
+        <v>5</v>
       </c>
       <c r="T139" s="0" t="n">
         <v>0</v>
       </c>
+      <c r="U139" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="V139" s="0" t="n">
+        <v>0</v>
+      </c>
       <c r="W139" s="0" t="n">
-        <v>13000700001</v>
+        <v>3000500001</v>
       </c>
       <c r="X139" s="0" t="n">
-        <v>13000700001</v>
+        <v>3000500001</v>
       </c>
       <c r="Y139" s="0" t="inlineStr">
         <is>
-          <t>受到攻击时，反弹承伤的{Percentage}%给攻击者（上限为自身当前生命值）</t>
+          <t>死亡回旋Lv5-每5秒发射5枚回旋镖,伤害=魔王攻击力,逐目标减半保底1</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" s="0" t="n">
-        <v>13000800001</v>
+        <v>13000700001</v>
       </c>
       <c r="C140" s="0" t="n">
         <v>13</v>
@@ -8832,7 +8846,7 @@
       </c>
       <c r="H140" s="0" t="inlineStr">
         <is>
-          <t>BuffEntityConditionalLifeSteal</t>
+          <t>BuffEntityConditionalThorns</t>
         </is>
       </c>
       <c r="I140" s="0" t="inlineStr">
@@ -8850,20 +8864,20 @@
         <v>0</v>
       </c>
       <c r="W140" s="0" t="n">
-        <v>13000800001</v>
+        <v>13000700001</v>
       </c>
       <c r="X140" s="0" t="n">
-        <v>13000800001</v>
+        <v>13000700001</v>
       </c>
       <c r="Y140" s="0" t="inlineStr">
         <is>
-          <t>造成伤害的{Percentage}%转化为自身生命</t>
+          <t>受到攻击时，反弹承伤的{Percentage}%给攻击者（上限为自身当前生命值）</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" s="0" t="n">
-        <v>13000900001</v>
+        <v>13000800001</v>
       </c>
       <c r="C141" s="0" t="n">
         <v>13</v>
@@ -8873,97 +8887,79 @@
       </c>
       <c r="H141" s="0" t="inlineStr">
         <is>
-          <t>BuffEntityConditionalInvincible</t>
-        </is>
-      </c>
-      <c r="K141" s="0" t="inlineStr">
-        <is>
-          <t>#FFD700</t>
-        </is>
-      </c>
-      <c r="M141" s="0" t="n">
-        <v>10</v>
-      </c>
-      <c r="N141" s="0" t="n">
-        <v>5</v>
+          <t>BuffEntityConditionalLifeSteal</t>
+        </is>
+      </c>
+      <c r="I141" s="0" t="inlineStr">
+        <is>
+          <t>GameFightLogic_UnderAttack</t>
+        </is>
+      </c>
+      <c r="O141" s="0" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="P141" s="0" t="n">
+        <v>0.1</v>
       </c>
       <c r="T141" s="0" t="n">
         <v>0</v>
       </c>
       <c r="W141" s="0" t="n">
-        <v>13000900001</v>
+        <v>13000800001</v>
       </c>
       <c r="X141" s="0" t="n">
-        <v>13000900001</v>
+        <v>13000800001</v>
       </c>
       <c r="Y141" s="0" t="inlineStr">
         <is>
-          <t>上场后无敌{Value}秒，期间身体变为金色</t>
+          <t>造成伤害的{Percentage}%转化为自身生命</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" s="0" t="n">
-        <v>11001300001</v>
+        <v>13000900001</v>
       </c>
       <c r="C142" s="0" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="D142" s="0" t="n">
-        <v>2</v>
-      </c>
-      <c r="G142" s="0" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H142" s="0" t="inlineStr">
         <is>
-          <t>BuffEntityAttributeDecayByAllyCount</t>
-        </is>
-      </c>
-      <c r="J142" s="0" t="inlineStr">
-        <is>
-          <t>ATK</t>
+          <t>BuffEntityConditionalInvincible</t>
+        </is>
+      </c>
+      <c r="K142" s="0" t="inlineStr">
+        <is>
+          <t>#FFD700</t>
         </is>
       </c>
       <c r="M142" s="0" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="N142" s="0" t="n">
-        <v>50</v>
-      </c>
-      <c r="O142" s="0" t="n">
-        <v>3</v>
-      </c>
-      <c r="P142" s="0" t="n">
-        <v>3</v>
-      </c>
-      <c r="Q142" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="R142" s="0" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="T142" s="0" t="n">
         <v>0</v>
       </c>
-      <c r="U142" s="0" t="n">
-        <v>0</v>
-      </c>
       <c r="W142" s="0" t="n">
-        <v>11001300001</v>
+        <v>13000900001</v>
       </c>
       <c r="X142" s="0" t="n">
-        <v>11001300001</v>
+        <v>13000900001</v>
       </c>
       <c r="Y142" s="0" t="inlineStr">
         <is>
-          <t>独行者-A</t>
+          <t>上场后无敌{Value}秒，期间身体变为金色</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" s="0" t="n">
-        <v>11001300002</v>
+        <v>11001300001</v>
       </c>
       <c r="C143" s="0" t="n">
         <v>11</v>
@@ -8981,7 +8977,7 @@
       </c>
       <c r="J143" s="0" t="inlineStr">
         <is>
-          <t>ASPD</t>
+          <t>ATK</t>
         </is>
       </c>
       <c r="M143" s="0" t="n">
@@ -9009,20 +9005,20 @@
         <v>0</v>
       </c>
       <c r="W143" s="0" t="n">
-        <v>11001300002</v>
+        <v>11001300001</v>
       </c>
       <c r="X143" s="0" t="n">
-        <v>11001300002</v>
+        <v>11001300001</v>
       </c>
       <c r="Y143" s="0" t="inlineStr">
         <is>
-          <t>独行者-B</t>
+          <t>独行者-A</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" s="0" t="n">
-        <v>11001300003</v>
+        <v>11001300002</v>
       </c>
       <c r="C144" s="0" t="n">
         <v>11</v>
@@ -9040,7 +9036,7 @@
       </c>
       <c r="J144" s="0" t="inlineStr">
         <is>
-          <t>DR</t>
+          <t>ASPD</t>
         </is>
       </c>
       <c r="M144" s="0" t="n">
@@ -9068,20 +9064,20 @@
         <v>0</v>
       </c>
       <c r="W144" s="0" t="n">
-        <v>11001300003</v>
+        <v>11001300002</v>
       </c>
       <c r="X144" s="0" t="n">
-        <v>11001300003</v>
+        <v>11001300002</v>
       </c>
       <c r="Y144" s="0" t="inlineStr">
         <is>
-          <t>独行者-C</t>
+          <t>独行者-B</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" s="0" t="n">
-        <v>11001300004</v>
+        <v>11001300003</v>
       </c>
       <c r="C145" s="0" t="n">
         <v>11</v>
@@ -9099,7 +9095,7 @@
       </c>
       <c r="J145" s="0" t="inlineStr">
         <is>
-          <t>HP</t>
+          <t>DR</t>
         </is>
       </c>
       <c r="M145" s="0" t="n">
@@ -9127,12 +9123,71 @@
         <v>0</v>
       </c>
       <c r="W145" s="0" t="n">
+        <v>11001300003</v>
+      </c>
+      <c r="X145" s="0" t="n">
+        <v>11001300003</v>
+      </c>
+      <c r="Y145" s="0" t="inlineStr">
+        <is>
+          <t>独行者-C</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" s="0" t="n">
         <v>11001300004</v>
       </c>
-      <c r="X145" s="0" t="n">
+      <c r="C146" s="0" t="n">
+        <v>11</v>
+      </c>
+      <c r="D146" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="G146" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="H146" s="0" t="inlineStr">
+        <is>
+          <t>BuffEntityAttributeDecayByAllyCount</t>
+        </is>
+      </c>
+      <c r="J146" s="0" t="inlineStr">
+        <is>
+          <t>HP</t>
+        </is>
+      </c>
+      <c r="M146" s="0" t="n">
+        <v>50</v>
+      </c>
+      <c r="N146" s="0" t="n">
+        <v>50</v>
+      </c>
+      <c r="O146" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="P146" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q146" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="R146" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="T146" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="U146" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="W146" s="0" t="n">
         <v>11001300004</v>
       </c>
-      <c r="Y145" s="0" t="inlineStr">
+      <c r="X146" s="0" t="n">
+        <v>11001300004</v>
+      </c>
+      <c r="Y146" s="0" t="inlineStr">
         <is>
           <t>独行者-D</t>
         </is>

--- a/Demon Lord Roguelike/Assets/Data/Excel/excel_buff_info[buff信息].xlsx
+++ b/Demon Lord Roguelike/Assets/Data/Excel/excel_buff_info[buff信息].xlsx
@@ -6857,7 +6857,7 @@
         <v>0</v>
       </c>
       <c r="V101" s="0" t="n">
-        <v>500002</v>
+        <v>500001</v>
       </c>
       <c r="W101" s="0" t="n">
         <v>12000200001</v>

--- a/Demon Lord Roguelike/Assets/Data/Excel/excel_buff_info[buff信息].xlsx
+++ b/Demon Lord Roguelike/Assets/Data/Excel/excel_buff_info[buff信息].xlsx
@@ -1137,7 +1137,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y146"/>
+  <dimension ref="A1:Y148"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col width="24.25" customWidth="1" style="3" min="1" max="1"/>
@@ -2284,7 +2284,7 @@
       <c r="M18" s="2" t="n"/>
       <c r="N18" s="2" t="n"/>
       <c r="O18" s="2" t="n">
-        <v>-0.5</v>
+        <v>1</v>
       </c>
       <c r="P18" s="2" t="n"/>
       <c r="Q18" s="2" t="n"/>
@@ -9193,6 +9193,88 @@
         </is>
       </c>
     </row>
+    <row r="147">
+      <c r="A147" s="0" t="n">
+        <v>2000100003</v>
+      </c>
+      <c r="C147" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="D147" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="H147" s="0" t="inlineStr">
+        <is>
+          <t>BuffEntityAttribute</t>
+        </is>
+      </c>
+      <c r="J147" s="0" t="inlineStr">
+        <is>
+          <t>EVA</t>
+        </is>
+      </c>
+      <c r="O147" s="0" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="T147" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="U147" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="W147" s="0" t="n">
+        <v>2000100003</v>
+      </c>
+      <c r="X147" s="0" t="n">
+        <v>2000100003</v>
+      </c>
+      <c r="Y147" s="0" t="inlineStr">
+        <is>
+          <t>闪避20%</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" s="0" t="n">
+        <v>2000200002</v>
+      </c>
+      <c r="C148" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="D148" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="H148" s="0" t="inlineStr">
+        <is>
+          <t>BuffEntityAttribute</t>
+        </is>
+      </c>
+      <c r="J148" s="0" t="inlineStr">
+        <is>
+          <t>CRT</t>
+        </is>
+      </c>
+      <c r="O148" s="0" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="T148" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="U148" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="W148" s="0" t="n">
+        <v>2000200002</v>
+      </c>
+      <c r="X148" s="0" t="n">
+        <v>2000200002</v>
+      </c>
+      <c r="Y148" s="0" t="inlineStr">
+        <is>
+          <t>暴击20%</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" paperSize="9"/>

--- a/Demon Lord Roguelike/Assets/Data/Excel/excel_buff_info[buff信息].xlsx
+++ b/Demon Lord Roguelike/Assets/Data/Excel/excel_buff_info[buff信息].xlsx
@@ -1137,7 +1137,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y148"/>
+  <dimension ref="A1:Y147"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col width="24.25" customWidth="1" style="3" min="1" max="1"/>
@@ -2311,7 +2311,7 @@
     </row>
     <row r="19">
       <c r="A19" s="0" t="n">
-        <v>2000600001</v>
+        <v>2000700001</v>
       </c>
       <c r="C19" s="0" t="n">
         <v>2</v>
@@ -2321,79 +2321,72 @@
       </c>
       <c r="H19" s="0" t="inlineStr">
         <is>
-          <t>BuffEntityPeriodicShieldCast</t>
+          <t>BuffEntityConditionalShieldTransfer</t>
         </is>
       </c>
       <c r="J19" s="0" t="inlineStr">
         <is>
-          <t>3,2000700001</t>
-        </is>
+          <t>500004,0.6,0.5</t>
+        </is>
+      </c>
+      <c r="M19" s="0" t="n">
+        <v>9</v>
       </c>
       <c r="R19" s="0" t="n">
         <v>0</v>
       </c>
-      <c r="S19" s="0" t="n">
-        <v>10</v>
-      </c>
       <c r="T19" s="0" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="W19" s="0" t="n">
-        <v>2000600001</v>
+        <v>2000700001</v>
       </c>
       <c r="X19" s="0" t="n">
-        <v>2000600001</v>
+        <v>2000700001</v>
       </c>
       <c r="Y19" s="0" t="inlineStr">
         <is>
-          <t>大盾战士BOSS-每10秒给最前排3个友军套伤害转移护盾（护盾持续5秒）</t>
+          <t>伤害转移护盾-9秒内目标只承受50%伤害，其余50%转移给施加者（比例=class_entity_data第3项0~1，大盾战士援护护盾，堆叠策略须为Ignore）</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="0" t="n">
-        <v>2000700001</v>
+        <v>3000100001</v>
       </c>
       <c r="C20" s="0" t="n">
-        <v>2</v>
-      </c>
-      <c r="G20" s="0" t="n">
-        <v>2</v>
-      </c>
-      <c r="H20" s="0" t="inlineStr">
-        <is>
-          <t>BuffEntityConditionalShieldTransfer</t>
-        </is>
-      </c>
-      <c r="J20" s="0" t="inlineStr">
-        <is>
-          <t>500004,0.6</t>
-        </is>
-      </c>
-      <c r="M20" s="0" t="n">
-        <v>9</v>
-      </c>
-      <c r="R20" s="0" t="n">
-        <v>0</v>
-      </c>
+        <v>3</v>
+      </c>
+      <c r="D20" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="H20" s="7" t="inlineStr">
+        <is>
+          <t>BuffEntityInstantCloneDefenseCreature</t>
+        </is>
+      </c>
+      <c r="I20" s="7" t="n"/>
       <c r="T20" s="0" t="n">
-        <v>3</v>
+        <v>0</v>
+      </c>
+      <c r="U20" s="0" t="n">
+        <v>0</v>
       </c>
       <c r="W20" s="0" t="n">
-        <v>2000700001</v>
+        <v>3000100001</v>
       </c>
       <c r="X20" s="0" t="n">
-        <v>2000700001</v>
+        <v>3000100001</v>
       </c>
       <c r="Y20" s="0" t="inlineStr">
         <is>
-          <t>伤害转移护盾-9秒内目标零承伤，伤害转移给施加者（大盾战士BOSS援护护盾，堆叠策略须为Ignore）</t>
+          <t>增殖-随机复制一个已有的魔物</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="0" t="n">
-        <v>3000100001</v>
+        <v>3000200001</v>
       </c>
       <c r="C21" s="0" t="n">
         <v>3</v>
@@ -2401,12 +2394,25 @@
       <c r="D21" s="0" t="n">
         <v>1</v>
       </c>
+      <c r="E21" s="0" t="n">
+        <v>3000200001</v>
+      </c>
+      <c r="F21" s="0" t="n">
+        <v>1</v>
+      </c>
       <c r="H21" s="7" t="inlineStr">
         <is>
-          <t>BuffEntityInstantCloneDefenseCreature</t>
-        </is>
-      </c>
-      <c r="I21" s="7" t="n"/>
+          <t>BuffEntityConditionalAddDropCrystal</t>
+        </is>
+      </c>
+      <c r="I21" s="0" t="inlineStr">
+        <is>
+          <t>GameFightLogic_CreatureDeadDropCrystal</t>
+        </is>
+      </c>
+      <c r="Q21" s="0" t="n">
+        <v>0.2</v>
+      </c>
       <c r="T21" s="0" t="n">
         <v>0</v>
       </c>
@@ -2414,20 +2420,20 @@
         <v>0</v>
       </c>
       <c r="W21" s="0" t="n">
-        <v>3000100001</v>
+        <v>3000200001</v>
       </c>
       <c r="X21" s="0" t="n">
-        <v>3000100001</v>
+        <v>3000200001</v>
       </c>
       <c r="Y21" s="0" t="inlineStr">
         <is>
-          <t>增殖-随机复制一个已有的魔物</t>
+          <t>钱多多LV1-每一次击杀有20%的概率多掉落一次魔晶</t>
         </is>
       </c>
     </row>
     <row r="22" ht="15" customHeight="1" s="3">
       <c r="A22" s="0" t="n">
-        <v>3000200001</v>
+        <v>3000200002</v>
       </c>
       <c r="C22" s="0" t="n">
         <v>3</v>
@@ -2436,10 +2442,10 @@
         <v>1</v>
       </c>
       <c r="E22" s="0" t="n">
-        <v>3000200001</v>
+        <v>3000200002</v>
       </c>
       <c r="F22" s="0" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H22" s="7" t="inlineStr">
         <is>
@@ -2452,7 +2458,7 @@
         </is>
       </c>
       <c r="Q22" s="0" t="n">
-        <v>0.2</v>
+        <v>0.4</v>
       </c>
       <c r="T22" s="0" t="n">
         <v>0</v>
@@ -2468,13 +2474,13 @@
       </c>
       <c r="Y22" s="0" t="inlineStr">
         <is>
-          <t>钱多多LV1-每一次击杀有20%的概率多掉落一次魔晶</t>
+          <t>钱多多LV2-每一次击杀有40%的概率多掉落一次魔晶</t>
         </is>
       </c>
     </row>
     <row r="23" ht="15" customHeight="1" s="3">
       <c r="A23" s="0" t="n">
-        <v>3000200002</v>
+        <v>3000200003</v>
       </c>
       <c r="C23" s="0" t="n">
         <v>3</v>
@@ -2483,10 +2489,10 @@
         <v>1</v>
       </c>
       <c r="E23" s="0" t="n">
-        <v>3000200002</v>
+        <v>3000200003</v>
       </c>
       <c r="F23" s="0" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H23" s="7" t="inlineStr">
         <is>
@@ -2499,7 +2505,7 @@
         </is>
       </c>
       <c r="Q23" s="0" t="n">
-        <v>0.4</v>
+        <v>0.6</v>
       </c>
       <c r="T23" s="0" t="n">
         <v>0</v>
@@ -2515,13 +2521,13 @@
       </c>
       <c r="Y23" s="0" t="inlineStr">
         <is>
-          <t>钱多多LV2-每一次击杀有40%的概率多掉落一次魔晶</t>
+          <t>钱多多LV3-每一次击杀有60%的概率多掉落一次魔晶</t>
         </is>
       </c>
     </row>
     <row r="24" ht="15" customHeight="1" s="3">
       <c r="A24" s="0" t="n">
-        <v>3000200003</v>
+        <v>3000200004</v>
       </c>
       <c r="C24" s="0" t="n">
         <v>3</v>
@@ -2533,7 +2539,7 @@
         <v>3000200003</v>
       </c>
       <c r="F24" s="0" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H24" s="7" t="inlineStr">
         <is>
@@ -2546,7 +2552,7 @@
         </is>
       </c>
       <c r="Q24" s="0" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="T24" s="0" t="n">
         <v>0</v>
@@ -2562,13 +2568,13 @@
       </c>
       <c r="Y24" s="0" t="inlineStr">
         <is>
-          <t>钱多多LV3-每一次击杀有60%的概率多掉落一次魔晶</t>
+          <t>钱多多LV4-每一次击杀有80%的概率多掉落一次魔晶</t>
         </is>
       </c>
     </row>
     <row r="25" ht="15" customHeight="1" s="3">
       <c r="A25" s="0" t="n">
-        <v>3000200004</v>
+        <v>3000200005</v>
       </c>
       <c r="C25" s="0" t="n">
         <v>3</v>
@@ -2580,7 +2586,7 @@
         <v>3000200003</v>
       </c>
       <c r="F25" s="0" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H25" s="7" t="inlineStr">
         <is>
@@ -2593,7 +2599,7 @@
         </is>
       </c>
       <c r="Q25" s="0" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="T25" s="0" t="n">
         <v>0</v>
@@ -2609,60 +2615,60 @@
       </c>
       <c r="Y25" s="0" t="inlineStr">
         <is>
-          <t>钱多多LV4-每一次击杀有80%的概率多掉落一次魔晶</t>
+          <t>钱多多LV5-每一次击杀有100%的概率多掉落一次魔晶</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="0" t="n">
-        <v>3000200005</v>
+        <v>3000300001</v>
       </c>
       <c r="C26" s="0" t="n">
         <v>3</v>
       </c>
-      <c r="D26" s="0" t="n">
+      <c r="G26" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="H26" s="0" t="inlineStr">
+        <is>
+          <t>BuffEntityPeriodicAttackMultiInstant</t>
+        </is>
+      </c>
+      <c r="J26" s="0" t="inlineStr">
+        <is>
+          <t>1,300031</t>
+        </is>
+      </c>
+      <c r="M26" s="0" t="n">
         <v>1</v>
       </c>
-      <c r="E26" s="0" t="n">
-        <v>3000200003</v>
-      </c>
-      <c r="F26" s="0" t="n">
-        <v>5</v>
-      </c>
-      <c r="H26" s="7" t="inlineStr">
-        <is>
-          <t>BuffEntityConditionalAddDropCrystal</t>
-        </is>
-      </c>
-      <c r="I26" s="0" t="inlineStr">
-        <is>
-          <t>GameFightLogic_CreatureDeadDropCrystal</t>
-        </is>
-      </c>
       <c r="Q26" s="0" t="n">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="R26" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="S26" s="0" t="n">
+        <v>3</v>
       </c>
       <c r="T26" s="0" t="n">
         <v>0</v>
       </c>
-      <c r="U26" s="0" t="n">
-        <v>0</v>
-      </c>
       <c r="W26" s="0" t="n">
-        <v>3000200001</v>
+        <v>3000300001</v>
       </c>
       <c r="X26" s="0" t="n">
-        <v>3000200001</v>
+        <v>3000300001</v>
       </c>
       <c r="Y26" s="0" t="inlineStr">
         <is>
-          <t>钱多多LV5-每一次击杀有100%的概率多掉落一次魔晶</t>
+          <t>闪电Lv1-每3秒1道落雷,范围0.2,单雷最多命中1个目标,伤害=魔王攻击力</t>
         </is>
       </c>
     </row>
     <row r="27" ht="15" customHeight="1" s="3">
       <c r="A27" s="0" t="n">
-        <v>3000300001</v>
+        <v>3000300002</v>
       </c>
       <c r="C27" s="0" t="n">
         <v>3</v>
@@ -2677,7 +2683,7 @@
       </c>
       <c r="J27" s="0" t="inlineStr">
         <is>
-          <t>1,300031</t>
+          <t>2,300032</t>
         </is>
       </c>
       <c r="M27" s="0" t="n">
@@ -2703,13 +2709,13 @@
       </c>
       <c r="Y27" s="0" t="inlineStr">
         <is>
-          <t>闪电Lv1-每3秒1道落雷,范围0.2,单雷最多命中1个目标,伤害=魔王攻击力</t>
+          <t>闪电Lv2-每3秒2道落雷,范围0.4,单雷最多命中2个目标,伤害=魔王攻击力</t>
         </is>
       </c>
     </row>
     <row r="28" ht="15" customHeight="1" s="3">
       <c r="A28" s="0" t="n">
-        <v>3000300002</v>
+        <v>3000300003</v>
       </c>
       <c r="C28" s="0" t="n">
         <v>3</v>
@@ -2724,7 +2730,7 @@
       </c>
       <c r="J28" s="0" t="inlineStr">
         <is>
-          <t>2,300032</t>
+          <t>3,300033</t>
         </is>
       </c>
       <c r="M28" s="0" t="n">
@@ -2750,13 +2756,13 @@
       </c>
       <c r="Y28" s="0" t="inlineStr">
         <is>
-          <t>闪电Lv2-每3秒2道落雷,范围0.4,单雷最多命中2个目标,伤害=魔王攻击力</t>
+          <t>闪电Lv3-每3秒3道落雷,范围0.6,单雷最多命中3个目标,伤害=魔王攻击力</t>
         </is>
       </c>
     </row>
     <row r="29" ht="15" customHeight="1" s="3">
       <c r="A29" s="0" t="n">
-        <v>3000300003</v>
+        <v>3000300004</v>
       </c>
       <c r="C29" s="0" t="n">
         <v>3</v>
@@ -2771,7 +2777,7 @@
       </c>
       <c r="J29" s="0" t="inlineStr">
         <is>
-          <t>3,300033</t>
+          <t>4,300034</t>
         </is>
       </c>
       <c r="M29" s="0" t="n">
@@ -2797,13 +2803,13 @@
       </c>
       <c r="Y29" s="0" t="inlineStr">
         <is>
-          <t>闪电Lv3-每3秒3道落雷,范围0.6,单雷最多命中3个目标,伤害=魔王攻击力</t>
+          <t>闪电Lv4-每3秒4道落雷,范围0.8,单雷最多命中4个目标,伤害=魔王攻击力</t>
         </is>
       </c>
     </row>
     <row r="30" ht="15" customHeight="1" s="3">
       <c r="A30" s="0" t="n">
-        <v>3000300004</v>
+        <v>3000300005</v>
       </c>
       <c r="C30" s="0" t="n">
         <v>3</v>
@@ -2818,7 +2824,7 @@
       </c>
       <c r="J30" s="0" t="inlineStr">
         <is>
-          <t>4,300034</t>
+          <t>5,300035</t>
         </is>
       </c>
       <c r="M30" s="0" t="n">
@@ -2844,13 +2850,13 @@
       </c>
       <c r="Y30" s="0" t="inlineStr">
         <is>
-          <t>闪电Lv4-每3秒4道落雷,范围0.8,单雷最多命中4个目标,伤害=魔王攻击力</t>
+          <t>闪电Lv5-每3秒5道落雷,范围1,单雷最多命中5个目标,伤害=魔王攻击力</t>
         </is>
       </c>
     </row>
     <row r="31" customFormat="1" s="2">
       <c r="A31" s="0" t="n">
-        <v>3000300005</v>
+        <v>3000400001</v>
       </c>
       <c r="C31" s="0" t="n">
         <v>3</v>
@@ -2860,12 +2866,12 @@
       </c>
       <c r="H31" s="0" t="inlineStr">
         <is>
-          <t>BuffEntityPeriodicAttackMultiInstant</t>
+          <t>BuffEntityPeriodicAttackRoad</t>
         </is>
       </c>
       <c r="J31" s="0" t="inlineStr">
         <is>
-          <t>5,300035</t>
+          <t>1,300041</t>
         </is>
       </c>
       <c r="M31" s="0" t="n">
@@ -2878,26 +2884,26 @@
         <v>0</v>
       </c>
       <c r="S31" s="0" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T31" s="0" t="n">
         <v>0</v>
       </c>
       <c r="W31" s="0" t="n">
-        <v>3000300001</v>
+        <v>3000400001</v>
       </c>
       <c r="X31" s="0" t="n">
-        <v>3000300001</v>
+        <v>3000400001</v>
       </c>
       <c r="Y31" s="0" t="inlineStr">
         <is>
-          <t>闪电Lv5-每3秒5道落雷,范围1,单雷最多命中5个目标,伤害=魔王攻击力</t>
+          <t>失控的矿车Lv1-每5秒随机1条道路各出1辆矿车，第1个目标伤害=魔王攻击力，之后每撞1个减半</t>
         </is>
       </c>
     </row>
     <row r="32" customFormat="1" s="2">
       <c r="A32" s="0" t="n">
-        <v>3000400001</v>
+        <v>3000400002</v>
       </c>
       <c r="C32" s="0" t="n">
         <v>3</v>
@@ -2912,7 +2918,7 @@
       </c>
       <c r="J32" s="0" t="inlineStr">
         <is>
-          <t>1,300041</t>
+          <t>2,300041</t>
         </is>
       </c>
       <c r="M32" s="0" t="n">
@@ -2938,13 +2944,13 @@
       </c>
       <c r="Y32" s="0" t="inlineStr">
         <is>
-          <t>失控的矿车Lv1-每5秒随机1条道路各出1辆矿车，第1个目标伤害=魔王攻击力，之后每撞1个减半</t>
+          <t>失控的矿车Lv2-每5秒随机2条道路各出1辆矿车，第1个目标伤害=魔王攻击力，之后每撞1个减半</t>
         </is>
       </c>
     </row>
     <row r="33" customFormat="1" s="2">
       <c r="A33" s="0" t="n">
-        <v>3000400002</v>
+        <v>3000400003</v>
       </c>
       <c r="C33" s="0" t="n">
         <v>3</v>
@@ -2959,7 +2965,7 @@
       </c>
       <c r="J33" s="0" t="inlineStr">
         <is>
-          <t>2,300041</t>
+          <t>3,300041</t>
         </is>
       </c>
       <c r="M33" s="0" t="n">
@@ -2985,13 +2991,13 @@
       </c>
       <c r="Y33" s="0" t="inlineStr">
         <is>
-          <t>失控的矿车Lv2-每5秒随机2条道路各出1辆矿车，第1个目标伤害=魔王攻击力，之后每撞1个减半</t>
+          <t>失控的矿车Lv3-每5秒随机3条道路各出1辆矿车，第1个目标伤害=魔王攻击力，之后每撞1个减半</t>
         </is>
       </c>
     </row>
     <row r="34" ht="13" customHeight="1" s="3">
       <c r="A34" s="0" t="n">
-        <v>3000400003</v>
+        <v>3000400004</v>
       </c>
       <c r="C34" s="0" t="n">
         <v>3</v>
@@ -3006,7 +3012,7 @@
       </c>
       <c r="J34" s="0" t="inlineStr">
         <is>
-          <t>3,300041</t>
+          <t>4,300041</t>
         </is>
       </c>
       <c r="M34" s="0" t="n">
@@ -3032,13 +3038,13 @@
       </c>
       <c r="Y34" s="0" t="inlineStr">
         <is>
-          <t>失控的矿车Lv3-每5秒随机3条道路各出1辆矿车，第1个目标伤害=魔王攻击力，之后每撞1个减半</t>
+          <t>失控的矿车Lv4-每5秒随机4条道路各出1辆矿车，第1个目标伤害=魔王攻击力，之后每撞1个减半</t>
         </is>
       </c>
     </row>
     <row r="35" ht="14.25" customHeight="1" s="3">
       <c r="A35" s="0" t="n">
-        <v>3000400004</v>
+        <v>3000400005</v>
       </c>
       <c r="C35" s="0" t="n">
         <v>3</v>
@@ -3053,7 +3059,7 @@
       </c>
       <c r="J35" s="0" t="inlineStr">
         <is>
-          <t>4,300041</t>
+          <t>5,300041</t>
         </is>
       </c>
       <c r="M35" s="0" t="n">
@@ -3079,33 +3085,51 @@
       </c>
       <c r="Y35" s="0" t="inlineStr">
         <is>
-          <t>失控的矿车Lv4-每5秒随机4条道路各出1辆矿车，第1个目标伤害=魔王攻击力，之后每撞1个减半</t>
+          <t>失控的矿车Lv5-每5秒随机5条道路各出1辆矿车，第1个目标伤害=魔王攻击力，之后每撞1个减半</t>
         </is>
       </c>
     </row>
     <row r="36" ht="14.25" customHeight="1" s="3">
       <c r="A36" s="0" t="n">
-        <v>3000400005</v>
+        <v>3000600001</v>
       </c>
       <c r="C36" s="0" t="n">
         <v>3</v>
+      </c>
+      <c r="D36" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="E36" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="F36" s="0" t="n">
+        <v>0</v>
       </c>
       <c r="G36" s="0" t="n">
         <v>2</v>
       </c>
       <c r="H36" s="0" t="inlineStr">
         <is>
-          <t>BuffEntityPeriodicAttackRoad</t>
+          <t>BuffEntityPeriodicAttackBounceAxe</t>
         </is>
       </c>
       <c r="J36" s="0" t="inlineStr">
         <is>
-          <t>5,300041</t>
+          <t>1,300061,1</t>
         </is>
       </c>
       <c r="M36" s="0" t="n">
         <v>1</v>
       </c>
+      <c r="N36" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="O36" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="P36" s="0" t="n">
+        <v>0</v>
+      </c>
       <c r="Q36" s="0" t="n">
         <v>0</v>
       </c>
@@ -3118,21 +3142,27 @@
       <c r="T36" s="0" t="n">
         <v>0</v>
       </c>
+      <c r="U36" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="V36" s="0" t="n">
+        <v>0</v>
+      </c>
       <c r="W36" s="0" t="n">
-        <v>3000400001</v>
+        <v>3000600001</v>
       </c>
       <c r="X36" s="0" t="n">
-        <v>3000400001</v>
+        <v>3000600001</v>
       </c>
       <c r="Y36" s="0" t="inlineStr">
         <is>
-          <t>失控的矿车Lv5-每5秒随机5条道路各出1辆矿车，第1个目标伤害=魔王攻击力，之后每撞1个减半</t>
+          <t>跳跳斧Lv1-每5秒扔出1把斧头,伤害=魔王攻击力,命中后弹跳1次,伤害逐目标减半保底1</t>
         </is>
       </c>
     </row>
     <row r="37" ht="14.25" customHeight="1" s="3">
       <c r="A37" s="0" t="n">
-        <v>3000600001</v>
+        <v>3000600002</v>
       </c>
       <c r="C37" s="0" t="n">
         <v>3</v>
@@ -3156,7 +3186,7 @@
       </c>
       <c r="J37" s="0" t="inlineStr">
         <is>
-          <t>1,300061,1</t>
+          <t>2,300061,2</t>
         </is>
       </c>
       <c r="M37" s="0" t="n">
@@ -3197,13 +3227,13 @@
       </c>
       <c r="Y37" s="0" t="inlineStr">
         <is>
-          <t>跳跳斧Lv1-每5秒扔出1把斧头,伤害=魔王攻击力,命中后弹跳1次,伤害逐目标减半保底1</t>
+          <t>跳跳斧Lv2-每5秒扔出2把斧头,命中后弹跳2次,伤害逐目标减半保底1</t>
         </is>
       </c>
     </row>
     <row r="38" ht="14.25" customHeight="1" s="3">
       <c r="A38" s="0" t="n">
-        <v>3000600002</v>
+        <v>3000600003</v>
       </c>
       <c r="C38" s="0" t="n">
         <v>3</v>
@@ -3227,7 +3257,7 @@
       </c>
       <c r="J38" s="0" t="inlineStr">
         <is>
-          <t>2,300061,2</t>
+          <t>3,300061,3</t>
         </is>
       </c>
       <c r="M38" s="0" t="n">
@@ -3268,13 +3298,13 @@
       </c>
       <c r="Y38" s="0" t="inlineStr">
         <is>
-          <t>跳跳斧Lv2-每5秒扔出2把斧头,命中后弹跳2次,伤害逐目标减半保底1</t>
+          <t>跳跳斧Lv3-每5秒扔出3把斧头,命中后弹跳3次,伤害逐目标减半保底1</t>
         </is>
       </c>
     </row>
     <row r="39" ht="14.25" customHeight="1" s="3">
       <c r="A39" s="0" t="n">
-        <v>3000600003</v>
+        <v>3000600004</v>
       </c>
       <c r="C39" s="0" t="n">
         <v>3</v>
@@ -3298,7 +3328,7 @@
       </c>
       <c r="J39" s="0" t="inlineStr">
         <is>
-          <t>3,300061,3</t>
+          <t>4,300061,4</t>
         </is>
       </c>
       <c r="M39" s="0" t="n">
@@ -3339,13 +3369,13 @@
       </c>
       <c r="Y39" s="0" t="inlineStr">
         <is>
-          <t>跳跳斧Lv3-每5秒扔出3把斧头,命中后弹跳3次,伤害逐目标减半保底1</t>
+          <t>跳跳斧Lv4-每5秒扔出4把斧头,命中后弹跳4次,伤害逐目标减半保底1</t>
         </is>
       </c>
     </row>
     <row r="40" ht="14.25" customHeight="1" s="3">
       <c r="A40" s="0" t="n">
-        <v>3000600004</v>
+        <v>3000600005</v>
       </c>
       <c r="C40" s="0" t="n">
         <v>3</v>
@@ -3369,7 +3399,7 @@
       </c>
       <c r="J40" s="0" t="inlineStr">
         <is>
-          <t>4,300061,4</t>
+          <t>5,300061,5</t>
         </is>
       </c>
       <c r="M40" s="0" t="n">
@@ -3410,13 +3440,13 @@
       </c>
       <c r="Y40" s="0" t="inlineStr">
         <is>
-          <t>跳跳斧Lv4-每5秒扔出4把斧头,命中后弹跳4次,伤害逐目标减半保底1</t>
+          <t>跳跳斧Lv5-每5秒扔出5把斧头,命中后弹跳5次,伤害逐目标减半保底1</t>
         </is>
       </c>
     </row>
     <row r="41" ht="14.25" customHeight="1" s="3">
       <c r="A41" s="0" t="n">
-        <v>3000600005</v>
+        <v>3000700001</v>
       </c>
       <c r="C41" s="0" t="n">
         <v>3</v>
@@ -3435,16 +3465,16 @@
       </c>
       <c r="H41" s="0" t="inlineStr">
         <is>
-          <t>BuffEntityPeriodicAttackBounceAxe</t>
+          <t>BuffEntityPeriodicAttackOrbit</t>
         </is>
       </c>
       <c r="J41" s="0" t="inlineStr">
         <is>
-          <t>5,300061,5</t>
+          <t>1,300071,0.6</t>
         </is>
       </c>
       <c r="M41" s="0" t="n">
-        <v>1</v>
+        <v>0.4</v>
       </c>
       <c r="N41" s="0" t="n">
         <v>0</v>
@@ -3462,7 +3492,7 @@
         <v>0</v>
       </c>
       <c r="S41" s="0" t="n">
-        <v>5</v>
+        <v>9999</v>
       </c>
       <c r="T41" s="0" t="n">
         <v>0</v>
@@ -3474,20 +3504,20 @@
         <v>0</v>
       </c>
       <c r="W41" s="0" t="n">
-        <v>3000600001</v>
+        <v>3000700001</v>
       </c>
       <c r="X41" s="0" t="n">
-        <v>3000600001</v>
+        <v>3000700001</v>
       </c>
       <c r="Y41" s="0" t="inlineStr">
         <is>
-          <t>跳跳斧Lv5-每5秒扔出5把斧头,命中后弹跳5次,伤害逐目标减半保底1</t>
+          <t>知识的力量Lv1-环绕1本书(半径0.75,转速0.6弧度/秒),触碰伤害=魔王攻击力40%</t>
         </is>
       </c>
     </row>
     <row r="42" ht="14.25" customHeight="1" s="3">
       <c r="A42" s="0" t="n">
-        <v>3000700001</v>
+        <v>3000700002</v>
       </c>
       <c r="C42" s="0" t="n">
         <v>3</v>
@@ -3511,7 +3541,7 @@
       </c>
       <c r="J42" s="0" t="inlineStr">
         <is>
-          <t>1,300071,0.6</t>
+          <t>2,300071,1.2</t>
         </is>
       </c>
       <c r="M42" s="0" t="n">
@@ -3552,13 +3582,13 @@
       </c>
       <c r="Y42" s="0" t="inlineStr">
         <is>
-          <t>知识的力量Lv1-环绕1本书(半径0.75,转速0.6弧度/秒),触碰伤害=魔王攻击力40%</t>
+          <t>知识的力量Lv2-环绕2本书(半径0.75,转速1.2弧度/秒),触碰伤害=魔王攻击力40%</t>
         </is>
       </c>
     </row>
     <row r="43" ht="14.25" customHeight="1" s="3">
       <c r="A43" s="0" t="n">
-        <v>3000700002</v>
+        <v>3000700003</v>
       </c>
       <c r="C43" s="0" t="n">
         <v>3</v>
@@ -3582,7 +3612,7 @@
       </c>
       <c r="J43" s="0" t="inlineStr">
         <is>
-          <t>2,300071,1.2</t>
+          <t>3,300071,1.8</t>
         </is>
       </c>
       <c r="M43" s="0" t="n">
@@ -3623,13 +3653,13 @@
       </c>
       <c r="Y43" s="0" t="inlineStr">
         <is>
-          <t>知识的力量Lv2-环绕2本书(半径0.75,转速1.2弧度/秒),触碰伤害=魔王攻击力40%</t>
+          <t>知识的力量Lv3-环绕3本书(半径0.75,转速1.8弧度/秒),触碰伤害=魔王攻击力40%</t>
         </is>
       </c>
     </row>
     <row r="44" ht="14.25" customHeight="1" s="3">
       <c r="A44" s="0" t="n">
-        <v>3000700003</v>
+        <v>3000700004</v>
       </c>
       <c r="C44" s="0" t="n">
         <v>3</v>
@@ -3653,7 +3683,7 @@
       </c>
       <c r="J44" s="0" t="inlineStr">
         <is>
-          <t>3,300071,1.8</t>
+          <t>4,300071,2.4</t>
         </is>
       </c>
       <c r="M44" s="0" t="n">
@@ -3694,13 +3724,13 @@
       </c>
       <c r="Y44" s="0" t="inlineStr">
         <is>
-          <t>知识的力量Lv3-环绕3本书(半径0.75,转速1.8弧度/秒),触碰伤害=魔王攻击力40%</t>
+          <t>知识的力量Lv4-环绕4本书(半径0.75,转速2.4弧度/秒),触碰伤害=魔王攻击力40%</t>
         </is>
       </c>
     </row>
     <row r="45" ht="14.25" customHeight="1" s="3">
       <c r="A45" s="0" t="n">
-        <v>3000700004</v>
+        <v>3000700005</v>
       </c>
       <c r="C45" s="0" t="n">
         <v>3</v>
@@ -3724,7 +3754,7 @@
       </c>
       <c r="J45" s="0" t="inlineStr">
         <is>
-          <t>4,300071,2.4</t>
+          <t>5,300071,3</t>
         </is>
       </c>
       <c r="M45" s="0" t="n">
@@ -3765,13 +3795,13 @@
       </c>
       <c r="Y45" s="0" t="inlineStr">
         <is>
-          <t>知识的力量Lv4-环绕4本书(半径0.75,转速2.4弧度/秒),触碰伤害=魔王攻击力40%</t>
+          <t>知识的力量Lv5-环绕5本书(半径0.75,转速3弧度/秒),触碰伤害=魔王攻击力40%</t>
         </is>
       </c>
     </row>
     <row r="46" ht="14.25" customHeight="1" s="3">
       <c r="A46" s="0" t="n">
-        <v>3000700005</v>
+        <v>3000800001</v>
       </c>
       <c r="C46" s="0" t="n">
         <v>3</v>
@@ -3790,16 +3820,16 @@
       </c>
       <c r="H46" s="0" t="inlineStr">
         <is>
-          <t>BuffEntityPeriodicAttackOrbit</t>
+          <t>BuffEntityPeriodicAttackRebound</t>
         </is>
       </c>
       <c r="J46" s="0" t="inlineStr">
         <is>
-          <t>5,300071,3</t>
+          <t>1,300081</t>
         </is>
       </c>
       <c r="M46" s="0" t="n">
-        <v>0.4</v>
+        <v>1</v>
       </c>
       <c r="N46" s="0" t="n">
         <v>0</v>
@@ -3817,7 +3847,7 @@
         <v>0</v>
       </c>
       <c r="S46" s="0" t="n">
-        <v>9999</v>
+        <v>1</v>
       </c>
       <c r="T46" s="0" t="n">
         <v>0</v>
@@ -3829,20 +3859,20 @@
         <v>0</v>
       </c>
       <c r="W46" s="0" t="n">
-        <v>3000700001</v>
+        <v>3000800001</v>
       </c>
       <c r="X46" s="0" t="n">
-        <v>3000700001</v>
+        <v>3000800001</v>
       </c>
       <c r="Y46" s="0" t="inlineStr">
         <is>
-          <t>知识的力量Lv5-环绕5本书(半径0.75,转速3弧度/秒),触碰伤害=魔王攻击力40%</t>
+          <t>回弹菱块Lv1-场上维持1颗永久反弹菱块(速度2),伤害=魔王攻击力100%,同目标1秒冷却</t>
         </is>
       </c>
     </row>
     <row r="47" ht="14.25" customHeight="1" s="3">
       <c r="A47" s="0" t="n">
-        <v>3000800001</v>
+        <v>3000800002</v>
       </c>
       <c r="C47" s="0" t="n">
         <v>3</v>
@@ -3866,7 +3896,7 @@
       </c>
       <c r="J47" s="0" t="inlineStr">
         <is>
-          <t>1,300081</t>
+          <t>2,300082</t>
         </is>
       </c>
       <c r="M47" s="0" t="n">
@@ -3907,13 +3937,13 @@
       </c>
       <c r="Y47" s="0" t="inlineStr">
         <is>
-          <t>回弹菱块Lv1-场上维持1颗永久反弹菱块(速度2),伤害=魔王攻击力100%,同目标1秒冷却</t>
+          <t>回弹菱块Lv2-场上维持2颗永久反弹菱块(速度2.5),伤害=魔王攻击力100%,同目标1秒冷却</t>
         </is>
       </c>
     </row>
     <row r="48" ht="14.25" customHeight="1" s="3">
       <c r="A48" s="0" t="n">
-        <v>3000800002</v>
+        <v>3000800003</v>
       </c>
       <c r="C48" s="0" t="n">
         <v>3</v>
@@ -3937,7 +3967,7 @@
       </c>
       <c r="J48" s="0" t="inlineStr">
         <is>
-          <t>2,300082</t>
+          <t>3,300083</t>
         </is>
       </c>
       <c r="M48" s="0" t="n">
@@ -3978,13 +4008,13 @@
       </c>
       <c r="Y48" s="0" t="inlineStr">
         <is>
-          <t>回弹菱块Lv2-场上维持2颗永久反弹菱块(速度2.5),伤害=魔王攻击力100%,同目标1秒冷却</t>
+          <t>回弹菱块Lv3-场上维持3颗永久反弹菱块(速度3),伤害=魔王攻击力100%,同目标1秒冷却</t>
         </is>
       </c>
     </row>
     <row r="49" ht="15" customHeight="1" s="3">
       <c r="A49" s="0" t="n">
-        <v>3000800003</v>
+        <v>3000800004</v>
       </c>
       <c r="C49" s="0" t="n">
         <v>3</v>
@@ -4008,7 +4038,7 @@
       </c>
       <c r="J49" s="0" t="inlineStr">
         <is>
-          <t>3,300083</t>
+          <t>4,300084</t>
         </is>
       </c>
       <c r="M49" s="0" t="n">
@@ -4049,13 +4079,13 @@
       </c>
       <c r="Y49" s="0" t="inlineStr">
         <is>
-          <t>回弹菱块Lv3-场上维持3颗永久反弹菱块(速度3),伤害=魔王攻击力100%,同目标1秒冷却</t>
+          <t>回弹菱块Lv4-场上维持4颗永久反弹菱块(速度3.5),伤害=魔王攻击力100%,同目标1秒冷却</t>
         </is>
       </c>
     </row>
     <row r="50" ht="14.25" customHeight="1" s="3">
       <c r="A50" s="0" t="n">
-        <v>3000800004</v>
+        <v>3000800005</v>
       </c>
       <c r="C50" s="0" t="n">
         <v>3</v>
@@ -4079,7 +4109,7 @@
       </c>
       <c r="J50" s="0" t="inlineStr">
         <is>
-          <t>4,300084</t>
+          <t>5,300085</t>
         </is>
       </c>
       <c r="M50" s="0" t="n">
@@ -4120,84 +4150,50 @@
       </c>
       <c r="Y50" s="0" t="inlineStr">
         <is>
-          <t>回弹菱块Lv4-场上维持4颗永久反弹菱块(速度3.5),伤害=魔王攻击力100%,同目标1秒冷却</t>
+          <t>回弹菱块Lv5-场上维持5颗永久反弹菱块(速度4),伤害=魔王攻击力100%,同目标1秒冷却</t>
         </is>
       </c>
     </row>
     <row r="51" ht="14.25" customHeight="1" s="3">
-      <c r="A51" s="0" t="n">
-        <v>3000800005</v>
-      </c>
-      <c r="C51" s="0" t="n">
-        <v>3</v>
-      </c>
-      <c r="D51" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="E51" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="F51" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="G51" s="0" t="n">
-        <v>2</v>
-      </c>
-      <c r="H51" s="0" t="inlineStr">
-        <is>
-          <t>BuffEntityPeriodicAttackRebound</t>
-        </is>
-      </c>
-      <c r="J51" s="0" t="inlineStr">
-        <is>
-          <t>5,300085</t>
-        </is>
-      </c>
-      <c r="M51" s="0" t="n">
+      <c r="A51" s="2" t="n">
+        <v>3000900001</v>
+      </c>
+      <c r="C51" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="D51" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="N51" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="O51" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="P51" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q51" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="R51" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="S51" s="0" t="n">
-        <v>1</v>
-      </c>
+      <c r="H51" s="2" t="inlineStr">
+        <is>
+          <t>BuffEntityInstantRewardMoreItem</t>
+        </is>
+      </c>
+      <c r="I51" s="2" t="n"/>
+      <c r="J51" s="2" t="n"/>
+      <c r="O51" s="2" t="n"/>
+      <c r="P51" s="2" t="n"/>
       <c r="T51" s="0" t="n">
         <v>0</v>
       </c>
       <c r="U51" s="0" t="n">
         <v>0</v>
       </c>
-      <c r="V51" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="W51" s="0" t="n">
-        <v>3000800001</v>
-      </c>
-      <c r="X51" s="0" t="n">
-        <v>3000800001</v>
-      </c>
-      <c r="Y51" s="0" t="inlineStr">
-        <is>
-          <t>回弹菱块Lv5-场上维持5颗永久反弹菱块(速度4),伤害=魔王攻击力100%,同目标1秒冷却</t>
+      <c r="W51" s="2" t="n">
+        <v>3000900001</v>
+      </c>
+      <c r="X51" s="2" t="n">
+        <v>3000900001</v>
+      </c>
+      <c r="Y51" s="2" t="inlineStr">
+        <is>
+          <t>奖励多多-通关奖励数量+1</t>
         </is>
       </c>
     </row>
     <row r="52" ht="14.25" customHeight="1" s="3">
       <c r="A52" s="2" t="n">
-        <v>3000900001</v>
+        <v>3001000001</v>
       </c>
       <c r="C52" s="2" t="n">
         <v>3</v>
@@ -4207,7 +4203,7 @@
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
-          <t>BuffEntityInstantRewardMoreItem</t>
+          <t>BuffEntityInstantRewardMoreSelect</t>
         </is>
       </c>
       <c r="I52" s="2" t="n"/>
@@ -4221,57 +4217,91 @@
         <v>0</v>
       </c>
       <c r="W52" s="2" t="n">
-        <v>3000900001</v>
+        <v>3001000001</v>
       </c>
       <c r="X52" s="2" t="n">
-        <v>3000900001</v>
+        <v>3001000001</v>
       </c>
       <c r="Y52" s="2" t="inlineStr">
         <is>
-          <t>奖励多多-通关奖励数量+1</t>
+          <t>再来一瓶-通关奖励可选次数+1</t>
         </is>
       </c>
     </row>
     <row r="53" ht="14.25" customHeight="1" s="3">
-      <c r="A53" s="2" t="n">
-        <v>3001000001</v>
-      </c>
-      <c r="C53" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="D53" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="H53" s="2" t="inlineStr">
-        <is>
-          <t>BuffEntityInstantRewardMoreSelect</t>
-        </is>
-      </c>
-      <c r="I53" s="2" t="n"/>
-      <c r="J53" s="2" t="n"/>
-      <c r="O53" s="2" t="n"/>
-      <c r="P53" s="2" t="n"/>
+      <c r="A53" s="0" t="n">
+        <v>3001100005</v>
+      </c>
+      <c r="C53" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="D53" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="E53" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="F53" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="G53" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="H53" s="0" t="inlineStr">
+        <is>
+          <t>BuffEntityPeriodicAttackShockwave</t>
+        </is>
+      </c>
+      <c r="J53" s="0" t="inlineStr">
+        <is>
+          <t>300091</t>
+        </is>
+      </c>
+      <c r="M53" s="0" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="N53" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="O53" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="P53" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q53" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="R53" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="S53" s="0" t="n">
+        <v>10</v>
+      </c>
       <c r="T53" s="0" t="n">
         <v>0</v>
       </c>
       <c r="U53" s="0" t="n">
         <v>0</v>
       </c>
-      <c r="W53" s="2" t="n">
-        <v>3001000001</v>
-      </c>
-      <c r="X53" s="2" t="n">
-        <v>3001000001</v>
-      </c>
-      <c r="Y53" s="2" t="inlineStr">
-        <is>
-          <t>再来一瓶-通关奖励可选次数+1</t>
+      <c r="V53" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="W53" s="0" t="n">
+        <v>3001100005</v>
+      </c>
+      <c r="X53" s="0" t="n">
+        <v>3001100005</v>
+      </c>
+      <c r="Y53" s="0" t="inlineStr">
+        <is>
+          <t>第六次冲击Lv5-每10秒从魔王发出冲击波，伤害=魔王攻击力x0.3</t>
         </is>
       </c>
     </row>
     <row r="54" ht="14.25" customHeight="1" s="3">
       <c r="A54" s="0" t="n">
-        <v>3001100005</v>
+        <v>3001100004</v>
       </c>
       <c r="C54" s="0" t="n">
         <v>3</v>
@@ -4299,7 +4329,7 @@
         </is>
       </c>
       <c r="M54" s="0" t="n">
-        <v>0.3</v>
+        <v>0.25</v>
       </c>
       <c r="N54" s="0" t="n">
         <v>0</v>
@@ -4329,20 +4359,20 @@
         <v>0</v>
       </c>
       <c r="W54" s="0" t="n">
-        <v>3001100005</v>
+        <v>3001100004</v>
       </c>
       <c r="X54" s="0" t="n">
-        <v>3001100005</v>
+        <v>3001100004</v>
       </c>
       <c r="Y54" s="0" t="inlineStr">
         <is>
-          <t>第六次冲击Lv5-每10秒从魔王发出冲击波，伤害=魔王攻击力x0.3</t>
+          <t>第六次冲击Lv4-每10秒从魔王发出冲击波，伤害=魔王攻击力x0.25</t>
         </is>
       </c>
     </row>
     <row r="55" ht="14.25" customFormat="1" customHeight="1" s="2">
       <c r="A55" s="0" t="n">
-        <v>3001100004</v>
+        <v>3001100003</v>
       </c>
       <c r="C55" s="0" t="n">
         <v>3</v>
@@ -4370,7 +4400,7 @@
         </is>
       </c>
       <c r="M55" s="0" t="n">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="N55" s="0" t="n">
         <v>0</v>
@@ -4400,20 +4430,20 @@
         <v>0</v>
       </c>
       <c r="W55" s="0" t="n">
-        <v>3001100004</v>
+        <v>3001100003</v>
       </c>
       <c r="X55" s="0" t="n">
-        <v>3001100004</v>
+        <v>3001100003</v>
       </c>
       <c r="Y55" s="0" t="inlineStr">
         <is>
-          <t>第六次冲击Lv4-每10秒从魔王发出冲击波，伤害=魔王攻击力x0.25</t>
+          <t>第六次冲击Lv3-每10秒从魔王发出冲击波，伤害=魔王攻击力x0.2</t>
         </is>
       </c>
     </row>
     <row r="56" ht="14.25" customFormat="1" customHeight="1" s="2">
       <c r="A56" s="0" t="n">
-        <v>3001100003</v>
+        <v>3001100002</v>
       </c>
       <c r="C56" s="0" t="n">
         <v>3</v>
@@ -4441,7 +4471,7 @@
         </is>
       </c>
       <c r="M56" s="0" t="n">
-        <v>0.2</v>
+        <v>0.15</v>
       </c>
       <c r="N56" s="0" t="n">
         <v>0</v>
@@ -4471,20 +4501,20 @@
         <v>0</v>
       </c>
       <c r="W56" s="0" t="n">
-        <v>3001100003</v>
+        <v>3001100002</v>
       </c>
       <c r="X56" s="0" t="n">
-        <v>3001100003</v>
+        <v>3001100002</v>
       </c>
       <c r="Y56" s="0" t="inlineStr">
         <is>
-          <t>第六次冲击Lv3-每10秒从魔王发出冲击波，伤害=魔王攻击力x0.2</t>
+          <t>第六次冲击Lv2-每10秒从魔王发出冲击波，伤害=魔王攻击力x0.15</t>
         </is>
       </c>
     </row>
     <row r="57" ht="14.25" customFormat="1" customHeight="1" s="2">
       <c r="A57" s="0" t="n">
-        <v>3001100002</v>
+        <v>3001100001</v>
       </c>
       <c r="C57" s="0" t="n">
         <v>3</v>
@@ -4512,7 +4542,7 @@
         </is>
       </c>
       <c r="M57" s="0" t="n">
-        <v>0.15</v>
+        <v>0.1</v>
       </c>
       <c r="N57" s="0" t="n">
         <v>0</v>
@@ -4542,21 +4572,22 @@
         <v>0</v>
       </c>
       <c r="W57" s="0" t="n">
-        <v>3001100002</v>
+        <v>3001100001</v>
       </c>
       <c r="X57" s="0" t="n">
-        <v>3001100002</v>
+        <v>3001100001</v>
       </c>
       <c r="Y57" s="0" t="inlineStr">
         <is>
-          <t>第六次冲击Lv2-每10秒从魔王发出冲击波，伤害=魔王攻击力x0.15</t>
+          <t>第六次冲击Lv1-每10秒从魔王发出冲击波，伤害=魔王攻击力x0.1</t>
         </is>
       </c>
     </row>
     <row r="58" ht="14.25" customFormat="1" customHeight="1" s="2">
       <c r="A58" s="0" t="n">
-        <v>3001100001</v>
-      </c>
+        <v>3001200001</v>
+      </c>
+      <c r="B58" s="0" t="inlineStr"/>
       <c r="C58" s="0" t="n">
         <v>3</v>
       </c>
@@ -4574,16 +4605,19 @@
       </c>
       <c r="H58" s="0" t="inlineStr">
         <is>
-          <t>BuffEntityPeriodicAttackShockwave</t>
-        </is>
-      </c>
+          <t>BuffEntityPeriodicAttackFireBottle</t>
+        </is>
+      </c>
+      <c r="I58" s="0" t="inlineStr"/>
       <c r="J58" s="0" t="inlineStr">
         <is>
-          <t>300091</t>
-        </is>
-      </c>
+          <t>1,300101</t>
+        </is>
+      </c>
+      <c r="K58" s="0" t="inlineStr"/>
+      <c r="L58" s="0" t="inlineStr"/>
       <c r="M58" s="0" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="N58" s="0" t="n">
         <v>0</v>
@@ -4613,20 +4647,20 @@
         <v>0</v>
       </c>
       <c r="W58" s="0" t="n">
-        <v>3001100001</v>
+        <v>3001200001</v>
       </c>
       <c r="X58" s="0" t="n">
-        <v>3001100001</v>
+        <v>3001200001</v>
       </c>
       <c r="Y58" s="0" t="inlineStr">
         <is>
-          <t>第六次冲击Lv1-每10秒从魔王发出冲击波，伤害=魔王攻击力x0.1</t>
+          <t>瓶装炼狱火Lv1-每10秒向1个敌人投掷炼狱火瓶,落地燃放地形火焰,每1秒对半径1.2内敌人造成魔王攻击力20%伤害,持续5秒</t>
         </is>
       </c>
     </row>
     <row r="59" ht="14.25" customFormat="1" customHeight="1" s="2">
       <c r="A59" s="0" t="n">
-        <v>3001200001</v>
+        <v>3001200002</v>
       </c>
       <c r="B59" s="0" t="inlineStr"/>
       <c r="C59" s="0" t="n">
@@ -4652,7 +4686,7 @@
       <c r="I59" s="0" t="inlineStr"/>
       <c r="J59" s="0" t="inlineStr">
         <is>
-          <t>1,300101</t>
+          <t>2,300101</t>
         </is>
       </c>
       <c r="K59" s="0" t="inlineStr"/>
@@ -4695,13 +4729,13 @@
       </c>
       <c r="Y59" s="0" t="inlineStr">
         <is>
-          <t>瓶装炼狱火Lv1-每10秒向1个敌人投掷炼狱火瓶,落地燃放地形火焰,每1秒对半径1.2内敌人造成魔王攻击力20%伤害,持续5秒</t>
+          <t>瓶装炼狱火Lv2-每10秒向2个敌人投掷炼狱火瓶,落地燃放地形火焰,每1秒对半径1.2内敌人造成魔王攻击力20%伤害,持续5秒</t>
         </is>
       </c>
     </row>
     <row r="60" ht="14.25" customFormat="1" customHeight="1" s="2">
       <c r="A60" s="0" t="n">
-        <v>3001200002</v>
+        <v>3001200003</v>
       </c>
       <c r="B60" s="0" t="inlineStr"/>
       <c r="C60" s="0" t="n">
@@ -4727,7 +4761,7 @@
       <c r="I60" s="0" t="inlineStr"/>
       <c r="J60" s="0" t="inlineStr">
         <is>
-          <t>2,300101</t>
+          <t>3,300101</t>
         </is>
       </c>
       <c r="K60" s="0" t="inlineStr"/>
@@ -4770,13 +4804,13 @@
       </c>
       <c r="Y60" s="0" t="inlineStr">
         <is>
-          <t>瓶装炼狱火Lv2-每10秒向2个敌人投掷炼狱火瓶,落地燃放地形火焰,每1秒对半径1.2内敌人造成魔王攻击力20%伤害,持续5秒</t>
+          <t>瓶装炼狱火Lv3-每10秒向3个敌人投掷炼狱火瓶,落地燃放地形火焰,每1秒对半径1.2内敌人造成魔王攻击力20%伤害,持续5秒</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="0" t="n">
-        <v>3001200003</v>
+        <v>3001200004</v>
       </c>
       <c r="B61" s="0" t="inlineStr"/>
       <c r="C61" s="0" t="n">
@@ -4802,7 +4836,7 @@
       <c r="I61" s="0" t="inlineStr"/>
       <c r="J61" s="0" t="inlineStr">
         <is>
-          <t>3,300101</t>
+          <t>4,300101</t>
         </is>
       </c>
       <c r="K61" s="0" t="inlineStr"/>
@@ -4845,13 +4879,13 @@
       </c>
       <c r="Y61" s="0" t="inlineStr">
         <is>
-          <t>瓶装炼狱火Lv3-每10秒向3个敌人投掷炼狱火瓶,落地燃放地形火焰,每1秒对半径1.2内敌人造成魔王攻击力20%伤害,持续5秒</t>
+          <t>瓶装炼狱火Lv4-每10秒向4个敌人投掷炼狱火瓶,落地燃放地形火焰,每1秒对半径1.2内敌人造成魔王攻击力20%伤害,持续5秒</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="0" t="n">
-        <v>3001200004</v>
+        <v>3001200005</v>
       </c>
       <c r="B62" s="0" t="inlineStr"/>
       <c r="C62" s="0" t="n">
@@ -4877,7 +4911,7 @@
       <c r="I62" s="0" t="inlineStr"/>
       <c r="J62" s="0" t="inlineStr">
         <is>
-          <t>4,300101</t>
+          <t>5,300101</t>
         </is>
       </c>
       <c r="K62" s="0" t="inlineStr"/>
@@ -4920,63 +4954,40 @@
       </c>
       <c r="Y62" s="0" t="inlineStr">
         <is>
-          <t>瓶装炼狱火Lv4-每10秒向4个敌人投掷炼狱火瓶,落地燃放地形火焰,每1秒对半径1.2内敌人造成魔王攻击力20%伤害,持续5秒</t>
+          <t>瓶装炼狱火Lv5-每10秒向5个敌人投掷炼狱火瓶,落地燃放地形火焰,每1秒对半径1.2内敌人造成魔王攻击力20%伤害,持续5秒</t>
         </is>
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="0" t="n">
-        <v>3001200005</v>
-      </c>
-      <c r="B63" s="0" t="inlineStr"/>
-      <c r="C63" s="0" t="n">
-        <v>3</v>
-      </c>
-      <c r="D63" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="E63" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="F63" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="G63" s="0" t="n">
+      <c r="A63" s="2" t="n">
+        <v>11000100001</v>
+      </c>
+      <c r="C63" s="2" t="n">
+        <v>11</v>
+      </c>
+      <c r="D63" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="H63" s="0" t="inlineStr">
-        <is>
-          <t>BuffEntityPeriodicAttackFireBottle</t>
-        </is>
-      </c>
-      <c r="I63" s="0" t="inlineStr"/>
-      <c r="J63" s="0" t="inlineStr">
-        <is>
-          <t>5,300101</t>
-        </is>
-      </c>
-      <c r="K63" s="0" t="inlineStr"/>
-      <c r="L63" s="0" t="inlineStr"/>
-      <c r="M63" s="0" t="n">
+      <c r="H63" s="2" t="inlineStr">
+        <is>
+          <t>BuffEntityAttribute</t>
+        </is>
+      </c>
+      <c r="I63" s="5" t="inlineStr">
+        <is>
+          <t>GameFightLogic_CreatureDeadEnd</t>
+        </is>
+      </c>
+      <c r="J63" s="5" t="inlineStr">
+        <is>
+          <t>HP</t>
+        </is>
+      </c>
+      <c r="O63" s="2" t="n">
         <v>0.2</v>
       </c>
-      <c r="N63" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="O63" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="P63" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q63" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="R63" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="S63" s="0" t="n">
-        <v>10</v>
+      <c r="P63" s="2" t="n">
+        <v>0.1</v>
       </c>
       <c r="T63" s="0" t="n">
         <v>0</v>
@@ -4984,24 +4995,21 @@
       <c r="U63" s="0" t="n">
         <v>0</v>
       </c>
-      <c r="V63" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="W63" s="0" t="n">
-        <v>3001200001</v>
-      </c>
-      <c r="X63" s="0" t="n">
-        <v>3001200001</v>
-      </c>
-      <c r="Y63" s="0" t="inlineStr">
-        <is>
-          <t>瓶装炼狱火Lv5-每10秒向5个敌人投掷炼狱火瓶,落地燃放地形火焰,每1秒对半径1.2内敌人造成魔王攻击力20%伤害,持续5秒</t>
+      <c r="W63" s="2" t="n">
+        <v>11000100001</v>
+      </c>
+      <c r="X63" s="2" t="n">
+        <v>11000100001</v>
+      </c>
+      <c r="Y63" s="2" t="inlineStr">
+        <is>
+          <t>生命增加{Percentage}%</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="n">
-        <v>11000100001</v>
+        <v>11000200001</v>
       </c>
       <c r="C64" s="2" t="n">
         <v>11</v>
@@ -5021,7 +5029,7 @@
       </c>
       <c r="J64" s="5" t="inlineStr">
         <is>
-          <t>HP</t>
+          <t>DR</t>
         </is>
       </c>
       <c r="O64" s="2" t="n">
@@ -5037,20 +5045,20 @@
         <v>0</v>
       </c>
       <c r="W64" s="2" t="n">
-        <v>11000100001</v>
+        <v>11000200001</v>
       </c>
       <c r="X64" s="2" t="n">
-        <v>11000100001</v>
+        <v>11000200001</v>
       </c>
       <c r="Y64" s="2" t="inlineStr">
         <is>
-          <t>生命增加{Percentage}%</t>
+          <t>护甲增加{Percentage}%</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="n">
-        <v>11000200001</v>
+        <v>11000300001</v>
       </c>
       <c r="C65" s="2" t="n">
         <v>11</v>
@@ -5068,17 +5076,20 @@
           <t>GameFightLogic_CreatureDeadEnd</t>
         </is>
       </c>
-      <c r="J65" s="5" t="inlineStr">
-        <is>
-          <t>DR</t>
-        </is>
-      </c>
-      <c r="O65" s="2" t="n">
+      <c r="J65" s="0" t="inlineStr">
+        <is>
+          <t>ATK</t>
+        </is>
+      </c>
+      <c r="O65" s="0" t="n">
         <v>0.2</v>
       </c>
-      <c r="P65" s="2" t="n">
+      <c r="P65" s="0" t="n">
         <v>0.1</v>
       </c>
+      <c r="Q65" s="2" t="n">
+        <v>0.2</v>
+      </c>
       <c r="T65" s="0" t="n">
         <v>0</v>
       </c>
@@ -5086,50 +5097,42 @@
         <v>0</v>
       </c>
       <c r="W65" s="2" t="n">
-        <v>11000200001</v>
+        <v>11000300001</v>
       </c>
       <c r="X65" s="2" t="n">
-        <v>11000200001</v>
+        <v>11000300001</v>
       </c>
       <c r="Y65" s="2" t="inlineStr">
         <is>
-          <t>护甲增加{Percentage}%</t>
+          <t>攻击力增加{Percentage}%</t>
         </is>
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="2" t="n">
-        <v>11000300001</v>
-      </c>
-      <c r="C66" s="2" t="n">
+      <c r="A66" s="0" t="n">
+        <v>11000400001</v>
+      </c>
+      <c r="C66" s="0" t="n">
         <v>11</v>
       </c>
-      <c r="D66" s="2" t="n">
+      <c r="D66" s="0" t="n">
         <v>2</v>
       </c>
-      <c r="H66" s="2" t="inlineStr">
+      <c r="H66" s="0" t="inlineStr">
         <is>
           <t>BuffEntityAttribute</t>
         </is>
       </c>
-      <c r="I66" s="5" t="inlineStr">
-        <is>
-          <t>GameFightLogic_CreatureDeadEnd</t>
-        </is>
-      </c>
       <c r="J66" s="0" t="inlineStr">
         <is>
-          <t>ATK</t>
+          <t>ASPD</t>
         </is>
       </c>
       <c r="O66" s="0" t="n">
-        <v>0.2</v>
+        <v>1</v>
       </c>
       <c r="P66" s="0" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="Q66" s="2" t="n">
-        <v>0.2</v>
+        <v>0.5</v>
       </c>
       <c r="T66" s="0" t="n">
         <v>0</v>
@@ -5137,21 +5140,21 @@
       <c r="U66" s="0" t="n">
         <v>0</v>
       </c>
-      <c r="W66" s="2" t="n">
-        <v>11000300001</v>
-      </c>
-      <c r="X66" s="2" t="n">
-        <v>11000300001</v>
-      </c>
-      <c r="Y66" s="2" t="inlineStr">
-        <is>
-          <t>攻击力增加{Percentage}%</t>
+      <c r="W66" s="0" t="n">
+        <v>11000400001</v>
+      </c>
+      <c r="X66" s="0" t="n">
+        <v>11000400001</v>
+      </c>
+      <c r="Y66" s="0" t="inlineStr">
+        <is>
+          <t>攻击速度增加{Percentage}%</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="0" t="n">
-        <v>11000400001</v>
+        <v>11000500001</v>
       </c>
       <c r="C67" s="0" t="n">
         <v>11</v>
@@ -5166,14 +5169,14 @@
       </c>
       <c r="J67" s="0" t="inlineStr">
         <is>
-          <t>ASPD</t>
+          <t>RCD</t>
         </is>
       </c>
       <c r="O67" s="0" t="n">
-        <v>1</v>
+        <v>-0.25</v>
       </c>
       <c r="P67" s="0" t="n">
-        <v>0.5</v>
+        <v>-0.5</v>
       </c>
       <c r="T67" s="0" t="n">
         <v>0</v>
@@ -5182,20 +5185,20 @@
         <v>0</v>
       </c>
       <c r="W67" s="0" t="n">
-        <v>11000400001</v>
+        <v>11000500001</v>
       </c>
       <c r="X67" s="0" t="n">
-        <v>11000400001</v>
+        <v>11000500001</v>
       </c>
       <c r="Y67" s="0" t="inlineStr">
         <is>
-          <t>攻击速度增加{Percentage}%</t>
+          <t>召唤CD{Percentage}%</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="0" t="n">
-        <v>11000500001</v>
+        <v>11000600001</v>
       </c>
       <c r="C68" s="0" t="n">
         <v>11</v>
@@ -5210,7 +5213,7 @@
       </c>
       <c r="J68" s="0" t="inlineStr">
         <is>
-          <t>RCD</t>
+          <t>CMP</t>
         </is>
       </c>
       <c r="O68" s="0" t="n">
@@ -5226,20 +5229,20 @@
         <v>0</v>
       </c>
       <c r="W68" s="0" t="n">
-        <v>11000500001</v>
+        <v>11000600001</v>
       </c>
       <c r="X68" s="0" t="n">
-        <v>11000500001</v>
+        <v>11000600001</v>
       </c>
       <c r="Y68" s="0" t="inlineStr">
         <is>
-          <t>召唤CD{Percentage}%</t>
+          <t>召唤魔力消耗{Percentage}%</t>
         </is>
       </c>
     </row>
     <row r="69" ht="15" customHeight="1" s="3">
       <c r="A69" s="0" t="n">
-        <v>11000600001</v>
+        <v>11000700001</v>
       </c>
       <c r="C69" s="0" t="n">
         <v>11</v>
@@ -5247,21 +5250,27 @@
       <c r="D69" s="0" t="n">
         <v>2</v>
       </c>
+      <c r="G69" s="0" t="n">
+        <v>0</v>
+      </c>
       <c r="H69" s="0" t="inlineStr">
         <is>
-          <t>BuffEntityAttribute</t>
+          <t>BuffEntityAttributeMulti</t>
         </is>
       </c>
       <c r="J69" s="0" t="inlineStr">
         <is>
-          <t>CMP</t>
+          <t>ATK:1|HP:-1</t>
         </is>
       </c>
       <c r="O69" s="0" t="n">
-        <v>-0.25</v>
+        <v>0.5</v>
       </c>
       <c r="P69" s="0" t="n">
-        <v>-0.5</v>
+        <v>0.2</v>
+      </c>
+      <c r="R69" s="0" t="n">
+        <v>0</v>
       </c>
       <c r="T69" s="0" t="n">
         <v>0</v>
@@ -5270,20 +5279,20 @@
         <v>0</v>
       </c>
       <c r="W69" s="0" t="n">
-        <v>11000600001</v>
+        <v>11000700001</v>
       </c>
       <c r="X69" s="0" t="n">
-        <v>11000600001</v>
+        <v>11000700001</v>
       </c>
       <c r="Y69" s="0" t="inlineStr">
         <is>
-          <t>召唤魔力消耗{Percentage}%</t>
+          <t>狂战士-A</t>
         </is>
       </c>
     </row>
     <row r="70" ht="15" customHeight="1" s="3">
       <c r="A70" s="0" t="n">
-        <v>11000700001</v>
+        <v>11000700002</v>
       </c>
       <c r="C70" s="0" t="n">
         <v>11</v>
@@ -5301,7 +5310,7 @@
       </c>
       <c r="J70" s="0" t="inlineStr">
         <is>
-          <t>ATK:1|HP:-1</t>
+          <t>ATK:1|DR:-1</t>
         </is>
       </c>
       <c r="O70" s="0" t="n">
@@ -5320,20 +5329,20 @@
         <v>0</v>
       </c>
       <c r="W70" s="0" t="n">
-        <v>11000700001</v>
+        <v>11000700002</v>
       </c>
       <c r="X70" s="0" t="n">
-        <v>11000700001</v>
+        <v>11000700002</v>
       </c>
       <c r="Y70" s="0" t="inlineStr">
         <is>
-          <t>狂战士-A</t>
+          <t>狂战士-B</t>
         </is>
       </c>
     </row>
     <row r="71" ht="15" customHeight="1" s="3">
       <c r="A71" s="0" t="n">
-        <v>11000700002</v>
+        <v>11000700003</v>
       </c>
       <c r="C71" s="0" t="n">
         <v>11</v>
@@ -5351,7 +5360,7 @@
       </c>
       <c r="J71" s="0" t="inlineStr">
         <is>
-          <t>ATK:1|DR:-1</t>
+          <t>ATK:1|ASPD:-1</t>
         </is>
       </c>
       <c r="O71" s="0" t="n">
@@ -5370,20 +5379,20 @@
         <v>0</v>
       </c>
       <c r="W71" s="0" t="n">
-        <v>11000700002</v>
+        <v>11000700003</v>
       </c>
       <c r="X71" s="0" t="n">
-        <v>11000700002</v>
+        <v>11000700003</v>
       </c>
       <c r="Y71" s="0" t="inlineStr">
         <is>
-          <t>狂战士-B</t>
+          <t>狂战士-C</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="0" t="n">
-        <v>11000700003</v>
+        <v>11000800001</v>
       </c>
       <c r="C72" s="0" t="n">
         <v>11</v>
@@ -5401,7 +5410,7 @@
       </c>
       <c r="J72" s="0" t="inlineStr">
         <is>
-          <t>ATK:1|ASPD:-1</t>
+          <t>ASPD:1|DR:-1</t>
         </is>
       </c>
       <c r="O72" s="0" t="n">
@@ -5420,20 +5429,20 @@
         <v>0</v>
       </c>
       <c r="W72" s="0" t="n">
-        <v>11000700003</v>
+        <v>11000800001</v>
       </c>
       <c r="X72" s="0" t="n">
-        <v>11000700003</v>
+        <v>11000800001</v>
       </c>
       <c r="Y72" s="0" t="inlineStr">
         <is>
-          <t>狂战士-C</t>
+          <t>快枪手-A</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="0" t="n">
-        <v>11000800001</v>
+        <v>11000800002</v>
       </c>
       <c r="C73" s="0" t="n">
         <v>11</v>
@@ -5451,7 +5460,7 @@
       </c>
       <c r="J73" s="0" t="inlineStr">
         <is>
-          <t>ASPD:1|DR:-1</t>
+          <t>ASPD:1|HP:-1</t>
         </is>
       </c>
       <c r="O73" s="0" t="n">
@@ -5470,20 +5479,20 @@
         <v>0</v>
       </c>
       <c r="W73" s="0" t="n">
-        <v>11000800001</v>
+        <v>11000800002</v>
       </c>
       <c r="X73" s="0" t="n">
-        <v>11000800001</v>
+        <v>11000800002</v>
       </c>
       <c r="Y73" s="0" t="inlineStr">
         <is>
-          <t>快枪手-A</t>
+          <t>快枪手-B</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="0" t="n">
-        <v>11000800002</v>
+        <v>11000800003</v>
       </c>
       <c r="C74" s="0" t="n">
         <v>11</v>
@@ -5501,7 +5510,7 @@
       </c>
       <c r="J74" s="0" t="inlineStr">
         <is>
-          <t>ASPD:1|HP:-1</t>
+          <t>ASPD:1|ATK:-1</t>
         </is>
       </c>
       <c r="O74" s="0" t="n">
@@ -5520,20 +5529,20 @@
         <v>0</v>
       </c>
       <c r="W74" s="0" t="n">
-        <v>11000800002</v>
+        <v>11000800003</v>
       </c>
       <c r="X74" s="0" t="n">
-        <v>11000800002</v>
+        <v>11000800003</v>
       </c>
       <c r="Y74" s="0" t="inlineStr">
         <is>
-          <t>快枪手-B</t>
+          <t>快枪手-C</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="0" t="n">
-        <v>11000800003</v>
+        <v>11000900001</v>
       </c>
       <c r="C75" s="0" t="n">
         <v>11</v>
@@ -5551,7 +5560,7 @@
       </c>
       <c r="J75" s="0" t="inlineStr">
         <is>
-          <t>ASPD:1|ATK:-1</t>
+          <t>DR:1|HP:-1</t>
         </is>
       </c>
       <c r="O75" s="0" t="n">
@@ -5570,20 +5579,20 @@
         <v>0</v>
       </c>
       <c r="W75" s="0" t="n">
-        <v>11000800003</v>
+        <v>11000900001</v>
       </c>
       <c r="X75" s="0" t="n">
-        <v>11000800003</v>
+        <v>11000900001</v>
       </c>
       <c r="Y75" s="0" t="inlineStr">
         <is>
-          <t>快枪手-C</t>
+          <t>铜墙铁壁-A</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="0" t="n">
-        <v>11000900001</v>
+        <v>11000900002</v>
       </c>
       <c r="C76" s="0" t="n">
         <v>11</v>
@@ -5601,7 +5610,7 @@
       </c>
       <c r="J76" s="0" t="inlineStr">
         <is>
-          <t>DR:1|HP:-1</t>
+          <t>DR:1|ATK:-1</t>
         </is>
       </c>
       <c r="O76" s="0" t="n">
@@ -5620,20 +5629,20 @@
         <v>0</v>
       </c>
       <c r="W76" s="0" t="n">
-        <v>11000900001</v>
+        <v>11000900002</v>
       </c>
       <c r="X76" s="0" t="n">
-        <v>11000900001</v>
+        <v>11000900002</v>
       </c>
       <c r="Y76" s="0" t="inlineStr">
         <is>
-          <t>铜墙铁壁-A</t>
+          <t>铜墙铁壁-B</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="0" t="n">
-        <v>11000900002</v>
+        <v>11000900003</v>
       </c>
       <c r="C77" s="0" t="n">
         <v>11</v>
@@ -5651,7 +5660,7 @@
       </c>
       <c r="J77" s="0" t="inlineStr">
         <is>
-          <t>DR:1|ATK:-1</t>
+          <t>DR:1|ASPD:-1</t>
         </is>
       </c>
       <c r="O77" s="0" t="n">
@@ -5670,20 +5679,20 @@
         <v>0</v>
       </c>
       <c r="W77" s="0" t="n">
-        <v>11000900002</v>
+        <v>11000900003</v>
       </c>
       <c r="X77" s="0" t="n">
-        <v>11000900002</v>
+        <v>11000900003</v>
       </c>
       <c r="Y77" s="0" t="inlineStr">
         <is>
-          <t>铜墙铁壁-B</t>
+          <t>铜墙铁壁-C</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="0" t="n">
-        <v>11000900003</v>
+        <v>11001000001</v>
       </c>
       <c r="C78" s="0" t="n">
         <v>11</v>
@@ -5701,7 +5710,7 @@
       </c>
       <c r="J78" s="0" t="inlineStr">
         <is>
-          <t>DR:1|ASPD:-1</t>
+          <t>HP:1|ASPD:-1</t>
         </is>
       </c>
       <c r="O78" s="0" t="n">
@@ -5720,20 +5729,20 @@
         <v>0</v>
       </c>
       <c r="W78" s="0" t="n">
-        <v>11000900003</v>
+        <v>11001000001</v>
       </c>
       <c r="X78" s="0" t="n">
-        <v>11000900003</v>
+        <v>11001000001</v>
       </c>
       <c r="Y78" s="0" t="inlineStr">
         <is>
-          <t>铜墙铁壁-C</t>
+          <t>大块头-A</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="0" t="n">
-        <v>11001000001</v>
+        <v>11001000002</v>
       </c>
       <c r="C79" s="0" t="n">
         <v>11</v>
@@ -5751,7 +5760,7 @@
       </c>
       <c r="J79" s="0" t="inlineStr">
         <is>
-          <t>HP:1|ASPD:-1</t>
+          <t>HP:1|DR:-1</t>
         </is>
       </c>
       <c r="O79" s="0" t="n">
@@ -5770,20 +5779,20 @@
         <v>0</v>
       </c>
       <c r="W79" s="0" t="n">
-        <v>11001000001</v>
+        <v>11001000002</v>
       </c>
       <c r="X79" s="0" t="n">
-        <v>11001000001</v>
+        <v>11001000002</v>
       </c>
       <c r="Y79" s="0" t="inlineStr">
         <is>
-          <t>大块头-A</t>
+          <t>大块头-B</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="0" t="n">
-        <v>11001000002</v>
+        <v>11001000003</v>
       </c>
       <c r="C80" s="0" t="n">
         <v>11</v>
@@ -5801,7 +5810,7 @@
       </c>
       <c r="J80" s="0" t="inlineStr">
         <is>
-          <t>HP:1|DR:-1</t>
+          <t>HP:1|ATK:-1</t>
         </is>
       </c>
       <c r="O80" s="0" t="n">
@@ -5820,20 +5829,20 @@
         <v>0</v>
       </c>
       <c r="W80" s="0" t="n">
-        <v>11001000002</v>
+        <v>11001000003</v>
       </c>
       <c r="X80" s="0" t="n">
-        <v>11001000002</v>
+        <v>11001000003</v>
       </c>
       <c r="Y80" s="0" t="inlineStr">
         <is>
-          <t>大块头-B</t>
+          <t>大块头-C</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="0" t="n">
-        <v>11001000003</v>
+        <v>11000700004</v>
       </c>
       <c r="C81" s="0" t="n">
         <v>11</v>
@@ -5851,7 +5860,7 @@
       </c>
       <c r="J81" s="0" t="inlineStr">
         <is>
-          <t>HP:1|ATK:-1</t>
+          <t>ATK:1|RCD:1</t>
         </is>
       </c>
       <c r="O81" s="0" t="n">
@@ -5870,20 +5879,20 @@
         <v>0</v>
       </c>
       <c r="W81" s="0" t="n">
-        <v>11001000003</v>
+        <v>11000700004</v>
       </c>
       <c r="X81" s="0" t="n">
-        <v>11001000003</v>
+        <v>11000700004</v>
       </c>
       <c r="Y81" s="0" t="inlineStr">
         <is>
-          <t>大块头-C</t>
+          <t>狂战士-D</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="0" t="n">
-        <v>11000700004</v>
+        <v>11000700005</v>
       </c>
       <c r="C82" s="0" t="n">
         <v>11</v>
@@ -5901,7 +5910,7 @@
       </c>
       <c r="J82" s="0" t="inlineStr">
         <is>
-          <t>ATK:1|RCD:1</t>
+          <t>ATK:1|CMP:1</t>
         </is>
       </c>
       <c r="O82" s="0" t="n">
@@ -5920,20 +5929,20 @@
         <v>0</v>
       </c>
       <c r="W82" s="0" t="n">
-        <v>11000700004</v>
+        <v>11000700005</v>
       </c>
       <c r="X82" s="0" t="n">
-        <v>11000700004</v>
+        <v>11000700005</v>
       </c>
       <c r="Y82" s="0" t="inlineStr">
         <is>
-          <t>狂战士-D</t>
+          <t>狂战士-E</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="0" t="n">
-        <v>11000700005</v>
+        <v>11000800004</v>
       </c>
       <c r="C83" s="0" t="n">
         <v>11</v>
@@ -5951,7 +5960,7 @@
       </c>
       <c r="J83" s="0" t="inlineStr">
         <is>
-          <t>ATK:1|CMP:1</t>
+          <t>ASPD:1|RCD:1</t>
         </is>
       </c>
       <c r="O83" s="0" t="n">
@@ -5970,20 +5979,20 @@
         <v>0</v>
       </c>
       <c r="W83" s="0" t="n">
-        <v>11000700005</v>
+        <v>11000800004</v>
       </c>
       <c r="X83" s="0" t="n">
-        <v>11000700005</v>
+        <v>11000800004</v>
       </c>
       <c r="Y83" s="0" t="inlineStr">
         <is>
-          <t>狂战士-E</t>
+          <t>快枪手-D</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="0" t="n">
-        <v>11000800004</v>
+        <v>11000800005</v>
       </c>
       <c r="C84" s="0" t="n">
         <v>11</v>
@@ -6001,7 +6010,7 @@
       </c>
       <c r="J84" s="0" t="inlineStr">
         <is>
-          <t>ASPD:1|RCD:1</t>
+          <t>ASPD:1|CMP:1</t>
         </is>
       </c>
       <c r="O84" s="0" t="n">
@@ -6020,20 +6029,20 @@
         <v>0</v>
       </c>
       <c r="W84" s="0" t="n">
-        <v>11000800004</v>
+        <v>11000800005</v>
       </c>
       <c r="X84" s="0" t="n">
-        <v>11000800004</v>
+        <v>11000800005</v>
       </c>
       <c r="Y84" s="0" t="inlineStr">
         <is>
-          <t>快枪手-D</t>
+          <t>快枪手-E</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="0" t="n">
-        <v>11000800005</v>
+        <v>11000900004</v>
       </c>
       <c r="C85" s="0" t="n">
         <v>11</v>
@@ -6051,7 +6060,7 @@
       </c>
       <c r="J85" s="0" t="inlineStr">
         <is>
-          <t>ASPD:1|CMP:1</t>
+          <t>DR:1|RCD:1</t>
         </is>
       </c>
       <c r="O85" s="0" t="n">
@@ -6070,20 +6079,20 @@
         <v>0</v>
       </c>
       <c r="W85" s="0" t="n">
-        <v>11000800005</v>
+        <v>11000900004</v>
       </c>
       <c r="X85" s="0" t="n">
-        <v>11000800005</v>
+        <v>11000900004</v>
       </c>
       <c r="Y85" s="0" t="inlineStr">
         <is>
-          <t>快枪手-E</t>
+          <t>铜墙铁壁-D</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="0" t="n">
-        <v>11000900004</v>
+        <v>11000900005</v>
       </c>
       <c r="C86" s="0" t="n">
         <v>11</v>
@@ -6101,7 +6110,7 @@
       </c>
       <c r="J86" s="0" t="inlineStr">
         <is>
-          <t>DR:1|RCD:1</t>
+          <t>DR:1|CMP:1</t>
         </is>
       </c>
       <c r="O86" s="0" t="n">
@@ -6120,20 +6129,20 @@
         <v>0</v>
       </c>
       <c r="W86" s="0" t="n">
-        <v>11000900004</v>
+        <v>11000900005</v>
       </c>
       <c r="X86" s="0" t="n">
-        <v>11000900004</v>
+        <v>11000900005</v>
       </c>
       <c r="Y86" s="0" t="inlineStr">
         <is>
-          <t>铜墙铁壁-D</t>
+          <t>铜墙铁壁-E</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="0" t="n">
-        <v>11000900005</v>
+        <v>11001000004</v>
       </c>
       <c r="C87" s="0" t="n">
         <v>11</v>
@@ -6151,7 +6160,7 @@
       </c>
       <c r="J87" s="0" t="inlineStr">
         <is>
-          <t>DR:1|CMP:1</t>
+          <t>HP:1|RCD:1</t>
         </is>
       </c>
       <c r="O87" s="0" t="n">
@@ -6170,20 +6179,20 @@
         <v>0</v>
       </c>
       <c r="W87" s="0" t="n">
-        <v>11000900005</v>
+        <v>11001000004</v>
       </c>
       <c r="X87" s="0" t="n">
-        <v>11000900005</v>
+        <v>11001000004</v>
       </c>
       <c r="Y87" s="0" t="inlineStr">
         <is>
-          <t>铜墙铁壁-E</t>
+          <t>大块头-D</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="0" t="n">
-        <v>11001000004</v>
+        <v>11001000005</v>
       </c>
       <c r="C88" s="0" t="n">
         <v>11</v>
@@ -6201,7 +6210,7 @@
       </c>
       <c r="J88" s="0" t="inlineStr">
         <is>
-          <t>HP:1|RCD:1</t>
+          <t>HP:1|CMP:1</t>
         </is>
       </c>
       <c r="O88" s="0" t="n">
@@ -6220,20 +6229,20 @@
         <v>0</v>
       </c>
       <c r="W88" s="0" t="n">
-        <v>11001000004</v>
+        <v>11001000005</v>
       </c>
       <c r="X88" s="0" t="n">
-        <v>11001000004</v>
+        <v>11001000005</v>
       </c>
       <c r="Y88" s="0" t="inlineStr">
         <is>
-          <t>大块头-D</t>
+          <t>大块头-E</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="0" t="n">
-        <v>11001000005</v>
+        <v>11001100001</v>
       </c>
       <c r="C89" s="0" t="n">
         <v>11</v>
@@ -6251,15 +6260,15 @@
       </c>
       <c r="J89" s="0" t="inlineStr">
         <is>
-          <t>HP:1|CMP:1</t>
+          <t>RCD:-1|HP:-0.5</t>
         </is>
       </c>
       <c r="O89" s="0" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="P89" s="0" t="n">
         <v>0.5</v>
       </c>
-      <c r="P89" s="0" t="n">
-        <v>0.2</v>
-      </c>
       <c r="R89" s="0" t="n">
         <v>0</v>
       </c>
@@ -6270,20 +6279,20 @@
         <v>0</v>
       </c>
       <c r="W89" s="0" t="n">
-        <v>11001000005</v>
+        <v>11001100001</v>
       </c>
       <c r="X89" s="0" t="n">
-        <v>11001000005</v>
+        <v>11001100001</v>
       </c>
       <c r="Y89" s="0" t="inlineStr">
         <is>
-          <t>大块头-E</t>
+          <t>魂牵梦绕-A</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="0" t="n">
-        <v>11001100001</v>
+        <v>11001100002</v>
       </c>
       <c r="C90" s="0" t="n">
         <v>11</v>
@@ -6301,7 +6310,7 @@
       </c>
       <c r="J90" s="0" t="inlineStr">
         <is>
-          <t>RCD:-1|HP:-0.5</t>
+          <t>RCD:-1|DR:-0.5</t>
         </is>
       </c>
       <c r="O90" s="0" t="n">
@@ -6320,20 +6329,20 @@
         <v>0</v>
       </c>
       <c r="W90" s="0" t="n">
-        <v>11001100001</v>
+        <v>11001100002</v>
       </c>
       <c r="X90" s="0" t="n">
-        <v>11001100001</v>
+        <v>11001100002</v>
       </c>
       <c r="Y90" s="0" t="inlineStr">
         <is>
-          <t>魂牵梦绕-A</t>
+          <t>魂牵梦绕-B</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="0" t="n">
-        <v>11001100002</v>
+        <v>11001100003</v>
       </c>
       <c r="C91" s="0" t="n">
         <v>11</v>
@@ -6351,7 +6360,7 @@
       </c>
       <c r="J91" s="0" t="inlineStr">
         <is>
-          <t>RCD:-1|DR:-0.5</t>
+          <t>RCD:-1|ATK:-0.5</t>
         </is>
       </c>
       <c r="O91" s="0" t="n">
@@ -6370,20 +6379,20 @@
         <v>0</v>
       </c>
       <c r="W91" s="0" t="n">
-        <v>11001100002</v>
+        <v>11001100003</v>
       </c>
       <c r="X91" s="0" t="n">
-        <v>11001100002</v>
+        <v>11001100003</v>
       </c>
       <c r="Y91" s="0" t="inlineStr">
         <is>
-          <t>魂牵梦绕-B</t>
+          <t>魂牵梦绕-C</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="0" t="n">
-        <v>11001100003</v>
+        <v>11001100004</v>
       </c>
       <c r="C92" s="0" t="n">
         <v>11</v>
@@ -6401,7 +6410,7 @@
       </c>
       <c r="J92" s="0" t="inlineStr">
         <is>
-          <t>RCD:-1|ATK:-0.5</t>
+          <t>RCD:-1|ASPD:-0.5</t>
         </is>
       </c>
       <c r="O92" s="0" t="n">
@@ -6420,20 +6429,20 @@
         <v>0</v>
       </c>
       <c r="W92" s="0" t="n">
-        <v>11001100003</v>
+        <v>11001100004</v>
       </c>
       <c r="X92" s="0" t="n">
-        <v>11001100003</v>
+        <v>11001100004</v>
       </c>
       <c r="Y92" s="0" t="inlineStr">
         <is>
-          <t>魂牵梦绕-C</t>
+          <t>魂牵梦绕-D</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="0" t="n">
-        <v>11001100004</v>
+        <v>11001100005</v>
       </c>
       <c r="C93" s="0" t="n">
         <v>11</v>
@@ -6451,7 +6460,7 @@
       </c>
       <c r="J93" s="0" t="inlineStr">
         <is>
-          <t>RCD:-1|ASPD:-0.5</t>
+          <t>RCD:-1|CMP:0.5</t>
         </is>
       </c>
       <c r="O93" s="0" t="n">
@@ -6470,20 +6479,20 @@
         <v>0</v>
       </c>
       <c r="W93" s="0" t="n">
-        <v>11001100004</v>
+        <v>11001100005</v>
       </c>
       <c r="X93" s="0" t="n">
-        <v>11001100004</v>
+        <v>11001100005</v>
       </c>
       <c r="Y93" s="0" t="inlineStr">
         <is>
-          <t>魂牵梦绕-D</t>
+          <t>魂牵梦绕-E</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="0" t="n">
-        <v>11001100005</v>
+        <v>11001200001</v>
       </c>
       <c r="C94" s="0" t="n">
         <v>11</v>
@@ -6501,7 +6510,7 @@
       </c>
       <c r="J94" s="0" t="inlineStr">
         <is>
-          <t>RCD:-1|CMP:0.5</t>
+          <t>CMP:-1|HP:-0.5</t>
         </is>
       </c>
       <c r="O94" s="0" t="n">
@@ -6520,20 +6529,20 @@
         <v>0</v>
       </c>
       <c r="W94" s="0" t="n">
-        <v>11001100005</v>
+        <v>11001200001</v>
       </c>
       <c r="X94" s="0" t="n">
-        <v>11001100005</v>
+        <v>11001200001</v>
       </c>
       <c r="Y94" s="0" t="inlineStr">
         <is>
-          <t>魂牵梦绕-E</t>
+          <t>折上折-A</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="0" t="n">
-        <v>11001200001</v>
+        <v>11001200002</v>
       </c>
       <c r="C95" s="0" t="n">
         <v>11</v>
@@ -6551,7 +6560,7 @@
       </c>
       <c r="J95" s="0" t="inlineStr">
         <is>
-          <t>CMP:-1|HP:-0.5</t>
+          <t>CMP:-1|DR:-0.5</t>
         </is>
       </c>
       <c r="O95" s="0" t="n">
@@ -6570,20 +6579,20 @@
         <v>0</v>
       </c>
       <c r="W95" s="0" t="n">
-        <v>11001200001</v>
+        <v>11001200002</v>
       </c>
       <c r="X95" s="0" t="n">
-        <v>11001200001</v>
+        <v>11001200002</v>
       </c>
       <c r="Y95" s="0" t="inlineStr">
         <is>
-          <t>折上折-A</t>
+          <t>折上折-B</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="0" t="n">
-        <v>11001200002</v>
+        <v>11001200003</v>
       </c>
       <c r="C96" s="0" t="n">
         <v>11</v>
@@ -6601,7 +6610,7 @@
       </c>
       <c r="J96" s="0" t="inlineStr">
         <is>
-          <t>CMP:-1|DR:-0.5</t>
+          <t>CMP:-1|ATK:-0.5</t>
         </is>
       </c>
       <c r="O96" s="0" t="n">
@@ -6620,20 +6629,20 @@
         <v>0</v>
       </c>
       <c r="W96" s="0" t="n">
-        <v>11001200002</v>
+        <v>11001200003</v>
       </c>
       <c r="X96" s="0" t="n">
-        <v>11001200002</v>
+        <v>11001200003</v>
       </c>
       <c r="Y96" s="0" t="inlineStr">
         <is>
-          <t>折上折-B</t>
+          <t>折上折-C</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="0" t="n">
-        <v>11001200003</v>
+        <v>11001200004</v>
       </c>
       <c r="C97" s="0" t="n">
         <v>11</v>
@@ -6651,7 +6660,7 @@
       </c>
       <c r="J97" s="0" t="inlineStr">
         <is>
-          <t>CMP:-1|ATK:-0.5</t>
+          <t>CMP:-1|ASPD:-0.5</t>
         </is>
       </c>
       <c r="O97" s="0" t="n">
@@ -6670,20 +6679,20 @@
         <v>0</v>
       </c>
       <c r="W97" s="0" t="n">
-        <v>11001200003</v>
+        <v>11001200004</v>
       </c>
       <c r="X97" s="0" t="n">
-        <v>11001200003</v>
+        <v>11001200004</v>
       </c>
       <c r="Y97" s="0" t="inlineStr">
         <is>
-          <t>折上折-C</t>
+          <t>折上折-D</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="0" t="n">
-        <v>11001200004</v>
+        <v>11001200005</v>
       </c>
       <c r="C98" s="0" t="n">
         <v>11</v>
@@ -6701,7 +6710,7 @@
       </c>
       <c r="J98" s="0" t="inlineStr">
         <is>
-          <t>CMP:-1|ASPD:-0.5</t>
+          <t>CMP:-1|RCD:0.5</t>
         </is>
       </c>
       <c r="O98" s="0" t="n">
@@ -6720,48 +6729,40 @@
         <v>0</v>
       </c>
       <c r="W98" s="0" t="n">
-        <v>11001200004</v>
+        <v>11001200005</v>
       </c>
       <c r="X98" s="0" t="n">
-        <v>11001200004</v>
+        <v>11001200005</v>
       </c>
       <c r="Y98" s="0" t="inlineStr">
         <is>
-          <t>折上折-D</t>
+          <t>折上折-E</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="0" t="n">
-        <v>11001200005</v>
+        <v>12000100001</v>
       </c>
       <c r="C99" s="0" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D99" s="0" t="n">
-        <v>2</v>
-      </c>
-      <c r="G99" s="0" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H99" s="0" t="inlineStr">
         <is>
-          <t>BuffEntityAttributeMulti</t>
-        </is>
-      </c>
-      <c r="J99" s="0" t="inlineStr">
-        <is>
-          <t>CMP:-1|RCD:0.5</t>
+          <t>BuffEntityBaseHPChange</t>
         </is>
       </c>
       <c r="O99" s="0" t="n">
-        <v>0.75</v>
+        <v>0.05</v>
       </c>
       <c r="P99" s="0" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="R99" s="0" t="n">
-        <v>0</v>
+        <v>0.01</v>
+      </c>
+      <c r="S99" s="0" t="n">
+        <v>5</v>
       </c>
       <c r="T99" s="0" t="n">
         <v>0</v>
@@ -6769,21 +6770,24 @@
       <c r="U99" s="0" t="n">
         <v>0</v>
       </c>
+      <c r="V99" s="0" t="n">
+        <v>500001</v>
+      </c>
       <c r="W99" s="0" t="n">
-        <v>11001200005</v>
+        <v>12000100001</v>
       </c>
       <c r="X99" s="0" t="n">
-        <v>11001200005</v>
+        <v>12000100001</v>
       </c>
       <c r="Y99" s="0" t="inlineStr">
         <is>
-          <t>折上折-E</t>
+          <t>每隔{Time_S}秒恢复{Percentage}%生命</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="0" t="n">
-        <v>12000100001</v>
+        <v>12000200001</v>
       </c>
       <c r="C100" s="0" t="n">
         <v>12</v>
@@ -6793,7 +6797,7 @@
       </c>
       <c r="H100" s="0" t="inlineStr">
         <is>
-          <t>BuffEntityBaseHPChange</t>
+          <t>BuffEntityBaseDRChange</t>
         </is>
       </c>
       <c r="O100" s="0" t="n">
@@ -6815,20 +6819,20 @@
         <v>500001</v>
       </c>
       <c r="W100" s="0" t="n">
-        <v>12000100001</v>
+        <v>12000200001</v>
       </c>
       <c r="X100" s="0" t="n">
-        <v>12000100001</v>
+        <v>12000200001</v>
       </c>
       <c r="Y100" s="0" t="inlineStr">
         <is>
-          <t>每隔{Time_S}秒恢复{Percentage}%生命</t>
+          <t>每隔{Time_S}秒恢复{Percentage}%护甲</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="0" t="n">
-        <v>12000200001</v>
+        <v>12000300001</v>
       </c>
       <c r="C101" s="0" t="n">
         <v>12</v>
@@ -6838,14 +6842,8 @@
       </c>
       <c r="H101" s="0" t="inlineStr">
         <is>
-          <t>BuffEntityBaseDRChange</t>
-        </is>
-      </c>
-      <c r="O101" s="0" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="P101" s="0" t="n">
-        <v>0.01</v>
+          <t>BuffEntityPeriodicAttackAgain</t>
+        </is>
       </c>
       <c r="S101" s="0" t="n">
         <v>5</v>
@@ -6856,24 +6854,21 @@
       <c r="U101" s="0" t="n">
         <v>0</v>
       </c>
-      <c r="V101" s="0" t="n">
-        <v>500001</v>
-      </c>
       <c r="W101" s="0" t="n">
-        <v>12000200001</v>
+        <v>12000300001</v>
       </c>
       <c r="X101" s="0" t="n">
-        <v>12000200001</v>
+        <v>12000300001</v>
       </c>
       <c r="Y101" s="0" t="inlineStr">
         <is>
-          <t>每隔{Time_S}秒恢复{Percentage}%护甲</t>
+          <t>每隔{Time_S}秒立即攻击一次</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="0" t="n">
-        <v>12000300001</v>
+        <v>12001100001</v>
       </c>
       <c r="C102" s="0" t="n">
         <v>12</v>
@@ -6883,11 +6878,29 @@
       </c>
       <c r="H102" s="0" t="inlineStr">
         <is>
-          <t>BuffEntityPeriodicAttackAgain</t>
-        </is>
-      </c>
-      <c r="S102" s="0" t="n">
-        <v>5</v>
+          <t>BuffEntityConditionalAttribute</t>
+        </is>
+      </c>
+      <c r="I102" s="0" t="inlineStr">
+        <is>
+          <t>GameFightLogic_UnderAttack_Dead</t>
+        </is>
+      </c>
+      <c r="J102" s="0" t="inlineStr">
+        <is>
+          <t>HP</t>
+        </is>
+      </c>
+      <c r="L102" s="0" t="inlineStr">
+        <is>
+          <t>2001:10&amp;</t>
+        </is>
+      </c>
+      <c r="O102" s="0" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="P102" s="0" t="n">
+        <v>0.1</v>
       </c>
       <c r="T102" s="0" t="n">
         <v>0</v>
@@ -6896,20 +6909,20 @@
         <v>0</v>
       </c>
       <c r="W102" s="0" t="n">
-        <v>12000300001</v>
+        <v>12001100001</v>
       </c>
       <c r="X102" s="0" t="n">
-        <v>12000300001</v>
+        <v>12001100001</v>
       </c>
       <c r="Y102" s="0" t="inlineStr">
         <is>
-          <t>每隔{Time_S}秒立即攻击一次</t>
+          <t>击杀{KillNum}次生物，生命增加{Percentage}%</t>
         </is>
       </c>
     </row>
     <row r="103" ht="12" customHeight="1" s="3">
       <c r="A103" s="0" t="n">
-        <v>12001100001</v>
+        <v>12001200001</v>
       </c>
       <c r="C103" s="0" t="n">
         <v>12</v>
@@ -6929,7 +6942,7 @@
       </c>
       <c r="J103" s="0" t="inlineStr">
         <is>
-          <t>HP</t>
+          <t>DR</t>
         </is>
       </c>
       <c r="L103" s="0" t="inlineStr">
@@ -6950,20 +6963,20 @@
         <v>0</v>
       </c>
       <c r="W103" s="0" t="n">
-        <v>12001100001</v>
+        <v>12001200001</v>
       </c>
       <c r="X103" s="0" t="n">
-        <v>12001100001</v>
+        <v>12001200001</v>
       </c>
       <c r="Y103" s="0" t="inlineStr">
         <is>
-          <t>击杀{KillNum}次生物，生命增加{Percentage}%</t>
+          <t>击杀{KillNum}次生物，护甲增加{Percentage}%</t>
         </is>
       </c>
     </row>
     <row r="104" ht="12" customHeight="1" s="3">
       <c r="A104" s="0" t="n">
-        <v>12001200001</v>
+        <v>12001300001</v>
       </c>
       <c r="C104" s="0" t="n">
         <v>12</v>
@@ -6983,7 +6996,7 @@
       </c>
       <c r="J104" s="0" t="inlineStr">
         <is>
-          <t>DR</t>
+          <t>ATK</t>
         </is>
       </c>
       <c r="L104" s="0" t="inlineStr">
@@ -7004,20 +7017,20 @@
         <v>0</v>
       </c>
       <c r="W104" s="0" t="n">
-        <v>12001200001</v>
+        <v>12001300001</v>
       </c>
       <c r="X104" s="0" t="n">
-        <v>12001200001</v>
+        <v>12001300001</v>
       </c>
       <c r="Y104" s="0" t="inlineStr">
         <is>
-          <t>击杀{KillNum}次生物，护甲增加{Percentage}%</t>
+          <t>击杀{KillNum}次生物，攻击力增加{Percentage}%</t>
         </is>
       </c>
     </row>
     <row r="105" ht="12" customHeight="1" s="3">
       <c r="A105" s="0" t="n">
-        <v>12001300001</v>
+        <v>12001400001</v>
       </c>
       <c r="C105" s="0" t="n">
         <v>12</v>
@@ -7037,7 +7050,7 @@
       </c>
       <c r="J105" s="0" t="inlineStr">
         <is>
-          <t>ATK</t>
+          <t>ASPD</t>
         </is>
       </c>
       <c r="L105" s="0" t="inlineStr">
@@ -7058,20 +7071,20 @@
         <v>0</v>
       </c>
       <c r="W105" s="0" t="n">
-        <v>12001300001</v>
+        <v>12001400001</v>
       </c>
       <c r="X105" s="0" t="n">
-        <v>12001300001</v>
+        <v>12001400001</v>
       </c>
       <c r="Y105" s="0" t="inlineStr">
         <is>
-          <t>击杀{KillNum}次生物，攻击力增加{Percentage}%</t>
+          <t>击杀{KillNum}次生物，攻击速度增加{Percentage}%</t>
         </is>
       </c>
     </row>
     <row r="106" ht="12" customHeight="1" s="3">
       <c r="A106" s="0" t="n">
-        <v>12001400001</v>
+        <v>12002100001</v>
       </c>
       <c r="C106" s="0" t="n">
         <v>12</v>
@@ -7086,17 +7099,17 @@
       </c>
       <c r="I106" s="0" t="inlineStr">
         <is>
-          <t>GameFightLogic_UnderAttack_Dead</t>
+          <t>GameFightLogic_UnderAttack</t>
         </is>
       </c>
       <c r="J106" s="0" t="inlineStr">
         <is>
-          <t>ASPD</t>
+          <t>HP</t>
         </is>
       </c>
       <c r="L106" s="0" t="inlineStr">
         <is>
-          <t>2001:10&amp;</t>
+          <t>3001:100&amp;</t>
         </is>
       </c>
       <c r="O106" s="0" t="n">
@@ -7112,20 +7125,20 @@
         <v>0</v>
       </c>
       <c r="W106" s="0" t="n">
-        <v>12001400001</v>
+        <v>12002100001</v>
       </c>
       <c r="X106" s="0" t="n">
-        <v>12001400001</v>
+        <v>12002100001</v>
       </c>
       <c r="Y106" s="0" t="inlineStr">
         <is>
-          <t>击杀{KillNum}次生物，攻击速度增加{Percentage}%</t>
+          <t>受到{UnderAttackDamage}点伤害，生命增加{Percentage}%</t>
         </is>
       </c>
     </row>
     <row r="107" ht="12" customHeight="1" s="3">
       <c r="A107" s="0" t="n">
-        <v>12002100001</v>
+        <v>12002200001</v>
       </c>
       <c r="C107" s="0" t="n">
         <v>12</v>
@@ -7145,7 +7158,7 @@
       </c>
       <c r="J107" s="0" t="inlineStr">
         <is>
-          <t>HP</t>
+          <t>DR</t>
         </is>
       </c>
       <c r="L107" s="0" t="inlineStr">
@@ -7166,20 +7179,20 @@
         <v>0</v>
       </c>
       <c r="W107" s="0" t="n">
-        <v>12002100001</v>
+        <v>12002200001</v>
       </c>
       <c r="X107" s="0" t="n">
-        <v>12002100001</v>
+        <v>12002200001</v>
       </c>
       <c r="Y107" s="0" t="inlineStr">
         <is>
-          <t>受到{UnderAttackDamage}点伤害，生命增加{Percentage}%</t>
+          <t>受到{UnderAttackDamage}点伤害，护甲增加{Percentage}%</t>
         </is>
       </c>
     </row>
     <row r="108" ht="12" customHeight="1" s="3">
       <c r="A108" s="0" t="n">
-        <v>12002200001</v>
+        <v>12002300001</v>
       </c>
       <c r="C108" s="0" t="n">
         <v>12</v>
@@ -7199,7 +7212,7 @@
       </c>
       <c r="J108" s="0" t="inlineStr">
         <is>
-          <t>DR</t>
+          <t>ATK</t>
         </is>
       </c>
       <c r="L108" s="0" t="inlineStr">
@@ -7220,20 +7233,20 @@
         <v>0</v>
       </c>
       <c r="W108" s="0" t="n">
-        <v>12002200001</v>
+        <v>12002300001</v>
       </c>
       <c r="X108" s="0" t="n">
-        <v>12002200001</v>
+        <v>12002300001</v>
       </c>
       <c r="Y108" s="0" t="inlineStr">
         <is>
-          <t>受到{UnderAttackDamage}点伤害，护甲增加{Percentage}%</t>
+          <t>受到{UnderAttackDamage}点伤害，攻击力增加{Percentage}%</t>
         </is>
       </c>
     </row>
     <row r="109" ht="12" customHeight="1" s="3">
       <c r="A109" s="0" t="n">
-        <v>12002300001</v>
+        <v>12002400001</v>
       </c>
       <c r="C109" s="0" t="n">
         <v>12</v>
@@ -7253,7 +7266,7 @@
       </c>
       <c r="J109" s="0" t="inlineStr">
         <is>
-          <t>ATK</t>
+          <t>ASPD</t>
         </is>
       </c>
       <c r="L109" s="0" t="inlineStr">
@@ -7274,20 +7287,20 @@
         <v>0</v>
       </c>
       <c r="W109" s="0" t="n">
-        <v>12002300001</v>
+        <v>12002400001</v>
       </c>
       <c r="X109" s="0" t="n">
-        <v>12002300001</v>
+        <v>12002400001</v>
       </c>
       <c r="Y109" s="0" t="inlineStr">
         <is>
-          <t>受到{UnderAttackDamage}点伤害，攻击力增加{Percentage}%</t>
+          <t>受到{UnderAttackDamage}点伤害，攻击速度增加{Percentage}%</t>
         </is>
       </c>
     </row>
     <row r="110" ht="12" customHeight="1" s="3">
       <c r="A110" s="0" t="n">
-        <v>12002400001</v>
+        <v>12003100001</v>
       </c>
       <c r="C110" s="0" t="n">
         <v>12</v>
@@ -7307,12 +7320,12 @@
       </c>
       <c r="J110" s="0" t="inlineStr">
         <is>
-          <t>ASPD</t>
+          <t>HP</t>
         </is>
       </c>
       <c r="L110" s="0" t="inlineStr">
         <is>
-          <t>3001:100&amp;</t>
+          <t>1001:0.5&amp;</t>
         </is>
       </c>
       <c r="O110" s="0" t="n">
@@ -7328,20 +7341,20 @@
         <v>0</v>
       </c>
       <c r="W110" s="0" t="n">
-        <v>12002400001</v>
+        <v>12003100001</v>
       </c>
       <c r="X110" s="0" t="n">
-        <v>12002400001</v>
+        <v>12003100001</v>
       </c>
       <c r="Y110" s="0" t="inlineStr">
         <is>
-          <t>受到{UnderAttackDamage}点伤害，攻击速度增加{Percentage}%</t>
+          <t>血量少于{HPRateLess}%，生命增加{Percentage}%</t>
         </is>
       </c>
     </row>
     <row r="111" ht="12" customHeight="1" s="3">
       <c r="A111" s="0" t="n">
-        <v>12003100001</v>
+        <v>12003200001</v>
       </c>
       <c r="C111" s="0" t="n">
         <v>12</v>
@@ -7361,7 +7374,7 @@
       </c>
       <c r="J111" s="0" t="inlineStr">
         <is>
-          <t>HP</t>
+          <t>DR</t>
         </is>
       </c>
       <c r="L111" s="0" t="inlineStr">
@@ -7382,20 +7395,20 @@
         <v>0</v>
       </c>
       <c r="W111" s="0" t="n">
-        <v>12003100001</v>
+        <v>12003200001</v>
       </c>
       <c r="X111" s="0" t="n">
-        <v>12003100001</v>
+        <v>12003200001</v>
       </c>
       <c r="Y111" s="0" t="inlineStr">
         <is>
-          <t>血量少于{HPRateLess}%，生命增加{Percentage}%</t>
+          <t>血量少于{HPRateLess}%，护甲增加{Percentage}%</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="0" t="n">
-        <v>12003200001</v>
+        <v>12003300001</v>
       </c>
       <c r="C112" s="0" t="n">
         <v>12</v>
@@ -7415,7 +7428,7 @@
       </c>
       <c r="J112" s="0" t="inlineStr">
         <is>
-          <t>DR</t>
+          <t>ATK</t>
         </is>
       </c>
       <c r="L112" s="0" t="inlineStr">
@@ -7436,20 +7449,20 @@
         <v>0</v>
       </c>
       <c r="W112" s="0" t="n">
-        <v>12003200001</v>
+        <v>12003300001</v>
       </c>
       <c r="X112" s="0" t="n">
-        <v>12003200001</v>
+        <v>12003300001</v>
       </c>
       <c r="Y112" s="0" t="inlineStr">
         <is>
-          <t>血量少于{HPRateLess}%，护甲增加{Percentage}%</t>
+          <t>血量少于{HPRateLess}%，攻击力增加{Percentage}%</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="0" t="n">
-        <v>12003300001</v>
+        <v>12003400001</v>
       </c>
       <c r="C113" s="0" t="n">
         <v>12</v>
@@ -7469,7 +7482,7 @@
       </c>
       <c r="J113" s="0" t="inlineStr">
         <is>
-          <t>ATK</t>
+          <t>ASPD</t>
         </is>
       </c>
       <c r="L113" s="0" t="inlineStr">
@@ -7490,20 +7503,20 @@
         <v>0</v>
       </c>
       <c r="W113" s="0" t="n">
-        <v>12003300001</v>
+        <v>12003400001</v>
       </c>
       <c r="X113" s="0" t="n">
-        <v>12003300001</v>
+        <v>12003400001</v>
       </c>
       <c r="Y113" s="0" t="inlineStr">
         <is>
-          <t>血量少于{HPRateLess}%，攻击力增加{Percentage}%</t>
+          <t>血量少于{HPRateLess}%，攻击速度增加{Percentage}%</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="0" t="n">
-        <v>12003400001</v>
+        <v>12004100001</v>
       </c>
       <c r="C114" s="0" t="n">
         <v>12</v>
@@ -7513,22 +7526,18 @@
       </c>
       <c r="H114" s="0" t="inlineStr">
         <is>
-          <t>BuffEntityConditionalAttribute</t>
-        </is>
-      </c>
-      <c r="I114" s="0" t="inlineStr">
-        <is>
-          <t>GameFightLogic_UnderAttack</t>
-        </is>
-      </c>
+          <t>BuffEntityConditionalAttributeTime</t>
+        </is>
+      </c>
+      <c r="I114" s="0" t="inlineStr"/>
       <c r="J114" s="0" t="inlineStr">
         <is>
-          <t>ASPD</t>
+          <t>HP</t>
         </is>
       </c>
       <c r="L114" s="0" t="inlineStr">
         <is>
-          <t>1001:0.5&amp;</t>
+          <t>7001:300&amp;</t>
         </is>
       </c>
       <c r="O114" s="0" t="n">
@@ -7544,20 +7553,20 @@
         <v>0</v>
       </c>
       <c r="W114" s="0" t="n">
-        <v>12003400001</v>
+        <v>12004100001</v>
       </c>
       <c r="X114" s="0" t="n">
-        <v>12003400001</v>
+        <v>12004100001</v>
       </c>
       <c r="Y114" s="0" t="inlineStr">
         <is>
-          <t>血量少于{HPRateLess}%，攻击速度增加{Percentage}%</t>
+          <t>在场存活超过{OnFieldTime}秒后，生命增加{Percentage}%</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="0" t="n">
-        <v>12004100001</v>
+        <v>12004200001</v>
       </c>
       <c r="C115" s="0" t="n">
         <v>12</v>
@@ -7573,7 +7582,7 @@
       <c r="I115" s="0" t="inlineStr"/>
       <c r="J115" s="0" t="inlineStr">
         <is>
-          <t>HP</t>
+          <t>DR</t>
         </is>
       </c>
       <c r="L115" s="0" t="inlineStr">
@@ -7594,20 +7603,20 @@
         <v>0</v>
       </c>
       <c r="W115" s="0" t="n">
-        <v>12004100001</v>
+        <v>12004200001</v>
       </c>
       <c r="X115" s="0" t="n">
-        <v>12004100001</v>
+        <v>12004200001</v>
       </c>
       <c r="Y115" s="0" t="inlineStr">
         <is>
-          <t>在场存活超过{OnFieldTime}秒后，生命增加{Percentage}%</t>
+          <t>在场存活超过{OnFieldTime}秒后，护甲增加{Percentage}%</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="0" t="n">
-        <v>12004200001</v>
+        <v>12004300001</v>
       </c>
       <c r="C116" s="0" t="n">
         <v>12</v>
@@ -7623,7 +7632,7 @@
       <c r="I116" s="0" t="inlineStr"/>
       <c r="J116" s="0" t="inlineStr">
         <is>
-          <t>DR</t>
+          <t>ATK</t>
         </is>
       </c>
       <c r="L116" s="0" t="inlineStr">
@@ -7644,20 +7653,20 @@
         <v>0</v>
       </c>
       <c r="W116" s="0" t="n">
-        <v>12004200001</v>
+        <v>12004300001</v>
       </c>
       <c r="X116" s="0" t="n">
-        <v>12004200001</v>
+        <v>12004300001</v>
       </c>
       <c r="Y116" s="0" t="inlineStr">
         <is>
-          <t>在场存活超过{OnFieldTime}秒后，护甲增加{Percentage}%</t>
+          <t>在场存活超过{OnFieldTime}秒后，攻击力增加{Percentage}%</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="0" t="n">
-        <v>12004300001</v>
+        <v>12004400001</v>
       </c>
       <c r="C117" s="0" t="n">
         <v>12</v>
@@ -7673,7 +7682,7 @@
       <c r="I117" s="0" t="inlineStr"/>
       <c r="J117" s="0" t="inlineStr">
         <is>
-          <t>ATK</t>
+          <t>ASPD</t>
         </is>
       </c>
       <c r="L117" s="0" t="inlineStr">
@@ -7694,20 +7703,20 @@
         <v>0</v>
       </c>
       <c r="W117" s="0" t="n">
-        <v>12004300001</v>
+        <v>12004400001</v>
       </c>
       <c r="X117" s="0" t="n">
-        <v>12004300001</v>
+        <v>12004400001</v>
       </c>
       <c r="Y117" s="0" t="inlineStr">
         <is>
-          <t>在场存活超过{OnFieldTime}秒后，攻击力增加{Percentage}%</t>
+          <t>在场存活超过{OnFieldTime}秒后，攻击速度增加{Percentage}%</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="0" t="n">
-        <v>12004400001</v>
+        <v>12010100001</v>
       </c>
       <c r="C118" s="0" t="n">
         <v>12</v>
@@ -7717,25 +7726,18 @@
       </c>
       <c r="H118" s="0" t="inlineStr">
         <is>
-          <t>BuffEntityConditionalAttributeTime</t>
-        </is>
-      </c>
-      <c r="I118" s="0" t="inlineStr"/>
-      <c r="J118" s="0" t="inlineStr">
-        <is>
-          <t>ASPD</t>
+          <t>BuffEntityConditionalCreateCrystal</t>
+        </is>
+      </c>
+      <c r="I118" s="0" t="inlineStr">
+        <is>
+          <t>GameFightLogic_UnderAttack_Dead</t>
         </is>
       </c>
       <c r="L118" s="0" t="inlineStr">
         <is>
-          <t>7001:300&amp;</t>
-        </is>
-      </c>
-      <c r="O118" s="0" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="P118" s="0" t="n">
-        <v>0.1</v>
+          <t>2001:10&amp;</t>
+        </is>
       </c>
       <c r="T118" s="0" t="n">
         <v>0</v>
@@ -7744,20 +7746,20 @@
         <v>0</v>
       </c>
       <c r="W118" s="0" t="n">
-        <v>12004400001</v>
+        <v>12010100001</v>
       </c>
       <c r="X118" s="0" t="n">
-        <v>12004400001</v>
+        <v>12010100001</v>
       </c>
       <c r="Y118" s="0" t="inlineStr">
         <is>
-          <t>在场存活超过{OnFieldTime}秒后，攻击速度增加{Percentage}%</t>
+          <t>击杀{KillNum}次生物，掉落一次魔晶</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="0" t="n">
-        <v>12010100001</v>
+        <v>12010200001</v>
       </c>
       <c r="C119" s="0" t="n">
         <v>12</v>
@@ -7772,12 +7774,12 @@
       </c>
       <c r="I119" s="0" t="inlineStr">
         <is>
-          <t>GameFightLogic_UnderAttack_Dead</t>
+          <t>GameFightLogic_UnderAttack</t>
         </is>
       </c>
       <c r="L119" s="0" t="inlineStr">
         <is>
-          <t>2001:10&amp;</t>
+          <t>3001:100&amp;</t>
         </is>
       </c>
       <c r="T119" s="0" t="n">
@@ -7787,20 +7789,20 @@
         <v>0</v>
       </c>
       <c r="W119" s="0" t="n">
-        <v>12010100001</v>
+        <v>12010200001</v>
       </c>
       <c r="X119" s="0" t="n">
-        <v>12010100001</v>
+        <v>12010200001</v>
       </c>
       <c r="Y119" s="0" t="inlineStr">
         <is>
-          <t>击杀{KillNum}次生物，掉落一次魔晶</t>
+          <t>受到{UnderAttackDamage}点伤害，掉落一次魔晶</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="0" t="n">
-        <v>12010200001</v>
+        <v>12010300001</v>
       </c>
       <c r="C120" s="0" t="n">
         <v>12</v>
@@ -7820,7 +7822,7 @@
       </c>
       <c r="L120" s="0" t="inlineStr">
         <is>
-          <t>3001:100&amp;</t>
+          <t>4001:1000&amp;</t>
         </is>
       </c>
       <c r="T120" s="0" t="n">
@@ -7830,20 +7832,20 @@
         <v>0</v>
       </c>
       <c r="W120" s="0" t="n">
-        <v>12010200001</v>
+        <v>12010300001</v>
       </c>
       <c r="X120" s="0" t="n">
-        <v>12010200001</v>
+        <v>12010300001</v>
       </c>
       <c r="Y120" s="0" t="inlineStr">
         <is>
-          <t>受到{UnderAttackDamage}点伤害，掉落一次魔晶</t>
+          <t>造成{AttackDamage}点伤害，掉落一次魔晶</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="0" t="n">
-        <v>12010300001</v>
+        <v>12010400001</v>
       </c>
       <c r="C121" s="0" t="n">
         <v>12</v>
@@ -7858,12 +7860,12 @@
       </c>
       <c r="I121" s="0" t="inlineStr">
         <is>
-          <t>GameFightLogic_UnderAttack</t>
+          <t>GameFightLogic_RegainHP</t>
         </is>
       </c>
       <c r="L121" s="0" t="inlineStr">
         <is>
-          <t>4001:1000&amp;</t>
+          <t>5001:500&amp;</t>
         </is>
       </c>
       <c r="T121" s="0" t="n">
@@ -7873,20 +7875,20 @@
         <v>0</v>
       </c>
       <c r="W121" s="0" t="n">
-        <v>12010300001</v>
+        <v>12010400001</v>
       </c>
       <c r="X121" s="0" t="n">
-        <v>12010300001</v>
+        <v>12010400001</v>
       </c>
       <c r="Y121" s="0" t="inlineStr">
         <is>
-          <t>造成{AttackDamage}点伤害，掉落一次魔晶</t>
+          <t>累计被治疗{RegainHPReceived}点，掉落一次魔晶</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="0" t="n">
-        <v>12010400001</v>
+        <v>12010500001</v>
       </c>
       <c r="C122" s="0" t="n">
         <v>12</v>
@@ -7906,7 +7908,7 @@
       </c>
       <c r="L122" s="0" t="inlineStr">
         <is>
-          <t>5001:500&amp;</t>
+          <t>6001:1000&amp;</t>
         </is>
       </c>
       <c r="T122" s="0" t="n">
@@ -7916,20 +7918,20 @@
         <v>0</v>
       </c>
       <c r="W122" s="0" t="n">
-        <v>12010400001</v>
+        <v>12010500001</v>
       </c>
       <c r="X122" s="0" t="n">
-        <v>12010400001</v>
+        <v>12010500001</v>
       </c>
       <c r="Y122" s="0" t="inlineStr">
         <is>
-          <t>累计被治疗{RegainHPReceived}点，掉落一次魔晶</t>
+          <t>累计治疗{RegainHPCast}点，掉落一次魔晶</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="0" t="n">
-        <v>12010500001</v>
+        <v>12011100001</v>
       </c>
       <c r="C123" s="0" t="n">
         <v>12</v>
@@ -7939,17 +7941,17 @@
       </c>
       <c r="H123" s="0" t="inlineStr">
         <is>
-          <t>BuffEntityConditionalCreateCrystal</t>
+          <t>BuffEntityConditionalAttackAgain</t>
         </is>
       </c>
       <c r="I123" s="0" t="inlineStr">
         <is>
-          <t>GameFightLogic_RegainHP</t>
+          <t>GameFightLogic_UnderAttack_Dead</t>
         </is>
       </c>
       <c r="L123" s="0" t="inlineStr">
         <is>
-          <t>6001:1000&amp;</t>
+          <t>2001:1&amp;</t>
         </is>
       </c>
       <c r="T123" s="0" t="n">
@@ -7959,20 +7961,20 @@
         <v>0</v>
       </c>
       <c r="W123" s="0" t="n">
-        <v>12010500001</v>
+        <v>12011100001</v>
       </c>
       <c r="X123" s="0" t="n">
-        <v>12010500001</v>
+        <v>12011100001</v>
       </c>
       <c r="Y123" s="0" t="inlineStr">
         <is>
-          <t>累计治疗{RegainHPCast}点，掉落一次魔晶</t>
+          <t>击杀{KillNum}次生物，立即攻击一次</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="0" t="n">
-        <v>12011100001</v>
+        <v>12011200001</v>
       </c>
       <c r="C124" s="0" t="n">
         <v>12</v>
@@ -7987,12 +7989,12 @@
       </c>
       <c r="I124" s="0" t="inlineStr">
         <is>
-          <t>GameFightLogic_UnderAttack_Dead</t>
+          <t>GameFightLogic_UnderAttack</t>
         </is>
       </c>
       <c r="L124" s="0" t="inlineStr">
         <is>
-          <t>2001:1&amp;</t>
+          <t>3001:100&amp;</t>
         </is>
       </c>
       <c r="T124" s="0" t="n">
@@ -8002,20 +8004,20 @@
         <v>0</v>
       </c>
       <c r="W124" s="0" t="n">
-        <v>12011100001</v>
+        <v>12011200001</v>
       </c>
       <c r="X124" s="0" t="n">
-        <v>12011100001</v>
+        <v>12011200001</v>
       </c>
       <c r="Y124" s="0" t="inlineStr">
         <is>
-          <t>击杀{KillNum}次生物，立即攻击一次</t>
+          <t>受到{UnderAttackDamage}点伤害，秒再攻击一次</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="0" t="n">
-        <v>12011200001</v>
+        <v>12011300001</v>
       </c>
       <c r="C125" s="0" t="n">
         <v>12</v>
@@ -8035,7 +8037,7 @@
       </c>
       <c r="L125" s="0" t="inlineStr">
         <is>
-          <t>3001:100&amp;</t>
+          <t>4001:200&amp;</t>
         </is>
       </c>
       <c r="T125" s="0" t="n">
@@ -8045,20 +8047,20 @@
         <v>0</v>
       </c>
       <c r="W125" s="0" t="n">
-        <v>12011200001</v>
+        <v>12011300001</v>
       </c>
       <c r="X125" s="0" t="n">
-        <v>12011200001</v>
+        <v>12011300001</v>
       </c>
       <c r="Y125" s="0" t="inlineStr">
         <is>
-          <t>受到{UnderAttackDamage}点伤害，秒再攻击一次</t>
+          <t>造成{AttackDamage}点伤害，秒再攻击一次</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="0" t="n">
-        <v>12011300001</v>
+        <v>12012100001</v>
       </c>
       <c r="C126" s="0" t="n">
         <v>12</v>
@@ -8068,18 +8070,24 @@
       </c>
       <c r="H126" s="0" t="inlineStr">
         <is>
-          <t>BuffEntityConditionalAttackAgain</t>
+          <t>BuffEntityConditionalDemonLordMPRegain</t>
         </is>
       </c>
       <c r="I126" s="0" t="inlineStr">
         <is>
-          <t>GameFightLogic_UnderAttack</t>
+          <t>GameFightLogic_UnderAttack_Dead</t>
         </is>
       </c>
       <c r="L126" s="0" t="inlineStr">
         <is>
-          <t>4001:200&amp;</t>
-        </is>
+          <t>2001:1&amp;</t>
+        </is>
+      </c>
+      <c r="M126" s="0" t="n">
+        <v>20</v>
+      </c>
+      <c r="N126" s="0" t="n">
+        <v>10</v>
       </c>
       <c r="T126" s="0" t="n">
         <v>0</v>
@@ -8088,20 +8096,20 @@
         <v>0</v>
       </c>
       <c r="W126" s="0" t="n">
-        <v>12011300001</v>
+        <v>12012100001</v>
       </c>
       <c r="X126" s="0" t="n">
-        <v>12011300001</v>
+        <v>12012100001</v>
       </c>
       <c r="Y126" s="0" t="inlineStr">
         <is>
-          <t>造成{AttackDamage}点伤害，秒再攻击一次</t>
+          <t>每击杀{KillNum}个生物，魔王回复{Value}点魔力</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" s="0" t="n">
-        <v>12012100001</v>
+        <v>12012200001</v>
       </c>
       <c r="C127" s="0" t="n">
         <v>12</v>
@@ -8116,12 +8124,12 @@
       </c>
       <c r="I127" s="0" t="inlineStr">
         <is>
-          <t>GameFightLogic_UnderAttack_Dead</t>
+          <t>GameFightLogic_UnderAttack</t>
         </is>
       </c>
       <c r="L127" s="0" t="inlineStr">
         <is>
-          <t>2001:1&amp;</t>
+          <t>3001:100&amp;</t>
         </is>
       </c>
       <c r="M127" s="0" t="n">
@@ -8137,47 +8145,40 @@
         <v>0</v>
       </c>
       <c r="W127" s="0" t="n">
-        <v>12012100001</v>
+        <v>12012200001</v>
       </c>
       <c r="X127" s="0" t="n">
-        <v>12012100001</v>
+        <v>12012200001</v>
       </c>
       <c r="Y127" s="0" t="inlineStr">
         <is>
-          <t>每击杀{KillNum}个生物，魔王回复{Value}点魔力</t>
+          <t>累计受到{UnderAttackDamage}点伤害，魔王回复{Value}点魔力</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" s="0" t="n">
-        <v>12012200001</v>
+        <v>13000100001</v>
       </c>
       <c r="C128" s="0" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D128" s="0" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H128" s="0" t="inlineStr">
         <is>
-          <t>BuffEntityConditionalDemonLordMPRegain</t>
-        </is>
-      </c>
-      <c r="I128" s="0" t="inlineStr">
-        <is>
-          <t>GameFightLogic_UnderAttack</t>
-        </is>
-      </c>
-      <c r="L128" s="0" t="inlineStr">
-        <is>
-          <t>3001:100&amp;</t>
+          <t>BuffEntityPeriodicPickupCrystal</t>
         </is>
       </c>
       <c r="M128" s="0" t="n">
-        <v>20</v>
+        <v>3</v>
       </c>
       <c r="N128" s="0" t="n">
-        <v>10</v>
+        <v>1</v>
+      </c>
+      <c r="S128" s="0" t="n">
+        <v>3</v>
       </c>
       <c r="T128" s="0" t="n">
         <v>0</v>
@@ -8186,20 +8187,20 @@
         <v>0</v>
       </c>
       <c r="W128" s="0" t="n">
-        <v>12012200001</v>
+        <v>13000100001</v>
       </c>
       <c r="X128" s="0" t="n">
-        <v>12012200001</v>
+        <v>13000100001</v>
       </c>
       <c r="Y128" s="0" t="inlineStr">
         <is>
-          <t>累计受到{UnderAttackDamage}点伤害，魔王回复{Value}点魔力</t>
+          <t>每隔{Time_S}秒自动拾取附近魔晶</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" s="0" t="n">
-        <v>13000100001</v>
+        <v>13000200001</v>
       </c>
       <c r="C129" s="0" t="n">
         <v>13</v>
@@ -8209,17 +8210,13 @@
       </c>
       <c r="H129" s="0" t="inlineStr">
         <is>
-          <t>BuffEntityPeriodicPickupCrystal</t>
-        </is>
-      </c>
-      <c r="M129" s="0" t="n">
-        <v>3</v>
-      </c>
-      <c r="N129" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="S129" s="0" t="n">
-        <v>3</v>
+          <t>BuffEntityConditionalDeadRebirth</t>
+        </is>
+      </c>
+      <c r="I129" s="0" t="inlineStr">
+        <is>
+          <t>GameFightLogic_CreatureDeadEnd</t>
+        </is>
       </c>
       <c r="T129" s="0" t="n">
         <v>0</v>
@@ -8227,21 +8224,24 @@
       <c r="U129" s="0" t="n">
         <v>0</v>
       </c>
+      <c r="V129" s="0" t="n">
+        <v>500001</v>
+      </c>
       <c r="W129" s="0" t="n">
-        <v>13000100001</v>
+        <v>13000200001</v>
       </c>
       <c r="X129" s="0" t="n">
-        <v>13000100001</v>
+        <v>13000200001</v>
       </c>
       <c r="Y129" s="0" t="inlineStr">
         <is>
-          <t>每隔{Time_S}秒自动拾取附近魔晶</t>
+          <t>死亡后重生</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" s="0" t="n">
-        <v>13000200001</v>
+        <v>13000300001</v>
       </c>
       <c r="C130" s="0" t="n">
         <v>13</v>
@@ -8251,7 +8251,7 @@
       </c>
       <c r="H130" s="0" t="inlineStr">
         <is>
-          <t>BuffEntityConditionalDeadRebirth</t>
+          <t>BuffEntityConditionalDeadAttack</t>
         </is>
       </c>
       <c r="I130" s="0" t="inlineStr">
@@ -8259,30 +8259,33 @@
           <t>GameFightLogic_CreatureDeadEnd</t>
         </is>
       </c>
+      <c r="J130" s="0" t="n">
+        <v>300001</v>
+      </c>
+      <c r="O130" s="0" t="n">
+        <v>1</v>
+      </c>
       <c r="T130" s="0" t="n">
         <v>0</v>
       </c>
       <c r="U130" s="0" t="n">
         <v>0</v>
       </c>
-      <c r="V130" s="0" t="n">
-        <v>500001</v>
-      </c>
       <c r="W130" s="0" t="n">
-        <v>13000200001</v>
+        <v>13000300001</v>
       </c>
       <c r="X130" s="0" t="n">
-        <v>13000200001</v>
+        <v>13000300001</v>
       </c>
       <c r="Y130" s="0" t="inlineStr">
         <is>
-          <t>死亡后重生</t>
+          <t>死亡后爆炸</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" s="0" t="n">
-        <v>13000300001</v>
+        <v>13000400001</v>
       </c>
       <c r="C131" s="0" t="n">
         <v>13</v>
@@ -8292,7 +8295,7 @@
       </c>
       <c r="H131" s="0" t="inlineStr">
         <is>
-          <t>BuffEntityConditionalDeadAttack</t>
+          <t>BuffEntityConditionalDeadAreaHPChange</t>
         </is>
       </c>
       <c r="I131" s="0" t="inlineStr">
@@ -8301,10 +8304,13 @@
         </is>
       </c>
       <c r="J131" s="0" t="n">
-        <v>300001</v>
+        <v>1</v>
       </c>
       <c r="O131" s="0" t="n">
-        <v>1</v>
+        <v>0.05</v>
+      </c>
+      <c r="P131" s="0" t="n">
+        <v>0.01</v>
       </c>
       <c r="T131" s="0" t="n">
         <v>0</v>
@@ -8313,20 +8319,20 @@
         <v>0</v>
       </c>
       <c r="W131" s="0" t="n">
-        <v>13000300001</v>
+        <v>13000400001</v>
       </c>
       <c r="X131" s="0" t="n">
-        <v>13000300001</v>
+        <v>13000400001</v>
       </c>
       <c r="Y131" s="0" t="inlineStr">
         <is>
-          <t>死亡后爆炸</t>
+          <t>死亡后恢复附近友军生命，恢复量:自身生命上限的{Percentage}%</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" s="0" t="n">
-        <v>13000400001</v>
+        <v>13000500001</v>
       </c>
       <c r="C132" s="0" t="n">
         <v>13</v>
@@ -8336,7 +8342,7 @@
       </c>
       <c r="H132" s="0" t="inlineStr">
         <is>
-          <t>BuffEntityConditionalDeadAreaHPChange</t>
+          <t>BuffEntityConditionalDeadAreaDRChange</t>
         </is>
       </c>
       <c r="I132" s="0" t="inlineStr">
@@ -8360,20 +8366,20 @@
         <v>0</v>
       </c>
       <c r="W132" s="0" t="n">
-        <v>13000400001</v>
+        <v>13000500001</v>
       </c>
       <c r="X132" s="0" t="n">
-        <v>13000400001</v>
+        <v>13000500001</v>
       </c>
       <c r="Y132" s="0" t="inlineStr">
         <is>
-          <t>死亡后恢复附近友军生命，恢复量:自身生命上限的{Percentage}%</t>
+          <t>死亡后恢复附近友军护甲，恢复量:自身护甲上限的{Percentage}%</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" s="0" t="n">
-        <v>13000500001</v>
+        <v>13000600001</v>
       </c>
       <c r="C133" s="0" t="n">
         <v>13</v>
@@ -8383,7 +8389,7 @@
       </c>
       <c r="H133" s="0" t="inlineStr">
         <is>
-          <t>BuffEntityConditionalDeadAreaDRChange</t>
+          <t>BuffEntityConditionalDeadCreateCrystal</t>
         </is>
       </c>
       <c r="I133" s="0" t="inlineStr">
@@ -8391,14 +8397,8 @@
           <t>GameFightLogic_CreatureDeadEnd</t>
         </is>
       </c>
-      <c r="J133" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="O133" s="0" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="P133" s="0" t="n">
-        <v>0.01</v>
+      <c r="Q133" s="0" t="n">
+        <v>0.2</v>
       </c>
       <c r="T133" s="0" t="n">
         <v>0</v>
@@ -8407,39 +8407,70 @@
         <v>0</v>
       </c>
       <c r="W133" s="0" t="n">
-        <v>13000500001</v>
+        <v>13000600001</v>
       </c>
       <c r="X133" s="0" t="n">
-        <v>13000500001</v>
+        <v>13000600001</v>
       </c>
       <c r="Y133" s="0" t="inlineStr">
         <is>
-          <t>死亡后恢复附近友军护甲，恢复量:自身护甲上限的{Percentage}%</t>
+          <t>死亡后{Percentage}%生成魔晶</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" s="0" t="n">
-        <v>13000600001</v>
-      </c>
+        <v>3000500001</v>
+      </c>
+      <c r="B134" s="0" t="inlineStr"/>
       <c r="C134" s="0" t="n">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="D134" s="0" t="n">
-        <v>4</v>
+        <v>0</v>
+      </c>
+      <c r="E134" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="F134" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="G134" s="0" t="n">
+        <v>2</v>
       </c>
       <c r="H134" s="0" t="inlineStr">
         <is>
-          <t>BuffEntityConditionalDeadCreateCrystal</t>
-        </is>
-      </c>
-      <c r="I134" s="0" t="inlineStr">
-        <is>
-          <t>GameFightLogic_CreatureDeadEnd</t>
-        </is>
+          <t>BuffEntityPeriodicAttackBoomerang</t>
+        </is>
+      </c>
+      <c r="I134" s="0" t="inlineStr"/>
+      <c r="J134" s="0" t="inlineStr">
+        <is>
+          <t>1,300051</t>
+        </is>
+      </c>
+      <c r="K134" s="0" t="inlineStr"/>
+      <c r="L134" s="0" t="inlineStr"/>
+      <c r="M134" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="N134" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="O134" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="P134" s="0" t="n">
+        <v>0</v>
       </c>
       <c r="Q134" s="0" t="n">
-        <v>0.2</v>
+        <v>0</v>
+      </c>
+      <c r="R134" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="S134" s="0" t="n">
+        <v>5</v>
       </c>
       <c r="T134" s="0" t="n">
         <v>0</v>
@@ -8447,21 +8478,24 @@
       <c r="U134" s="0" t="n">
         <v>0</v>
       </c>
+      <c r="V134" s="0" t="n">
+        <v>0</v>
+      </c>
       <c r="W134" s="0" t="n">
-        <v>13000600001</v>
+        <v>3000500001</v>
       </c>
       <c r="X134" s="0" t="n">
-        <v>13000600001</v>
+        <v>3000500001</v>
       </c>
       <c r="Y134" s="0" t="inlineStr">
         <is>
-          <t>死亡后{Percentage}%生成魔晶</t>
+          <t>死亡回旋Lv1-每5秒发射1枚回旋镖,伤害=魔王攻击力,逐目标减半保底1</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" s="0" t="n">
-        <v>3000500001</v>
+        <v>3000500002</v>
       </c>
       <c r="B135" s="0" t="inlineStr"/>
       <c r="C135" s="0" t="n">
@@ -8487,7 +8521,7 @@
       <c r="I135" s="0" t="inlineStr"/>
       <c r="J135" s="0" t="inlineStr">
         <is>
-          <t>1,300051</t>
+          <t>2,300051</t>
         </is>
       </c>
       <c r="K135" s="0" t="inlineStr"/>
@@ -8530,13 +8564,13 @@
       </c>
       <c r="Y135" s="0" t="inlineStr">
         <is>
-          <t>死亡回旋Lv1-每5秒发射1枚回旋镖,伤害=魔王攻击力,逐目标减半保底1</t>
+          <t>死亡回旋Lv2-每5秒发射2枚回旋镖,伤害=魔王攻击力,逐目标减半保底1</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" s="0" t="n">
-        <v>3000500002</v>
+        <v>3000500003</v>
       </c>
       <c r="B136" s="0" t="inlineStr"/>
       <c r="C136" s="0" t="n">
@@ -8562,7 +8596,7 @@
       <c r="I136" s="0" t="inlineStr"/>
       <c r="J136" s="0" t="inlineStr">
         <is>
-          <t>2,300051</t>
+          <t>3,300051</t>
         </is>
       </c>
       <c r="K136" s="0" t="inlineStr"/>
@@ -8605,13 +8639,13 @@
       </c>
       <c r="Y136" s="0" t="inlineStr">
         <is>
-          <t>死亡回旋Lv2-每5秒发射2枚回旋镖,伤害=魔王攻击力,逐目标减半保底1</t>
+          <t>死亡回旋Lv3-每5秒发射3枚回旋镖,伤害=魔王攻击力,逐目标减半保底1</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" s="0" t="n">
-        <v>3000500003</v>
+        <v>3000500004</v>
       </c>
       <c r="B137" s="0" t="inlineStr"/>
       <c r="C137" s="0" t="n">
@@ -8637,7 +8671,7 @@
       <c r="I137" s="0" t="inlineStr"/>
       <c r="J137" s="0" t="inlineStr">
         <is>
-          <t>3,300051</t>
+          <t>4,300051</t>
         </is>
       </c>
       <c r="K137" s="0" t="inlineStr"/>
@@ -8680,13 +8714,13 @@
       </c>
       <c r="Y137" s="0" t="inlineStr">
         <is>
-          <t>死亡回旋Lv3-每5秒发射3枚回旋镖,伤害=魔王攻击力,逐目标减半保底1</t>
+          <t>死亡回旋Lv4-每5秒发射4枚回旋镖,伤害=魔王攻击力,逐目标减半保底1</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" s="0" t="n">
-        <v>3000500004</v>
+        <v>3000500005</v>
       </c>
       <c r="B138" s="0" t="inlineStr"/>
       <c r="C138" s="0" t="n">
@@ -8712,7 +8746,7 @@
       <c r="I138" s="0" t="inlineStr"/>
       <c r="J138" s="0" t="inlineStr">
         <is>
-          <t>4,300051</t>
+          <t>5,300051</t>
         </is>
       </c>
       <c r="K138" s="0" t="inlineStr"/>
@@ -8755,88 +8789,54 @@
       </c>
       <c r="Y138" s="0" t="inlineStr">
         <is>
-          <t>死亡回旋Lv4-每5秒发射4枚回旋镖,伤害=魔王攻击力,逐目标减半保底1</t>
+          <t>死亡回旋Lv5-每5秒发射5枚回旋镖,伤害=魔王攻击力,逐目标减半保底1</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" s="0" t="n">
-        <v>3000500005</v>
-      </c>
-      <c r="B139" s="0" t="inlineStr"/>
+        <v>13000700001</v>
+      </c>
       <c r="C139" s="0" t="n">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="D139" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="E139" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="F139" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="G139" s="0" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H139" s="0" t="inlineStr">
         <is>
-          <t>BuffEntityPeriodicAttackBoomerang</t>
-        </is>
-      </c>
-      <c r="I139" s="0" t="inlineStr"/>
-      <c r="J139" s="0" t="inlineStr">
-        <is>
-          <t>5,300051</t>
-        </is>
-      </c>
-      <c r="K139" s="0" t="inlineStr"/>
-      <c r="L139" s="0" t="inlineStr"/>
-      <c r="M139" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="N139" s="0" t="n">
-        <v>0</v>
+          <t>BuffEntityConditionalThorns</t>
+        </is>
+      </c>
+      <c r="I139" s="0" t="inlineStr">
+        <is>
+          <t>GameFightLogic_UnderAttack</t>
+        </is>
       </c>
       <c r="O139" s="0" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="P139" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q139" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="R139" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="S139" s="0" t="n">
-        <v>5</v>
+        <v>0.1</v>
       </c>
       <c r="T139" s="0" t="n">
         <v>0</v>
       </c>
-      <c r="U139" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="V139" s="0" t="n">
-        <v>0</v>
-      </c>
       <c r="W139" s="0" t="n">
-        <v>3000500001</v>
+        <v>13000700001</v>
       </c>
       <c r="X139" s="0" t="n">
-        <v>3000500001</v>
+        <v>13000700001</v>
       </c>
       <c r="Y139" s="0" t="inlineStr">
         <is>
-          <t>死亡回旋Lv5-每5秒发射5枚回旋镖,伤害=魔王攻击力,逐目标减半保底1</t>
+          <t>受到攻击时，反弹承伤的{Percentage}%给攻击者（上限为自身当前生命值）</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" s="0" t="n">
-        <v>13000700001</v>
+        <v>13000800001</v>
       </c>
       <c r="C140" s="0" t="n">
         <v>13</v>
@@ -8846,7 +8846,7 @@
       </c>
       <c r="H140" s="0" t="inlineStr">
         <is>
-          <t>BuffEntityConditionalThorns</t>
+          <t>BuffEntityConditionalLifeSteal</t>
         </is>
       </c>
       <c r="I140" s="0" t="inlineStr">
@@ -8864,20 +8864,20 @@
         <v>0</v>
       </c>
       <c r="W140" s="0" t="n">
-        <v>13000700001</v>
+        <v>13000800001</v>
       </c>
       <c r="X140" s="0" t="n">
-        <v>13000700001</v>
+        <v>13000800001</v>
       </c>
       <c r="Y140" s="0" t="inlineStr">
         <is>
-          <t>受到攻击时，反弹承伤的{Percentage}%给攻击者（上限为自身当前生命值）</t>
+          <t>造成伤害的{Percentage}%转化为自身生命</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" s="0" t="n">
-        <v>13000800001</v>
+        <v>13000900001</v>
       </c>
       <c r="C141" s="0" t="n">
         <v>13</v>
@@ -8887,79 +8887,97 @@
       </c>
       <c r="H141" s="0" t="inlineStr">
         <is>
-          <t>BuffEntityConditionalLifeSteal</t>
-        </is>
-      </c>
-      <c r="I141" s="0" t="inlineStr">
-        <is>
-          <t>GameFightLogic_UnderAttack</t>
-        </is>
-      </c>
-      <c r="O141" s="0" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="P141" s="0" t="n">
-        <v>0.1</v>
+          <t>BuffEntityConditionalInvincible</t>
+        </is>
+      </c>
+      <c r="K141" s="0" t="inlineStr">
+        <is>
+          <t>#FFD700</t>
+        </is>
+      </c>
+      <c r="M141" s="0" t="n">
+        <v>10</v>
+      </c>
+      <c r="N141" s="0" t="n">
+        <v>5</v>
       </c>
       <c r="T141" s="0" t="n">
         <v>0</v>
       </c>
       <c r="W141" s="0" t="n">
-        <v>13000800001</v>
+        <v>13000900001</v>
       </c>
       <c r="X141" s="0" t="n">
-        <v>13000800001</v>
+        <v>13000900001</v>
       </c>
       <c r="Y141" s="0" t="inlineStr">
         <is>
-          <t>造成伤害的{Percentage}%转化为自身生命</t>
+          <t>上场后无敌{Value}秒，期间身体变为金色</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" s="0" t="n">
-        <v>13000900001</v>
+        <v>11001300001</v>
       </c>
       <c r="C142" s="0" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="D142" s="0" t="n">
-        <v>4</v>
+        <v>2</v>
+      </c>
+      <c r="G142" s="0" t="n">
+        <v>1</v>
       </c>
       <c r="H142" s="0" t="inlineStr">
         <is>
-          <t>BuffEntityConditionalInvincible</t>
-        </is>
-      </c>
-      <c r="K142" s="0" t="inlineStr">
-        <is>
-          <t>#FFD700</t>
+          <t>BuffEntityAttributeDecayByAllyCount</t>
+        </is>
+      </c>
+      <c r="J142" s="0" t="inlineStr">
+        <is>
+          <t>ATK</t>
         </is>
       </c>
       <c r="M142" s="0" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="N142" s="0" t="n">
-        <v>5</v>
+        <v>50</v>
+      </c>
+      <c r="O142" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="P142" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q142" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="R142" s="0" t="n">
+        <v>0</v>
       </c>
       <c r="T142" s="0" t="n">
         <v>0</v>
       </c>
+      <c r="U142" s="0" t="n">
+        <v>0</v>
+      </c>
       <c r="W142" s="0" t="n">
-        <v>13000900001</v>
+        <v>11001300001</v>
       </c>
       <c r="X142" s="0" t="n">
-        <v>13000900001</v>
+        <v>11001300001</v>
       </c>
       <c r="Y142" s="0" t="inlineStr">
         <is>
-          <t>上场后无敌{Value}秒，期间身体变为金色</t>
+          <t>独行者-A</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" s="0" t="n">
-        <v>11001300001</v>
+        <v>11001300002</v>
       </c>
       <c r="C143" s="0" t="n">
         <v>11</v>
@@ -8977,7 +8995,7 @@
       </c>
       <c r="J143" s="0" t="inlineStr">
         <is>
-          <t>ATK</t>
+          <t>ASPD</t>
         </is>
       </c>
       <c r="M143" s="0" t="n">
@@ -9005,20 +9023,20 @@
         <v>0</v>
       </c>
       <c r="W143" s="0" t="n">
-        <v>11001300001</v>
+        <v>11001300002</v>
       </c>
       <c r="X143" s="0" t="n">
-        <v>11001300001</v>
+        <v>11001300002</v>
       </c>
       <c r="Y143" s="0" t="inlineStr">
         <is>
-          <t>独行者-A</t>
+          <t>独行者-B</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" s="0" t="n">
-        <v>11001300002</v>
+        <v>11001300003</v>
       </c>
       <c r="C144" s="0" t="n">
         <v>11</v>
@@ -9036,7 +9054,7 @@
       </c>
       <c r="J144" s="0" t="inlineStr">
         <is>
-          <t>ASPD</t>
+          <t>DR</t>
         </is>
       </c>
       <c r="M144" s="0" t="n">
@@ -9064,20 +9082,20 @@
         <v>0</v>
       </c>
       <c r="W144" s="0" t="n">
-        <v>11001300002</v>
+        <v>11001300003</v>
       </c>
       <c r="X144" s="0" t="n">
-        <v>11001300002</v>
+        <v>11001300003</v>
       </c>
       <c r="Y144" s="0" t="inlineStr">
         <is>
-          <t>独行者-B</t>
+          <t>独行者-C</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" s="0" t="n">
-        <v>11001300003</v>
+        <v>11001300004</v>
       </c>
       <c r="C145" s="0" t="n">
         <v>11</v>
@@ -9095,7 +9113,7 @@
       </c>
       <c r="J145" s="0" t="inlineStr">
         <is>
-          <t>DR</t>
+          <t>HP</t>
         </is>
       </c>
       <c r="M145" s="0" t="n">
@@ -9123,57 +9141,39 @@
         <v>0</v>
       </c>
       <c r="W145" s="0" t="n">
-        <v>11001300003</v>
+        <v>11001300004</v>
       </c>
       <c r="X145" s="0" t="n">
-        <v>11001300003</v>
+        <v>11001300004</v>
       </c>
       <c r="Y145" s="0" t="inlineStr">
         <is>
-          <t>独行者-C</t>
+          <t>独行者-D</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" s="0" t="n">
-        <v>11001300004</v>
+        <v>2000100003</v>
       </c>
       <c r="C146" s="0" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="D146" s="0" t="n">
-        <v>2</v>
-      </c>
-      <c r="G146" s="0" t="n">
         <v>1</v>
       </c>
       <c r="H146" s="0" t="inlineStr">
         <is>
-          <t>BuffEntityAttributeDecayByAllyCount</t>
+          <t>BuffEntityAttribute</t>
         </is>
       </c>
       <c r="J146" s="0" t="inlineStr">
         <is>
-          <t>HP</t>
-        </is>
-      </c>
-      <c r="M146" s="0" t="n">
-        <v>50</v>
-      </c>
-      <c r="N146" s="0" t="n">
-        <v>50</v>
+          <t>EVA</t>
+        </is>
       </c>
       <c r="O146" s="0" t="n">
-        <v>3</v>
-      </c>
-      <c r="P146" s="0" t="n">
-        <v>3</v>
-      </c>
-      <c r="Q146" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="R146" s="0" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="T146" s="0" t="n">
         <v>0</v>
@@ -9182,20 +9182,20 @@
         <v>0</v>
       </c>
       <c r="W146" s="0" t="n">
-        <v>11001300004</v>
+        <v>2000100003</v>
       </c>
       <c r="X146" s="0" t="n">
-        <v>11001300004</v>
+        <v>2000100003</v>
       </c>
       <c r="Y146" s="0" t="inlineStr">
         <is>
-          <t>独行者-D</t>
+          <t>闪避20%</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" s="0" t="n">
-        <v>2000100003</v>
+        <v>2000200002</v>
       </c>
       <c r="C147" s="0" t="n">
         <v>2</v>
@@ -9210,7 +9210,7 @@
       </c>
       <c r="J147" s="0" t="inlineStr">
         <is>
-          <t>EVA</t>
+          <t>CRT</t>
         </is>
       </c>
       <c r="O147" s="0" t="n">
@@ -9223,53 +9223,12 @@
         <v>0</v>
       </c>
       <c r="W147" s="0" t="n">
-        <v>2000100003</v>
+        <v>2000200002</v>
       </c>
       <c r="X147" s="0" t="n">
-        <v>2000100003</v>
+        <v>2000200002</v>
       </c>
       <c r="Y147" s="0" t="inlineStr">
-        <is>
-          <t>闪避20%</t>
-        </is>
-      </c>
-    </row>
-    <row r="148">
-      <c r="A148" s="0" t="n">
-        <v>2000200002</v>
-      </c>
-      <c r="C148" s="0" t="n">
-        <v>2</v>
-      </c>
-      <c r="D148" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="H148" s="0" t="inlineStr">
-        <is>
-          <t>BuffEntityAttribute</t>
-        </is>
-      </c>
-      <c r="J148" s="0" t="inlineStr">
-        <is>
-          <t>CRT</t>
-        </is>
-      </c>
-      <c r="O148" s="0" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="T148" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="U148" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="W148" s="0" t="n">
-        <v>2000200002</v>
-      </c>
-      <c r="X148" s="0" t="n">
-        <v>2000200002</v>
-      </c>
-      <c r="Y148" s="0" t="inlineStr">
         <is>
           <t>暴击20%</t>
         </is>
